--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0974A66-F106-4FB6-8246-4EA3734CBACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED85A1C5-EC98-4329-817B-088C84E7EEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1417,25 +1417,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>HPが減るたび、遅延ダメージ含めCD0.8秒で1スタック獲得。最大30スタックで与ダメ+15%、被ダメ軽減15%。効果時間3秒、スタックを獲得するたびに時間は更新される</t>
-    <rPh sb="57" eb="61">
-      <t>コウカジカン</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="69" eb="71">
-      <t>カクトク</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>itaminasi_buff</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1452,28 +1433,6 @@
   </si>
   <si>
     <t>ウォームアップ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>スタック数に応じて与えるダメージが上がり、受けるダメージが下がる。</t>
-    <rPh sb="4" eb="5">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>サ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1610,26 +1569,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>1スタックごとに与ダメ補正+0.5%、被ダメ補正-0.5%を得る。最大30スタック。効果時間3秒
-スタックを獲得するたびに効果時間はリセットされる。スタックの獲得には0.8秒のクールタイムがある。</t>
-    <rPh sb="8" eb="9">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ホセイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ホセイ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>エ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>受けるダメージの1/3を5分割にし、1秒ごとの遅延ダメージで受ける。遅延ダメージは最低1ダメージ。HPが減るたびに"逆境"を１つ獲得する。</t>
     <rPh sb="0" eb="1">
       <t>ウ</t>
@@ -1722,6 +1661,67 @@
     </rPh>
     <rPh sb="70" eb="71">
       <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スタック数に応じて攻撃力と防御力が上昇する</t>
+    <rPh sb="4" eb="5">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HPが減るたび、遅延ダメージ含めCD0.8秒で1スタック獲得。最大20スタックで攻撃力+10%、防御力+10%。効果時間3秒、スタックを獲得するたびに時間は更新される</t>
+    <rPh sb="40" eb="43">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="48" eb="51">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="56" eb="60">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1スタックごとに攻撃力+0.5%、防御力+0.5%を得る。最大20スタック。効果時間3秒
+スタックを獲得するたびに効果時間はリセットされる。スタックの獲得には0.8秒のクールタイムがある。</t>
+    <rPh sb="8" eb="11">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>エ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1822,7 +1822,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1850,14 +1850,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3422,11 +3421,11 @@
       <c r="S22" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="T22" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="U22" s="13" t="s">
-        <v>398</v>
+      <c r="T22" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="U22" s="12" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="72">
@@ -3479,13 +3478,13 @@
         <v>29</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="T23" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="U23" s="13" t="s">
-        <v>402</v>
+        <v>393</v>
+      </c>
+      <c r="T23" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="U23" s="12" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="72">
@@ -3538,13 +3537,13 @@
         <v>29</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="T24" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="T24" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="U24" s="12" t="s">
         <v>400</v>
-      </c>
-      <c r="U24" s="13" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="36">
@@ -5111,10 +5110,10 @@
       <c r="J2" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="4" t="s">
         <v>387</v>
       </c>
     </row>
@@ -5149,10 +5148,10 @@
       <c r="J3" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="4" t="s">
         <v>387</v>
       </c>
     </row>
@@ -5187,10 +5186,10 @@
       <c r="J4" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="4" t="s">
         <v>387</v>
       </c>
     </row>
@@ -5213,7 +5212,7 @@
       <c r="F5" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="4" t="s">
         <v>382</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -5225,10 +5224,10 @@
       <c r="J5" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="4" t="s">
         <v>387</v>
       </c>
     </row>
@@ -5274,42 +5273,42 @@
     </row>
     <row r="2" spans="1:6" ht="37.200000000000003" customHeight="1">
       <c r="A2" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>391</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>384</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>394</v>
+        <v>405</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>404</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36">
       <c r="A3" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>393</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>384</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>406</v>
+        <v>401</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED85A1C5-EC98-4329-817B-088C84E7EEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE93D09-1967-4BB2-B6F9-AB2DF7850E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1470,32 +1470,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>受けるダメージの一部を分割して受ける
-HPが減るたびに逆境のスタックを獲得する</t>
-    <rPh sb="0" eb="1">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>イチブ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ブンカツ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ヘ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ギャッキョウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>カクトク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>会心率が増加する。代わりに会心ダメージが低下する</t>
     <rPh sb="0" eb="3">
       <t>カイシンリツ</t>
@@ -1549,22 +1523,6 @@
     </rPh>
     <rPh sb="14" eb="15">
       <t>ハヤ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>敵に魔法ダメージを与えるたびにウォームアップのスタックを獲得する。</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>カクトク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1722,6 +1680,48 @@
     </rPh>
     <rPh sb="26" eb="27">
       <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受けるダメージの一部を分割して受ける
+HPが減るたびに"逆境"を獲得する</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ギャッキョウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カクトク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に魔法ダメージを与えるたびに"ウォームアップ"を獲得する。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カクトク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3422,10 +3422,10 @@
         <v>266</v>
       </c>
       <c r="T22" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="U22" s="12" t="s">
         <v>395</v>
-      </c>
-      <c r="U22" s="12" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="72">
@@ -3481,10 +3481,10 @@
         <v>393</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="U23" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="72">
@@ -3537,13 +3537,13 @@
         <v>29</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="T24" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="U24" s="12" t="s">
         <v>398</v>
-      </c>
-      <c r="U24" s="12" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="36">
@@ -5282,13 +5282,13 @@
         <v>384</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E2" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>404</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36">
@@ -5302,13 +5302,13 @@
         <v>384</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>401</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7570E4-A332-417C-B902-EB06993C7838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E520F545-F0A9-443C-B7D3-95480656390E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="573">
   <si>
     <t>ID</t>
   </si>
@@ -500,9 +500,6 @@
   </si>
   <si>
     <t>22px</t>
-  </si>
-  <si>
-    <t>指示</t>
   </si>
   <si>
     <t>7.5秒</t>
@@ -814,14 +811,6 @@
   </si>
   <si>
     <t>daiti_punch</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>daiti_wave</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>masic_3_shot</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3095,18 +3084,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>chacka</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>チャッカ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>魔力 * 0.15</t>
-    <rPh sb="0" eb="2">
-      <t>マリョク</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3136,53 +3114,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>防御力が下がり、継続的にダメージを受ける。</t>
-    <rPh sb="0" eb="3">
-      <t>ボウギョリョク</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>サ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>ケイゾクテキ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>燃焼が付与されている間防御力-10%。さらに毎秒(式=値)の魔法ダメージを受ける。</t>
-    <rPh sb="0" eb="2">
-      <t>ネンショウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>ボウギョリョク</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>マイビョウ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>シキ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>燃焼(debuff_burn)</t>
     <rPh sb="0" eb="2">
       <t>ネンショウ</t>
@@ -3190,22 +3121,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>燃焼(状態ID"debuff_burn")を４秒付与</t>
-    <rPh sb="0" eb="2">
-      <t>ネンショウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>フヨ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>回復</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3293,52 +3208,6 @@
     </rPh>
     <rPh sb="47" eb="48">
       <t>フク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>１秒の詠唱を行った後、対象の敵１体に(式=値)の魔法ダメージを与え、４秒の"燃焼"を付与する。</t>
-    <rPh sb="1" eb="2">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>エイショウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>アト</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>シキ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ネンショウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>フヨ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4520,59 +4389,6 @@
     </rPh>
     <rPh sb="37" eb="39">
       <t>ゾウカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>毎秒の(計算式:現在HPの1%分)の魔法ダメージを受ける。これは魔法ダメージであり、相手の魔法防御力などの影響でダメージが減少する可能性がある
-燃焼が付与されている間防御力が-10%される</t>
-    <rPh sb="0" eb="2">
-      <t>マイビョウ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ケイサンシキ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="45" eb="50">
-      <t>マホウボウギョリョク</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>エイキョウ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ゲンショウ</t>
-    </rPh>
-    <rPh sb="65" eb="68">
-      <t>カノウセイ</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>ネンショウ</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="82" eb="83">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="83" eb="86">
-      <t>ボウギョリョク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4744,13 +4560,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>6秒</t>
-    <rPh sb="1" eb="2">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>レベルが上がるごとに無視される確率が(75/65/55/45/35/25)%にまで低下</t>
     <rPh sb="4" eb="5">
       <t>ア</t>
@@ -4811,34 +4620,6 @@
     </rPh>
     <rPh sb="41" eb="43">
       <t>テイカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>詠唱後、対象の敵１体に魔法ダメージを与え、"燃焼"を付与する。</t>
-    <rPh sb="0" eb="3">
-      <t>エイショウゴ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ネンショウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>フヨ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -5292,6 +5073,370 @@
     <t>マイナスステータス１つごとの上限値</t>
     <rPh sb="14" eb="17">
       <t>ジョウゲンチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ファイア</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力 * 0.55</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>14秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3秒</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>燃焼(状態ID"debuff_burn")を付与</t>
+    <rPh sb="0" eb="2">
+      <t>ネンショウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、対象の敵１体に炎を放ち、魔法ダメージを与え、"燃焼"を付与する。</t>
+    <rPh sb="0" eb="3">
+      <t>エイショウゴ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ネンショウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>１秒の詠唱を行った後、対象の敵１体に炎を放ち、(式=値)の魔法ダメージを与え、3秒の"燃焼"を付与する。</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エイショウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ネンショウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>fire</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>毎秒の(計算式:現在HPの1%分)の魔法ダメージを受ける。これは魔法ダメージであり、相手の魔法防御力などの影響でダメージが減少する可能性がある</t>
+    <rPh sb="0" eb="2">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ケイサンシキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="45" eb="50">
+      <t>マホウボウギョリョク</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="65" eb="68">
+      <t>カノウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>継続的に魔法ダメージを受ける。</t>
+    <rPh sb="0" eb="3">
+      <t>ケイゾクテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>燃焼が付与されている間、毎秒(式=値)の魔法ダメージを受ける。</t>
+    <rPh sb="0" eb="2">
+      <t>ネンショウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>杖/魔導書/魔楽器</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>マドウショ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ランウェーブ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>lan_wave</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>take_aim</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スキル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フォーカス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>40秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象指定</t>
+    <rPh sb="0" eb="4">
+      <t>タイショウシテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>550px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>20秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象した敵を味方AIが必ず対象を攻撃するようになる</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>指定した敵1体を一定時間、味方達が狙うようになる</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>タチ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ネラ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>指定した敵1体を味方達が狙うようになる。20秒経過するか対象が戦闘不能になるまで続く</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ミカタタチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ネラ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケイカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>セントウフノウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ツヅ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -5874,7 +6019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -5900,19 +6045,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -5930,7 +6075,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>9</v>
@@ -5945,7 +6090,7 @@
         <v>12</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>13</v>
@@ -5957,36 +6102,36 @@
         <v>15</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="36">
       <c r="A2" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>18</v>
@@ -6001,69 +6146,69 @@
         <v>15</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="S2" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="U2" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="T2" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="U2" s="12" t="s">
-        <v>373</v>
-      </c>
       <c r="V2" s="12" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="X2" s="12" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="36">
       <c r="A3" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>25</v>
@@ -6087,7 +6232,7 @@
         <v>29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>30</v>
@@ -6102,45 +6247,45 @@
         <v>32</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="36">
       <c r="A4" s="3" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>33</v>
@@ -6161,81 +6306,81 @@
         <v>28</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="54">
       <c r="A5" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>40</v>
@@ -6256,51 +6401,51 @@
         <v>32</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="U5" s="12" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="V5" s="12" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="W5" s="12" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="Y5" s="12" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="36">
       <c r="A6" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>20</v>
@@ -6309,7 +6454,7 @@
         <v>24</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>24</v>
@@ -6330,48 +6475,48 @@
         <v>24</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="T6" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="U6" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="U6" s="12" t="s">
-        <v>278</v>
-      </c>
       <c r="V6" s="12" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="W6" s="12" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="X6" s="12" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="Y6" s="12" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="54">
       <c r="A7" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F7" s="2">
         <v>18</v>
@@ -6392,146 +6537,146 @@
         <v>50</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="U7" s="12" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="X7" s="12" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="Y7" s="12" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="54">
       <c r="A8" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>38</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="U8" s="12" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="V8" s="12" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="W8" s="12" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="Y8" s="12" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="36">
       <c r="A9" s="3" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F9" s="2">
         <v>20</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>20</v>
@@ -6540,75 +6685,75 @@
         <v>24</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>54</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>55</v>
       </c>
       <c r="U9" s="12" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="V9" s="12" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="W9" s="12" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="X9" s="12" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="Y9" s="12" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="72">
       <c r="A10" s="3" t="s">
-        <v>222</v>
+        <v>559</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>56</v>
+        <v>248</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>558</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>20</v>
@@ -6620,25 +6765,25 @@
         <v>57</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>58</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>24</v>
@@ -6650,42 +6795,42 @@
         <v>59</v>
       </c>
       <c r="U10" s="12" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="V10" s="12" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="W10" s="12" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="X10" s="12" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="Y10" s="12" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="36">
       <c r="A11" s="3" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>20</v>
@@ -6703,10 +6848,10 @@
         <v>54</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>47</v>
@@ -6715,54 +6860,54 @@
         <v>60</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="U11" s="12" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="V11" s="12" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="W11" s="12" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="X11" s="12" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="Y11" s="12" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="72">
       <c r="A12" s="3" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F12" s="2">
         <v>15</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>20</v>
@@ -6771,141 +6916,141 @@
         <v>20</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>63</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>24</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="U12" s="12" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="V12" s="12" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="X12" s="12" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="Y12" s="12" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="72">
-      <c r="A13" s="3" t="s">
-        <v>480</v>
+    <row r="13" spans="1:25" ht="54">
+      <c r="A13" s="12" t="s">
+        <v>553</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="F13" s="3">
-        <v>32</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="2">
+        <v>201</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="F13">
+        <v>30</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="I13">
         <v>40</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="U13" s="12" t="s">
-        <v>361</v>
+      <c r="J13" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q13" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="R13" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="S13" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="T13" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="U13" s="16" t="s">
+        <v>551</v>
       </c>
       <c r="V13" s="12" t="s">
-        <v>362</v>
+        <v>552</v>
       </c>
       <c r="W13" s="12" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="Y13" s="12" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="143.4" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>199</v>
+        <v>557</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>65</v>
@@ -6914,7 +7059,7 @@
         <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>20</v>
@@ -6923,10 +7068,10 @@
         <v>24</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>54</v>
@@ -6935,57 +7080,57 @@
         <v>24</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="U14" s="12" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="V14" s="12" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="W14" s="12" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="X14" s="12" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="Y14" s="12" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="54">
       <c r="A15" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>150</v>
+        <v>451</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>561</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>24</v>
@@ -7000,7 +7145,7 @@
         <v>131</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>24</v>
@@ -7009,10 +7154,10 @@
         <v>29</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>31</v>
@@ -7021,48 +7166,48 @@
         <v>24</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T15" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="U15" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="V15" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="W15" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="X15" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="Y15" s="12" t="s">
         <v>442</v>
-      </c>
-      <c r="U15" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="V15" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="W15" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="X15" s="12" t="s">
-        <v>450</v>
-      </c>
-      <c r="Y15" s="12" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="54">
       <c r="A16" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>150</v>
+        <v>451</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>561</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>24</v>
@@ -7077,7 +7222,7 @@
         <v>131</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>24</v>
@@ -7086,10 +7231,10 @@
         <v>29</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>31</v>
@@ -7098,48 +7243,48 @@
         <v>24</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="T16" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="U16" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="V16" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="W16" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="X16" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="Y16" s="12" t="s">
         <v>443</v>
-      </c>
-      <c r="U16" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="V16" s="12" t="s">
-        <v>448</v>
-      </c>
-      <c r="W16" s="12" t="s">
-        <v>475</v>
-      </c>
-      <c r="X16" s="12" t="s">
-        <v>450</v>
-      </c>
-      <c r="Y16" s="12" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:25" ht="54">
       <c r="A17" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>150</v>
+        <v>451</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>561</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>24</v>
@@ -7154,19 +7299,19 @@
         <v>131</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>31</v>
@@ -7175,48 +7320,48 @@
         <v>24</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T17" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="U17" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="V17" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="W17" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="X17" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="Y17" s="12" t="s">
         <v>444</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="V17" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="W17" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="X17" s="12" t="s">
-        <v>450</v>
-      </c>
-      <c r="Y17" s="12" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="54">
       <c r="A18" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>150</v>
+        <v>451</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>561</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>24</v>
@@ -7231,19 +7376,19 @@
         <v>131</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>31</v>
@@ -7252,48 +7397,48 @@
         <v>24</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T18" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="U18" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="V18" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="W18" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="X18" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="Y18" s="12" t="s">
         <v>445</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="V18" s="12" t="s">
-        <v>446</v>
-      </c>
-      <c r="W18" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="X18" s="12" t="s">
-        <v>450</v>
-      </c>
-      <c r="Y18" s="12" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="36">
       <c r="A19" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>24</v>
@@ -7314,55 +7459,55 @@
         <v>24</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>24</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>24</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="U19" s="13" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="V19" s="12" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="W19" s="12"/>
     </row>
     <row r="20" spans="1:25" ht="72">
       <c r="A20" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>24</v>
@@ -7383,56 +7528,56 @@
         <v>24</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P20" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q20" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="Q20" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="R20" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="U20" s="12" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="V20" s="12" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="W20" s="12"/>
       <c r="X20" s="16"/>
     </row>
     <row r="21" spans="1:25" ht="72">
       <c r="A21" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>24</v>
@@ -7453,182 +7598,244 @@
         <v>24</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="V21" s="12" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="W21" s="12"/>
     </row>
     <row r="22" spans="1:25" ht="54">
       <c r="A22" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="G22" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="N22" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D22" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="O22" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="S22" s="2"/>
       <c r="T22" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="V22" s="12" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="W22" s="12"/>
     </row>
     <row r="23" spans="1:25" ht="36">
       <c r="A23" s="12" t="s">
-        <v>382</v>
+        <v>560</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C23" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>565</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>566</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="P23" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="Q23" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="S23" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="T23" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="U23" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="V23" s="12" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="72">
+      <c r="A31" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="F23">
-        <v>10</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="I23">
-        <v>15</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="M23" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="O23" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="P23" s="12" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q23" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="R23" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="S23" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="T23" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="U23" s="16" t="s">
-        <v>478</v>
-      </c>
-      <c r="V23" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="W23" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="X23" s="12" t="s">
-        <v>456</v>
-      </c>
-      <c r="Y23" s="12" t="s">
-        <v>457</v>
+      <c r="D31" s="14" t="s">
+        <v>502</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="F31" s="3">
+        <v>32</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" s="2">
+        <v>40</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="U31" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="V31" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="W31" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="X31" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="Y31" s="12" t="s">
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -7672,19 +7879,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -7717,7 +7924,7 @@
         <v>12</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>13</v>
@@ -7729,19 +7936,19 @@
         <v>15</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -7752,7 +7959,7 @@
         <v>67</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>43</v>
@@ -7811,7 +8018,7 @@
         <v>67</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>76</v>
@@ -7870,7 +8077,7 @@
         <v>67</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>86</v>
@@ -8327,7 +8534,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14.296875" customWidth="1"/>
@@ -8349,114 +8556,118 @@
         <v>93</v>
       </c>
       <c r="D1" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>239</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="37.200000000000003" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36">
       <c r="A3" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="54">
       <c r="A4" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>310</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="54">
+    <row r="6" spans="1:6" ht="36">
       <c r="A6" s="4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>458</v>
+        <v>554</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>390</v>
+        <v>555</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>391</v>
-      </c>
+        <v>556</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
@@ -8513,7 +8724,7 @@
         <v>101</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>102</v>
@@ -8525,10 +8736,10 @@
         <v>104</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>105</v>
@@ -8540,7 +8751,7 @@
         <v>107</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>108</v>
@@ -8555,7 +8766,7 @@
         <v>15</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:45">
@@ -8566,7 +8777,7 @@
         <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>112</v>
@@ -8581,7 +8792,7 @@
         <v>90</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I2" s="2">
         <v>95</v>
@@ -8590,7 +8801,7 @@
         <v>95</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L2" s="15">
         <v>0.5</v>
@@ -8608,7 +8819,7 @@
         <v>113</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>113</v>
@@ -8632,7 +8843,7 @@
         <v>24</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
@@ -8663,7 +8874,7 @@
         <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>112</v>
@@ -8678,10 +8889,10 @@
         <v>110</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J3" s="2">
         <v>100</v>
@@ -8726,7 +8937,7 @@
         <v>122</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
@@ -8758,7 +8969,7 @@
         <v>53</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>112</v>
@@ -8770,7 +8981,7 @@
         <v>290</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H4" s="2">
         <v>80</v>
@@ -8779,10 +8990,10 @@
         <v>100</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="L4" s="15">
         <v>0.5</v>
@@ -8821,7 +9032,7 @@
         <v>125</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
@@ -8853,7 +9064,7 @@
         <v>61</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>112</v>
@@ -8862,22 +9073,22 @@
         <v>480</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="H5" s="2">
         <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="L5" s="15">
         <v>0.5</v>
@@ -8916,7 +9127,7 @@
         <v>117</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
@@ -8948,7 +9159,7 @@
         <v>129</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>112</v>
@@ -8966,10 +9177,10 @@
         <v>131</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>113</v>
@@ -9011,10 +9222,10 @@
         <v>117</v>
       </c>
       <c r="X6" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y6" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
@@ -9045,7 +9256,7 @@
         <v>129</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>112</v>
@@ -9063,10 +9274,10 @@
         <v>131</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>113</v>
@@ -9108,10 +9319,10 @@
         <v>136</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
@@ -9142,7 +9353,7 @@
         <v>138</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>112</v>
@@ -9160,10 +9371,10 @@
         <v>131</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>113</v>
@@ -9205,10 +9416,10 @@
         <v>140</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
@@ -9239,7 +9450,7 @@
         <v>142</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>112</v>
@@ -9257,10 +9468,10 @@
         <v>131</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>113</v>
@@ -9305,7 +9516,7 @@
         <v>115</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
@@ -9336,7 +9547,7 @@
         <v>146</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>112</v>
@@ -9354,10 +9565,10 @@
         <v>131</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>113</v>
@@ -9399,10 +9610,10 @@
         <v>149</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
@@ -9460,137 +9671,137 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="K1" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="L1" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>241</v>
-      </c>
       <c r="M1" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="Q1" s="18"/>
       <c r="R1" s="18"/>
     </row>
     <row r="2" spans="1:18" ht="36">
       <c r="A2" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -9600,41 +9811,41 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>235</v>
-      </c>
       <c r="L4" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
@@ -9644,41 +9855,41 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
@@ -9718,43 +9929,43 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="J1" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>241</v>
-      </c>
       <c r="L1" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -9782,22 +9993,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="E1" s="21" t="s">
         <v>15</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -9825,40 +10036,40 @@
         <v>2</v>
       </c>
       <c r="C1" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="J1" s="17" t="s">
         <v>483</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>490</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>493</v>
-      </c>
-      <c r="I1" s="17" t="s">
-        <v>494</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>495</v>
-      </c>
       <c r="K1" s="17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L1" s="17" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="M1" s="17" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="N1" s="17" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="O1" s="17" t="s">
         <v>15</v>
@@ -9886,51 +10097,51 @@
   <sheetData>
     <row r="2" spans="2:13">
       <c r="B2" s="23" t="s">
+        <v>494</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>544</v>
+      </c>
+      <c r="I2" s="23" t="s">
         <v>506</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>513</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>556</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>518</v>
-      </c>
       <c r="J2" s="28" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M2" s="23" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="23" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M3" s="24">
         <v>1</v>
@@ -9938,25 +10149,25 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="23" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="J4" s="28" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="M4" s="24">
         <v>2</v>
@@ -9964,25 +10175,25 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="23" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="M5" s="24">
         <v>3</v>
@@ -9990,25 +10201,25 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="23" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="M6" s="24">
         <v>4</v>
@@ -10016,25 +10227,25 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="23" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="M7" s="24">
         <v>5</v>
@@ -10042,104 +10253,104 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="23" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
       <c r="F8" s="26"/>
       <c r="I8" s="23" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9" spans="2:13">
       <c r="I9" s="23" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="J9" s="28" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10" spans="2:13">
       <c r="I10" s="23" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="J10" s="28" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
     </row>
     <row r="11" spans="2:13">
       <c r="I11" s="23" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
     <row r="12" spans="2:13">
       <c r="I12" s="23" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="J12" s="28" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="I13" s="23" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14" spans="2:13">
       <c r="I14" s="23" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="I15" s="23" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="I16" s="23" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" spans="9:10">
       <c r="I17" s="23" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
     </row>
     <row r="18" spans="9:10">
       <c r="I18" s="23" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
     <row r="19" spans="9:10">
       <c r="I19" s="23" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E520F545-F0A9-443C-B7D3-95480656390E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0324372-A5DA-4D04-963C-897200BACCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,12 @@
     <sheet name="ステータス説明" sheetId="11" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">アイテム!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">アイテム!$A$1:$O$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">キャラ!$A$1:$Z$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">セット効果!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">敵スキル!$A$1:$S$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">防具!$A$1:$M$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">味方スキル!$A$1:$S$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">セット効果!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">敵スキル!$A$1:$T$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">防具!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">味方スキル!$A$1:$T$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="679">
   <si>
     <t>ID</t>
   </si>
@@ -115,9 +115,6 @@
     <t/>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>1秒</t>
   </si>
   <si>
@@ -238,9 +235,6 @@
     <t>スシア</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>3発/線幅16px/弾半径5px</t>
   </si>
   <si>
@@ -409,9 +403,6 @@
     <t>ulpes</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>20%</t>
   </si>
   <si>
@@ -442,9 +433,6 @@
     <t>魔物</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -454,9 +442,6 @@
     <t>skirmisher</t>
   </si>
   <si>
-    <t>80</t>
-  </si>
-  <si>
     <t>118px</t>
   </si>
   <si>
@@ -469,9 +454,6 @@
     <t>小魔物</t>
   </si>
   <si>
-    <t>62</t>
-  </si>
-  <si>
     <t>11px</t>
   </si>
   <si>
@@ -481,9 +463,6 @@
     <t>射手</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>62px</t>
   </si>
   <si>
@@ -491,9 +470,6 @@
   </si>
   <si>
     <t>大魔物</t>
-  </si>
-  <si>
-    <t>250</t>
   </si>
   <si>
     <t>68px</t>
@@ -807,10 +783,6 @@
   </si>
   <si>
     <t>hero_one_slash</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>daiti_punch</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -4670,9 +4642,6 @@
     <t>対象</t>
   </si>
   <si>
-    <t>消費/回数</t>
-  </si>
-  <si>
     <t>最大所持数</t>
   </si>
   <si>
@@ -4700,10 +4669,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>追加ステータス(1.0/1.1/1.2/1.3/1.4/1.5)倍
-以下同文</t>
-  </si>
-  <si>
     <t>追加ステータス乱数</t>
     <rPh sb="0" eb="2">
       <t>ツイカ</t>
@@ -4720,57 +4685,6 @@
     <t>強化内容詳細説明文</t>
   </si>
   <si>
-    <t>レベルが上がるごとに武器の
-(追加ステータスのステータス名)が上昇する(以下同文)</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="36" eb="40">
-      <t>イカドウブン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>レベルが上がるごとに武器の(追加ステータスのステータス名)が(1.1/1.2/1.3/1.4/1.5)倍になる。少数は切り捨てされる。(以下同文)</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>バイ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ショウスウ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="68" eb="72">
-      <t>イカドウブン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>防具のランダムステータス</t>
     <rPh sb="0" eb="2">
       <t>ボウグ</t>
@@ -5438,6 +5352,1030 @@
     <rPh sb="40" eb="41">
       <t>ツヅ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱時間</t>
+    <rPh sb="0" eb="2">
+      <t>エイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CD</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_potion</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮ポーション</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>戦闘最大所持数</t>
+    <rPh sb="0" eb="4">
+      <t>セントウサイダイ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ショジスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ポーション</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>どこでも</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自分</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HPを250回複数</t>
+    <rPh sb="6" eb="9">
+      <t>カイフクスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>15秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>消費数</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>飲むと体力が回復する</t>
+    <rPh sb="0" eb="1">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>飲むとHPが250回復する</t>
+    <rPh sb="0" eb="1">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_ken</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_ryouken</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_kengu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_bougu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_tue</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_book</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_hue</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮の片手剣</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>カタテケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮の両手剣</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>リョウテケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮の拳具</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケング</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮の棒具</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ボウグ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮の杖</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮の魔導書</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>マドウショ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮の魔楽器</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>マガッキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>片手剣</t>
+    <rPh sb="0" eb="3">
+      <t>カタテケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>両手剣</t>
+    <rPh sb="0" eb="3">
+      <t>リョウテケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>拳具</t>
+    <rPh sb="0" eb="2">
+      <t>ケング</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>棒具</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>杖</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔導書</t>
+    <rPh sb="0" eb="3">
+      <t>マドウショ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔楽器</t>
+    <rPh sb="0" eb="3">
+      <t>マガッキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮シリーズ</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_dorop</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮素材</t>
+    <rPh sb="0" eb="3">
+      <t>カリソザイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素材</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全ての敵が100%でドロップ</t>
+  </si>
+  <si>
+    <t>全ての敵が100%で１つドロップする</t>
+    <rPh sb="0" eb="1">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>何か作るのに使えるかも</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮素材 * 3 + お金100</t>
+    <rPh sb="0" eb="3">
+      <t>カリソザイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カネ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力+20</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力+20</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hurihrai</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>huriharai</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>masic_shot</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shock</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮武器</t>
+    <rPh sb="0" eb="3">
+      <t>カリブキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>追加ステータス(1.0/1.1/1.2/1.3/1.4/1.5)倍
+以下全武器同文</t>
+    <rPh sb="36" eb="37">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ドウブン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_atama</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_huku</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_zubon</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_kutu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_te</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_akuse</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>装備箇所</t>
+    <rPh sb="0" eb="4">
+      <t>ソウビカショ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮ヘルメット</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮服</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮レギンス</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮ブーツ</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮グローブ</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮ネックレス</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>頭</t>
+    <rPh sb="0" eb="1">
+      <t>アタマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>足</t>
+    <rPh sb="0" eb="1">
+      <t>アシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>胴</t>
+    <rPh sb="0" eb="1">
+      <t>ドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>靴</t>
+    <rPh sb="0" eb="1">
+      <t>クツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>手</t>
+    <rPh sb="0" eb="1">
+      <t>テ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アクセサリ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_set</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮素材 * 3 + お金100</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カネ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮装備</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルを上げるごとにその装備のランダムなステータス値が
+値ごとに(1.0/1.1/1.2/1.3/1.4/1.5)倍になる(以下アクセサリ以外全防具同文)</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソウビ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="71" eb="74">
+      <t>ゼンボウグ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ドウブン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルを上がるごとに武器の
+(追加ステータスのステータス名)が上昇する(以下全武器同文)</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ドウブン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルを上げるごとにこの装備のランダムな
+ステータスが強化される(以下アクセサリ以外全防具同文)</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソウビ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="42" eb="47">
+      <t>ゼンボウグドウブン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルを上げるごとにこの装備のランダムなステータス値がそれぞれ(1.1/1.2/1.3/1.4/1.5)倍になる
+(以下アクセサリ以外全防具同文)</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソウビ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="65" eb="70">
+      <t>イガイゼンボウグ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ドウブン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>強化素材(1~5Lv)</t>
+    <rPh sb="0" eb="4">
+      <t>キョウカソザイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HPとMPが30%上昇する</t>
+    <rPh sb="9" eb="11">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力と魔力が30%上昇する</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2セット効果詳細説明</t>
+    <rPh sb="4" eb="6">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ショウサイセツメイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2セット効果簡易説明文</t>
+    <rPh sb="4" eb="6">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5セット効果簡易説明文</t>
+    <rPh sb="4" eb="6">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5セット効果詳細説明文</t>
+    <rPh sb="4" eb="6">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HPとMPが上昇する</t>
+    <rPh sb="6" eb="8">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力と魔力が上昇する</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HPとMPが30%が上昇する</t>
+    <rPh sb="10" eb="12">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ドロップアイテム/確率</t>
+    <rPh sb="9" eb="11">
+      <t>カクリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮素材 * 1 + 30G/仮素材 * 2 + 30G/ 仮素材 * 3 + 30G/
+仮素材 * 4 + 30G/仮素材 * 5 + 30G</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>カリソザイ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>カリソザイ</t>
+    </rPh>
+    <rPh sb="44" eb="47">
+      <t>カリソザイ</t>
+    </rPh>
+    <rPh sb="58" eb="61">
+      <t>カリソザイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>d_power_flag</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>力の結晶(D)</t>
+    <rPh sb="0" eb="1">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素材</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>非戦闘中</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1" eb="4">
+      <t>セントウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>未所持または強化がまだ終わっていない
+スキルを獲得、強化する
+そのランクのスキルが全て獲得、さらに
+強化終了しているならお金を300獲得</t>
+    <rPh sb="0" eb="3">
+      <t>ミショジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>カネ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>カクトク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Dランクのスキルの獲得、または強化</t>
+    <rPh sb="9" eb="11">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Dランクのスキルを獲得、強化できる</t>
+    <rPh sb="9" eb="11">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>100G/100%.(アイテムID:kari_dorop) * 1/100%.(アイテムID:d_power_flag) * 1/30%</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フォーカスした敵の被ダメージ率上昇(+0/+2/+4/+6/+8/+10)%</t>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに指定した敵1体の狙っている間の受けるダメージが上昇する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ネラ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに指定した敵1体の狙っている間の被ダメージ率(+2/+4/+6/+8/+10)%</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ネラ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルを上がるごとに武器の(追加ステータスのステータス名)が約10%上昇する。少数は切り捨てされる。(以下全武器同文)</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スキルタイプ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>範囲攻撃</t>
+    <rPh sb="0" eb="4">
+      <t>ハンイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全体回復</t>
+    <rPh sb="0" eb="4">
+      <t>ゼンタイカイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単体回復</t>
+    <rPh sb="0" eb="2">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単体シールド</t>
+    <rPh sb="0" eb="2">
+      <t>タンタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単体攻撃</t>
+    <rPh sb="0" eb="4">
+      <t>タンタイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>範囲デバフ</t>
+    <rPh sb="0" eb="2">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>方向指定攻撃</t>
+    <rPh sb="0" eb="4">
+      <t>ホウコウシテイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象指示</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象指示</t>
+    <rPh sb="0" eb="4">
+      <t>タイショウシジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>範囲指示</t>
+    <rPh sb="0" eb="4">
+      <t>ハンイシジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>125px</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -5479,7 +6417,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5513,6 +6451,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF275317"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -5614,7 +6558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5685,6 +6629,31 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -6019,7 +6988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:Z35"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6027,1816 +6996,1905 @@
     <col min="3" max="3" width="15.8984375" customWidth="1"/>
     <col min="4" max="4" width="9.3984375" style="6" customWidth="1"/>
     <col min="5" max="5" width="21.796875" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="24.3984375" customWidth="1"/>
-    <col min="8" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="24.09765625" customWidth="1"/>
-    <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="42" customWidth="1"/>
-    <col min="21" max="21" width="41.796875" customWidth="1"/>
-    <col min="22" max="22" width="43.59765625" customWidth="1"/>
-    <col min="23" max="23" width="56.69921875" customWidth="1"/>
-    <col min="24" max="24" width="60.796875" customWidth="1"/>
-    <col min="25" max="25" width="72.796875" customWidth="1"/>
+    <col min="6" max="6" width="18.796875" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="24.3984375" customWidth="1"/>
+    <col min="9" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="24.09765625" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="42" customWidth="1"/>
+    <col min="22" max="22" width="41.796875" customWidth="1"/>
+    <col min="23" max="23" width="43.59765625" customWidth="1"/>
+    <col min="24" max="24" width="56.69921875" customWidth="1"/>
+    <col min="25" max="25" width="60.796875" customWidth="1"/>
+    <col min="26" max="26" width="72.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="27" customHeight="1">
+    <row r="1" spans="1:26" ht="27" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>266</v>
+      <c r="F1" s="36" t="s">
+        <v>667</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="M1" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="V1" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>399</v>
+        <v>230</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>393</v>
+        <v>383</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="36">
+    <row r="2" spans="1:26" ht="36">
       <c r="A2" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="F2" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J2" s="2">
         <v>15</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="N2" s="2" t="s">
+      <c r="P2" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>367</v>
+      <c r="R2" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="U2" s="12" t="s">
-        <v>370</v>
+        <v>358</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>360</v>
       </c>
       <c r="V2" s="12" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>406</v>
+        <v>362</v>
       </c>
       <c r="X2" s="12" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>407</v>
+        <v>385</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>398</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="36">
+    <row r="3" spans="1:26" ht="36">
       <c r="A3" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="F3" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2">
+        <v>20</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="2">
-        <v>20</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="N3" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="N3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="V3" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="W3" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="S3" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="U3" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="V3" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="W3" s="12" t="s">
-        <v>396</v>
-      </c>
       <c r="X3" s="12" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>408</v>
+        <v>386</v>
+      </c>
+      <c r="Z3" s="12" t="s">
+        <v>399</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="36">
+    <row r="4" spans="1:26" ht="36">
       <c r="A4" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="F4" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="2">
+        <v>25</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="L4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="V4" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="W4" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="X4" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="Y4" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="Z4" s="12" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="54">
+      <c r="A5" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="2">
-        <v>25</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="U4" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="V4" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="W4" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="X4" s="12" t="s">
-        <v>397</v>
-      </c>
-      <c r="Y4" s="12" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="54">
-      <c r="A5" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>459</v>
+        <v>256</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>40</v>
+        <v>450</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>259</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="O5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="S5" s="3" t="s">
-        <v>378</v>
+        <v>246</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="U5" s="12" t="s">
-        <v>282</v>
+        <v>369</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>260</v>
       </c>
       <c r="V5" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="W5" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="X5" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="Y5" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="Z5" s="12" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="36">
+      <c r="A6" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>672</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="V6" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="W6" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="X6" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="X5" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="Y5" s="12" t="s">
-        <v>404</v>
+      <c r="Y6" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="Z6" s="12" t="s">
+        <v>403</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="36">
-      <c r="A6" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="U6" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="V6" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="W6" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="X6" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="Y6" s="12" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="54">
+    <row r="7" spans="1:26" ht="54">
       <c r="A7" s="3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="F7" s="2">
+        <v>292</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="G7" s="2">
         <v>18</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="2">
+        <v>10</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="L7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="V7" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="W7" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="X7" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="Y7" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="Z7" s="12" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="54">
+      <c r="A8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>672</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="2">
-        <v>10</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N7" s="3" t="s">
+      <c r="J8" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="V8" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="T7" s="3" t="s">
+      <c r="W8" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="X8" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="Y8" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="Z8" s="12" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="36">
+      <c r="A9" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="G9" s="2">
+        <v>20</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="U7" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="Y7" s="12" t="s">
-        <v>413</v>
+      <c r="I9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V9" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="W9" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="X9" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="Y9" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="Z9" s="12" t="s">
+        <v>398</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="54">
-      <c r="A8" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="U8" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="V8" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="W8" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="X8" s="12" t="s">
-        <v>416</v>
-      </c>
-      <c r="Y8" s="12" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="36">
-      <c r="A9" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="F9" s="2">
-        <v>20</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="U9" s="12" t="s">
-        <v>349</v>
-      </c>
-      <c r="V9" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="W9" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="X9" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="Y9" s="12" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="72">
+    <row r="10" spans="1:26" ht="72">
       <c r="A10" s="3" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>297</v>
+        <v>545</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>668</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="H10" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="2">
+      <c r="J10" s="2">
         <v>15</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="L10" s="3" t="s">
+      <c r="O10" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V10" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="W10" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="X10" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="Y10" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="Z10" s="12" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="36">
+      <c r="A11" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N10" s="3" t="s">
+      <c r="O11" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="T10" s="2" t="s">
+      <c r="P11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="U10" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="V10" s="12" t="s">
+      <c r="R11" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="V11" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="W11" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="X11" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="Y11" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="Z11" s="12" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="72">
+      <c r="A12" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>674</v>
+      </c>
+      <c r="G12" s="2">
+        <v>15</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="2">
+        <v>20</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="V12" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="W10" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="X10" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="Y10" s="12" t="s">
-        <v>420</v>
+      <c r="W12" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="X12" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="Y12" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="Z12" s="12" t="s">
+        <v>417</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="36">
-      <c r="A11" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="U11" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="V11" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="W11" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="X11" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="Y11" s="12" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="72">
-      <c r="A12" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="F12" s="2">
-        <v>15</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="2">
-        <v>20</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="U12" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="V12" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="W12" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="X12" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="Y12" s="12" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="54">
+    <row r="13" spans="1:26" ht="54">
       <c r="A13" s="12" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>545</v>
-      </c>
-      <c r="F13">
+        <v>532</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>672</v>
+      </c>
+      <c r="G13">
         <v>30</v>
       </c>
-      <c r="G13" s="12" t="s">
-        <v>546</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="I13">
+      <c r="H13" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="J13">
         <v>40</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="K13" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q13" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="R13" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="S13" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="T13" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="U13" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="V13" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="W13" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="X13" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="Y13" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="Z13" s="12" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="143.4" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="V14" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="W14" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="X14" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="Y14" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z14" s="12" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="54">
+      <c r="A15" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="V15" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="W15" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="X15" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="Y15" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="Z15" s="12" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="54">
+      <c r="A16" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="V16" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="W16" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="X16" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="Y16" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="Z16" s="12" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" ht="54">
+      <c r="A17" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="V17" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="W17" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="X17" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="Y17" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="Z17" s="12" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="54">
+      <c r="A18" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="V18" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="W18" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="X18" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="Y18" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="Z18" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="36">
+      <c r="A19" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="V19" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="W19" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="X19" s="12"/>
+    </row>
+    <row r="20" spans="1:26" ht="72">
+      <c r="A20" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="V20" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="W20" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="16"/>
+    </row>
+    <row r="21" spans="1:26" ht="72">
+      <c r="A21" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="V21" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="W21" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="X21" s="12"/>
+    </row>
+    <row r="22" spans="1:26" ht="54">
+      <c r="A22" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="T22" s="2"/>
+      <c r="U22" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="V22" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="W22" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="X22" s="12"/>
+    </row>
+    <row r="23" spans="1:26" ht="36">
+      <c r="A23" s="12" t="s">
         <v>547</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="B23" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>548</v>
       </c>
-      <c r="L13" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="N13" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="P13" s="12" t="s">
+      <c r="D23" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="Q13" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="R13" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="S13" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="T13" s="12" t="s">
+      <c r="E23" s="13" t="s">
         <v>550</v>
       </c>
-      <c r="U13" s="16" t="s">
+      <c r="F23" s="13" t="s">
+        <v>676</v>
+      </c>
+      <c r="G23" s="13" t="s">
         <v>551</v>
       </c>
-      <c r="V13" s="12" t="s">
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="13" t="s">
         <v>552</v>
       </c>
-      <c r="W13" s="12" t="s">
-        <v>446</v>
-      </c>
-      <c r="X13" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="Y13" s="12" t="s">
-        <v>448</v>
+      <c r="L23" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="O23" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="P23" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="Q23" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="R23" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="S23" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="T23" s="13" t="s">
+        <v>550</v>
+      </c>
+      <c r="U23" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="V23" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="W23" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="X23" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="Y23" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="Z23" s="12" t="s">
+        <v>665</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="143.4" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="U14" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="V14" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="W14" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="X14" s="12" t="s">
-        <v>431</v>
-      </c>
-      <c r="Y14" s="12" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="54">
-      <c r="A15" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="U15" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="V15" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="W15" s="12" t="s">
-        <v>463</v>
-      </c>
-      <c r="X15" s="12" t="s">
-        <v>441</v>
-      </c>
-      <c r="Y15" s="12" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="54">
-      <c r="A16" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="U16" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="V16" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="W16" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="X16" s="12" t="s">
-        <v>441</v>
-      </c>
-      <c r="Y16" s="12" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" ht="54">
-      <c r="A17" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="V17" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="W17" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="X17" s="12" t="s">
-        <v>441</v>
-      </c>
-      <c r="Y17" s="12" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" ht="54">
-      <c r="A18" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="V18" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="W18" s="12" t="s">
-        <v>466</v>
-      </c>
-      <c r="X18" s="12" t="s">
-        <v>441</v>
-      </c>
-      <c r="Y18" s="12" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" ht="36">
-      <c r="A19" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="U19" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="V19" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="W19" s="12"/>
-    </row>
-    <row r="20" spans="1:25" ht="72">
-      <c r="A20" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="U20" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="V20" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="W20" s="12"/>
-      <c r="X20" s="16"/>
-    </row>
-    <row r="21" spans="1:25" ht="72">
-      <c r="A21" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="U21" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="V21" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="W21" s="12"/>
-    </row>
-    <row r="22" spans="1:25" ht="54">
-      <c r="A22" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="S22" s="2"/>
-      <c r="T22" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="U22" s="11" t="s">
-        <v>388</v>
-      </c>
-      <c r="V22" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="W22" s="12"/>
-    </row>
-    <row r="23" spans="1:25" ht="36">
-      <c r="A23" s="12" t="s">
-        <v>560</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>561</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>563</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>564</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>565</v>
-      </c>
-      <c r="K23" s="12" t="s">
-        <v>564</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>566</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>564</v>
-      </c>
-      <c r="O23" s="12" t="s">
-        <v>568</v>
-      </c>
-      <c r="P23" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="Q23" s="12" t="s">
-        <v>564</v>
-      </c>
-      <c r="R23" s="13" t="s">
-        <v>564</v>
-      </c>
-      <c r="S23" s="13" t="s">
-        <v>563</v>
-      </c>
-      <c r="T23" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="U23" s="12" t="s">
-        <v>571</v>
-      </c>
-      <c r="V23" s="12" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" ht="72">
+    <row r="31" spans="1:26" ht="72">
       <c r="A31" s="3" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>502</v>
+        <v>193</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="F31" s="3">
+        <v>458</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="G31" s="3">
         <v>32</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I31" s="2">
+      <c r="J31" s="2">
         <v>40</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="K31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>325</v>
+        <v>62</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>467</v>
+        <v>246</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="U31" s="12" t="s">
-        <v>358</v>
+        <v>458</v>
+      </c>
+      <c r="U31" s="3" t="s">
+        <v>318</v>
       </c>
       <c r="V31" s="12" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="W31" s="12" t="s">
-        <v>427</v>
+        <v>350</v>
       </c>
       <c r="X31" s="12" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="Y31" s="12" t="s">
-        <v>429</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="Z31" s="12" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="M34" s="4"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S25" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -7858,7 +8916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E325287-6FF5-4811-9C1B-B61C8E79C27E}">
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -7866,275 +8924,278 @@
     <col min="3" max="3" width="15.8984375" customWidth="1"/>
     <col min="4" max="4" width="9.3984375" style="6" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="42" customWidth="1"/>
-    <col min="21" max="23" width="39" customWidth="1"/>
-    <col min="24" max="24" width="54.5" customWidth="1"/>
-    <col min="25" max="25" width="52" customWidth="1"/>
-    <col min="26" max="26" width="49.19921875" customWidth="1"/>
+    <col min="6" max="6" width="14.59765625" customWidth="1"/>
+    <col min="7" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="42" customWidth="1"/>
+    <col min="22" max="24" width="39" customWidth="1"/>
+    <col min="25" max="25" width="54.5" customWidth="1"/>
+    <col min="26" max="26" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="24" customHeight="1">
+    <row r="1" spans="1:26" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>266</v>
+      <c r="F1" s="37" t="s">
+        <v>667</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="V1" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>399</v>
+        <v>230</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>393</v>
+        <v>383</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="38"/>
+      <c r="G2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="M2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="36">
+      <c r="A3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>74</v>
+      <c r="N4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="36">
-      <c r="A3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:26">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="2"/>
       <c r="D5" s="14"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -8149,14 +9210,14 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:26">
       <c r="A6" s="3"/>
       <c r="B6" s="4"/>
       <c r="C6" s="2"/>
       <c r="D6" s="14"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -8171,14 +9232,14 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:26">
       <c r="A7" s="3"/>
       <c r="B7" s="4"/>
       <c r="C7" s="2"/>
       <c r="D7" s="14"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -8193,14 +9254,14 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:26">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
       <c r="C8" s="2"/>
       <c r="D8" s="14"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -8215,14 +9276,14 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:26">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="2"/>
       <c r="D9" s="14"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -8237,14 +9298,14 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:26">
       <c r="A10" s="3"/>
       <c r="B10" s="4"/>
       <c r="C10" s="2"/>
       <c r="D10" s="14"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -8259,14 +9320,14 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:26">
       <c r="A11" s="3"/>
       <c r="B11" s="4"/>
       <c r="C11" s="2"/>
       <c r="D11" s="14"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -8281,14 +9342,14 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:26">
       <c r="A12" s="3"/>
       <c r="B12" s="4"/>
       <c r="C12" s="2"/>
       <c r="D12" s="14"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -8303,14 +9364,14 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:26">
       <c r="A13" s="3"/>
       <c r="B13" s="4"/>
       <c r="C13" s="2"/>
       <c r="D13" s="14"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -8325,14 +9386,14 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:26">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
       <c r="C14" s="2"/>
       <c r="D14" s="14"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -8347,13 +9408,13 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:24">
       <c r="A18" s="3"/>
       <c r="C18" s="2"/>
       <c r="D18" s="14"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -8366,15 +9427,15 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="2"/>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:24">
       <c r="A19" s="3"/>
       <c r="C19" s="2"/>
       <c r="D19" s="14"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -8387,15 +9448,15 @@
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="2"/>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:24">
       <c r="A20" s="3"/>
       <c r="C20" s="2"/>
       <c r="D20" s="14"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -8408,15 +9469,15 @@
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="2"/>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:24">
       <c r="A21" s="3"/>
       <c r="C21" s="2"/>
       <c r="D21" s="14"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -8429,15 +9490,15 @@
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="2"/>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:24">
       <c r="A22" s="3"/>
       <c r="C22" s="2"/>
       <c r="D22" s="14"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -8452,16 +9513,16 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
-      <c r="U22" s="13"/>
-      <c r="V22" s="12"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="13"/>
       <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:24">
       <c r="A23" s="3"/>
       <c r="C23" s="2"/>
       <c r="D23" s="14"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -8475,17 +9536,17 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="12"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="3"/>
       <c r="V23" s="12"/>
       <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:24">
       <c r="A24" s="3"/>
       <c r="C24" s="2"/>
       <c r="D24" s="14"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -8499,17 +9560,17 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="12"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="3"/>
       <c r="V24" s="12"/>
       <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:24">
       <c r="A25" s="3"/>
       <c r="C25" s="2"/>
       <c r="D25" s="14"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -8523,7 +9584,8 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
-      <c r="T25" s="3"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S25" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -8553,116 +9615,116 @@
         <v>2</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="37.200000000000003" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36">
       <c r="A3" s="4" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="54">
       <c r="A4" s="4" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="36">
       <c r="A6" s="4" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8686,7 +9748,8 @@
     <col min="5" max="24" width="14" customWidth="1"/>
     <col min="25" max="25" width="48" customWidth="1"/>
     <col min="26" max="26" width="46.69921875" customWidth="1"/>
-    <col min="27" max="45" width="14" customWidth="1"/>
+    <col min="27" max="27" width="73.09765625" customWidth="1"/>
+    <col min="28" max="45" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45">
@@ -8697,90 +9760,93 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>456</v>
+        <v>447</v>
+      </c>
+      <c r="AA1" s="35" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="2" spans="1:45">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E2" s="2">
         <v>490</v>
@@ -8792,7 +9858,7 @@
         <v>90</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="I2" s="2">
         <v>95</v>
@@ -8801,52 +9867,54 @@
         <v>95</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="L2" s="15">
         <v>0.5</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="V2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="U2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="X2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
+      <c r="AA2" s="3" t="s">
+        <v>650</v>
+      </c>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
@@ -8868,16 +9936,16 @@
     </row>
     <row r="3" spans="1:45" ht="54">
       <c r="A3" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E3" s="2">
         <v>500</v>
@@ -8889,10 +9957,10 @@
         <v>110</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J3" s="2">
         <v>100</v>
@@ -8904,44 +9972,46 @@
         <v>0.5</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q3" s="15">
         <v>1</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="S3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="W3" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
-      <c r="AA3" s="2"/>
+      <c r="AA3" s="3" t="s">
+        <v>650</v>
+      </c>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
@@ -8963,16 +10033,16 @@
     </row>
     <row r="4" spans="1:45" ht="54">
       <c r="A4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E4" s="2">
         <v>530</v>
@@ -8981,7 +10051,7 @@
         <v>290</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="H4" s="2">
         <v>80</v>
@@ -8990,53 +10060,55 @@
         <v>100</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="L4" s="15">
         <v>0.5</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q4" s="15">
         <v>1</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="S4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="V4" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="W4" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
+      <c r="AA4" s="3" t="s">
+        <v>650</v>
+      </c>
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
@@ -9058,80 +10130,82 @@
     </row>
     <row r="5" spans="1:45" ht="54">
       <c r="A5" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E5" s="2">
         <v>480</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="H5" s="2">
         <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="L5" s="15">
         <v>0.5</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q5" s="15">
         <v>1</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="S5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="W5" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
-      <c r="AA5" s="2"/>
+      <c r="AA5" s="3" t="s">
+        <v>650</v>
+      </c>
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
@@ -9153,82 +10227,84 @@
     </row>
     <row r="6" spans="1:45">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>130</v>
+        <v>110</v>
+      </c>
+      <c r="E6" s="2">
+        <v>300</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>21</v>
+        <v>127</v>
+      </c>
+      <c r="G6" s="2">
+        <v>8</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L6" s="15">
         <v>0.5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>27</v>
+        <v>111</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>1</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="Z6" s="2"/>
-      <c r="AA6" s="2"/>
+      <c r="AA6" s="3" t="s">
+        <v>662</v>
+      </c>
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
       <c r="AD6" s="2"/>
@@ -9250,82 +10326,84 @@
     </row>
     <row r="7" spans="1:45">
       <c r="A7" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
+      </c>
+      <c r="E7" s="2">
+        <v>250</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L7" s="15">
         <v>0.5</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>27</v>
+        <v>111</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>1</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
+      <c r="AA7" s="3" t="s">
+        <v>662</v>
+      </c>
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
@@ -9347,82 +10425,84 @@
     </row>
     <row r="8" spans="1:45">
       <c r="A8" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="2">
         <v>180</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
+      </c>
+      <c r="G8" s="2">
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L8" s="15">
         <v>0.5</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>27</v>
+        <v>111</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>1</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
+      <c r="AA8" s="3" t="s">
+        <v>662</v>
+      </c>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -9444,82 +10524,84 @@
     </row>
     <row r="9" spans="1:45" ht="36">
       <c r="A9" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>143</v>
+        <v>110</v>
+      </c>
+      <c r="E9" s="2">
+        <v>200</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>21</v>
+        <v>127</v>
+      </c>
+      <c r="G9" s="2">
+        <v>6</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L9" s="15">
         <v>0.5</v>
       </c>
       <c r="M9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q9" s="15">
+        <v>1</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="X9" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="Y9" s="2" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
+      <c r="AA9" s="3" t="s">
+        <v>662</v>
+      </c>
       <c r="AB9" s="2"/>
       <c r="AC9" s="2"/>
       <c r="AD9" s="2"/>
@@ -9541,82 +10623,84 @@
     </row>
     <row r="10" spans="1:45" ht="36">
       <c r="A10" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>147</v>
+        <v>110</v>
+      </c>
+      <c r="E10" s="2">
+        <v>700</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>62</v>
+        <v>127</v>
+      </c>
+      <c r="G10" s="2">
+        <v>10</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L10" s="15">
         <v>0.5</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>27</v>
+        <v>111</v>
+      </c>
+      <c r="Q10" s="15">
+        <v>1</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
+      <c r="AA10" s="3" t="s">
+        <v>662</v>
+      </c>
       <c r="AB10" s="2"/>
       <c r="AC10" s="2"/>
       <c r="AD10" s="2"/>
@@ -9645,7 +10729,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -9655,12 +10739,14 @@
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="8" width="30" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="40.5" customWidth="1"/>
-    <col min="12" max="13" width="60.3984375" customWidth="1"/>
-    <col min="14" max="14" width="40.5" customWidth="1"/>
-    <col min="15" max="15" width="48.59765625" customWidth="1"/>
-    <col min="16" max="18" width="60.3984375" customWidth="1"/>
+    <col min="10" max="10" width="47.796875" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="40.5" customWidth="1"/>
+    <col min="13" max="14" width="60.3984375" customWidth="1"/>
+    <col min="15" max="15" width="40.5" customWidth="1"/>
+    <col min="16" max="16" width="53" customWidth="1"/>
+    <col min="17" max="17" width="63.8984375" customWidth="1"/>
+    <col min="18" max="18" width="60.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="22.8" customHeight="1">
@@ -9671,139 +10757,145 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>235</v>
+        <v>186</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>490</v>
+        <v>229</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="O1" s="19" t="s">
+        <v>463</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>491</v>
-      </c>
-      <c r="Q1" s="18"/>
+        <v>479</v>
+      </c>
+      <c r="Q1" s="20" t="s">
+        <v>480</v>
+      </c>
       <c r="R1" s="18"/>
     </row>
     <row r="2" spans="1:18" ht="36">
       <c r="A2" s="4" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>229</v>
+        <v>600</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>488</v>
+        <v>220</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>220</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>492</v>
+        <v>612</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q2" s="4"/>
+        <v>636</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>666</v>
+      </c>
       <c r="R2" s="4"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="I3" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>231</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="N3" s="4"/>
+        <v>220</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>220</v>
+      </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
@@ -9811,43 +10903,45 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="4" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>229</v>
+        <v>600</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="N4" s="4"/>
+        <v>220</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>220</v>
+      </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
@@ -9855,67 +10949,342 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>229</v>
+        <v>600</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="N5" s="4"/>
+        <v>220</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>220</v>
+      </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
     </row>
+    <row r="7" spans="1:18" ht="36">
+      <c r="A7" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="H7" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="36">
+      <c r="A8" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="H8" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="36">
+      <c r="A9" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="H9" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>608</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="36">
+      <c r="A10" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="H10" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>608</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="36">
+      <c r="A11" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H11" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>609</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="36">
+      <c r="A12" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H12" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>610</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="36">
+      <c r="A13" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H13" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>610</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>651</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74530E38-EDB4-4883-BA3E-6C72C076C507}">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.69921875" customWidth="1"/>
     <col min="2" max="2" width="20.69921875" customWidth="1"/>
-    <col min="3" max="9" width="16.69921875" customWidth="1"/>
+    <col min="3" max="5" width="16.69921875" customWidth="1"/>
+    <col min="6" max="6" width="24.296875" customWidth="1"/>
+    <col min="7" max="8" width="16.69921875" customWidth="1"/>
+    <col min="9" max="9" width="50.3984375" customWidth="1"/>
     <col min="10" max="10" width="27.296875" customWidth="1"/>
     <col min="11" max="11" width="53.8984375" customWidth="1"/>
     <col min="12" max="12" width="48.59765625" customWidth="1"/>
-    <col min="13" max="13" width="27.296875" customWidth="1"/>
+    <col min="13" max="13" width="49.296875" customWidth="1"/>
     <col min="14" max="14" width="53.8984375" customWidth="1"/>
     <col min="15" max="15" width="48.59765625" customWidth="1"/>
     <col min="18" max="18" width="24" customWidth="1"/>
@@ -9929,50 +11298,269 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>191</v>
+        <v>619</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>639</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
       <c r="R1" s="18"/>
     </row>
+    <row r="2" spans="1:18" ht="54">
+      <c r="A2" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="36">
+      <c r="A3" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="36">
+      <c r="A4" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="36">
+      <c r="A5" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="36">
+      <c r="A6" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="36">
+      <c r="A7" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M1" xr:uid="{74530E38-EDB4-4883-BA3E-6C72C076C507}"/>
+  <autoFilter ref="A1:H7" xr:uid="{74530E38-EDB4-4883-BA3E-6C72C076C507}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9980,39 +11568,78 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{679D6C04-1546-44B7-B4BC-9388FD23F265}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.69921875" customWidth="1"/>
     <col min="2" max="2" width="20.69921875" customWidth="1"/>
-    <col min="3" max="10" width="16.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="51.5" customWidth="1"/>
+    <col min="5" max="5" width="38.19921875" customWidth="1"/>
+    <col min="6" max="6" width="48.3984375" customWidth="1"/>
+    <col min="7" max="7" width="59.09765625" customWidth="1"/>
+    <col min="8" max="8" width="47.5" customWidth="1"/>
+    <col min="9" max="9" width="57.3984375" customWidth="1"/>
+    <col min="10" max="10" width="16.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.05" customHeight="1">
+    <row r="1" spans="1:9" ht="22.05" customHeight="1">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E1" s="21" t="s">
         <v>15</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>473</v>
+        <v>643</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>474</v>
+        <v>642</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>644</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>641</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{679D6C04-1546-44B7-B4BC-9388FD23F265}"/>
+  <autoFilter ref="A1:B1" xr:uid="{679D6C04-1546-44B7-B4BC-9388FD23F265}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10020,15 +11647,26 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD2C904-A80C-4DD6-9EC2-BF8829F6BFCA}">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.69921875" customWidth="1"/>
     <col min="2" max="2" width="20.69921875" customWidth="1"/>
-    <col min="3" max="15" width="16.69921875" customWidth="1"/>
+    <col min="3" max="6" width="16.69921875" customWidth="1"/>
+    <col min="7" max="7" width="34.296875" customWidth="1"/>
+    <col min="8" max="8" width="16.69921875" customWidth="1"/>
+    <col min="9" max="9" width="10.796875" customWidth="1"/>
+    <col min="10" max="10" width="10.69921875" customWidth="1"/>
+    <col min="11" max="11" width="16.69921875" customWidth="1"/>
+    <col min="12" max="12" width="17.796875" customWidth="1"/>
+    <col min="13" max="14" width="16.69921875" customWidth="1"/>
+    <col min="15" max="15" width="31" customWidth="1"/>
+    <col min="16" max="16" width="33.8984375" customWidth="1"/>
+    <col min="17" max="17" width="40.59765625" customWidth="1"/>
+    <col min="18" max="18" width="44.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="22.05" customHeight="1">
+    <row r="1" spans="1:18" ht="22.05" customHeight="1">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -10036,47 +11674,159 @@
         <v>2</v>
       </c>
       <c r="C1" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>471</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>480</v>
-      </c>
       <c r="G1" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>481</v>
-      </c>
-      <c r="I1" s="17" t="s">
-        <v>482</v>
+        <v>227</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>560</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>561</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>483</v>
+        <v>571</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>484</v>
+        <v>472</v>
+      </c>
+      <c r="L1" s="31" t="s">
+        <v>564</v>
       </c>
       <c r="M1" s="17" t="s">
-        <v>473</v>
+        <v>184</v>
       </c>
       <c r="N1" s="17" t="s">
         <v>474</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="O1" s="32" t="s">
+        <v>473</v>
+      </c>
+      <c r="P1" s="17" t="s">
         <v>15</v>
+      </c>
+      <c r="Q1" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="R1" s="17" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="N2">
+        <v>50</v>
+      </c>
+      <c r="O2" s="4"/>
+      <c r="Q2" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="72">
+      <c r="A4" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>661</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1" xr:uid="{7CD2C904-A80C-4DD6-9EC2-BF8829F6BFCA}"/>
+  <autoFilter ref="A1:O2" xr:uid="{7CD2C904-A80C-4DD6-9EC2-BF8829F6BFCA}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10097,51 +11847,51 @@
   <sheetData>
     <row r="2" spans="2:13">
       <c r="B2" s="23" t="s">
+        <v>481</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>488</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>531</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>493</v>
+      </c>
+      <c r="J2" s="28" t="s">
         <v>494</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>501</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>544</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>506</v>
-      </c>
-      <c r="J2" s="28" t="s">
-        <v>507</v>
-      </c>
       <c r="L2" s="23" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="M2" s="23" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="23" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="M3" s="24">
         <v>1</v>
@@ -10149,25 +11899,25 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="23" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="J4" s="28" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="M4" s="24">
         <v>2</v>
@@ -10175,25 +11925,25 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="23" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="M5" s="24">
         <v>3</v>
@@ -10201,25 +11951,25 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="23" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="M6" s="24">
         <v>4</v>
@@ -10227,25 +11977,25 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="23" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="M7" s="24">
         <v>5</v>
@@ -10253,104 +12003,104 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="23" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
       <c r="F8" s="26"/>
       <c r="I8" s="23" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
     </row>
     <row r="9" spans="2:13">
       <c r="I9" s="23" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="J9" s="28" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10" spans="2:13">
       <c r="I10" s="23" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="J10" s="28" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" spans="2:13">
       <c r="I11" s="23" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
     </row>
     <row r="12" spans="2:13">
       <c r="I12" s="23" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="J12" s="28" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="I13" s="23" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
     </row>
     <row r="14" spans="2:13">
       <c r="I14" s="23" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="I15" s="23" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="I16" s="23" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17" spans="9:10">
       <c r="I17" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="J17" s="28" t="s">
         <v>516</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="18" spans="9:10">
       <c r="I18" s="23" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
     </row>
     <row r="19" spans="9:10">
       <c r="I19" s="23" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0324372-A5DA-4D04-963C-897200BACCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBA71BC-19F5-4A6B-86CC-0321C7D27E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="防具" sheetId="7" r:id="rId6"/>
     <sheet name="セット効果" sheetId="8" r:id="rId7"/>
     <sheet name="アイテム" sheetId="9" r:id="rId8"/>
-    <sheet name="ランダムステータス" sheetId="10" r:id="rId9"/>
+    <sheet name="ランダムステータス(今ランダム抽選はなし)" sheetId="10" r:id="rId9"/>
     <sheet name="ステータス説明" sheetId="11" r:id="rId10"/>
   </sheets>
   <definedNames>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="685">
   <si>
     <t>ID</t>
   </si>
@@ -5979,26 +5979,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>HPとMPが30%上昇する</t>
-    <rPh sb="9" eb="11">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>攻撃力と魔力が30%上昇する</t>
-    <rPh sb="0" eb="3">
-      <t>コウゲキリョク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>マリョク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>2セット効果詳細説明</t>
     <rPh sb="4" eb="6">
       <t>コウカ</t>
@@ -6026,33 +6006,6 @@
     <t>5セット効果詳細説明文</t>
     <rPh sb="4" eb="6">
       <t>コウカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>HPとMPが上昇する</t>
-    <rPh sb="6" eb="8">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>攻撃力と魔力が上昇する</t>
-    <rPh sb="0" eb="3">
-      <t>コウゲキリョク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>マリョク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>HPとMPが30%が上昇する</t>
-    <rPh sb="10" eb="12">
-      <t>ジョウショウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -6376,6 +6329,92 @@
   </si>
   <si>
     <t>125px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>被ダメージ率-10%</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HPが10%上昇する</t>
+    <rPh sb="6" eb="8">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>防御が10%上昇する</t>
+    <rPh sb="0" eb="2">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HPが上昇する</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>防御力が10%上昇する</t>
+    <rPh sb="0" eb="3">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>防御力が上昇する</t>
+    <rPh sb="0" eb="3">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HP+50</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>防御+5</t>
+    <rPh sb="0" eb="2">
+      <t>ボウギョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔防+5</t>
+    <rPh sb="0" eb="2">
+      <t>マボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+7</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力+7</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7027,7 +7066,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>257</v>
@@ -7107,7 +7146,7 @@
         <v>358</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>18</v>
@@ -7187,7 +7226,7 @@
         <v>363</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
@@ -7267,7 +7306,7 @@
         <v>368</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>32</v>
@@ -7347,7 +7386,7 @@
         <v>369</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>258</v>
@@ -7427,7 +7466,7 @@
         <v>291</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>43</v>
@@ -7507,7 +7546,7 @@
         <v>292</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="G7" s="2">
         <v>18</v>
@@ -7587,7 +7626,7 @@
         <v>268</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>51</v>
@@ -7667,7 +7706,7 @@
         <v>275</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="G9" s="2">
         <v>20</v>
@@ -7747,7 +7786,7 @@
         <v>545</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>288</v>
@@ -7827,7 +7866,7 @@
         <v>289</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
@@ -7907,7 +7946,7 @@
         <v>312</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="G12" s="2">
         <v>15</v>
@@ -7985,7 +8024,7 @@
         <v>532</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="G13">
         <v>30</v>
@@ -8065,7 +8104,7 @@
         <v>63</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>43</v>
@@ -8145,7 +8184,7 @@
         <v>146</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>23</v>
@@ -8225,7 +8264,7 @@
         <v>147</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>23</v>
@@ -8305,7 +8344,7 @@
         <v>148</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>23</v>
@@ -8385,7 +8424,7 @@
         <v>149</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>23</v>
@@ -8740,7 +8779,7 @@
         <v>550</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>551</v>
@@ -8788,13 +8827,13 @@
         <v>559</v>
       </c>
       <c r="X23" s="12" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="Y23" s="12" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="Z23" s="12" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="72">
@@ -8814,7 +8853,7 @@
         <v>458</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="G31" s="3">
         <v>32</v>
@@ -8949,7 +8988,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>257</v>
@@ -9832,7 +9871,7 @@
         <v>447</v>
       </c>
       <c r="AA1" s="35" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
     </row>
     <row r="2" spans="1:45">
@@ -9894,7 +9933,7 @@
         <v>112</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>111</v>
@@ -9913,7 +9952,7 @@
       </c>
       <c r="Z2" s="2"/>
       <c r="AA2" s="3" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
@@ -10010,7 +10049,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
       <c r="AA3" s="3" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
@@ -10107,7 +10146,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
       <c r="AA4" s="3" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
@@ -10204,7 +10243,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
       <c r="AA5" s="3" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
@@ -10303,7 +10342,7 @@
       </c>
       <c r="Z6" s="2"/>
       <c r="AA6" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
@@ -10402,7 +10441,7 @@
       </c>
       <c r="Z7" s="2"/>
       <c r="AA7" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
@@ -10501,7 +10540,7 @@
       </c>
       <c r="Z8" s="2"/>
       <c r="AA8" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
@@ -10600,7 +10639,7 @@
       </c>
       <c r="Z9" s="2"/>
       <c r="AA9" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="AB9" s="2"/>
       <c r="AC9" s="2"/>
@@ -10699,7 +10738,7 @@
       </c>
       <c r="Z10" s="2"/>
       <c r="AA10" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="AB10" s="2"/>
       <c r="AC10" s="2"/>
@@ -10851,7 +10890,7 @@
         <v>636</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="R2" s="4"/>
     </row>
@@ -11022,7 +11061,7 @@
         <v>209</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>611</v>
@@ -11063,7 +11102,7 @@
         <v>441</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>611</v>
@@ -11104,7 +11143,7 @@
         <v>608</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>611</v>
@@ -11145,7 +11184,7 @@
         <v>608</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>611</v>
@@ -11186,7 +11225,7 @@
         <v>609</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>611</v>
@@ -11227,7 +11266,7 @@
         <v>610</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="36">
@@ -11259,7 +11298,7 @@
         <v>610</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -11359,11 +11398,14 @@
       <c r="F2" s="4" t="s">
         <v>633</v>
       </c>
+      <c r="G2" s="11" t="s">
+        <v>680</v>
+      </c>
       <c r="H2" s="4" t="s">
         <v>600</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>634</v>
@@ -11403,11 +11445,14 @@
       <c r="F3" s="4" t="s">
         <v>633</v>
       </c>
+      <c r="G3" s="4" t="s">
+        <v>681</v>
+      </c>
       <c r="H3" s="4" t="s">
         <v>600</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>634</v>
@@ -11438,11 +11483,14 @@
       <c r="F4" s="4" t="s">
         <v>633</v>
       </c>
+      <c r="G4" s="4" t="s">
+        <v>682</v>
+      </c>
       <c r="H4" s="4" t="s">
         <v>600</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>634</v>
@@ -11473,11 +11521,14 @@
       <c r="F5" s="4" t="s">
         <v>633</v>
       </c>
+      <c r="G5" s="4" t="s">
+        <v>683</v>
+      </c>
       <c r="H5" s="4" t="s">
         <v>600</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>634</v>
@@ -11508,11 +11559,14 @@
       <c r="F6" s="4" t="s">
         <v>633</v>
       </c>
+      <c r="G6" s="4" t="s">
+        <v>684</v>
+      </c>
       <c r="H6" s="4" t="s">
         <v>600</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>634</v>
@@ -11543,11 +11597,14 @@
       <c r="F7" s="4" t="s">
         <v>633</v>
       </c>
+      <c r="G7" s="4" t="s">
+        <v>674</v>
+      </c>
       <c r="H7" s="4" t="s">
         <v>600</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>634</v>
@@ -11600,16 +11657,16 @@
         <v>15</v>
       </c>
       <c r="F1" s="22" t="s">
+        <v>641</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>640</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>642</v>
+      </c>
+      <c r="I1" s="22" t="s">
         <v>643</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>642</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>644</v>
-      </c>
-      <c r="I1" s="22" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -11620,22 +11677,22 @@
         <v>596</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>640</v>
+        <v>675</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>641</v>
+        <v>676</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>646</v>
+        <v>677</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>648</v>
+        <v>675</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>647</v>
+        <v>679</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>641</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -11778,7 +11835,7 @@
         <v>600</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>601</v>
@@ -11795,34 +11852,34 @@
     </row>
     <row r="4" spans="1:18" ht="72">
       <c r="A4" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="G4" s="11" t="s">
         <v>654</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>659</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>661</v>
-      </c>
       <c r="R4" s="4" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
     </row>
   </sheetData>
@@ -11837,7 +11894,7 @@
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="22.3984375" customWidth="1"/>
+    <col min="2" max="2" width="27.59765625" customWidth="1"/>
     <col min="3" max="3" width="8.796875" customWidth="1"/>
     <col min="4" max="5" width="6" customWidth="1"/>
     <col min="6" max="6" width="33" customWidth="1"/>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBA71BC-19F5-4A6B-86CC-0321C7D27E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6E9693-D614-4030-A135-A1E1A0655149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -26,11 +26,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">アイテム!$A$1:$O$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">キャラ!$A$1:$Z$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">キャラ!$A$1:$AA$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">セット効果!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">敵スキル!$A$1:$T$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">敵スキル!$A$1:$S$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">防具!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">味方スキル!$A$1:$T$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">味方スキル!$A$1:$S$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="772">
   <si>
     <t>ID</t>
   </si>
@@ -76,12 +76,6 @@
     <t>詠唱時間</t>
   </si>
   <si>
-    <t>指定方法</t>
-  </si>
-  <si>
-    <t>射程</t>
-  </si>
-  <si>
     <t>範囲</t>
   </si>
   <si>
@@ -229,9 +223,6 @@
     <t>接近スキル。衝撃波は魔法扱い</t>
   </si>
   <si>
-    <t>5.5秒</t>
-  </si>
-  <si>
     <t>スシア</t>
   </si>
   <si>
@@ -247,9 +238,6 @@
     <t>enemy_attack</t>
   </si>
   <si>
-    <t>敵技</t>
-  </si>
-  <si>
     <t>攻撃力 + 8</t>
   </si>
   <si>
@@ -328,9 +316,6 @@
     <t>種別</t>
   </si>
   <si>
-    <t>レベル</t>
-  </si>
-  <si>
     <t>HP</t>
   </si>
   <si>
@@ -361,9 +346,6 @@
     <t>詠唱速度</t>
   </si>
   <si>
-    <t>ガード率</t>
-  </si>
-  <si>
     <t>ガード軽減率</t>
   </si>
   <si>
@@ -382,9 +364,6 @@
     <t>finald</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>0%</t>
   </si>
   <si>
@@ -406,25 +385,16 @@
     <t>20%</t>
   </si>
   <si>
-    <t>150px</t>
-  </si>
-  <si>
     <t>16px</t>
   </si>
   <si>
     <t>rihas</t>
   </si>
   <si>
-    <t>135px</t>
-  </si>
-  <si>
     <t>17px</t>
   </si>
   <si>
     <t>sushia</t>
-  </si>
-  <si>
-    <t>120px</t>
   </si>
   <si>
     <t>brute</t>
@@ -542,12 +512,6 @@
     <t>被ダメ時</t>
   </si>
   <si>
-    <t>遅延5秒/スタック2秒</t>
-  </si>
-  <si>
-    <t>遅延ダメージ・痛みなしスタック</t>
-  </si>
-  <si>
     <t>あったまってきたよ！</t>
   </si>
   <si>
@@ -564,9 +528,6 @@
     <t>HP再生率</t>
   </si>
   <si>
-    <t>味方/白魔法士</t>
-  </si>
-  <si>
     <t>300</t>
   </si>
   <si>
@@ -579,24 +540,12 @@
     <t>なし</t>
   </si>
   <si>
-    <t>味方/勇者</t>
-  </si>
-  <si>
     <t>攻防/調子で変動: 前衛65px基準</t>
   </si>
   <si>
-    <t>味方/モンク</t>
-  </si>
-  <si>
-    <t>味方/黒魔法士</t>
-  </si>
-  <si>
     <t>攻防/調子で変動: 後衛230px基準</t>
   </si>
   <si>
-    <t>敵/近接</t>
-  </si>
-  <si>
     <t>65px</t>
   </si>
   <si>
@@ -609,13 +558,7 @@
     <t>増援用の小型前衛。</t>
   </si>
   <si>
-    <t>敵/遠距離</t>
-  </si>
-  <si>
     <t>遠距離直線攻撃。射撃線のスキルCDはスキルシート側で管理。</t>
-  </si>
-  <si>
-    <t>敵/大型</t>
   </si>
   <si>
     <t>大型敵。ヘビースラムのスキルCDはスキルシート側で管理。</t>
@@ -1734,40 +1677,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>受けたダメージの1/3を1秒ごと5回の遅延ダメージで受ける。遅延ダメージは最低1ダメージ。HPが減るたび、逆境(状態ID"buff_itaminasi")を1/30獲得、効果時間は3秒、獲得するごとに時間は更新</t>
-    <rPh sb="30" eb="32">
-      <t>チエン</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>サイテイ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>ギャッキョウ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="82" eb="84">
-      <t>カクトク</t>
-    </rPh>
-    <rPh sb="85" eb="89">
-      <t>コウカジカン</t>
-    </rPh>
-    <rPh sb="91" eb="92">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="93" eb="95">
-      <t>カクトク</t>
-    </rPh>
-    <rPh sb="100" eb="102">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="103" eb="105">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>シールドの効果時間は5.5秒、自身にシールド付与、敵には(状態ID"debuff_taunt")を付与</t>
     <rPh sb="5" eb="9">
       <t>コウカジカン</t>
@@ -1971,46 +1880,6 @@
       <t>ジゾク</t>
     </rPh>
     <rPh sb="37" eb="39">
-      <t>カクトク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>受けるダメージの1/3を5分割にし、1秒ごとの遅延ダメージで受ける。遅延ダメージは最低1ダメージ。HPが減るたびに３秒間持続する"逆境"を１スタック獲得する。</t>
-    <rPh sb="0" eb="1">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ブンカツ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>チエン</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>チエン</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>サイテイ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>ヘ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>ビョウカン</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>ジゾク</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>ギャッキョウ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
       <t>カクトク</t>
     </rPh>
     <phoneticPr fontId="2"/>
@@ -2103,14 +1972,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>遅延ダメージ・痛みなし(buff_itaminasi)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ウォームアップ(buff_warmup)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>半径330px</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2413,13 +2274,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>8秒</t>
-    <rPh sb="1" eb="2">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>魔力 * 0.18</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3056,10 +2910,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>チャッカ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>対象指定</t>
     <rPh sb="0" eb="4">
       <t>タイショウシテイ</t>
@@ -3083,13 +2933,6 @@
   </si>
   <si>
     <t>ダメージデバフ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>燃焼(debuff_burn)</t>
-    <rPh sb="0" eb="2">
-      <t>ネンショウ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -4239,54 +4082,6 @@
   </si>
   <si>
     <t>レベルが上がるごとに無視される確率が-(10/20/30/40/50)%低下する</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ムシ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カクリツ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>テイカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>レベルが上がるごとに無視される確率が-(10/20/30/40/51)%低下する</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ムシ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カクリツ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>テイカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>レベルが上がるごとに無視される確率が-(10/20/30/40/52)%低下する</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ムシ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カクリツ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>テイカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>レベルが上がるごとに無視される確率が-(10/20/30/40/53)%低下する</t>
     <rPh sb="4" eb="5">
       <t>ア</t>
     </rPh>
@@ -4548,54 +4343,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>レベルが上がるごとに無視される確率が(75/65/55/45/35/26)%にまで低下</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ムシ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カクリツ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>テイカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>レベルが上がるごとに無視される確率が(75/65/55/45/35/27)%にまで低下</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ムシ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カクリツ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>テイカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>レベルが上がるごとに無視される確率が(75/65/55/45/35/28)%にまで低下</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ムシ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カクリツ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>テイカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ボンバー</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -4995,13 +4742,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>魔力 * 0.55</t>
-    <rPh sb="0" eb="2">
-      <t>マリョク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>14秒</t>
     <rPh sb="2" eb="3">
       <t>ビョウ</t>
@@ -5009,17 +4749,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>3秒</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>3秒</t>
-    <rPh sb="1" eb="2">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>燃焼(状態ID"debuff_burn")を付与</t>
     <rPh sb="0" eb="2">
       <t>ネンショウ</t>
@@ -5123,46 +4852,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>毎秒の(計算式:現在HPの1%分)の魔法ダメージを受ける。これは魔法ダメージであり、相手の魔法防御力などの影響でダメージが減少する可能性がある</t>
-    <rPh sb="0" eb="2">
-      <t>マイビョウ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ケイサンシキ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="45" eb="50">
-      <t>マホウボウギョリョク</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>エイキョウ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ゲンショウ</t>
-    </rPh>
-    <rPh sb="65" eb="68">
-      <t>カノウセイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>継続的に魔法ダメージを受ける。</t>
     <rPh sb="0" eb="3">
       <t>ケイゾクテキ</t>
@@ -5176,34 +4865,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>燃焼が付与されている間、毎秒(式=値)の魔法ダメージを受ける。</t>
-    <rPh sb="0" eb="2">
-      <t>ネンショウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>マイビョウ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>シキ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>杖/魔導書/魔楽器</t>
     <rPh sb="0" eb="1">
       <t>ツエ</t>
@@ -5267,35 +4928,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>20秒</t>
-    <rPh sb="2" eb="3">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>対象した敵を味方AIが必ず対象を攻撃するようになる</t>
-    <rPh sb="0" eb="2">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ミカタ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>カナラ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>指定した敵1体を一定時間、味方達が狙うようになる</t>
     <rPh sb="0" eb="2">
       <t>シテイ</t>
@@ -5317,40 +4949,6 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>ネラ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>指定した敵1体を味方達が狙うようになる。20秒経過するか対象が戦闘不能になるまで続く</t>
-    <rPh sb="0" eb="2">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>ミカタタチ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ネラ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ケイカ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="31" eb="35">
-      <t>セントウフノウ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>ツヅ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -6151,78 +5749,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>フォーカスした敵の被ダメージ率上昇(+0/+2/+4/+6/+8/+10)%</t>
-    <rPh sb="7" eb="8">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>レベルが上がるごとに指定した敵1体の狙っている間の受けるダメージが上昇する</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ネラ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>レベルが上がるごとに指定した敵1体の狙っている間の被ダメージ率(+2/+4/+6/+8/+10)%</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ネラ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>リツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>レベルを上がるごとに武器の(追加ステータスのステータス名)が約10%上昇する。少数は切り捨てされる。(以下全武器同文)</t>
     <rPh sb="4" eb="5">
       <t>ア</t>
@@ -6328,10 +5854,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>125px</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>被ダメージ率-10%</t>
     <rPh sb="0" eb="1">
       <t>ヒ</t>
@@ -6386,35 +5908,1229 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>HP+50</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>防御+5</t>
+    <t>HP+5%</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>防御+3%</t>
     <rPh sb="0" eb="2">
       <t>ボウギョ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>魔防+5</t>
+    <t>魔防+3%</t>
     <rPh sb="0" eb="2">
       <t>マボウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>攻撃+7</t>
+    <t>攻撃+3%</t>
     <rPh sb="0" eb="2">
       <t>コウゲキ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>魔力+7</t>
+    <t>魔力+3%</t>
     <rPh sb="0" eb="2">
       <t>マリョク</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力 * 0.45</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ツノウサギ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>corner_rabbit</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>白魔法士</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>勇者</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>モンク</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒魔法士</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>遠距離</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>近距離</t>
+    <rPh sb="0" eb="3">
+      <t>キンキョリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ランク</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>70px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>110px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>105px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>110px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>65px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵の中でHPが最も低い敵を狙う</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヒク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ネラ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>使用スキル</t>
+    <rPh sb="0" eb="2">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>rush</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>突進</t>
+    <rPh sb="0" eb="2">
+      <t>トッシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単体攻撃</t>
+    <rPh sb="0" eb="4">
+      <t>タンタイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.3</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>射程</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>範囲</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>指定方法</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>状態異常・バフ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>d_enemy_attack</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>通常攻撃</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.2</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象指定</t>
+    <rPh sb="0" eb="4">
+      <t>タイショウシテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>50px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>物理</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Dランクの敵用の物理通常攻撃</t>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="14">
+      <t>ブツリツウジョウコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.35</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>8秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>0.5秒</t>
+    <rPh sb="3" eb="4">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>80px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>85px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>連続噛みつき</t>
+    <rPh sb="0" eb="3">
+      <t>レンゾクカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>multi_biting</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単体攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>このスキルは一度の発動で2度ダメージを与えることができ、それぞれダメージ計算が別で行われる</t>
+    <rPh sb="6" eb="8">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵スキルID(d_enemy_attack,rush,multi_biting)</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>つぼみのアルラウネ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_Alraune</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>12px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>30px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>！！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>噛みつき</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>突撃</t>
+    <rPh sb="0" eb="2">
+      <t>トツゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>連続噛みつき</t>
+    <rPh sb="0" eb="2">
+      <t>レンゾク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>debuff_sleep</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>睡眠</t>
+    <rPh sb="0" eb="2">
+      <t>スイミン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>行動デバフ</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全行動ができなくなる、睡眠中行動CDは進まない、スキルCDは進む。
+ドットダメージ以外のダメージを受けるか効果時間が切れるまで続く</t>
+    <rPh sb="0" eb="3">
+      <t>ゼンコウドウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>スイミンチュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="53" eb="57">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>寝てしまい、行動ができなくなる</t>
+    <rPh sb="0" eb="1">
+      <t>ネ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>寝てしまい、一切の行動ができなくなる。睡眠中は行動クールタイムは停止する。
+ドットダメージ以外のダメージで解除することができる</t>
+    <rPh sb="0" eb="1">
+      <t>ネ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イッサイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>スイミンチュウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>テイシ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>毎秒の(計算式:現在HPの1%分)の魔法ドットダメージを受ける。これは魔法ダメージであり、相手の魔法防御力などの影響でダメージが減少する可能性がある</t>
+    <rPh sb="0" eb="2">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ケイサンシキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="48" eb="53">
+      <t>マホウボウギョリョク</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="68" eb="71">
+      <t>カノウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>燃焼が付与されている間、毎秒(式=値)の魔法ドットダメージを受ける。</t>
+    <rPh sb="0" eb="2">
+      <t>ネンショウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受けたダメージの1/3を1秒ごと5回の遅延ダメージで受ける。遅延ダメージは最低1ダメージ。遅延ダメージはドットダメージ判定、HPが減るたび、逆境(状態ID"buff_itaminasi")を1/30獲得、効果時間は3秒、獲得するごとに時間は更新</t>
+    <rPh sb="30" eb="32">
+      <t>チエン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>サイテイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>チエン</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ギャッキョウ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="102" eb="106">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="108" eb="109">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受けるダメージの1/3を5分割にし、1秒ごとの遅延ダメージで受ける。遅延ダメージはドットダメージとしてみなされる。HPが減るたびに３秒間持続する"逆境"を１スタック獲得する。</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>チエン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>チエン</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ジゾク</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ギャッキョウ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>カクトク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>vine_punch</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>つるの打撃</t>
+    <rPh sb="3" eb="5">
+      <t>ダゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>100px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sleep_scent</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>甘い香り</t>
+    <rPh sb="0" eb="1">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>範囲デバフ</t>
+    <rPh sb="0" eb="2">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>20秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>範囲指定</t>
+    <rPh sb="0" eb="4">
+      <t>ハンイシテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自分中心</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自分中心</t>
+    <rPh sb="0" eb="4">
+      <t>ジブンチュウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>130px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シールド:8s</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>燃焼(debuff_burn):3s</t>
+    <rPh sb="0" eb="2">
+      <t>ネンショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>痛みなし(buff_itaminasi):2s</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>遅延5秒</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ウォームアップ(buff_warmup):8s</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:debuff_sleep)12s</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3秒間香りをただよらせ、触れた敵に(状態ID:debuff_sleep)を最大12秒付与</t>
+    <rPh sb="1" eb="3">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>pollen_spraying</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>花粉散布</t>
+    <rPh sb="0" eb="2">
+      <t>カフン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サンプ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力 * 0.1</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>25秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>140px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>花粉散布</t>
+    <rPh sb="0" eb="4">
+      <t>カフンサンプ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>指定した範囲内にいる敵に毎秒ダメージを与える
+最大5ヒット、このダメージはドットダメージ判定</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵スキルID(d_enemy_attack,vine_punch,sleep_scent,
+pollen_spraying)</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シャドウウルフ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シャドウウルフが同じ戦闘に複数体いる場合すべてのシャドウウルフのターゲットが同じ対象になる</t>
+    <rPh sb="8" eb="9">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>biting</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>範囲攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>15秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>負傷</t>
+    <rPh sb="0" eb="2">
+      <t>フショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ステータスデバフ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動速度-10%,防御力-10%</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動速度と防御力が低下する</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>リョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動速度と防御力が10%ずつ低下する</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Injury</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:Injury)4s</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:Injury)を4秒付与</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_dash</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>影走り</t>
+    <rPh sb="0" eb="2">
+      <t>カゲバシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象バフ</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自身</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>喉笛狩り</t>
+    <rPh sb="0" eb="2">
+      <t>ノドブエ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>throat_hunt</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.1 * (1 + (対象の減少HP割合)/ 3)</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ワリアイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ガード率</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(移動速度+50%,行動速度+30%)10s</t>
+    <rPh sb="1" eb="5">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自身の移動速度を50%、購読速度を30%上昇させる</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>コウドクソクド</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>喉笛狩り</t>
+    <rPh sb="0" eb="3">
+      <t>ノドブエガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵スキルID(d_enemy_attack,biting,shadow_dash,throat_hunt)</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.3 * (1 + (対象の減少HP割合) )</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ワリアイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ドット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ドット魔法</t>
+    <rPh sb="3" eb="5">
+      <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象した敵を味方AIが必ず対象を攻撃するようになる。調子70%以上、もしくは調子30%以下の時、70%で無視される。無視される判定はこのスキルの発動時に判定</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>チョウシ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>チョウシ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ムシ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ムシ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="72" eb="75">
+      <t>ハツドウジ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>指定した敵1体を味方達が狙うようになる。15秒経過するか対象が戦闘不能になるまで続く。調子70%以上、もしくは30%以下の時70%の確率で無視される。</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ミカタタチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ネラ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケイカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>セントウフノウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>チョウシ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ムシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルがあがるごとに無視される確率が(70/60/50/40/30/20)%にまで低下</t>
+    <rPh sb="10" eb="12">
+      <t>ムシ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>引継ぎ</t>
+    <rPh sb="0" eb="2">
+      <t>ヒキツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>なし</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -6500,7 +7216,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -6593,11 +7309,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD0D7CF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6692,6 +7417,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7054,22 +7782,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>662</v>
+        <v>619</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -7087,1833 +7815,1833 @@
         <v>7</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="V1" s="1" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="36">
       <c r="A2" s="3" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>663</v>
+        <v>620</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="J2" s="2">
         <v>15</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="R2" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="V2" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="W2" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="Y2" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="V2" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="X2" s="12" t="s">
-        <v>397</v>
-      </c>
-      <c r="Y2" s="12" t="s">
-        <v>385</v>
-      </c>
       <c r="Z2" s="12" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="36">
       <c r="A3" s="3" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>665</v>
+        <v>622</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J3" s="2">
         <v>20</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="N3" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="O3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="S3" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="Z3" s="12" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="36">
       <c r="A4" s="3" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>666</v>
+        <v>623</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J4" s="2">
         <v>25</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>365</v>
+        <v>227</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>246</v>
+        <v>722</v>
       </c>
       <c r="T4" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="V4" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="W4" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="X4" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y4" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="Z4" s="12" t="s">
         <v>368</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="V4" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="W4" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="X4" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="Y4" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="Z4" s="12" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="54">
       <c r="A5" s="3" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D5" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="V5" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="W5" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="X5" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="Y5" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z5" s="12" t="s">
         <v>369</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>664</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="V5" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="W5" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="X5" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="Y5" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="Z5" s="12" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="36">
       <c r="A6" s="3" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>667</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="Q6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="V6" s="12" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="W6" s="12" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="X6" s="12" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="Y6" s="12" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="Z6" s="12" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="54">
       <c r="A7" s="3" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>663</v>
+        <v>620</v>
       </c>
       <c r="G7" s="2">
         <v>18</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J7" s="2">
         <v>10</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="O7" s="3" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="X7" s="12" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="Y7" s="12" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="Z7" s="12" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="54">
       <c r="A8" s="3" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>667</v>
+        <v>624</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="V8" s="12" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="W8" s="12" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="Y8" s="12" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="Z8" s="12" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="36">
       <c r="A9" s="3" t="s">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>663</v>
+        <v>620</v>
       </c>
       <c r="G9" s="2">
         <v>20</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>460</v>
+        <v>428</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="V9" s="12" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="W9" s="12" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="X9" s="12" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="Y9" s="12" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="Z9" s="12" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="72">
       <c r="A10" s="3" t="s">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>545</v>
+        <v>508</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>663</v>
+        <v>620</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J10" s="2">
         <v>15</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="U10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="V10" s="12" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="W10" s="12" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="X10" s="12" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="Y10" s="12" t="s">
-        <v>409</v>
+        <v>383</v>
       </c>
       <c r="Z10" s="12" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="36">
       <c r="A11" s="3" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>668</v>
+        <v>625</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="V11" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="W11" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="V11" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="W11" s="12" t="s">
-        <v>310</v>
-      </c>
       <c r="X11" s="12" t="s">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="Y11" s="12" t="s">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="Z11" s="12" t="s">
-        <v>414</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="72">
       <c r="A12" s="3" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>669</v>
+        <v>626</v>
       </c>
       <c r="G12" s="2">
         <v>15</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J12" s="2">
         <v>20</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>460</v>
+        <v>428</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="3" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="V12" s="12" t="s">
-        <v>347</v>
+        <v>323</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="X12" s="12" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="Y12" s="12" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="Z12" s="12" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="54">
       <c r="A13" s="12" t="s">
-        <v>540</v>
+        <v>505</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>532</v>
+        <v>500</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>667</v>
+        <v>624</v>
       </c>
       <c r="G13">
         <v>30</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>533</v>
+        <v>641</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="J13">
         <v>40</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>534</v>
+        <v>501</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>535</v>
+        <v>264</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>536</v>
+        <v>227</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="S13" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="T13" s="13" t="s">
-        <v>370</v>
+        <v>261</v>
+      </c>
+      <c r="S13" s="12" t="s">
+        <v>723</v>
+      </c>
+      <c r="T13" s="12" t="s">
+        <v>500</v>
       </c>
       <c r="U13" s="12" t="s">
-        <v>537</v>
+        <v>502</v>
       </c>
       <c r="V13" s="16" t="s">
-        <v>538</v>
+        <v>503</v>
       </c>
       <c r="W13" s="12" t="s">
-        <v>539</v>
+        <v>504</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>437</v>
+        <v>408</v>
       </c>
       <c r="Y13" s="12" t="s">
-        <v>438</v>
+        <v>409</v>
       </c>
       <c r="Z13" s="12" t="s">
-        <v>439</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="143.4" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>663</v>
+        <v>620</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>451</v>
+        <v>422</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>53</v>
+        <v>240</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>719</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>452</v>
+        <v>423</v>
       </c>
       <c r="V14" s="12" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="W14" s="12" t="s">
-        <v>453</v>
+        <v>424</v>
       </c>
       <c r="X14" s="12" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="Y14" s="12" t="s">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="Z14" s="12" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="54">
       <c r="A15" s="3" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>548</v>
+        <v>511</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>670</v>
+        <v>627</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="P15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N15" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="Q15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>143</v>
+        <v>21</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>765</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="V15" s="12" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="W15" s="12" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="X15" s="12" t="s">
-        <v>454</v>
+        <v>425</v>
       </c>
       <c r="Y15" s="12" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="Z15" s="12" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="54">
       <c r="A16" s="3" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>548</v>
+        <v>511</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="P16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N16" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="Q16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>144</v>
+        <v>21</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>765</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="U16" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="V16" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="W16" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="X16" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="V16" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="W16" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="X16" s="12" t="s">
-        <v>455</v>
-      </c>
       <c r="Y16" s="12" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="Z16" s="12" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="54">
       <c r="A17" s="3" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>548</v>
+        <v>511</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>143</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>765</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="V17" s="12" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="W17" s="12" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="X17" s="12" t="s">
-        <v>456</v>
+        <v>425</v>
       </c>
       <c r="Y17" s="12" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="Z17" s="12" t="s">
-        <v>435</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="54">
       <c r="A18" s="3" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>548</v>
+        <v>511</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>144</v>
+        <v>21</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>765</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="V18" s="12" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="W18" s="12" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="X18" s="12" t="s">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="Y18" s="12" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="Z18" s="12" t="s">
-        <v>436</v>
+        <v>407</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="36">
       <c r="A19" s="3" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>446</v>
+        <v>417</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>160</v>
+        <v>141</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="V19" s="13" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="W19" s="12" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="X19" s="12"/>
     </row>
-    <row r="20" spans="1:26" ht="72">
+    <row r="20" spans="1:26" ht="90">
       <c r="A20" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="V20" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="V20" s="12" t="s">
-        <v>237</v>
-      </c>
       <c r="W20" s="12" t="s">
-        <v>324</v>
+        <v>708</v>
       </c>
       <c r="X20" s="12"/>
       <c r="Y20" s="16"/>
     </row>
     <row r="21" spans="1:26" ht="72">
       <c r="A21" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="V21" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="V21" s="12" t="s">
-        <v>238</v>
-      </c>
       <c r="W21" s="12" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="X21" s="12"/>
     </row>
     <row r="22" spans="1:26" ht="54">
       <c r="A22" s="3" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>377</v>
+        <v>351</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="T22" s="2"/>
       <c r="U22" s="3" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="W22" s="12" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="X22" s="12"/>
     </row>
-    <row r="23" spans="1:26" ht="36">
+    <row r="23" spans="1:26" ht="72">
       <c r="A23" s="12" t="s">
-        <v>547</v>
+        <v>510</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>548</v>
+        <v>511</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>549</v>
+        <v>512</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>550</v>
+        <v>513</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>551</v>
+        <v>514</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>552</v>
+        <v>515</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>551</v>
+        <v>514</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>553</v>
+        <v>516</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>554</v>
+        <v>517</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>551</v>
+        <v>514</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>555</v>
+        <v>518</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>556</v>
+        <v>530</v>
       </c>
       <c r="R23" s="12" t="s">
-        <v>551</v>
+        <v>514</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>551</v>
+        <v>514</v>
       </c>
       <c r="T23" s="13" t="s">
-        <v>550</v>
+        <v>513</v>
       </c>
       <c r="U23" s="12" t="s">
-        <v>557</v>
+        <v>767</v>
       </c>
       <c r="V23" s="12" t="s">
-        <v>558</v>
+        <v>519</v>
       </c>
       <c r="W23" s="12" t="s">
-        <v>559</v>
+        <v>768</v>
       </c>
       <c r="X23" s="12" t="s">
-        <v>658</v>
+        <v>769</v>
       </c>
       <c r="Y23" s="12" t="s">
-        <v>659</v>
+        <v>406</v>
       </c>
       <c r="Z23" s="12" t="s">
-        <v>660</v>
+        <v>407</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="72">
       <c r="A31" s="3" t="s">
-        <v>459</v>
+        <v>427</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>663</v>
+        <v>620</v>
       </c>
       <c r="G31" s="3">
         <v>32</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J31" s="2">
         <v>40</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="V31" s="12" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
       <c r="W31" s="12" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="X31" s="12" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="Y31" s="12" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="Z31" s="12" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -8955,312 +9683,321 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E325287-6FF5-4811-9C1B-B61C8E79C27E}">
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="15.8984375" customWidth="1"/>
-    <col min="4" max="4" width="9.3984375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="14.59765625" customWidth="1"/>
-    <col min="7" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="42" customWidth="1"/>
-    <col min="22" max="24" width="39" customWidth="1"/>
-    <col min="25" max="25" width="54.5" customWidth="1"/>
-    <col min="26" max="26" width="52" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14.59765625" customWidth="1"/>
+    <col min="6" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="42" customWidth="1"/>
+    <col min="21" max="23" width="39" customWidth="1"/>
+    <col min="24" max="24" width="54.5" customWidth="1"/>
+    <col min="25" max="25" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="24" customHeight="1">
+    <row r="1" spans="1:25" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>175</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="37" t="s">
-        <v>662</v>
+      <c r="E1" s="37" t="s">
+        <v>619</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>257</v>
+        <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>7</v>
+        <v>666</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="Q1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="U1" s="1" t="s">
-        <v>15</v>
+        <v>210</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>230</v>
+        <v>364</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>390</v>
+        <v>357</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:25">
       <c r="A2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="38"/>
+      <c r="F2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="38"/>
-      <c r="G2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="O2" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:25" ht="36">
+      <c r="A3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="C3" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U2" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>72</v>
       </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" ht="36">
-      <c r="A3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="4" spans="1:25">
+      <c r="A4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>82</v>
+      <c r="M4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>90</v>
+    <row r="5" spans="1:25" ht="18.600000000000001" customHeight="1">
+      <c r="A5" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>671</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>672</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>668</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>668</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>678</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+    <row r="6" spans="1:25">
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -9271,189 +10008,470 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="3"/>
+    <row r="7" spans="1:25">
+      <c r="A7" s="3" t="s">
+        <v>660</v>
+      </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="C7" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>679</v>
+      </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
+      <c r="I7" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>697</v>
+      </c>
       <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="1:26">
-      <c r="A8" s="3"/>
+    <row r="8" spans="1:25" ht="54">
+      <c r="A8" s="3" t="s">
+        <v>685</v>
+      </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="C8" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="F8" s="2">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>757</v>
+      </c>
       <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
+      <c r="I8" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>688</v>
+      </c>
     </row>
-    <row r="9" spans="1:26">
-      <c r="A9" s="3"/>
+    <row r="9" spans="1:25">
+      <c r="A9" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="C9" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="F9" s="2">
+        <v>13</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>663</v>
+      </c>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
+      <c r="I9" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>710</v>
+      </c>
       <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="1:26">
-      <c r="A10" s="3"/>
+    <row r="10" spans="1:25" ht="36">
+      <c r="A10" s="3" t="s">
+        <v>713</v>
+      </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="C10" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>668</v>
+      </c>
       <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
+      <c r="I10" s="2">
+        <v>20</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>728</v>
+      </c>
     </row>
-    <row r="11" spans="1:26">
-      <c r="A11" s="3"/>
+    <row r="11" spans="1:25" ht="36">
+      <c r="A11" s="3" t="s">
+        <v>729</v>
+      </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="C11" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>731</v>
+      </c>
       <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
+      <c r="I11" s="2">
+        <v>20</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>735</v>
+      </c>
     </row>
-    <row r="12" spans="1:26">
-      <c r="A12" s="3"/>
+    <row r="12" spans="1:25">
+      <c r="A12" s="3" t="s">
+        <v>740</v>
+      </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="C12" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="F12" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>672</v>
+      </c>
       <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
+      <c r="I12" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>750</v>
+      </c>
     </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="3"/>
+    <row r="13" spans="1:25" ht="36">
+      <c r="A13" s="3" t="s">
+        <v>751</v>
+      </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="C13" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>668</v>
+      </c>
       <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
+      <c r="I13" s="2">
+        <v>10</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>760</v>
+      </c>
     </row>
-    <row r="14" spans="1:26">
-      <c r="A14" s="3"/>
+    <row r="14" spans="1:25" ht="54">
+      <c r="A14" s="3" t="s">
+        <v>756</v>
+      </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="C14" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>763</v>
+      </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
+      <c r="I14" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>761</v>
+      </c>
       <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:23">
       <c r="A18" s="3"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="3"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="3"/>
+      <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -9466,15 +10484,14 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="2"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="2"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:23">
       <c r="A19" s="3"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="3"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="3"/>
+      <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -9487,15 +10504,14 @@
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="2"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="2"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:23">
       <c r="A20" s="3"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="3"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="3"/>
+      <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -9508,15 +10524,14 @@
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="2"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="2"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:23">
       <c r="A21" s="3"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="3"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="3"/>
+      <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -9529,15 +10544,14 @@
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="2"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="2"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:23">
       <c r="A22" s="3"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="2"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="2"/>
+      <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -9552,16 +10566,15 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="13"/>
+      <c r="U22" s="13"/>
+      <c r="V22" s="12"/>
       <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:23">
       <c r="A23" s="3"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="2"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="2"/>
+      <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -9575,17 +10588,16 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="12"/>
       <c r="V23" s="12"/>
       <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:23">
       <c r="A24" s="3"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="2"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="2"/>
+      <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -9599,17 +10611,16 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="12"/>
       <c r="V24" s="12"/>
       <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:23">
       <c r="A25" s="3"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="2"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="2"/>
+      <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -9623,8 +10634,7 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="3"/>
+      <c r="T25" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S25" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -9635,18 +10645,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14.296875" customWidth="1"/>
     <col min="2" max="2" width="15.296875" customWidth="1"/>
     <col min="3" max="3" width="17.3984375" customWidth="1"/>
-    <col min="4" max="4" width="79" customWidth="1"/>
-    <col min="5" max="5" width="62.59765625" customWidth="1"/>
-    <col min="6" max="6" width="97" customWidth="1"/>
+    <col min="4" max="4" width="10.59765625" customWidth="1"/>
+    <col min="5" max="5" width="79" customWidth="1"/>
+    <col min="6" max="6" width="62.59765625" customWidth="1"/>
+    <col min="7" max="7" width="97" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -9654,121 +10665,181 @@
         <v>2</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>227</v>
+        <v>87</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>770</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>230</v>
+        <v>210</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="37.200000000000003" customHeight="1">
+    <row r="2" spans="1:7" ht="37.200000000000003" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E2" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="36">
+      <c r="A3" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="54">
+      <c r="A4" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>325</v>
+      <c r="C5" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="36">
-      <c r="A3" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>326</v>
+    <row r="6" spans="1:7" ht="36">
+      <c r="A6" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>705</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>706</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="54">
-      <c r="A4" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>299</v>
+    <row r="7" spans="1:7" ht="36">
+      <c r="A7" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>702</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>704</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="36">
-      <c r="A6" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>541</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>747</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
@@ -9779,16 +10850,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AS10"/>
+  <dimension ref="A1:AS13"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="4" width="16" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="8.3984375" customWidth="1"/>
     <col min="5" max="24" width="14" customWidth="1"/>
     <col min="25" max="25" width="48" customWidth="1"/>
-    <col min="26" max="26" width="46.69921875" customWidth="1"/>
-    <col min="27" max="27" width="73.09765625" customWidth="1"/>
-    <col min="28" max="45" width="14" customWidth="1"/>
+    <col min="26" max="26" width="47.09765625" customWidth="1"/>
+    <col min="27" max="27" width="46.69921875" customWidth="1"/>
+    <col min="28" max="28" width="73.09765625" customWidth="1"/>
+    <col min="29" max="45" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45">
@@ -9799,94 +10872,95 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="U1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="Y1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="AA1" s="35" t="s">
-        <v>644</v>
+        <v>13</v>
+      </c>
+      <c r="Z1" s="35" t="s">
+        <v>659</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="AB1" s="35" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="2" spans="1:45">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>110</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="2">
         <v>490</v>
       </c>
@@ -9897,7 +10971,7 @@
         <v>90</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="I2" s="2">
         <v>95</v>
@@ -9906,55 +10980,55 @@
         <v>95</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="L2" s="15">
         <v>0.5</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>111</v>
+      <c r="M2" s="15">
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>673</v>
+        <v>655</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="AB2" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="Z2" s="8"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="3" t="s">
+        <v>605</v>
+      </c>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
@@ -9975,17 +11049,15 @@
     </row>
     <row r="3" spans="1:45" ht="54">
       <c r="A3" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>110</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2">
         <v>500</v>
       </c>
@@ -9996,10 +11068,10 @@
         <v>110</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="J3" s="2">
         <v>100</v>
@@ -10011,47 +11083,46 @@
         <v>0.5</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q3" s="15">
         <v>1</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>118</v>
+        <v>105</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>653</v>
       </c>
       <c r="U3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="X3" s="2" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="AB3" s="2"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="3" t="s">
+        <v>605</v>
+      </c>
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
@@ -10072,17 +11143,15 @@
     </row>
     <row r="4" spans="1:45" ht="54">
       <c r="A4" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>110</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2">
         <v>530</v>
       </c>
@@ -10090,7 +11159,7 @@
         <v>290</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="H4" s="2">
         <v>80</v>
@@ -10099,56 +11168,55 @@
         <v>100</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="L4" s="15">
         <v>0.5</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q4" s="15">
         <v>1</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>121</v>
+        <v>105</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>654</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="AB4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="3" t="s">
+        <v>605</v>
+      </c>
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
@@ -10169,83 +11237,80 @@
     </row>
     <row r="5" spans="1:45" ht="54">
       <c r="A5" s="2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>110</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="D5" s="2"/>
       <c r="E5" s="2">
         <v>480</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="H5" s="2">
         <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="L5" s="15">
         <v>0.5</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q5" s="15">
         <v>1</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>124</v>
+        <v>105</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>654</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="AB5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="3" t="s">
+        <v>605</v>
+      </c>
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
       <c r="AE5" s="2"/>
@@ -10266,85 +11331,84 @@
     </row>
     <row r="6" spans="1:45">
       <c r="A6" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>651</v>
       </c>
       <c r="E6" s="2">
         <v>300</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G6" s="2">
         <v>8</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L6" s="15">
         <v>0.5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q6" s="15">
         <v>1</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="AB6" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="3" t="s">
+        <v>617</v>
+      </c>
       <c r="AC6" s="2"/>
       <c r="AD6" s="2"/>
       <c r="AE6" s="2"/>
@@ -10365,85 +11429,84 @@
     </row>
     <row r="7" spans="1:45">
       <c r="A7" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>651</v>
       </c>
       <c r="E7" s="2">
         <v>250</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G7" s="2">
         <v>4</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L7" s="15">
         <v>0.5</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q7" s="15">
         <v>1</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="AB7" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="3" t="s">
+        <v>617</v>
+      </c>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
       <c r="AE7" s="2"/>
@@ -10464,85 +11527,84 @@
     </row>
     <row r="8" spans="1:45">
       <c r="A8" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>651</v>
       </c>
       <c r="E8" s="2">
         <v>180</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G8" s="2">
         <v>4</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L8" s="15">
         <v>0.5</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q8" s="15">
         <v>1</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="AB8" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="3" t="s">
+        <v>617</v>
+      </c>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
       <c r="AE8" s="2"/>
@@ -10563,85 +11625,84 @@
     </row>
     <row r="9" spans="1:45" ht="36">
       <c r="A9" s="2" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>110</v>
+        <v>126</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>651</v>
       </c>
       <c r="E9" s="2">
         <v>200</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G9" s="2">
         <v>6</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L9" s="15">
         <v>0.5</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q9" s="15">
         <v>1</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="AB9" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="3" t="s">
+        <v>617</v>
+      </c>
       <c r="AC9" s="2"/>
       <c r="AD9" s="2"/>
       <c r="AE9" s="2"/>
@@ -10662,85 +11723,84 @@
     </row>
     <row r="10" spans="1:45" ht="36">
       <c r="A10" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>651</v>
       </c>
       <c r="E10" s="2">
         <v>700</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G10" s="2">
         <v>10</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L10" s="15">
         <v>0.5</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q10" s="15">
         <v>1</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="AB10" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="3" t="s">
+        <v>617</v>
+      </c>
       <c r="AC10" s="2"/>
       <c r="AD10" s="2"/>
       <c r="AE10" s="2"/>
@@ -10758,6 +11818,244 @@
       <c r="AQ10" s="2"/>
       <c r="AR10" s="2"/>
       <c r="AS10" s="2"/>
+    </row>
+    <row r="11" spans="1:45">
+      <c r="A11" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>642</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="E11" s="13">
+        <v>400</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13">
+        <v>90</v>
+      </c>
+      <c r="H11" s="13">
+        <v>50</v>
+      </c>
+      <c r="I11" s="13">
+        <v>95</v>
+      </c>
+      <c r="J11" s="13">
+        <v>100</v>
+      </c>
+      <c r="K11" s="33">
+        <v>0</v>
+      </c>
+      <c r="L11" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="M11" s="33">
+        <v>0</v>
+      </c>
+      <c r="N11" s="33">
+        <v>0</v>
+      </c>
+      <c r="O11" s="33">
+        <v>0</v>
+      </c>
+      <c r="P11" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="33">
+        <v>1</v>
+      </c>
+      <c r="R11" s="33">
+        <v>0</v>
+      </c>
+      <c r="S11" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="T11" s="13" t="s">
+        <v>652</v>
+      </c>
+      <c r="U11" s="33">
+        <v>0</v>
+      </c>
+      <c r="V11" s="33">
+        <v>0</v>
+      </c>
+      <c r="W11" s="13" t="s">
+        <v>656</v>
+      </c>
+      <c r="X11" s="13" t="s">
+        <v>657</v>
+      </c>
+      <c r="Y11" s="13" t="s">
+        <v>658</v>
+      </c>
+      <c r="Z11" s="34" t="s">
+        <v>689</v>
+      </c>
+      <c r="AA11" s="34"/>
+    </row>
+    <row r="12" spans="1:45" ht="36">
+      <c r="A12" s="39" t="s">
+        <v>691</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>690</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="E12" s="13">
+        <v>370</v>
+      </c>
+      <c r="F12">
+        <v>80</v>
+      </c>
+      <c r="G12" s="13">
+        <v>75</v>
+      </c>
+      <c r="H12" s="13">
+        <v>110</v>
+      </c>
+      <c r="I12" s="13">
+        <v>100</v>
+      </c>
+      <c r="J12" s="13">
+        <v>90</v>
+      </c>
+      <c r="K12" s="33">
+        <v>0</v>
+      </c>
+      <c r="L12" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="33">
+        <v>0</v>
+      </c>
+      <c r="N12" s="33">
+        <v>0</v>
+      </c>
+      <c r="O12" s="33">
+        <v>0</v>
+      </c>
+      <c r="P12" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="33">
+        <v>1</v>
+      </c>
+      <c r="R12" s="33">
+        <v>0</v>
+      </c>
+      <c r="S12" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="T12" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="U12" s="33">
+        <v>0</v>
+      </c>
+      <c r="V12" s="33">
+        <v>0</v>
+      </c>
+      <c r="W12" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="X12" s="13" t="s">
+        <v>682</v>
+      </c>
+      <c r="Z12" s="11" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="13" spans="1:45" ht="36">
+      <c r="A13" s="39" t="s">
+        <v>738</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>737</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="E13" s="13">
+        <v>480</v>
+      </c>
+      <c r="F13">
+        <v>20</v>
+      </c>
+      <c r="G13" s="13">
+        <v>110</v>
+      </c>
+      <c r="H13" s="13">
+        <v>10</v>
+      </c>
+      <c r="I13" s="13">
+        <v>105</v>
+      </c>
+      <c r="J13" s="13">
+        <v>95</v>
+      </c>
+      <c r="K13" s="33">
+        <v>0</v>
+      </c>
+      <c r="L13" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="M13" s="33">
+        <v>0</v>
+      </c>
+      <c r="N13" s="33">
+        <v>0</v>
+      </c>
+      <c r="O13" s="33">
+        <v>0</v>
+      </c>
+      <c r="P13" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="33">
+        <v>1</v>
+      </c>
+      <c r="R13" s="33">
+        <v>0</v>
+      </c>
+      <c r="S13" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="T13" s="12" t="s">
+        <v>712</v>
+      </c>
+      <c r="U13" s="33">
+        <v>0</v>
+      </c>
+      <c r="V13" s="33">
+        <v>0</v>
+      </c>
+      <c r="W13" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="X13" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="Y13" s="16" t="s">
+        <v>739</v>
+      </c>
+      <c r="Z13" s="34" t="s">
+        <v>762</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Z10" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
@@ -10796,144 +12094,144 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>475</v>
+        <v>443</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>478</v>
+        <v>446</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>639</v>
+        <v>599</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="O1" s="19" t="s">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="R1" s="18"/>
     </row>
     <row r="2" spans="1:18" ht="36">
       <c r="A2" s="4" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>476</v>
+        <v>444</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>612</v>
+        <v>572</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>636</v>
+        <v>596</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>661</v>
+        <v>618</v>
       </c>
       <c r="R2" s="4"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>476</v>
+        <v>444</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>607</v>
+        <v>567</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
@@ -10942,44 +12240,44 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="4" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>477</v>
+        <v>445</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
@@ -10988,44 +12286,44 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>477</v>
+        <v>445</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
@@ -11034,271 +12332,271 @@
     </row>
     <row r="7" spans="1:18" ht="36">
       <c r="A7" s="4" t="s">
-        <v>574</v>
+        <v>534</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>581</v>
+        <v>541</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>589</v>
+        <v>549</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>604</v>
+        <v>564</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>605</v>
+        <v>565</v>
       </c>
       <c r="H7" s="33">
         <v>0.1</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="36">
       <c r="A8" s="4" t="s">
-        <v>575</v>
+        <v>535</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>582</v>
+        <v>542</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>590</v>
+        <v>550</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>604</v>
+        <v>564</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>605</v>
+        <v>565</v>
       </c>
       <c r="H8" s="33">
         <v>0.1</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="36">
       <c r="A9" s="4" t="s">
-        <v>576</v>
+        <v>536</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>583</v>
+        <v>543</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>604</v>
+        <v>564</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>605</v>
+        <v>565</v>
       </c>
       <c r="H9" s="33">
         <v>0.1</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>608</v>
+        <v>568</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="36">
       <c r="A10" s="4" t="s">
-        <v>577</v>
+        <v>537</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>584</v>
+        <v>544</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>632</v>
-      </c>
       <c r="F10" s="4" t="s">
-        <v>604</v>
+        <v>564</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>605</v>
+        <v>565</v>
       </c>
       <c r="H10" s="33">
         <v>0.1</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>608</v>
+        <v>568</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="36">
       <c r="A11" s="4" t="s">
-        <v>578</v>
+        <v>538</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>585</v>
+        <v>545</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>593</v>
+        <v>553</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>604</v>
+        <v>564</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>606</v>
+        <v>566</v>
       </c>
       <c r="H11" s="33">
         <v>0.1</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>609</v>
+        <v>569</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="36">
       <c r="A12" s="4" t="s">
-        <v>579</v>
+        <v>539</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>586</v>
+        <v>546</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>594</v>
+        <v>554</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>604</v>
+        <v>564</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>606</v>
+        <v>566</v>
       </c>
       <c r="H12" s="33">
         <v>0.1</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>610</v>
+        <v>570</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="36">
       <c r="A13" s="4" t="s">
-        <v>580</v>
+        <v>540</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>587</v>
+        <v>547</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>595</v>
+        <v>555</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>604</v>
+        <v>564</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>606</v>
+        <v>566</v>
       </c>
       <c r="H13" s="33">
         <v>0.1</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>610</v>
+        <v>570</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -11337,43 +12635,43 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>619</v>
+        <v>579</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>475</v>
+        <v>443</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>639</v>
+        <v>599</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -11381,239 +12679,239 @@
     </row>
     <row r="2" spans="1:18" ht="54">
       <c r="A2" s="4" t="s">
-        <v>613</v>
+        <v>573</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>620</v>
+        <v>580</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>626</v>
+        <v>586</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>633</v>
+        <v>593</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>680</v>
+        <v>636</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>635</v>
+        <v>595</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>637</v>
+        <v>597</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>638</v>
+        <v>598</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="36">
       <c r="A3" s="4" t="s">
-        <v>614</v>
+        <v>574</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>621</v>
+        <v>581</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>628</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>633</v>
+        <v>593</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>681</v>
+        <v>637</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="36">
       <c r="A4" s="4" t="s">
-        <v>615</v>
+        <v>575</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>622</v>
+        <v>582</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>627</v>
+        <v>587</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>633</v>
+        <v>593</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>682</v>
+        <v>638</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="36">
       <c r="A5" s="4" t="s">
-        <v>616</v>
+        <v>576</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>623</v>
+        <v>583</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>629</v>
+        <v>589</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>633</v>
+        <v>593</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>683</v>
+        <v>639</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="36">
       <c r="A6" s="4" t="s">
-        <v>617</v>
+        <v>577</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>624</v>
+        <v>584</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>633</v>
+        <v>593</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>684</v>
+        <v>640</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="36">
       <c r="A7" s="4" t="s">
-        <v>618</v>
+        <v>578</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>625</v>
+        <v>585</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>631</v>
+        <v>591</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>633</v>
+        <v>593</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>674</v>
+        <v>630</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
     </row>
   </sheetData>
@@ -11645,54 +12943,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>466</v>
+        <v>434</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>467</v>
+        <v>435</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>468</v>
+        <v>436</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>641</v>
+        <v>601</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>640</v>
+        <v>600</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>642</v>
+        <v>602</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>643</v>
+        <v>603</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>676</v>
-      </c>
       <c r="F2" s="4" t="s">
-        <v>677</v>
+        <v>633</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>675</v>
+        <v>631</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>679</v>
+        <v>635</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>678</v>
+        <v>634</v>
       </c>
     </row>
   </sheetData>
@@ -11731,78 +13029,78 @@
         <v>2</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>462</v>
+        <v>430</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>469</v>
+        <v>437</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>471</v>
+        <v>439</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>560</v>
+        <v>520</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>561</v>
+        <v>521</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>571</v>
+        <v>531</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>472</v>
+        <v>440</v>
       </c>
       <c r="L1" s="31" t="s">
-        <v>564</v>
+        <v>524</v>
       </c>
       <c r="M1" s="17" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="N1" s="17" t="s">
-        <v>474</v>
+        <v>442</v>
       </c>
       <c r="O1" s="32" t="s">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="P1" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q1" s="17" t="s">
-        <v>464</v>
+        <v>432</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>465</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="4" t="s">
-        <v>562</v>
+        <v>522</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>563</v>
+        <v>523</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>565</v>
+        <v>525</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>566</v>
+        <v>526</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>567</v>
+        <v>527</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>568</v>
+        <v>528</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>569</v>
+        <v>529</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>570</v>
+        <v>530</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -11815,71 +13113,71 @@
       </c>
       <c r="O2" s="4"/>
       <c r="Q2" s="4" t="s">
-        <v>572</v>
+        <v>532</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>573</v>
+        <v>533</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>597</v>
+        <v>557</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>598</v>
+        <v>558</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>599</v>
+        <v>559</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>647</v>
+        <v>607</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>601</v>
+        <v>561</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>602</v>
+        <v>562</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>603</v>
+        <v>563</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>603</v>
+        <v>563</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="72">
       <c r="A4" s="4" t="s">
-        <v>648</v>
+        <v>608</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>649</v>
+        <v>609</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>650</v>
+        <v>610</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>652</v>
+        <v>612</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>653</v>
+        <v>613</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>654</v>
+        <v>614</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>655</v>
+        <v>615</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>656</v>
+        <v>616</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>656</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -11904,51 +13202,51 @@
   <sheetData>
     <row r="2" spans="2:13">
       <c r="B2" s="23" t="s">
-        <v>481</v>
+        <v>449</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>531</v>
+        <v>499</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="M2" s="23" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="23" t="s">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>521</v>
+        <v>489</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>526</v>
+        <v>494</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>496</v>
+        <v>464</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>514</v>
+        <v>482</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="M3" s="24">
         <v>1</v>
@@ -11956,25 +13254,25 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="23" t="s">
-        <v>487</v>
+        <v>455</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>489</v>
+        <v>457</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>522</v>
+        <v>490</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>527</v>
+        <v>495</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>497</v>
+        <v>465</v>
       </c>
       <c r="J4" s="28" t="s">
-        <v>515</v>
+        <v>483</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>489</v>
+        <v>457</v>
       </c>
       <c r="M4" s="24">
         <v>2</v>
@@ -11982,25 +13280,25 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="23" t="s">
+        <v>450</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>491</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>496</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="J5" s="28" t="s">
         <v>482</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>490</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>523</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>528</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>498</v>
-      </c>
-      <c r="J5" s="28" t="s">
-        <v>514</v>
-      </c>
       <c r="L5" s="23" t="s">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="M5" s="24">
         <v>3</v>
@@ -12008,25 +13306,25 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="23" t="s">
+        <v>451</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>492</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>497</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="J6" s="28" t="s">
         <v>483</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>491</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>524</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>529</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>499</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>515</v>
-      </c>
       <c r="L6" s="23" t="s">
-        <v>491</v>
+        <v>459</v>
       </c>
       <c r="M6" s="24">
         <v>4</v>
@@ -12034,25 +13332,25 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>460</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>493</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>498</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>476</v>
+      </c>
+      <c r="J7" s="28" t="s">
         <v>484</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>492</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>525</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>530</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>508</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>516</v>
-      </c>
       <c r="L7" s="23" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="M7" s="24">
         <v>5</v>
@@ -12060,104 +13358,104 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="23" t="s">
-        <v>485</v>
+        <v>453</v>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
       <c r="F8" s="26"/>
       <c r="I8" s="23" t="s">
-        <v>509</v>
+        <v>477</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>517</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" spans="2:13">
       <c r="I9" s="23" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="J9" s="28" t="s">
-        <v>514</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10" spans="2:13">
       <c r="I10" s="23" t="s">
-        <v>511</v>
+        <v>479</v>
       </c>
       <c r="J10" s="28" t="s">
-        <v>518</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" spans="2:13">
       <c r="I11" s="23" t="s">
-        <v>512</v>
+        <v>480</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>514</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" spans="2:13">
       <c r="I12" s="23" t="s">
-        <v>513</v>
+        <v>481</v>
       </c>
       <c r="J12" s="28" t="s">
-        <v>518</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="I13" s="23" t="s">
-        <v>505</v>
+        <v>473</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>519</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="2:13">
       <c r="I14" s="23" t="s">
-        <v>506</v>
+        <v>474</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>520</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="I15" s="23" t="s">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>514</v>
+        <v>482</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="I16" s="23" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>518</v>
+        <v>486</v>
       </c>
     </row>
     <row r="17" spans="9:10">
       <c r="I17" s="23" t="s">
-        <v>503</v>
+        <v>471</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>516</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="9:10">
       <c r="I18" s="23" t="s">
-        <v>504</v>
+        <v>472</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>514</v>
+        <v>482</v>
       </c>
     </row>
     <row r="19" spans="9:10">
       <c r="I19" s="23" t="s">
-        <v>507</v>
+        <v>475</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>514</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC0DDD4-C80F-4DA1-B740-B97D9037624F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9B9195-B6E0-406B-9131-B85495871651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="998">
   <si>
     <t>ID</t>
   </si>
@@ -4213,12 +4213,6 @@
   </si>
   <si>
     <t>セット名</t>
-  </si>
-  <si>
-    <t>2セット効果</t>
-  </si>
-  <si>
-    <t>5セット効果</t>
   </si>
   <si>
     <t>種類</t>
@@ -5694,16 +5688,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>防御が10%上昇する</t>
-    <rPh sb="0" eb="2">
-      <t>ボウギョ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>HPが上昇する</t>
     <rPh sb="3" eb="5">
       <t>ジョウショウ</t>
@@ -7406,16 +7390,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>魔防が25上昇する</t>
-    <rPh sb="0" eb="2">
-      <t>マボウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>2セット効果名</t>
     <rPh sb="4" eb="7">
       <t>コウカメイ</t>
@@ -8944,6 +8918,76 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラヘルム</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラアーマー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラレギンス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラブーツ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラグローブ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラペンダント</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_Alraune_helm</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_Alraune_armor</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_Alraune_leggings</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_Alraune_boots</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_Alraune_glove</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_Alraune_pendant</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_Alraune</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>つぼみのアルラウネ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ツタの棘</t>
+    <rPh sb="3" eb="4">
+      <t>トゲ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>つぼみの中</t>
+    <rPh sb="4" eb="5">
+      <t>ナカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -9611,7 +9655,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>223</v>
@@ -9635,10 +9679,10 @@
         <v>259</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>9</v>
@@ -9689,7 +9733,7 @@
         <v>314</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>16</v>
@@ -9713,10 +9757,10 @@
         <v>315</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>294</v>
@@ -9769,7 +9813,7 @@
         <v>319</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>21</v>
@@ -9793,7 +9837,7 @@
         <v>25</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>26</v>
@@ -9849,7 +9893,7 @@
         <v>324</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>29</v>
@@ -9873,7 +9917,7 @@
         <v>320</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>215</v>
@@ -9888,7 +9932,7 @@
         <v>32</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="T4" s="3" t="s">
         <v>324</v>
@@ -9929,7 +9973,7 @@
         <v>325</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>224</v>
@@ -10007,7 +10051,7 @@
         <v>256</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>40</v>
@@ -10031,10 +10075,10 @@
         <v>25</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>41</v>
@@ -10075,7 +10119,7 @@
         <v>181</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>15</v>
@@ -10087,7 +10131,7 @@
         <v>257</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G7" s="2">
         <v>18</v>
@@ -10111,10 +10155,10 @@
         <v>260</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>294</v>
@@ -10155,7 +10199,7 @@
         <v>182</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>33</v>
@@ -10167,7 +10211,7 @@
         <v>233</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>46</v>
@@ -10245,7 +10289,7 @@
         <v>240</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G9" s="2">
         <v>20</v>
@@ -10310,7 +10354,7 @@
     </row>
     <row r="10" spans="1:26" ht="72">
       <c r="A10" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>166</v>
@@ -10322,10 +10366,10 @@
         <v>210</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>253</v>
@@ -10349,7 +10393,7 @@
         <v>249</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>250</v>
@@ -10405,7 +10449,7 @@
         <v>254</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
@@ -10429,16 +10473,16 @@
         <v>48</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>276</v>
@@ -10483,7 +10527,7 @@
         <v>274</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G12" s="2">
         <v>15</v>
@@ -10510,7 +10554,7 @@
         <v>218</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>234</v>
@@ -10532,7 +10576,7 @@
         <v>304</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="X12" s="12" t="s">
         <v>369</v>
@@ -10546,7 +10590,7 @@
     </row>
     <row r="13" spans="1:26" ht="54">
       <c r="A13" s="12" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>165</v>
@@ -10558,16 +10602,16 @@
         <v>167</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G13">
         <v>30</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>215</v>
@@ -10576,7 +10620,7 @@
         <v>40</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L13" s="12" t="s">
         <v>248</v>
@@ -10600,19 +10644,19 @@
         <v>245</v>
       </c>
       <c r="S13" s="12" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="T13" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="U13" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="U13" s="12" t="s">
+      <c r="V13" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="W13" s="12" t="s">
         <v>482</v>
-      </c>
-      <c r="V13" s="16" t="s">
-        <v>483</v>
-      </c>
-      <c r="W13" s="12" t="s">
-        <v>484</v>
       </c>
       <c r="X13" s="12" t="s">
         <v>388</v>
@@ -10629,7 +10673,7 @@
         <v>183</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>33</v>
@@ -10641,7 +10685,7 @@
         <v>55</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>40</v>
@@ -10662,13 +10706,13 @@
         <v>225</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>234</v>
@@ -10712,7 +10756,7 @@
         <v>393</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>210</v>
@@ -10721,7 +10765,7 @@
         <v>131</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -10757,7 +10801,7 @@
         <v>20</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>128</v>
@@ -10792,7 +10836,7 @@
         <v>393</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>210</v>
@@ -10801,7 +10845,7 @@
         <v>132</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -10837,7 +10881,7 @@
         <v>20</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>129</v>
@@ -10872,7 +10916,7 @@
         <v>393</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>210</v>
@@ -10881,7 +10925,7 @@
         <v>133</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -10908,7 +10952,7 @@
         <v>215</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>27</v>
@@ -10917,7 +10961,7 @@
         <v>20</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>128</v>
@@ -10952,7 +10996,7 @@
         <v>393</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>210</v>
@@ -10961,7 +11005,7 @@
         <v>134</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -10988,7 +11032,7 @@
         <v>215</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>27</v>
@@ -10997,7 +11041,7 @@
         <v>20</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="S18" s="2" t="s">
         <v>129</v>
@@ -11140,25 +11184,25 @@
         <v>137</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="V20" s="12" t="s">
         <v>208</v>
       </c>
       <c r="W20" s="12" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="X20" s="12"/>
       <c r="Y20" s="16"/>
@@ -11210,13 +11254,13 @@
         <v>137</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>142</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>20</v>
@@ -11301,70 +11345,70 @@
     </row>
     <row r="23" spans="1:26" ht="72">
       <c r="A23" s="12" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>393</v>
       </c>
       <c r="C23" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>491</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="F23" s="13" t="s">
+        <v>603</v>
+      </c>
+      <c r="G23" s="13" t="s">
         <v>492</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>605</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>494</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="O23" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="P23" s="12" t="s">
         <v>495</v>
       </c>
-      <c r="L23" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="M23" s="13" t="s">
+      <c r="Q23" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="R23" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="S23" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="T23" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="U23" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="V23" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="N23" s="4" t="s">
-        <v>894</v>
-      </c>
-      <c r="O23" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="P23" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="Q23" s="12" t="s">
-        <v>508</v>
-      </c>
-      <c r="R23" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="S23" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="T23" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="U23" s="12" t="s">
-        <v>737</v>
-      </c>
-      <c r="V23" s="12" t="s">
-        <v>498</v>
-      </c>
       <c r="W23" s="12" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="X23" s="12" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="Y23" s="12" t="s">
         <v>386</v>
@@ -11375,279 +11419,279 @@
     </row>
     <row r="24" spans="1:26" ht="36">
       <c r="A24" s="12" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="G24">
         <v>13</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="K24" s="13" t="s">
         <v>408</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="O24" s="13" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="R24" s="12" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="T24" s="13" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="V24" s="12" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="W24" s="12" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="X24" s="12" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="Y24" s="12" t="s">
         <v>339</v>
       </c>
       <c r="Z24" s="12" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="36">
       <c r="A25" s="12" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="G25">
         <v>10</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="K25" s="13" t="s">
         <v>408</v>
       </c>
       <c r="L25" s="16" t="s">
+        <v>837</v>
+      </c>
+      <c r="M25" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="N25" s="13" t="s">
         <v>841</v>
       </c>
-      <c r="M25" s="12" t="s">
-        <v>842</v>
-      </c>
-      <c r="N25" s="13" t="s">
-        <v>845</v>
-      </c>
       <c r="O25" s="13" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="R25" s="12" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="T25" s="12" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="V25" s="12" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="W25" s="12" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="X25" s="12" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="Y25" s="12" t="s">
         <v>339</v>
       </c>
       <c r="Z25" s="12" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="36">
       <c r="A26" s="12" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="G26">
         <v>14</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="K26" s="13" t="s">
         <v>408</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="O26" s="13" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="R26" s="12" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="T26" s="12" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="V26" s="12" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="W26" s="12" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="X26" s="12" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="Y26" s="12" t="s">
         <v>339</v>
       </c>
       <c r="Z26" s="12" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="36">
       <c r="A27" s="12" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D27" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>826</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>830</v>
-      </c>
       <c r="F27" s="12" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="G27">
         <v>8</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="K27" s="13" t="s">
         <v>408</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="O27" s="13" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="R27" s="12" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="T27" s="12" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="V27" s="12" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="W27" s="12" t="s">
+        <v>872</v>
+      </c>
+      <c r="X27" s="12" t="s">
         <v>876</v>
-      </c>
-      <c r="X27" s="12" t="s">
-        <v>880</v>
       </c>
       <c r="Y27" s="12" t="s">
         <v>339</v>
       </c>
       <c r="Z27" s="12" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="72">
       <c r="A28" s="12" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="G28">
         <v>10</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="J28">
         <v>25</v>
@@ -11656,69 +11700,69 @@
         <v>408</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="O28" s="13" t="s">
+        <v>846</v>
+      </c>
+      <c r="P28" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="Q28" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="R28" s="12" t="s">
         <v>850</v>
       </c>
-      <c r="P28" s="12" t="s">
-        <v>852</v>
-      </c>
-      <c r="Q28" s="12" t="s">
-        <v>835</v>
-      </c>
-      <c r="R28" s="12" t="s">
-        <v>854</v>
-      </c>
       <c r="T28" s="12" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="V28" s="12" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="W28" s="12" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="X28" s="12" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="Y28" s="12" t="s">
         <v>339</v>
       </c>
       <c r="Z28" s="12" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="36">
       <c r="A29" s="12" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G29">
         <v>10</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="J29">
         <v>20</v>
@@ -11727,63 +11771,63 @@
         <v>408</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="R29" s="12" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="T29" s="12" t="s">
         <v>314</v>
       </c>
       <c r="V29" s="12" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="W29" s="12" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="X29" s="12" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="Y29" s="12" t="s">
         <v>339</v>
       </c>
       <c r="Z29" s="12" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="36">
       <c r="A30" s="12" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="H30" s="16" t="s">
         <v>215</v>
@@ -11795,43 +11839,43 @@
         <v>408</v>
       </c>
       <c r="L30" s="34" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="P30" s="12" t="s">
         <v>294</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="R30" s="12" t="s">
         <v>215</v>
       </c>
       <c r="T30" s="12" t="s">
+        <v>974</v>
+      </c>
+      <c r="V30" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="W30" s="12" t="s">
+        <v>975</v>
+      </c>
+      <c r="X30" s="12" t="s">
+        <v>977</v>
+      </c>
+      <c r="Y30" s="12" t="s">
         <v>978</v>
       </c>
-      <c r="V30" s="12" t="s">
-        <v>980</v>
-      </c>
-      <c r="W30" s="12" t="s">
+      <c r="Z30" s="12" t="s">
         <v>979</v>
-      </c>
-      <c r="X30" s="12" t="s">
-        <v>981</v>
-      </c>
-      <c r="Y30" s="12" t="s">
-        <v>982</v>
-      </c>
-      <c r="Z30" s="12" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -11870,7 +11914,7 @@
         <v>406</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G49" s="3">
         <v>32</v>
@@ -11982,7 +12026,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>223</v>
@@ -12003,10 +12047,10 @@
         <v>7</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
@@ -12021,7 +12065,7 @@
         <v>244</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>12</v>
@@ -12084,7 +12128,7 @@
         <v>62</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>20</v>
@@ -12140,7 +12184,7 @@
         <v>72</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>20</v>
@@ -12196,7 +12240,7 @@
         <v>80</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>20</v>
@@ -12216,55 +12260,55 @@
     </row>
     <row r="5" spans="1:25" ht="18.600000000000001" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="F5">
         <v>10</v>
       </c>
       <c r="G5" s="13" t="s">
+        <v>644</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>640</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>640</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="I5" s="13" t="s">
-        <v>643</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>643</v>
-      </c>
-      <c r="L5" s="3" t="s">
+      <c r="N5" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="R5" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="T5" s="3" t="s">
         <v>650</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -12281,457 +12325,457 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="3" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F7" s="2">
         <v>10</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="L7" s="3" t="s">
+      <c r="N7" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q7" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="M7" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="R7" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="T7" s="2"/>
     </row>
     <row r="8" spans="1:25" ht="54">
       <c r="A8" s="3" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="F8" s="2">
         <v>8</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="L8" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q8" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="R8" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="3" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F9" s="2">
         <v>13</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="L9" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q9" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="R9" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="T9" s="2"/>
     </row>
     <row r="10" spans="1:25" ht="72">
       <c r="A10" s="3" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2">
         <v>20</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="K10" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>695</v>
-      </c>
       <c r="M10" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="36">
       <c r="A11" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F11" s="2">
         <v>5</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2">
         <v>20</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="3" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F12" s="2">
         <v>15</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="L12" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q12" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="R12" s="3" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="36">
       <c r="A13" s="3" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="T13" s="3"/>
     </row>
     <row r="14" spans="1:25" ht="54">
       <c r="A14" s="3" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F14" s="2">
         <v>10</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="L14" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="R14" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="T14" s="2"/>
     </row>
@@ -12936,7 +12980,7 @@
         <v>82</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>198</v>
@@ -13054,59 +13098,59 @@
         <v>191</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="36">
       <c r="A7" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="G7" s="11" t="s">
         <v>676</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>677</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>714</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>716</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>717</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>719</v>
       </c>
     </row>
   </sheetData>
@@ -13143,7 +13187,7 @@
         <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>83</v>
@@ -13179,13 +13223,13 @@
         <v>92</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>93</v>
@@ -13209,13 +13253,13 @@
         <v>13</v>
       </c>
       <c r="Z1" s="35" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>398</v>
       </c>
       <c r="AB1" s="35" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="2" spans="1:45">
@@ -13226,7 +13270,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2">
@@ -13275,7 +13319,7 @@
         <v>100</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>99</v>
@@ -13295,7 +13339,7 @@
       <c r="Z2" s="8"/>
       <c r="AA2" s="2"/>
       <c r="AB2" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
@@ -13323,7 +13367,7 @@
         <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2">
@@ -13372,7 +13416,7 @@
         <v>100</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>99</v>
@@ -13389,7 +13433,7 @@
       <c r="Y3" s="2"/>
       <c r="AA3" s="2"/>
       <c r="AB3" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
@@ -13417,7 +13461,7 @@
         <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2">
@@ -13466,7 +13510,7 @@
         <v>100</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>99</v>
@@ -13483,7 +13527,7 @@
       <c r="Y4" s="2"/>
       <c r="AA4" s="2"/>
       <c r="AB4" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
@@ -13511,7 +13555,7 @@
         <v>53</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2">
@@ -13560,7 +13604,7 @@
         <v>100</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="U5" s="2" t="s">
         <v>99</v>
@@ -13577,7 +13621,7 @@
       <c r="Y5" s="2"/>
       <c r="AA5" s="2"/>
       <c r="AB5" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
@@ -13605,10 +13649,10 @@
         <v>111</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E6" s="2">
         <v>300</v>
@@ -13675,7 +13719,7 @@
       </c>
       <c r="AA6" s="2"/>
       <c r="AB6" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AC6" s="2"/>
       <c r="AD6" s="2"/>
@@ -13703,10 +13747,10 @@
         <v>111</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E7" s="2">
         <v>250</v>
@@ -13773,7 +13817,7 @@
       </c>
       <c r="AA7" s="2"/>
       <c r="AB7" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
@@ -13801,10 +13845,10 @@
         <v>118</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E8" s="2">
         <v>180</v>
@@ -13871,7 +13915,7 @@
       </c>
       <c r="AA8" s="2"/>
       <c r="AB8" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -13899,10 +13943,10 @@
         <v>121</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>624</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>627</v>
       </c>
       <c r="E9" s="2">
         <v>200</v>
@@ -13969,7 +14013,7 @@
       </c>
       <c r="AA9" s="2"/>
       <c r="AB9" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" s="2"/>
@@ -13997,10 +14041,10 @@
         <v>124</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E10" s="2">
         <v>700</v>
@@ -14067,7 +14111,7 @@
       </c>
       <c r="AA10" s="2"/>
       <c r="AB10" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AC10" s="2"/>
       <c r="AD10" s="2"/>
@@ -14089,16 +14133,16 @@
     </row>
     <row r="11" spans="1:45" ht="54">
       <c r="A11" s="12" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E11" s="13">
         <v>400</v>
@@ -14146,7 +14190,7 @@
         <v>0.5</v>
       </c>
       <c r="T11" s="12" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="U11" s="33">
         <v>0</v>
@@ -14155,36 +14199,36 @@
         <v>0</v>
       </c>
       <c r="W11" s="13" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="X11" s="13" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="Y11" s="12" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="Z11" s="34" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="AA11" s="34" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="AB11" s="12" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="36">
       <c r="A12" s="40" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E12" s="13">
         <v>370</v>
@@ -14232,7 +14276,7 @@
         <v>0.5</v>
       </c>
       <c r="T12" s="12" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="U12" s="33">
         <v>0</v>
@@ -14241,33 +14285,33 @@
         <v>0</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="X12" s="13" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="Z12" s="11" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="AA12" s="4" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="AB12" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="108">
       <c r="A13" s="39" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E13" s="13">
         <v>480</v>
@@ -14315,7 +14359,7 @@
         <v>0.5</v>
       </c>
       <c r="T13" s="12" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="U13" s="33">
         <v>0</v>
@@ -14324,22 +14368,22 @@
         <v>0</v>
       </c>
       <c r="W13" s="12" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="Y13" s="16" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="Z13" s="34" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="AA13" s="34" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="AB13" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
     </row>
   </sheetData>
@@ -14385,7 +14429,7 @@
         <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>160</v>
@@ -14394,13 +14438,13 @@
         <v>161</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>162</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>163</v>
@@ -14418,10 +14462,10 @@
         <v>411</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="R1" s="18"/>
     </row>
@@ -14436,14 +14480,14 @@
         <v>167</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>191</v>
@@ -14452,7 +14496,7 @@
         <v>180</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>191</v>
@@ -14467,13 +14511,13 @@
         <v>191</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="R2" s="4"/>
     </row>
@@ -14495,16 +14539,16 @@
         <v>196</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>191</v>
@@ -14528,7 +14572,7 @@
         <v>175</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>167</v>
@@ -14541,7 +14585,7 @@
         <v>196</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>191</v>
@@ -14550,7 +14594,7 @@
         <v>391</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>191</v>
@@ -14574,7 +14618,7 @@
         <v>176</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>167</v>
@@ -14587,7 +14631,7 @@
         <v>196</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>191</v>
@@ -14596,7 +14640,7 @@
         <v>177</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>191</v>
@@ -14617,25 +14661,25 @@
     </row>
     <row r="7" spans="1:18" ht="36">
       <c r="A7" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H7" s="33">
         <v>0.1</v>
@@ -14644,39 +14688,39 @@
         <v>180</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="36">
       <c r="A8" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>526</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>528</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H8" s="33">
         <v>0.1</v>
@@ -14685,406 +14729,406 @@
         <v>392</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="36">
       <c r="A9" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H9" s="33">
         <v>0.1</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="36">
       <c r="A10" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H10" s="33">
         <v>0.1</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="36">
       <c r="A11" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>542</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>544</v>
       </c>
       <c r="H11" s="33">
         <v>0.1</v>
       </c>
       <c r="I11" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="L11" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="J11" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>549</v>
-      </c>
       <c r="M11" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="36">
       <c r="A12" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>526</v>
-      </c>
       <c r="D12" s="7" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F12" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>542</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>544</v>
       </c>
       <c r="H12" s="33">
         <v>0.1</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="36">
       <c r="A13" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>542</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>544</v>
       </c>
       <c r="H13" s="33">
         <v>0.1</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A14" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>918</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>808</v>
-      </c>
       <c r="D14" s="7" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="E14" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="73.8" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="E15" t="s">
+        <v>810</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>900</v>
       </c>
-      <c r="E15" t="s">
-        <v>813</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>909</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>904</v>
-      </c>
       <c r="I15" s="12" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="73.8" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>807</v>
+      </c>
+      <c r="E16" t="s">
         <v>810</v>
       </c>
-      <c r="E16" t="s">
-        <v>813</v>
-      </c>
       <c r="F16" s="11" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="73.8" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="E17" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="73.8" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="E18" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="73.8" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="E19" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="73.8" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="E20" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="G20" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>856</v>
+      </c>
+      <c r="J20" s="11" t="s">
         <v>908</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>860</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -15097,7 +15141,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74530E38-EDB4-4883-BA3E-6C72C076C507}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="26.3984375" customWidth="1"/>
@@ -15126,10 +15170,10 @@
         <v>168</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>160</v>
@@ -15141,7 +15185,7 @@
         <v>163</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>197</v>
@@ -15156,10 +15200,10 @@
         <v>411</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -15167,446 +15211,530 @@
     </row>
     <row r="2" spans="1:18" ht="54">
       <c r="A2" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>610</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="K2" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="M2" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="N2" s="11" t="s">
-        <v>575</v>
-      </c>
       <c r="O2" s="11" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="36">
       <c r="A3" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>572</v>
-      </c>
       <c r="K3" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="36">
       <c r="A4" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>572</v>
-      </c>
       <c r="K4" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="36">
       <c r="A5" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>572</v>
-      </c>
       <c r="K5" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="36">
       <c r="A6" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>572</v>
-      </c>
       <c r="K6" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="36">
       <c r="A7" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="G7" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>572</v>
-      </c>
       <c r="K7" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="36">
       <c r="A8" s="4" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>191</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>191</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="36">
       <c r="A10" s="4" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>191</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="36">
       <c r="A11" s="4" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>191</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="36">
       <c r="A12" s="4" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>191</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="4" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>191</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>956</v>
+        <v>952</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>567</v>
       </c>
     </row>
   </sheetData>
@@ -15618,23 +15746,21 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{679D6C04-1546-44B7-B4BC-9388FD23F265}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.69921875" customWidth="1"/>
     <col min="2" max="2" width="20.69921875" customWidth="1"/>
     <col min="3" max="3" width="25.8984375" customWidth="1"/>
     <col min="4" max="4" width="26.3984375" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="6" width="51.5" customWidth="1"/>
-    <col min="7" max="7" width="38.19921875" customWidth="1"/>
-    <col min="8" max="8" width="48.3984375" customWidth="1"/>
-    <col min="9" max="9" width="59.09765625" customWidth="1"/>
-    <col min="10" max="10" width="47.5" customWidth="1"/>
-    <col min="11" max="11" width="57.3984375" customWidth="1"/>
+    <col min="5" max="5" width="38.19921875" customWidth="1"/>
+    <col min="6" max="6" width="48.3984375" customWidth="1"/>
+    <col min="7" max="7" width="59.09765625" customWidth="1"/>
+    <col min="8" max="8" width="47.5" customWidth="1"/>
+    <col min="9" max="9" width="57.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="22.05" customHeight="1">
+    <row r="1" spans="1:9" ht="22.05" customHeight="1">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -15642,89 +15768,85 @@
         <v>414</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>415</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>416</v>
-      </c>
-      <c r="G1" s="21" t="s">
         <v>13</v>
       </c>
+      <c r="F1" s="22" t="s">
+        <v>577</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>576</v>
+      </c>
       <c r="H1" s="22" t="s">
+        <v>578</v>
+      </c>
+      <c r="I1" s="22" t="s">
         <v>579</v>
       </c>
-      <c r="I1" s="22" t="s">
-        <v>578</v>
-      </c>
-      <c r="J1" s="22" t="s">
-        <v>580</v>
-      </c>
-      <c r="K1" s="22" t="s">
-        <v>581</v>
-      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:9">
       <c r="A2" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>608</v>
+        <v>532</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>609</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>610</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>611</v>
-      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:9">
       <c r="A3" s="4" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>819</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>815</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>815</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>822</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>823</v>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>996</v>
       </c>
     </row>
   </sheetData>
@@ -15767,43 +15889,43 @@
         <v>410</v>
       </c>
       <c r="D1" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>417</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>419</v>
       </c>
       <c r="G1" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L1" s="31" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="M1" s="17" t="s">
         <v>160</v>
       </c>
       <c r="N1" s="17" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="O1" s="31" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="P1" s="32" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="Q1" s="17" t="s">
         <v>13</v>
@@ -15817,28 +15939,28 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>757</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>506</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>508</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -15851,144 +15973,144 @@
       </c>
       <c r="P2" s="4"/>
       <c r="R2" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="L3" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="P3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="Q3" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>541</v>
-      </c>
       <c r="S3" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="72">
       <c r="A4" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="Q4" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="R4" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="Q4" s="11" t="s">
-        <v>592</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>593</v>
-      </c>
       <c r="S4" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="4" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="4" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="4" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="4" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>755</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>754</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="E9" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="G9" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>758</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>759</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>760</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>761</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>762</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -16004,42 +16126,42 @@
         <v>15</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="4" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="G10" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>758</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="I10" s="4" t="s">
         <v>759</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>767</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>761</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>762</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -16055,42 +16177,42 @@
         <v>40</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>769</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>756</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>758</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>759</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>772</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>773</v>
-      </c>
       <c r="I11" s="4" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -16106,42 +16228,42 @@
         <v>150</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="4" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>758</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="G12" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>759</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>776</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>773</v>
-      </c>
       <c r="I12" s="4" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -16157,74 +16279,74 @@
         <v>150</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>191</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="O13">
         <v>50</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="54">
       <c r="A14" s="4" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>785</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>770</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>787</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>788</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>789</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>791</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -16236,141 +16358,141 @@
         <v>120</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="R14" s="11" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="S14" s="11" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="4" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>191</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="O15">
         <v>70</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="4" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>191</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="O16">
         <v>50</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="4" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>191</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="O17">
         <v>70</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="4" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>966</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>967</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>970</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>191</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
     </row>
   </sheetData>
@@ -16397,50 +16519,50 @@
   <sheetData>
     <row r="2" spans="2:17">
       <c r="B2" s="23" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="L2" s="23" t="s">
         <v>168</v>
       </c>
       <c r="M2" s="23" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
     </row>
     <row r="3" spans="2:17">
       <c r="B3" s="23" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>167</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L3" s="23" t="s">
         <v>167</v>
@@ -16453,25 +16575,25 @@
     </row>
     <row r="4" spans="2:17">
       <c r="B4" s="23" t="s">
+        <v>433</v>
+      </c>
+      <c r="D4" s="23" t="s">
         <v>435</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>437</v>
-      </c>
       <c r="E4" s="28" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J4" s="28" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M4" s="24">
         <v>2</v>
@@ -16481,25 +16603,25 @@
     </row>
     <row r="5" spans="2:17">
       <c r="B5" s="23" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="M5" s="24">
         <v>3</v>
@@ -16508,25 +16630,25 @@
     </row>
     <row r="6" spans="2:17">
       <c r="B6" s="23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="M6" s="24">
         <v>4</v>
@@ -16535,25 +16657,25 @@
     </row>
     <row r="7" spans="2:17">
       <c r="B7" s="23" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="M7" s="24">
         <v>5</v>
@@ -16562,106 +16684,106 @@
     </row>
     <row r="8" spans="2:17">
       <c r="B8" s="23" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
       <c r="F8" s="26"/>
       <c r="I8" s="23" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="P8" s="7"/>
     </row>
     <row r="9" spans="2:17">
       <c r="I9" s="23" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J9" s="28" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:17">
       <c r="I10" s="23" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J10" s="28" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="11" spans="2:17">
       <c r="I11" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="J11" s="28" t="s">
         <v>460</v>
-      </c>
-      <c r="J11" s="28" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="12" spans="2:17">
       <c r="I12" s="23" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J12" s="28" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="13" spans="2:17">
       <c r="I13" s="23" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" spans="2:17">
       <c r="I14" s="23" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" spans="2:17">
       <c r="I15" s="23" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="16" spans="2:17">
       <c r="I16" s="23" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" spans="9:10">
       <c r="I17" s="23" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="18" spans="9:10">
       <c r="I18" s="23" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" spans="9:10">
       <c r="I19" s="23" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9B9195-B6E0-406B-9131-B85495871651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1C19D3-7439-4DFB-BEE7-4A68CD6D3BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">セット効果!$A$1:$B$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">敵スキル!$A$1:$S$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">防具!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">味方スキル!$A$1:$S$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">味方スキル!$A$1:$S$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="1247">
   <si>
     <t>ID</t>
   </si>
@@ -4192,14 +4192,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>6秒</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>6秒</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ランク</t>
   </si>
   <si>
@@ -4213,6 +4205,12 @@
   </si>
   <si>
     <t>セット名</t>
+  </si>
+  <si>
+    <t>2セット効果</t>
+  </si>
+  <si>
+    <t>5セット効果</t>
   </si>
   <si>
     <t>種類</t>
@@ -5688,6 +5686,16 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>防御が10%上昇する</t>
+    <rPh sb="0" eb="2">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>HPが上昇する</t>
     <rPh sb="3" eb="5">
       <t>ジョウショウ</t>
@@ -6029,7 +6037,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>bud_Alraune</t>
+    <t>bud_alraune</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -6545,10 +6553,6 @@
     <rPh sb="14" eb="16">
       <t>テイカ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Injury</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -7390,6 +7394,16 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>魔防が25上昇する</t>
+    <rPh sb="0" eb="2">
+      <t>マボウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>2セット効果名</t>
     <rPh sb="4" eb="7">
       <t>コウカメイ</t>
@@ -8229,23 +8243,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アイテムID(horn_rabbit_fur) * 5 + アイテムID(horn_rabbit_tooth) * 1 +100G</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アイテムID(horn_rabbit_fur) * 5 + アイテムID(horn_rabbit_corner) * 1 +100G</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アイテムID(horn_rabbit_fur) * 1 +
-アイテムID(horn_rabbit_tooth) * 1 +50G</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アイテムID(horn_rabbit_corner) * 1 +50G</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>horn_rabbit</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -8364,24 +8361,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アイテムID(horn_rabbit_fur)*3+
-アイテムID(horn_rabbit_corner)*1+100G</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アイテムID(horn_rabbit_fur)*5+100G</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アイテムID(horn_rabbit_fur)*1+
-アイテムID(horn_rabbit_tooth)*4+100G</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アイテムID(horn_rabbit_corner)*3+150G</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>HP+5%,防御+3%</t>
     <rPh sb="6" eb="8">
       <t>ボウギョ</t>
@@ -8409,25 +8388,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アイテムID(horn_rabbit_fur)*2+
-アイテムID(horn_rabbit_tooth)*2+100G</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アイテムID(horn_rabbit_fur)*1+
-アイテムID(horn_rabbit_corner)*1+50G</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アイテムID(horn_rabbit_fur)*2+50G</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アイテムID(horn_rabbit_fur)*1+
-アイテムID(horn_rabbit_tooth)*1+50G</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>魔力+5%</t>
     <rPh sb="0" eb="2">
       <t>マリョク</t>
@@ -8442,90 +8402,12 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ツノウサギの毛皮を元に作られた暖かい頭装備</t>
-    <rPh sb="6" eb="8">
-      <t>ケガワ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>アタタ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>アタマソウビ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ツノウサギの毛皮を元に作られた暖かい胴装備</t>
-    <rPh sb="18" eb="21">
-      <t>ドウソウビ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ツノウサギの毛皮を元に作られた暖かい手装備</t>
-    <rPh sb="18" eb="19">
-      <t>テ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ソウビ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ツノウサギの毛皮を元に作られた暖かい足装備</t>
-    <rPh sb="18" eb="19">
-      <t>アシ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ソウビ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ツノウサギの毛皮を元に作られた暖かい靴装備</t>
-    <rPh sb="18" eb="19">
-      <t>クツ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ソウビ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ツノウサギの角を元に作られた魔力溢れるペンダント</t>
-    <rPh sb="6" eb="7">
-      <t>ツノ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>マリョク</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>アフ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ツサギフィスト</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>horn_rabbit_glove</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>(アイテムID:d_power_flag)*1/70%</t>
   </si>
   <si>
     <t>3秒間香りをただよらせ、触れた敵に(状態ID:debuff_sleep)を最大12秒付与。
@@ -8728,22 +8610,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アルラウネの根</t>
-    <rPh sb="6" eb="7">
-      <t>ネ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>D</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Alraune_root</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Alraune_leaf</t>
+    <t>alraune_leaf</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -8754,10 +8625,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>20G/100%.(アイテムID:horn_rabbit_fur)*1/70%.(アイテムID:horn_rabbit_fur)*1/70%.(アイテムID:horn_rabbit_corner)*1/50%.(アイテムID:horn_rabbit_tooth)*1/80%.(アイテムID:d_power_flag)*1/70%</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>-</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -8766,7 +8633,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Alraune_Ivy</t>
+    <t>alraune_ivy</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -8780,16 +8647,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>まだあまり長くないアルラウネの根</t>
-    <rPh sb="5" eb="6">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ネ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>魔力中和音</t>
     <rPh sb="0" eb="4">
       <t>マリョクチュウワ</t>
@@ -8807,59 +8664,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>詠唱後、周囲の敵の魔力を中和し、４秒間対象の魔力を5%減少させる</t>
-    <rPh sb="4" eb="6">
-      <t>シュウイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>マリョク</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>チュウワ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ビョウカン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>マリョク</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ゲンショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>詠唱後、周囲の敵の魔力を中和し、４秒間魔力を減少させる</t>
-    <rPh sb="4" eb="6">
-      <t>シュウイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>マリョク</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>チュウワ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ビョウカン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>マリョク</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ゲンショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>レベルごとに魔力の減少量+(0/1/2/3/4/5)</t>
     <rPh sb="6" eb="8">
       <t>マリョク</t>
@@ -8946,31 +8750,34 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>bud_Alraune_helm</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>bud_Alraune_armor</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>bud_Alraune_leggings</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>bud_Alraune_boots</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>bud_Alraune_glove</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>bud_Alraune_pendant</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>bud_Alraune</t>
+    <t>bud_alraune</t>
+  </si>
+  <si>
+    <t>bud_alraune_helm</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_armor</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_leggings</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_boots</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_glove</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_pendant</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -8988,6 +8795,2629 @@
     <t>つぼみの中</t>
     <rPh sb="4" eb="5">
       <t>ナカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法防御が上昇する</t>
+  </si>
+  <si>
+    <t>魔法防御力が10%上昇する</t>
+  </si>
+  <si>
+    <t>攻撃力が上昇する</t>
+  </si>
+  <si>
+    <t>攻撃力が10%上昇する</t>
+  </si>
+  <si>
+    <t>魔防が10%上昇する</t>
+    <rPh sb="0" eb="2">
+      <t>マボウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃が10%上昇する</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>alraune_bud</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラウネの蕾</t>
+    <rPh sb="6" eb="7">
+      <t>ツボミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まだほとんど開いていないアルラウネの蕾</t>
+    <rPh sb="6" eb="7">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツボミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>40G/100%.(アイテムID:alraune_leaf)*1/70%.(アイテムID:alraune_leaf)*1/70%.
+(アイテムID:alraune_ivy)*1/80%.(アイテムID:alraune_bud)*1/40%(アイテムID:d_power_flag)*1/70%</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>30G/100%.(アイテムID:horn_rabbit_fur)*1/70%.(アイテムID:horn_rabbit_fur)*1/70%.(アイテムID:horn_rabbit_corner)*1/40%.(アイテムID:horn_rabbit_tooth)*1/80%.(アイテムID:d_power_flag)*1/70%</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:horn_rabbit_fur) * 5 + (アイテムID:horn_rabbit_tooth) * 1 +100G</t>
+  </si>
+  <si>
+    <t>(アイテムID:horn_rabbit_fur) * 1 +
+(アイテムID:horn_rabbit_tooth) * 1 +50G</t>
+  </si>
+  <si>
+    <t>(アイテムID:horn_rabbit_fur) * 5 + (アイテムID:horn_rabbit_corner) * 1 +100G</t>
+  </si>
+  <si>
+    <t>(アイテムID:horn_rabbit_corner) * 1 +50G</t>
+  </si>
+  <si>
+    <t>(アイテムID:horn_rabbit_fur)*3+
+(アイテムID:horn_rabbit_corner)*1+100G</t>
+  </si>
+  <si>
+    <t>(アイテムID:horn_rabbit_fur)*1+
+(アイテムID:horn_rabbit_corner)*1+50G</t>
+  </si>
+  <si>
+    <t>(アイテムID:horn_rabbit_fur)*5+100G</t>
+  </si>
+  <si>
+    <t>(アイテムID:horn_rabbit_fur)*2+50G</t>
+  </si>
+  <si>
+    <t>(アイテムID:horn_rabbit_fur)*2+
+(アイテムID:horn_rabbit_tooth)*2+100G</t>
+  </si>
+  <si>
+    <t>(アイテムID:horn_rabbit_fur)*1+
+(アイテムID:horn_rabbit_tooth)*1+50G</t>
+  </si>
+  <si>
+    <t>(アイテムID:horn_rabbit_corner)*3+150G</t>
+  </si>
+  <si>
+    <t>ツノウサギの毛皮を元に作られた手装備</t>
+    <rPh sb="6" eb="8">
+      <t>ケガワ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HP+5%,攻撃+5%</t>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HP+5%,防御+10%</t>
+    <rPh sb="6" eb="8">
+      <t>ボウギョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_leaf)*4+(アイテムID:alraune_bud)*2+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_leaf)*3+(アイテムID:alraune_ivy)*3+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_leaf)*2+(アイテムID:alraune_ivy)*2+130G</t>
+  </si>
+  <si>
+    <t>HP+5%,攻撃+3%</t>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_leaf)*2+(アイテムID:alraune_bud)*2+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:horn_rabbit_fur)*1+
+(アイテムID:horn_rabbit_corner)*4+100G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HP+10%</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_leaf)*2+(アイテムID:alraune_ivy)*3+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+8%</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_ivy)*5+200G</t>
+  </si>
+  <si>
+    <t>物理与ダメ率+10%</t>
+    <rPh sb="0" eb="3">
+      <t>ブツリヨ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_leaf)*1+(アイテムID:alraune_ivy)*1+65G</t>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_leaf)*1+(アイテムID:alraune_bud)*1+65G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_leaf)*1+(アイテムID:alraune_bud)*1+65G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ツノウサギの毛皮を元に作られた頭装備</t>
+    <rPh sb="6" eb="8">
+      <t>ケガワ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>アタマソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ツノウサギの毛皮を元に作られた胴装備</t>
+    <rPh sb="15" eb="18">
+      <t>ドウソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ツノウサギの毛皮を元に作られた足装備</t>
+    <rPh sb="15" eb="16">
+      <t>アシ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ツノウサギの毛皮を元に作られた靴装備</t>
+    <rPh sb="15" eb="16">
+      <t>クツ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ツノウサギの角を元に作られたペンダント</t>
+    <rPh sb="6" eb="7">
+      <t>ツノ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラウネの葉を元に作られた頭装備</t>
+    <rPh sb="6" eb="7">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>アタマソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラウネの葉を元に作られた胴装備</t>
+    <rPh sb="14" eb="17">
+      <t>ドウソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラウネの葉を元に作られた足装備</t>
+    <rPh sb="14" eb="17">
+      <t>アシソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラウネの葉を元に作られた靴装備</t>
+    <rPh sb="14" eb="17">
+      <t>クツソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラウネの葉を元に作られた手装備</t>
+    <rPh sb="14" eb="17">
+      <t>テソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラウネの蕾を元に作られたペンダント</t>
+    <rPh sb="6" eb="7">
+      <t>ツボミ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラナイフ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラソード</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラフィスト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラスタッフ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラステッキ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔導書・アルラ</t>
+    <rPh sb="0" eb="3">
+      <t>マドウショ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルラフルート</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_knife</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_sword</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_fist</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_staff</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_stick</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_book</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_flute</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_ivy)*4+(アイテムID:alraune_bud)*1+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_bud)*4+
+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_leaf)*4+(アイテムID:alraune_ivy)*1+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_leaf)*3+(アイテムID:alraune_bud)*1+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_ivy)*5+(アイテムID:alraune_leaf)*1+(アイテムID:alraune_bud)*1+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+18</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+25</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+20</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力+15</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力+25</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_ivy)*1+65G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_bud)*1+65G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_leaf)*1+65G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.6</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.55</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力 * 0.5</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力 * 0.35</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>範囲バフ</t>
+    <rPh sb="0" eb="2">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>目覚まし</t>
+    <rPh sb="0" eb="2">
+      <t>メザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に剣を突き刺し、物理ダメージを与える。まれに敵に"睡眠"を付与する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>少しのチャージを行い、敵に剣を振りかざし、物理ダメージを与える。まれに"睡眠"を付与する</t>
+    <rPh sb="0" eb="1">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(睡眠(debuff_sleep)20%)3s</t>
+    <rPh sb="1" eb="3">
+      <t>スイミン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に剣を突き刺し、(式=値)の物理ダメージを与える。20%の確率で敵に３秒の"睡眠"を付与する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1秒のチャージ後、敵に剣を振りかざし、(式=値)の物理ダメージを与える。20%の確率で敵に３秒の"睡眠"を付与する</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵の顔を殴り、物理ダメージを与える。まれに"睡眠"を付与する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナグ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵の顔を殴り、(式=値)の物理ダメージを与える。20%の確率で敵に３秒の"睡眠"を付与する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナグ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>棒具を振り、端を1回ずつ当て、物理ダメージを与える。まれに睡眠を付与する</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>棒具を振り、端を2回ずつ当て、(式=値)の物理ダメージを2度与える。20%ずつの確率で敵に３秒の"睡眠"を付与する。１回目で"睡眠"を付与した場合、２回目のダメージが(攻撃力 * 0.15)分上昇する。この時の２回目の攻撃では"睡眠"は付与されない</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="84" eb="87">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="95" eb="96">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="103" eb="104">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この攻撃は2回ダメージを与える
+１回目で睡眠を付与した場合、２回目のダメージで解除される。この時の２回目のダメージの参照式に+(攻撃力 * 0.15)が追加される。
+この２回目のダメージで睡眠を付与することはできない</t>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カイジョ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="58" eb="61">
+      <t>サンショウシキ</t>
+    </rPh>
+    <rPh sb="64" eb="67">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、魔力で生成された弾を発射する。
+まれに"睡眠"を付与する</t>
+    <rPh sb="24" eb="26">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>１秒の詠唱を行った後、指定した方向に魔力で生成した弾を発射する。当たった敵に(式=値)の魔法ダメージを与える。魔力弾は敵に当たるか最大射程まで飛ぶと消滅する。20%の確率で敵に３秒の"睡眠"を付与する</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エイショウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ハッシャ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="55" eb="58">
+      <t>マリョクダン</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="65" eb="69">
+      <t>サイダイシャテイ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ショウメツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(睡眠(debuff_sleep)15%)2s</t>
+    <rPh sb="1" eb="3">
+      <t>スイミン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、指定した範囲内の敵に衝撃を与え、魔法ダメージを与える。まれに"睡眠"を付与する</t>
+    <rPh sb="0" eb="3">
+      <t>エイショウゴ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショウゲキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1秒の詠唱後、指定した範囲内の敵に衝撃を与え、(式=値)の魔法ダメージを与える。15%の確率で敵に2秒の"睡眠"を付与する</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>エイショウゴ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショウゲキ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>0.2秒</t>
+    <rPh sb="3" eb="4">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味方</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>睡眠(debuff_sleep)15%)解除</t>
+    <rPh sb="20" eb="22">
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象に睡眠が付与されている場合、即座に解除する</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソクザ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、周囲の敵の魔力を中和し、魔力を減少させる</t>
+    <rPh sb="4" eb="6">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>チュウワ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>0.5秒の詠唱後、周囲の敵の魔力を中和し、４秒間対象の魔力を5%減少させる</t>
+    <rPh sb="3" eb="4">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>エイショウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>チュウワ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、周囲の味方に大きな音を出し、味方に付与されている"睡眠"を解除する</t>
+    <rPh sb="4" eb="6">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>半径220px・90度</t>
+    <rPh sb="0" eb="2">
+      <t>ハンケイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルごとに睡眠の付与率が+(0/5/10/15/20/25)%増加</t>
+    <rPh sb="6" eb="8">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>フヨリツ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに"睡眠"の付与率が上昇する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>フヨリツ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに"睡眠"が+(5/10/15/20/25)%上昇する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルごとに範囲指定の角度が+(0/6/12/18/24/30)度</t>
+    <rPh sb="6" eb="10">
+      <t>ハンイシテイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとにスキルの範囲が拡大する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カクダイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとにスキルの範囲が+(6/12/18/24/30)度拡大する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カクダイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シャドウウルフの爪</t>
+    <rPh sb="8" eb="9">
+      <t>ツメ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シャドウウルフの毛皮</t>
+    <rPh sb="8" eb="10">
+      <t>ケガワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シャドウウルフの牙</t>
+    <rPh sb="8" eb="9">
+      <t>キバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_fur</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_fang</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_nail</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素材</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>綺麗なシャドウウルフの毛皮</t>
+    <rPh sb="0" eb="2">
+      <t>キレイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケガワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鋭いシャドウウルフの爪</t>
+    <rPh sb="0" eb="1">
+      <t>スルド</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツメ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>強靭なシャドウウルフの牙</t>
+    <rPh sb="0" eb="2">
+      <t>キョウジン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シャドウウルフ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ハントアイ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ハントダッシュ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動速度が20%上昇する</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HPが20%以下の敵に与えるダメージが必ずクリティカルになる</t>
+    <rPh sb="6" eb="8">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カナラ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動速度が上昇する</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HPが低い敵に攻撃をする時、会心が発生する</t>
+    <rPh sb="3" eb="4">
+      <t>ヒク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイシン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HPが20%以下の敵に対する攻撃が必ず会心になる</t>
+    <rPh sb="6" eb="8">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カイシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>影狼兜</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カブト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>影狼鎧</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヨロイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>影狼脚</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>影狼靴</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>クツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_helm</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_armor</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_leggings</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_boots</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_glove</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_pendant</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>影狼手</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>影狼飾</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>頭</t>
+    <rPh sb="0" eb="1">
+      <t>アタマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>胴</t>
+    <rPh sb="0" eb="1">
+      <t>ドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>足</t>
+    <rPh sb="0" eb="1">
+      <t>アシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>靴</t>
+    <rPh sb="0" eb="1">
+      <t>クツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>手</t>
+    <rPh sb="0" eb="1">
+      <t>テ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_nail)*5+200G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*3+(アイテムID:shadow_wolf_fang)*2+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*7+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*2+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>会心率+10%</t>
+    <rPh sb="0" eb="3">
+      <t>カイシンリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+8%</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法防御+10%</t>
+    <rPh sb="0" eb="4">
+      <t>マホウボウギョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HP+5%</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+5%</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>防御+5%</t>
+    <rPh sb="0" eb="2">
+      <t>ボウギョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*1+(アイテムID:shadow_wolf_fang)*1+65G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*1+65G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*2+65G</t>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*2+65G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シャドウウルフの毛皮を元に作られた頭装備</t>
+    <rPh sb="8" eb="10">
+      <t>ケガワ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>アタマソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シャドウウルフの毛皮を元に作られた胴装備</t>
+    <rPh sb="8" eb="10">
+      <t>ケガワ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ドウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シャドウウルフの毛皮を元に作られた足装備</t>
+    <rPh sb="8" eb="10">
+      <t>ケガワ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>アシソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シャドウウルフの毛皮を元に作られた靴装備</t>
+    <rPh sb="8" eb="10">
+      <t>ケガワ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>クツソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シャドウウルフの毛皮を元に作られた手装備</t>
+    <rPh sb="8" eb="10">
+      <t>ケガワ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シャドウウルフの爪を元に作られたペンダント</t>
+    <rPh sb="8" eb="9">
+      <t>ツメ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>武器別追加ステータス</t>
+    <rPh sb="0" eb="3">
+      <t>ブキベツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ステータス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>本</t>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>楽器</t>
+    <rPh sb="0" eb="2">
+      <t>ガッキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ガード率+20%</t>
+    <rPh sb="3" eb="4">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>会心ダメージ+40%</t>
+    <rPh sb="0" eb="2">
+      <t>カイシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱速度+20%</t>
+    <rPh sb="0" eb="4">
+      <t>エイショウソクド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法与ダメ率+20%</t>
+    <rPh sb="0" eb="3">
+      <t>マホウヨ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クールタイム-20%</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チャージ率+20%</t>
+    <rPh sb="4" eb="5">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>行動速度+10%</t>
+    <rPh sb="0" eb="4">
+      <t>コウドウソクド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>60G/100%,(アイテムID:shadow_wolf_fur)*2/50%,(アイテムID:shadow_wolf_fur)*1/80%,
+(アイテムID:shadow_wolf_nail)*1/70%,(アイテムID:shadow_wolf_fang)*1/70%,
+(アイテムID:d_power_flag)*1/70%</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_knife</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_sword</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_fist</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_staff</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_flute</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>影狼刃</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヤイバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>影狼刀</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カタナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>影狼爪</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツメ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>影狼薙</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>影狼笛</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>フエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>片手剣</t>
+    <rPh sb="0" eb="3">
+      <t>カタテケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>両手剣</t>
+    <rPh sb="0" eb="3">
+      <t>リョウテケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>拳具</t>
+    <rPh sb="0" eb="2">
+      <t>ケング</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>棒具</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>楽器</t>
+    <rPh sb="0" eb="2">
+      <t>ガッキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:alraune_leaf)*6+
+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*2+(アイテムID:shadow_wolf_fang)*2+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*1+(アイテムID:shadow_wolf_fang)*3+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+20</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+25</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+18</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+17</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+17</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力+17</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_attack_knife</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_attack_sword</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_attack_fist</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_attack_staff</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_attack_stick</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_attack_book</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraune_attack_flute</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>bud_alraunet_attack_fist</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_attack_knife</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_attack_sword</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_attack_fist</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_attack_staff</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shadow_wolf_attack_flute</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>遠吠え</t>
+    <rPh sb="0" eb="2">
+      <t>トオボ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>debuff_Injury</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>負傷(debuff_Injury)3s</t>
+    <rPh sb="0" eb="2">
+      <t>フショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に剣を突き刺し、物理ダメージを与え、敵に"負傷"を付与する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>フショウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>少しのチャージを行い、敵に剣を振りかざし、物理ダメージを与え、敵に"負傷"を付与する</t>
+    <rPh sb="0" eb="1">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵の顔を殴り、物理ダメージを与え、敵に"負傷"を付与する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナグ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>フショウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>棒具を振り、端を1回ずつ当て、物理ダメージを与え、敵に"負傷"を付与する</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ブツリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この攻撃は２回ダメージを与える</t>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に剣を突き刺し、(式=値)の物理ダメージを与え、３秒の"負傷"を付与する。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>フショウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1秒のチャージ後、敵に剣を振りかざし、(式=値)の物理ダメージを与え、３秒の"負傷"を付与する。</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵の顔を殴り、(式=値)の物理ダメージを与え、３秒の"負傷"を付与する。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナグ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>フショウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>棒具を振り、端を2回ずつ当て、(式=値)の物理ダメージを2度与え、３秒の"負傷"を付与する。</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この武器は後衛として扱われる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルごとに負傷の付与時間が+(0/1/2/3/4/5)秒延長</t>
+    <rPh sb="6" eb="8">
+      <t>フショウ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>フヨジカン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>エンチョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに"負傷"の効果時間が延びる</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>フショウ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに"負傷"の効果時間が+(1/2/3/4/5)秒延長される</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>フショウ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>エンチョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>半径150px</t>
+    <rPh sb="0" eb="2">
+      <t>ハンケイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象の味方の行動CDが残り0.3秒以上の場合、即座に残り0.3秒にまで短縮する</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ソクザ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、範囲内の味方を即座に行動させる</t>
+    <rPh sb="0" eb="3">
+      <t>エイショウゴ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ハンイナイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソクザ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>0.2秒の詠唱後、周囲の味方に大きな音を出し、"睡眠"が付与されている場合、即座に解除する</t>
+    <rPh sb="3" eb="4">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ソクザ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルごとに詠唱の時間-(0/0.5/1.0/1.5/2.0/2.5)秒短縮</t>
+    <rPh sb="6" eb="8">
+      <t>エイショウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに詠唱時間が短くなる</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>エイショウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ミジカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに詠唱時間が-(0.5/1.0/1.5/2.0/2.5)秒短縮される</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>エイショウジカン</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fang)*1+65G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_nail)*1+65G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*2+(アイテムID:shadow_wolf_nail)*2+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*1+(アイテムID:shadow_wolf_fang)*1+(アイテムID:shadow_wolf_nail)*1+130G</t>
+  </si>
+  <si>
+    <t>3秒の詠唱後、範囲内の味方の行動CDが残り0.3秒以上の場合、即座に残り0.3秒にまで短縮する</t>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*4+130G</t>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*2+(アイテムID:shadow_wolf_nail)*2+130G</t>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*1+(アイテムID:shadow_wolf_nail)*1+65G</t>
+  </si>
+  <si>
+    <t>２秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スキル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスタンス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>distance</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全体指示</t>
+    <rPh sb="0" eb="4">
+      <t>ゼンタイシジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象指定</t>
+    <rPh sb="0" eb="4">
+      <t>タイショウシテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>400px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>20秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>8秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一定時間、対象の敵を味方が狙わなくなる</t>
+    <rPh sb="0" eb="4">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ネラ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>効果時間中、対象の敵を味方AIがターゲットにすることがなくなる、あくまでターゲットにしないだけで合って範囲攻撃等での巻き込みはある</t>
+    <rPh sb="0" eb="5">
+      <t>コウカジカンチュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="51" eb="56">
+      <t>ハンイコウゲキトウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>８秒間、対象の敵を味方がターゲットにしなくなる</t>
+    <rPh sb="1" eb="3">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ミカタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルごとにCD-(0/2/4/6/8/10)秒短縮</t>
+    <rPh sb="23" eb="24">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとにスキルのクールタイムが短くなる</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ミジカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとにスキルのクールタイムが(2/4/6/8/10)秒短縮される</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>タンシュク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -9180,7 +11610,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9276,10 +11706,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9679,10 +12121,10 @@
         <v>259</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>9</v>
@@ -9748,7 +12190,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>409</v>
+        <v>1229</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>19</v>
@@ -9757,10 +12199,10 @@
         <v>315</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>294</v>
@@ -9837,7 +12279,7 @@
         <v>25</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>26</v>
@@ -9917,7 +12359,7 @@
         <v>320</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>215</v>
@@ -9932,7 +12374,7 @@
         <v>32</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="T4" s="3" t="s">
         <v>324</v>
@@ -10066,7 +12508,7 @@
         <v>20</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>408</v>
+        <v>1229</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>20</v>
@@ -10075,10 +12517,10 @@
         <v>25</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>41</v>
@@ -10155,10 +12597,10 @@
         <v>260</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>294</v>
@@ -10304,7 +12746,7 @@
         <v>20</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>408</v>
+        <v>1229</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>215</v>
@@ -10393,7 +12835,7 @@
         <v>249</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>250</v>
@@ -10473,16 +12915,16 @@
         <v>48</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>276</v>
@@ -10542,7 +12984,7 @@
         <v>20</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>408</v>
+        <v>1229</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>19</v>
@@ -10554,7 +12996,7 @@
         <v>218</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>234</v>
@@ -10576,7 +13018,7 @@
         <v>304</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="X12" s="12" t="s">
         <v>369</v>
@@ -10611,7 +13053,7 @@
         <v>30</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>215</v>
@@ -10644,7 +13086,7 @@
         <v>245</v>
       </c>
       <c r="S13" s="12" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="T13" s="12" t="s">
         <v>478</v>
@@ -10706,13 +13148,13 @@
         <v>225</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>234</v>
@@ -10952,7 +13394,7 @@
         <v>215</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>27</v>
@@ -11032,7 +13474,7 @@
         <v>215</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>27</v>
@@ -11184,25 +13626,25 @@
         <v>137</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>731</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="V20" s="12" t="s">
         <v>208</v>
       </c>
       <c r="W20" s="12" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="X20" s="12"/>
       <c r="Y20" s="16"/>
@@ -11254,13 +13696,13 @@
         <v>137</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>142</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>20</v>
@@ -11378,7 +13820,7 @@
         <v>494</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="O23" s="13" t="s">
         <v>492</v>
@@ -11419,415 +13861,415 @@
     </row>
     <row r="24" spans="1:26" ht="36">
       <c r="A24" s="12" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G24">
         <v>13</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>857</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>408</v>
+        <v>858</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>1229</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="O24" s="13" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="R24" s="12" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="T24" s="13" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="V24" s="12" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="W24" s="12" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="X24" s="12" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Y24" s="12" t="s">
         <v>339</v>
       </c>
       <c r="Z24" s="12" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="36">
       <c r="A25" s="12" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G25">
         <v>10</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>901</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>408</v>
+        <v>902</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>1229</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="O25" s="13" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="R25" s="12" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="T25" s="12" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="V25" s="12" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="W25" s="12" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="X25" s="12" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Y25" s="12" t="s">
         <v>339</v>
       </c>
       <c r="Z25" s="12" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="36">
       <c r="A26" s="12" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G26">
         <v>14</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>858</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>408</v>
+        <v>859</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>1229</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="O26" s="13" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="R26" s="12" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="T26" s="12" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="V26" s="12" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="W26" s="12" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="X26" s="12" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Y26" s="12" t="s">
         <v>339</v>
       </c>
       <c r="Z26" s="12" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="36">
       <c r="A27" s="12" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G27">
         <v>8</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>859</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>408</v>
+        <v>860</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>1229</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="O27" s="13" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="R27" s="12" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="T27" s="12" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="V27" s="12" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="W27" s="12" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="X27" s="12" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Y27" s="12" t="s">
         <v>339</v>
       </c>
       <c r="Z27" s="12" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="72">
       <c r="A28" s="12" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G28">
         <v>10</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J28">
         <v>25</v>
       </c>
-      <c r="K28" s="13" t="s">
-        <v>408</v>
+      <c r="K28" s="3" t="s">
+        <v>1229</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="O28" s="13" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="T28" s="12" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="V28" s="12" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="W28" s="12" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="X28" s="12" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Y28" s="12" t="s">
         <v>339</v>
       </c>
       <c r="Z28" s="12" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="36">
       <c r="A29" s="12" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="G29">
         <v>10</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="J29">
         <v>20</v>
       </c>
-      <c r="K29" s="13" t="s">
-        <v>408</v>
+      <c r="K29" s="3" t="s">
+        <v>1229</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="R29" s="12" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="T29" s="12" t="s">
         <v>314</v>
       </c>
       <c r="V29" s="12" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="W29" s="12" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="X29" s="12" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Y29" s="12" t="s">
         <v>339</v>
       </c>
       <c r="Z29" s="12" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="36">
       <c r="A30" s="12" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>164</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>973</v>
+        <v>951</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>600</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>968</v>
+        <v>947</v>
       </c>
       <c r="H30" s="16" t="s">
         <v>215</v>
@@ -11835,67 +14277,949 @@
       <c r="J30">
         <v>20</v>
       </c>
-      <c r="K30" s="13" t="s">
-        <v>408</v>
+      <c r="K30" s="3" t="s">
+        <v>1229</v>
       </c>
       <c r="L30" s="34" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="P30" s="12" t="s">
         <v>294</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="R30" s="12" t="s">
         <v>215</v>
       </c>
       <c r="T30" s="12" t="s">
-        <v>974</v>
+        <v>952</v>
       </c>
       <c r="V30" s="12" t="s">
-        <v>976</v>
+        <v>1079</v>
       </c>
       <c r="W30" s="12" t="s">
-        <v>975</v>
+        <v>1080</v>
       </c>
       <c r="X30" s="12" t="s">
-        <v>977</v>
+        <v>953</v>
       </c>
       <c r="Y30" s="12" t="s">
-        <v>978</v>
+        <v>954</v>
       </c>
       <c r="Z30" s="12" t="s">
-        <v>979</v>
+        <v>955</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="M34" s="4"/>
+    <row r="31" spans="1:26" ht="36">
+      <c r="A31" s="12" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>824</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>599</v>
+      </c>
+      <c r="G31">
+        <v>13</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>1052</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M31" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="N31" s="13" t="s">
+        <v>648</v>
+      </c>
+      <c r="O31" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="P31" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q31" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R31" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="S31" s="12" t="s">
+        <v>1062</v>
+      </c>
+      <c r="T31" s="13" t="s">
+        <v>824</v>
+      </c>
+      <c r="U31" s="12"/>
+      <c r="V31" s="12" t="s">
+        <v>1060</v>
+      </c>
+      <c r="W31" s="12" t="s">
+        <v>1063</v>
+      </c>
+      <c r="X31" s="12" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Y31" s="12" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Z31" s="12" t="s">
+        <v>1085</v>
+      </c>
     </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
+    <row r="32" spans="1:26" ht="54">
+      <c r="A32" s="12" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>659</v>
+      </c>
+      <c r="G32">
+        <v>10</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>1053</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>690</v>
+      </c>
+      <c r="M32" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="N32" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="O32" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="P32" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q32" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R32" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="S32" s="12" t="s">
+        <v>1062</v>
+      </c>
+      <c r="T32" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="V32" s="12" t="s">
+        <v>1061</v>
+      </c>
+      <c r="W32" s="12" t="s">
+        <v>1064</v>
+      </c>
+      <c r="X32" s="12" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Y32" s="12" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Z32" s="12" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" ht="36">
+      <c r="A33" s="12" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="G33">
+        <v>14</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>1054</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M33" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="N33" s="13" t="s">
+        <v>843</v>
+      </c>
+      <c r="O33" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="P33" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q33" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R33" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="S33" s="12" t="s">
+        <v>1062</v>
+      </c>
+      <c r="T33" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="V33" s="12" t="s">
+        <v>1065</v>
+      </c>
+      <c r="W33" s="12" t="s">
+        <v>1066</v>
+      </c>
+      <c r="X33" s="12" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Y33" s="12" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Z33" s="12" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" ht="108">
+      <c r="A34" s="12" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="G34">
+        <v>8</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>1055</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M34" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="N34" s="13" t="s">
+        <v>844</v>
+      </c>
+      <c r="O34" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="P34" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q34" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R34" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="S34" s="12" t="s">
+        <v>1062</v>
+      </c>
+      <c r="T34" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="U34" s="12" t="s">
+        <v>1069</v>
+      </c>
+      <c r="V34" s="12" t="s">
+        <v>1067</v>
+      </c>
+      <c r="W34" s="12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="X34" s="12" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Y34" s="12" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Z34" s="12" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" ht="90">
+      <c r="A35" s="12" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="G35">
+        <v>10</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J35">
+        <v>25</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="M35" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>892</v>
+      </c>
+      <c r="O35" s="13" t="s">
+        <v>666</v>
+      </c>
+      <c r="P35" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q35" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R35" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="S35" s="12" t="s">
+        <v>1062</v>
+      </c>
+      <c r="T35" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="U35" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="V35" s="12" t="s">
+        <v>1070</v>
+      </c>
+      <c r="W35" s="12" t="s">
+        <v>1071</v>
+      </c>
+      <c r="X35" s="12" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Y35" s="12" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Z35" s="12" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" ht="54">
+      <c r="A36" s="12" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="G36">
+        <v>10</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J36">
+        <v>20</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="M36" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>893</v>
+      </c>
+      <c r="O36" s="13" t="s">
+        <v>848</v>
+      </c>
+      <c r="P36" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q36" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R36" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="S36" s="12" t="s">
+        <v>1072</v>
+      </c>
+      <c r="T36" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="V36" s="12" t="s">
+        <v>1073</v>
+      </c>
+      <c r="W36" s="12" t="s">
+        <v>1074</v>
+      </c>
+      <c r="X36" s="12" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Y36" s="12" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Z36" s="12" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" ht="36">
+      <c r="A37" s="12" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="J37">
+        <v>25</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L37" s="34" t="s">
+        <v>1075</v>
+      </c>
+      <c r="M37" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="N37" s="13" t="s">
+        <v>846</v>
+      </c>
+      <c r="O37" s="12" t="s">
+        <v>1082</v>
+      </c>
+      <c r="P37" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Q37" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R37" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="S37" s="12" t="s">
+        <v>1077</v>
+      </c>
+      <c r="T37" s="12" t="s">
+        <v>1059</v>
+      </c>
+      <c r="U37" s="12" t="s">
+        <v>1078</v>
+      </c>
+      <c r="V37" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="W37" s="12" t="s">
+        <v>1217</v>
+      </c>
+      <c r="X37" s="12" t="s">
+        <v>1086</v>
+      </c>
+      <c r="Y37" s="12" t="s">
+        <v>1087</v>
+      </c>
+      <c r="Z37" s="12" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" ht="36">
+      <c r="A38" s="12" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>824</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>599</v>
+      </c>
+      <c r="G38">
+        <v>13</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>1052</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M38" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="N38" s="13" t="s">
+        <v>648</v>
+      </c>
+      <c r="O38" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="P38" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q38" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R38" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="S38" s="12" t="s">
+        <v>1200</v>
+      </c>
+      <c r="T38" s="13" t="s">
+        <v>824</v>
+      </c>
+      <c r="U38" s="12"/>
+      <c r="V38" s="12" t="s">
+        <v>1201</v>
+      </c>
+      <c r="W38" s="12" t="s">
+        <v>1206</v>
+      </c>
+      <c r="X38" s="12" t="s">
+        <v>1211</v>
+      </c>
+      <c r="Y38" s="12" t="s">
+        <v>1212</v>
+      </c>
+      <c r="Z38" s="12" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" ht="36">
+      <c r="A39" s="12" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>659</v>
+      </c>
+      <c r="G39">
+        <v>10</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>1053</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>690</v>
+      </c>
+      <c r="M39" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="N39" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="O39" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="P39" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q39" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R39" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="S39" s="12" t="s">
+        <v>1200</v>
+      </c>
+      <c r="T39" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="U39" s="12"/>
+      <c r="V39" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="W39" s="12" t="s">
+        <v>1207</v>
+      </c>
+      <c r="X39" s="12" t="s">
+        <v>1211</v>
+      </c>
+      <c r="Y39" s="12" t="s">
+        <v>1212</v>
+      </c>
+      <c r="Z39" s="12" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" ht="36">
+      <c r="A40" s="12" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="G40">
+        <v>14</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>1054</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="N40" s="13" t="s">
+        <v>843</v>
+      </c>
+      <c r="O40" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="P40" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q40" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R40" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="S40" s="12" t="s">
+        <v>1200</v>
+      </c>
+      <c r="T40" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="U40" s="12"/>
+      <c r="V40" s="12" t="s">
+        <v>1203</v>
+      </c>
+      <c r="W40" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="X40" s="12" t="s">
+        <v>1211</v>
+      </c>
+      <c r="Y40" s="12" t="s">
+        <v>1212</v>
+      </c>
+      <c r="Z40" s="12" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" ht="36">
+      <c r="A41" s="12" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="G41">
+        <v>8</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>1055</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M41" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="N41" s="13" t="s">
+        <v>844</v>
+      </c>
+      <c r="O41" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="P41" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q41" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R41" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="S41" s="12" t="s">
+        <v>1200</v>
+      </c>
+      <c r="T41" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="U41" s="12" t="s">
+        <v>1205</v>
+      </c>
+      <c r="V41" s="12" t="s">
+        <v>1204</v>
+      </c>
+      <c r="W41" s="12" t="s">
+        <v>1209</v>
+      </c>
+      <c r="X41" s="12" t="s">
+        <v>1211</v>
+      </c>
+      <c r="Y41" s="12" t="s">
+        <v>1212</v>
+      </c>
+      <c r="Z41" s="12" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" ht="36">
+      <c r="A42" s="12" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="J42">
+        <v>60</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L42" s="34" t="s">
+        <v>646</v>
+      </c>
+      <c r="M42" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="N42" s="13" t="s">
+        <v>846</v>
+      </c>
+      <c r="O42" s="12" t="s">
+        <v>1214</v>
+      </c>
+      <c r="P42" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Q42" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R42" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="S42" s="12"/>
+      <c r="T42" s="12" t="s">
+        <v>1198</v>
+      </c>
+      <c r="U42" s="12" t="s">
+        <v>1215</v>
+      </c>
+      <c r="V42" s="12" t="s">
+        <v>1216</v>
+      </c>
+      <c r="W42" s="12" t="s">
+        <v>1225</v>
+      </c>
+      <c r="X42" s="12" t="s">
+        <v>1218</v>
+      </c>
+      <c r="Y42" s="12" t="s">
+        <v>1219</v>
+      </c>
+      <c r="Z42" s="12" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" ht="54">
+      <c r="A43" s="41" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E43" s="41" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F43" s="41" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G43" s="41" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H43" s="42" t="s">
+        <v>1235</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" s="41" t="s">
+        <v>1239</v>
+      </c>
+      <c r="L43" s="43" t="s">
+        <v>1235</v>
+      </c>
+      <c r="M43" s="41" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N43" s="44" t="s">
+        <v>1237</v>
+      </c>
+      <c r="O43" s="41" t="s">
+        <v>1235</v>
+      </c>
+      <c r="P43" s="41" t="s">
+        <v>1238</v>
+      </c>
+      <c r="Q43" s="41" t="s">
+        <v>1240</v>
+      </c>
+      <c r="R43" s="41" t="s">
+        <v>1235</v>
+      </c>
+      <c r="T43" s="41" t="s">
+        <v>1232</v>
+      </c>
+      <c r="U43" s="41" t="s">
+        <v>1242</v>
+      </c>
+      <c r="V43" s="41" t="s">
+        <v>1241</v>
+      </c>
+      <c r="W43" s="41" t="s">
+        <v>1243</v>
+      </c>
+      <c r="X43" s="41" t="s">
+        <v>1244</v>
+      </c>
+      <c r="Y43" s="41" t="s">
+        <v>1245</v>
+      </c>
+      <c r="Z43" s="41" t="s">
+        <v>1246</v>
+      </c>
     </row>
     <row r="49" spans="1:26" ht="72">
       <c r="A49" s="3" t="s">
@@ -11978,7 +15302,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S25" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:S42" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -12047,10 +15371,10 @@
         <v>7</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
@@ -12065,7 +15389,7 @@
         <v>244</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>12</v>
@@ -12128,7 +15452,7 @@
         <v>62</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>20</v>
@@ -12184,7 +15508,7 @@
         <v>72</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>20</v>
@@ -12240,7 +15564,7 @@
         <v>80</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>20</v>
@@ -12260,55 +15584,55 @@
     </row>
     <row r="5" spans="1:25" ht="18.600000000000001" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F5">
         <v>10</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J5" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="K5" s="13" t="s">
         <v>641</v>
       </c>
-      <c r="K5" s="13" t="s">
-        <v>640</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -12325,73 +15649,73 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F7" s="2">
         <v>10</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="T7" s="2"/>
     </row>
     <row r="8" spans="1:25" ht="54">
       <c r="A8" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F8" s="2">
         <v>8</v>
@@ -12401,267 +15725,267 @@
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F9" s="2">
         <v>13</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>683</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>682</v>
       </c>
       <c r="T9" s="2"/>
     </row>
     <row r="10" spans="1:25" ht="72">
       <c r="A10" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2">
         <v>20</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>956</v>
+        <v>938</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="36">
       <c r="A11" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="F11" s="2">
         <v>5</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2">
         <v>20</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>733</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>960</v>
+        <v>942</v>
       </c>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="3" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F12" s="2">
         <v>15</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>718</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>719</v>
@@ -12673,7 +15997,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>721</v>
@@ -12682,41 +16006,41 @@
         <v>722</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>723</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O13" s="3" t="s">
         <v>723</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>957</v>
+        <v>939</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>721</v>
@@ -12729,13 +16053,13 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>724</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F14" s="2">
         <v>10</v>
@@ -12745,34 +16069,34 @@
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>728</v>
@@ -13098,59 +16422,59 @@
         <v>191</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>484</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="36">
       <c r="A7" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>738</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4" t="s">
-        <v>717</v>
+        <v>1199</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>738</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
   </sheetData>
@@ -13187,7 +16511,7 @@
         <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>83</v>
@@ -13253,7 +16577,7 @@
         <v>13</v>
       </c>
       <c r="Z1" s="35" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>398</v>
@@ -13270,7 +16594,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2">
@@ -13319,7 +16643,7 @@
         <v>100</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>99</v>
@@ -13367,7 +16691,7 @@
         <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2">
@@ -13416,7 +16740,7 @@
         <v>100</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>99</v>
@@ -13461,7 +16785,7 @@
         <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2">
@@ -13510,7 +16834,7 @@
         <v>100</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>99</v>
@@ -13555,7 +16879,7 @@
         <v>53</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2">
@@ -13604,7 +16928,7 @@
         <v>100</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="U5" s="2" t="s">
         <v>99</v>
@@ -13649,10 +16973,10 @@
         <v>111</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E6" s="2">
         <v>300</v>
@@ -13747,10 +17071,10 @@
         <v>111</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E7" s="2">
         <v>250</v>
@@ -13845,10 +17169,10 @@
         <v>118</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E8" s="2">
         <v>180</v>
@@ -13943,10 +17267,10 @@
         <v>121</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E9" s="2">
         <v>200</v>
@@ -14041,10 +17365,10 @@
         <v>124</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E10" s="2">
         <v>700</v>
@@ -14136,13 +17460,13 @@
         <v>798</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E11" s="13">
         <v>400</v>
@@ -14190,7 +17514,7 @@
         <v>0.5</v>
       </c>
       <c r="T11" s="12" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="U11" s="33">
         <v>0</v>
@@ -14199,36 +17523,36 @@
         <v>0</v>
       </c>
       <c r="W11" s="13" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="X11" s="13" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="Y11" s="12" t="s">
-        <v>958</v>
+        <v>940</v>
       </c>
       <c r="Z11" s="34" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AA11" s="34" t="s">
         <v>792</v>
       </c>
       <c r="AB11" s="12" t="s">
-        <v>967</v>
+        <v>985</v>
       </c>
     </row>
-    <row r="12" spans="1:45" ht="36">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:45" ht="54">
+      <c r="A12" s="39" t="s">
+        <v>664</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>663</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>662</v>
-      </c>
       <c r="C12" s="12" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E12" s="13">
         <v>370</v>
@@ -14276,7 +17600,7 @@
         <v>0.5</v>
       </c>
       <c r="T12" s="12" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="U12" s="33">
         <v>0</v>
@@ -14285,33 +17609,33 @@
         <v>0</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="X12" s="13" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="Z12" s="11" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AA12" s="4" t="s">
         <v>793</v>
       </c>
-      <c r="AB12" t="s">
-        <v>955</v>
+      <c r="AB12" s="11" t="s">
+        <v>984</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="108">
       <c r="A13" s="39" t="s">
+        <v>709</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>708</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>707</v>
-      </c>
       <c r="C13" s="12" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E13" s="13">
         <v>480</v>
@@ -14359,7 +17683,7 @@
         <v>0.5</v>
       </c>
       <c r="T13" s="12" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="U13" s="33">
         <v>0</v>
@@ -14368,13 +17692,13 @@
         <v>0</v>
       </c>
       <c r="W13" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="Y13" s="16" t="s">
-        <v>959</v>
+        <v>941</v>
       </c>
       <c r="Z13" s="34" t="s">
         <v>729</v>
@@ -14382,8 +17706,8 @@
       <c r="AA13" s="34" t="s">
         <v>794</v>
       </c>
-      <c r="AB13" t="s">
-        <v>955</v>
+      <c r="AB13" s="11" t="s">
+        <v>1158</v>
       </c>
     </row>
   </sheetData>
@@ -14395,10 +17719,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="19.59765625" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="8" style="6" customWidth="1"/>
     <col min="4" max="4" width="14" style="8" customWidth="1"/>
@@ -14459,7 +17783,7 @@
         <v>202</v>
       </c>
       <c r="O1" s="19" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="P1" s="20" t="s">
         <v>425</v>
@@ -14572,7 +17896,7 @@
         <v>175</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>167</v>
@@ -14618,7 +17942,7 @@
         <v>176</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>167</v>
@@ -14933,7 +18257,7 @@
         <v>802</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>805</v>
@@ -14945,53 +18269,53 @@
         <v>810</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>905</v>
+        <v>986</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>907</v>
+        <v>987</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="73.8" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E15" t="s">
         <v>810</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>905</v>
+        <v>986</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>907</v>
+        <v>987</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="73.8" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>953</v>
+        <v>936</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>167</v>
@@ -15003,53 +18327,53 @@
         <v>810</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>905</v>
+        <v>986</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>907</v>
+        <v>987</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="73.8" customHeight="1">
+    <row r="17" spans="1:12" ht="73.8" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E17" t="s">
         <v>810</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>905</v>
+        <v>986</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>907</v>
+        <v>987</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="73.8" customHeight="1">
+    <row r="18" spans="1:12" ht="73.8" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>803</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>167</v>
@@ -15061,53 +18385,53 @@
         <v>810</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>906</v>
+        <v>988</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>908</v>
+        <v>989</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="73.8" customHeight="1">
+    <row r="19" spans="1:12" ht="73.8" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E19" t="s">
         <v>810</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>906</v>
+        <v>988</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>908</v>
+        <v>989</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="73.8" customHeight="1">
+    <row r="20" spans="1:12" ht="73.8" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>804</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>167</v>
@@ -15119,17 +18443,380 @@
         <v>810</v>
       </c>
       <c r="F20" s="11" t="s">
+        <v>986</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>905</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>904</v>
-      </c>
       <c r="I20" s="12" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>908</v>
-      </c>
+        <v>989</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="36">
+      <c r="A21" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>1185</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="54">
+      <c r="A22" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>1186</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="36">
+      <c r="A23" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>1187</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="36">
+      <c r="A24" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>1188</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="36">
+      <c r="A25" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>1189</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="36">
+      <c r="A26" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>1190</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="36">
+      <c r="A27" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>1191</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="54">
+      <c r="A28" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>1193</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>1221</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="54">
+      <c r="A29" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>1180</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>1194</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>1221</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="54">
+      <c r="A30" s="4" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>1195</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="72">
+      <c r="A31" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>1183</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>1196</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>1221</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="72">
+      <c r="A32" s="4" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>1197</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -15141,7 +18828,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74530E38-EDB4-4883-BA3E-6C72C076C507}">
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="26.3984375" customWidth="1"/>
@@ -15197,7 +18884,7 @@
         <v>202</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N1" s="20" t="s">
         <v>425</v>
@@ -15229,10 +18916,10 @@
         <v>569</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>536</v>
+        <v>215</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>582</v>
@@ -15276,10 +18963,10 @@
         <v>569</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>536</v>
+        <v>215</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>582</v>
@@ -15314,10 +19001,10 @@
         <v>569</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>536</v>
+        <v>215</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>582</v>
@@ -15352,10 +19039,10 @@
         <v>569</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>536</v>
+        <v>215</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>582</v>
@@ -15390,10 +19077,10 @@
         <v>569</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>536</v>
+        <v>215</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>582</v>
@@ -15431,7 +19118,7 @@
         <v>605</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>536</v>
+        <v>215</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>582</v>
@@ -15448,185 +19135,185 @@
     </row>
     <row r="8" spans="1:18" ht="36">
       <c r="A8" s="4" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>934</v>
+        <v>990</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>946</v>
+        <v>935</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>942</v>
+        <v>991</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>947</v>
+        <v>1014</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>947</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>920</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>923</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>935</v>
+        <v>992</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>943</v>
+        <v>993</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>948</v>
+        <v>1015</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>948</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="36">
       <c r="A10" s="4" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="F10" s="11" t="s">
+        <v>990</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>934</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>945</v>
-      </c>
       <c r="H10" s="4" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>942</v>
+        <v>991</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>950</v>
+        <v>1016</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>950</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="36">
       <c r="A11" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>994</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>932</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>909</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>941</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>939</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>944</v>
+        <v>995</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>951</v>
+        <v>1017</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>951</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="36">
       <c r="A12" s="4" t="s">
-        <v>954</v>
+        <v>937</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>936</v>
+        <v>1005</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>944</v>
+        <v>995</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>949</v>
+        <v>997</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>949</v>
+        <v>997</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="4" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>167</v>
@@ -15635,30 +19322,30 @@
         <v>567</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>937</v>
+        <v>996</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>952</v>
+        <v>1018</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>952</v>
+        <v>1018</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" ht="36">
       <c r="A14" s="4" t="s">
-        <v>988</v>
+        <v>965</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>982</v>
+        <v>958</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>167</v>
@@ -15666,13 +19353,34 @@
       <c r="D14" s="4" t="s">
         <v>562</v>
       </c>
+      <c r="E14" t="s">
+        <v>964</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>1012</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>1019</v>
+      </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" ht="36">
       <c r="A15" s="4" t="s">
-        <v>989</v>
+        <v>966</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>983</v>
+        <v>959</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>167</v>
@@ -15680,13 +19388,34 @@
       <c r="D15" s="4" t="s">
         <v>564</v>
       </c>
+      <c r="E15" t="s">
+        <v>964</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>1020</v>
+      </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" ht="36">
       <c r="A16" s="4" t="s">
-        <v>990</v>
+        <v>967</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>984</v>
+        <v>960</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>167</v>
@@ -15694,13 +19423,34 @@
       <c r="D16" s="4" t="s">
         <v>563</v>
       </c>
+      <c r="E16" t="s">
+        <v>964</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>1021</v>
+      </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:12" ht="36">
       <c r="A17" s="4" t="s">
-        <v>991</v>
+        <v>968</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>985</v>
+        <v>961</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>167</v>
@@ -15708,13 +19458,34 @@
       <c r="D17" s="4" t="s">
         <v>565</v>
       </c>
+      <c r="E17" t="s">
+        <v>964</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>1022</v>
+      </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:12" ht="36">
       <c r="A18" s="4" t="s">
-        <v>992</v>
+        <v>969</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>986</v>
+        <v>962</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>167</v>
@@ -15722,19 +19493,266 @@
       <c r="D18" s="4" t="s">
         <v>566</v>
       </c>
+      <c r="E18" t="s">
+        <v>964</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>1023</v>
+      </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:12">
       <c r="A19" s="4" t="s">
-        <v>993</v>
+        <v>970</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>987</v>
+        <v>963</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>567</v>
+      </c>
+      <c r="E19" t="s">
+        <v>964</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="36">
+      <c r="A20" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>1140</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>1139</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="36">
+      <c r="A23" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>1227</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>1228</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>1138</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I25" s="11"/>
+      <c r="K25" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>1146</v>
       </c>
     </row>
   </sheetData>
@@ -15746,107 +19764,178 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{679D6C04-1546-44B7-B4BC-9388FD23F265}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.69921875" customWidth="1"/>
     <col min="2" max="2" width="20.69921875" customWidth="1"/>
     <col min="3" max="3" width="25.8984375" customWidth="1"/>
     <col min="4" max="4" width="26.3984375" customWidth="1"/>
-    <col min="5" max="5" width="38.19921875" customWidth="1"/>
-    <col min="6" max="6" width="48.3984375" customWidth="1"/>
-    <col min="7" max="7" width="59.09765625" customWidth="1"/>
-    <col min="8" max="8" width="47.5" customWidth="1"/>
-    <col min="9" max="9" width="57.3984375" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="51.5" customWidth="1"/>
+    <col min="7" max="7" width="38.19921875" customWidth="1"/>
+    <col min="8" max="8" width="48.3984375" customWidth="1"/>
+    <col min="9" max="9" width="59.09765625" customWidth="1"/>
+    <col min="10" max="10" width="47.5" customWidth="1"/>
+    <col min="11" max="11" width="57.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.05" customHeight="1">
+    <row r="1" spans="1:11" ht="22.05" customHeight="1">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>814</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>815</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="F1" s="21" t="s">
         <v>414</v>
       </c>
-      <c r="C1" s="35" t="s">
-        <v>813</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>814</v>
-      </c>
-      <c r="E1" s="21" t="s">
+      <c r="G1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="H1" s="22" t="s">
         <v>577</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="I1" s="22" t="s">
         <v>576</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="J1" s="22" t="s">
         <v>578</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="K1" s="22" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2" s="4" t="s">
         <v>568</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>532</v>
       </c>
+      <c r="E2" s="4" t="s">
+        <v>606</v>
+      </c>
       <c r="F2" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="J2" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>608</v>
-      </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>811</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>812</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>817</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>818</v>
       </c>
       <c r="I3" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>819</v>
       </c>
+      <c r="K3" s="4" t="s">
+        <v>820</v>
+      </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
-        <v>994</v>
+        <v>971</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>995</v>
+        <v>972</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>997</v>
+        <v>974</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>996</v>
+        <v>973</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>1108</v>
       </c>
     </row>
   </sheetData>
@@ -15858,7 +19947,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD2C904-A80C-4DD6-9EC2-BF8829F6BFCA}">
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.69921875" customWidth="1"/>
@@ -15886,7 +19975,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D1" s="17" t="s">
         <v>415</v>
@@ -15931,10 +20020,10 @@
         <v>13</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -16387,7 +20476,7 @@
         <v>783</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>968</v>
+        <v>947</v>
       </c>
       <c r="O15">
         <v>70</v>
@@ -16401,98 +20490,185 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="4" t="s">
-        <v>965</v>
+        <v>945</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>961</v>
+        <v>943</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>963</v>
+        <v>944</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>966</v>
+        <v>946</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>191</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>968</v>
+        <v>947</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>968</v>
+        <v>947</v>
       </c>
       <c r="O16">
         <v>50</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>971</v>
+        <v>950</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>971</v>
+        <v>950</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="4" t="s">
-        <v>970</v>
+        <v>949</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>969</v>
+        <v>948</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>963</v>
+        <v>944</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>966</v>
+        <v>946</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>191</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>968</v>
+        <v>947</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>968</v>
+        <v>947</v>
       </c>
       <c r="O17">
         <v>70</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>981</v>
+        <v>957</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>981</v>
+        <v>957</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="4" t="s">
-        <v>964</v>
+        <v>981</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>962</v>
+        <v>982</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>963</v>
+        <v>944</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>966</v>
+        <v>946</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>191</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>968</v>
+        <v>947</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>968</v>
+        <v>947</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>972</v>
+        <v>983</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="O19">
+        <v>60</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="O20">
+        <v>80</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="O21">
+        <v>110</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -16513,8 +20689,8 @@
     <col min="6" max="6" width="33" customWidth="1"/>
     <col min="9" max="9" width="27.3984375" customWidth="1"/>
     <col min="11" max="11" width="8.796875" style="27"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="12.296875" customWidth="1"/>
+    <col min="16" max="16" width="18.5" customWidth="1"/>
+    <col min="17" max="17" width="20.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -16542,8 +20718,12 @@
       <c r="M2" s="23" t="s">
         <v>441</v>
       </c>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
+      <c r="P2" s="23" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Q2" s="23" t="s">
+        <v>1148</v>
+      </c>
     </row>
     <row r="3" spans="2:17">
       <c r="B3" s="23" t="s">
@@ -16570,8 +20750,12 @@
       <c r="M3" s="24">
         <v>1</v>
       </c>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="4"/>
+      <c r="P3" s="40" t="s">
+        <v>525</v>
+      </c>
+      <c r="Q3" s="23" t="s">
+        <v>1151</v>
+      </c>
     </row>
     <row r="4" spans="2:17">
       <c r="B4" s="23" t="s">
@@ -16598,8 +20782,12 @@
       <c r="M4" s="24">
         <v>2</v>
       </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="4"/>
+      <c r="P4" s="40" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q4" s="23" t="s">
+        <v>1152</v>
+      </c>
     </row>
     <row r="5" spans="2:17">
       <c r="B5" s="23" t="s">
@@ -16626,7 +20814,12 @@
       <c r="M5" s="24">
         <v>3</v>
       </c>
-      <c r="P5" s="7"/>
+      <c r="P5" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q5" s="23" t="s">
+        <v>1157</v>
+      </c>
     </row>
     <row r="6" spans="2:17">
       <c r="B6" s="23" t="s">
@@ -16653,7 +20846,12 @@
       <c r="M6" s="24">
         <v>4</v>
       </c>
-      <c r="P6" s="7"/>
+      <c r="P6" s="40" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q6" s="23" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="7" spans="2:17">
       <c r="B7" s="23" t="s">
@@ -16680,7 +20878,12 @@
       <c r="M7" s="24">
         <v>5</v>
       </c>
-      <c r="P7" s="7"/>
+      <c r="P7" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q7" s="23" t="s">
+        <v>1154</v>
+      </c>
     </row>
     <row r="8" spans="2:17">
       <c r="B8" s="23" t="s">
@@ -16695,7 +20898,12 @@
       <c r="J8" s="28" t="s">
         <v>463</v>
       </c>
-      <c r="P8" s="7"/>
+      <c r="P8" s="40" t="s">
+        <v>1149</v>
+      </c>
+      <c r="Q8" s="23" t="s">
+        <v>1153</v>
+      </c>
     </row>
     <row r="9" spans="2:17">
       <c r="I9" s="23" t="s">
@@ -16704,7 +20912,12 @@
       <c r="J9" s="28" t="s">
         <v>460</v>
       </c>
-      <c r="P9" s="7"/>
+      <c r="P9" s="40" t="s">
+        <v>1150</v>
+      </c>
+      <c r="Q9" s="23" t="s">
+        <v>1156</v>
+      </c>
     </row>
     <row r="10" spans="2:17">
       <c r="I10" s="23" t="s">

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130ECE1D-C600-40AC-8B24-76FAC1D52377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99ADC95D-5A8F-496C-B5D9-CBAEAF070D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="1292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="1321">
   <si>
     <t>ID</t>
   </si>
@@ -6651,13 +6651,6 @@
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ドット魔法</t>
-    <rPh sb="3" eb="5">
-      <t>マホウ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -12170,6 +12163,285 @@
     </rPh>
     <rPh sb="23" eb="25">
       <t>チュウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ツル鞭</t>
+    <rPh sb="2" eb="3">
+      <t>ムチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>vine_whip</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単体攻撃</t>
+    <rPh sb="0" eb="4">
+      <t>タンタイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.3</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象指定</t>
+    <rPh sb="0" eb="4">
+      <t>タイショウシテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>150px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>物理</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ツル鞭</t>
+    <rPh sb="2" eb="3">
+      <t>ムチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>毒針</t>
+    <rPh sb="0" eb="2">
+      <t>ドクバリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>poisonous_stinger</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>130px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>30秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:debuff_poison)</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>毒針</t>
+    <rPh sb="0" eb="2">
+      <t>ドクハリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.1</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>吸収</t>
+    <rPh sb="0" eb="2">
+      <t>キュウシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>absorption of Reunion</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>120px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>4秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スキル効果時間中、対象と自身を行動不可(行動CDすら上がらない)にさせ、毎秒ダメージを与える
+与えたダメージ分発動者のHPを回復させる</t>
+    <rPh sb="3" eb="8">
+      <t>コウカジカンチュウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>コウドウフカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="55" eb="58">
+      <t>ハツドウシャ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.1 + 魔力 * 0.1</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法ドット</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>不変ドット</t>
+    <rPh sb="0" eb="2">
+      <t>フヘン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>再会</t>
+    <rPh sb="0" eb="2">
+      <t>サイカイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>reunion</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この状態が付与されている間に付与してきた相手にドット以外のダメージを与えた場合
+付与してきた相手の次の行動が(敵スキル:absorption of Reunion)に強制される
+相手の(敵スキル:absorption of Reunion)のターゲットは必ず自分になる</t>
+    <rPh sb="2" eb="4">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>キョウセイ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="127" eb="128">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="129" eb="131">
+      <t>ジブン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -12945,7 +13217,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>19</v>
@@ -12954,10 +13226,10 @@
         <v>313</v>
       </c>
       <c r="N2" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>877</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>878</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>292</v>
@@ -13034,7 +13306,7 @@
         <v>25</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>26</v>
@@ -13114,7 +13386,7 @@
         <v>318</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>214</v>
@@ -13263,7 +13535,7 @@
         <v>20</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>20</v>
@@ -13272,10 +13544,10 @@
         <v>25</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>41</v>
@@ -13352,10 +13624,10 @@
         <v>258</v>
       </c>
       <c r="N7" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>882</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>883</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>292</v>
@@ -13501,7 +13773,7 @@
         <v>20</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>214</v>
@@ -13590,7 +13862,7 @@
         <v>247</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>248</v>
@@ -13670,10 +13942,10 @@
         <v>48</v>
       </c>
       <c r="N11" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>884</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>885</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>41</v>
@@ -13739,7 +14011,7 @@
         <v>20</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>19</v>
@@ -13751,7 +14023,7 @@
         <v>217</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>233</v>
@@ -13773,7 +14045,7 @@
         <v>302</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="X12" s="12" t="s">
         <v>367</v>
@@ -13909,7 +14181,7 @@
         <v>20</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>233</v>
@@ -14149,7 +14421,7 @@
         <v>214</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>27</v>
@@ -14229,7 +14501,7 @@
         <v>214</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>27</v>
@@ -14439,7 +14711,7 @@
         <v>20</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>20</v>
@@ -14575,7 +14847,7 @@
         <v>492</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="O23" s="13" t="s">
         <v>490</v>
@@ -14596,16 +14868,16 @@
         <v>489</v>
       </c>
       <c r="U23" s="12" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="V23" s="12" t="s">
         <v>494</v>
       </c>
       <c r="W23" s="12" t="s">
+        <v>732</v>
+      </c>
+      <c r="X23" s="12" t="s">
         <v>733</v>
-      </c>
-      <c r="X23" s="12" t="s">
-        <v>734</v>
       </c>
       <c r="Y23" s="12" t="s">
         <v>384</v>
@@ -14616,415 +14888,415 @@
     </row>
     <row r="24" spans="1:26" ht="36">
       <c r="A24" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>821</v>
       </c>
-      <c r="E24" s="13" t="s">
-        <v>822</v>
-      </c>
       <c r="F24" s="13" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G24">
         <v>13</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="O24" s="13" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="P24" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="Q24" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="R24" s="12" t="s">
         <v>847</v>
       </c>
-      <c r="Q24" s="12" t="s">
-        <v>830</v>
-      </c>
-      <c r="R24" s="12" t="s">
-        <v>848</v>
-      </c>
       <c r="T24" s="13" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="V24" s="12" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="W24" s="12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="X24" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="Y24" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z24" s="12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="36">
       <c r="A25" s="12" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G25">
         <v>10</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L25" s="16" t="s">
+        <v>835</v>
+      </c>
+      <c r="M25" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="M25" s="12" t="s">
-        <v>837</v>
-      </c>
       <c r="N25" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O25" s="13" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="P25" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="Q25" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="R25" s="12" t="s">
         <v>847</v>
       </c>
-      <c r="Q25" s="12" t="s">
-        <v>830</v>
-      </c>
-      <c r="R25" s="12" t="s">
-        <v>848</v>
-      </c>
       <c r="T25" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="V25" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="W25" s="12" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="X25" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="Y25" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z25" s="12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="36">
       <c r="A26" s="12" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G26">
         <v>14</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="O26" s="13" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="P26" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="Q26" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="R26" s="12" t="s">
         <v>847</v>
       </c>
-      <c r="Q26" s="12" t="s">
-        <v>830</v>
-      </c>
-      <c r="R26" s="12" t="s">
-        <v>848</v>
-      </c>
       <c r="T26" s="12" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="V26" s="12" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="W26" s="12" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="X26" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="Y26" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z26" s="12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="36">
       <c r="A27" s="12" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G27">
         <v>8</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="O27" s="13" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="P27" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="Q27" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="R27" s="12" t="s">
         <v>847</v>
       </c>
-      <c r="Q27" s="12" t="s">
-        <v>830</v>
-      </c>
-      <c r="R27" s="12" t="s">
-        <v>848</v>
-      </c>
       <c r="T27" s="12" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="U27" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="V27" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="W27" s="12" t="s">
         <v>870</v>
       </c>
-      <c r="V27" s="12" t="s">
-        <v>863</v>
-      </c>
-      <c r="W27" s="12" t="s">
-        <v>871</v>
-      </c>
       <c r="X27" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="Y27" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z27" s="12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="72">
       <c r="A28" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G28">
         <v>10</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="J28">
         <v>25</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="O28" s="13" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="T28" s="12" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="U28" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="V28" s="12" t="s">
         <v>864</v>
       </c>
-      <c r="V28" s="12" t="s">
-        <v>865</v>
-      </c>
       <c r="W28" s="12" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="X28" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="Y28" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z28" s="12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="36">
       <c r="A29" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>312</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G29">
         <v>10</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J29">
         <v>20</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="O29" s="13" t="s">
+        <v>845</v>
+      </c>
+      <c r="P29" s="12" t="s">
         <v>846</v>
       </c>
-      <c r="P29" s="12" t="s">
-        <v>847</v>
-      </c>
       <c r="Q29" s="12" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="R29" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="T29" s="12" t="s">
         <v>312</v>
       </c>
       <c r="V29" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="W29" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="X29" s="12" t="s">
         <v>874</v>
-      </c>
-      <c r="X29" s="12" t="s">
-        <v>875</v>
       </c>
       <c r="Y29" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z29" s="12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="36">
       <c r="A30" s="12" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>598</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H30" s="16" t="s">
         <v>214</v>
@@ -15033,51 +15305,51 @@
         <v>20</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L30" s="34" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="P30" s="12" t="s">
         <v>292</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="R30" s="12" t="s">
         <v>214</v>
       </c>
       <c r="T30" s="12" t="s">
+        <v>949</v>
+      </c>
+      <c r="V30" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="W30" s="12" t="s">
+        <v>1077</v>
+      </c>
+      <c r="X30" s="12" t="s">
         <v>950</v>
       </c>
-      <c r="V30" s="12" t="s">
-        <v>1077</v>
-      </c>
-      <c r="W30" s="12" t="s">
-        <v>1078</v>
-      </c>
-      <c r="X30" s="12" t="s">
+      <c r="Y30" s="12" t="s">
         <v>951</v>
       </c>
-      <c r="Y30" s="12" t="s">
+      <c r="Z30" s="12" t="s">
         <v>952</v>
-      </c>
-      <c r="Z30" s="12" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="36">
       <c r="A31" s="12" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>163</v>
@@ -15086,7 +15358,7 @@
         <v>166</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>597</v>
@@ -15095,10 +15367,10 @@
         <v>13</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>324</v>
@@ -15119,31 +15391,31 @@
         <v>244</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="T31" s="13" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="U31" s="12"/>
       <c r="V31" s="12" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="W31" s="12" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="X31" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="Y31" s="12" t="s">
         <v>1081</v>
       </c>
-      <c r="Y31" s="12" t="s">
+      <c r="Z31" s="12" t="s">
         <v>1082</v>
-      </c>
-      <c r="Z31" s="12" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="54">
       <c r="A32" s="12" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>163</v>
@@ -15152,7 +15424,7 @@
         <v>166</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>657</v>
@@ -15161,10 +15433,10 @@
         <v>10</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>688</v>
@@ -15188,30 +15460,30 @@
         <v>244</v>
       </c>
       <c r="S32" s="12" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="T32" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="V32" s="12" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="W32" s="12" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="X32" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="Y32" s="12" t="s">
         <v>1081</v>
       </c>
-      <c r="Y32" s="12" t="s">
+      <c r="Z32" s="12" t="s">
         <v>1082</v>
-      </c>
-      <c r="Z32" s="12" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="36">
       <c r="A33" s="12" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>163</v>
@@ -15220,7 +15492,7 @@
         <v>166</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>597</v>
@@ -15229,16 +15501,16 @@
         <v>14</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>324</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="O33" s="13" t="s">
         <v>214</v>
@@ -15253,30 +15525,30 @@
         <v>244</v>
       </c>
       <c r="S33" s="12" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="T33" s="12" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="V33" s="12" t="s">
+        <v>1062</v>
+      </c>
+      <c r="W33" s="12" t="s">
         <v>1063</v>
       </c>
-      <c r="W33" s="12" t="s">
-        <v>1064</v>
-      </c>
       <c r="X33" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="Y33" s="12" t="s">
         <v>1081</v>
       </c>
-      <c r="Y33" s="12" t="s">
+      <c r="Z33" s="12" t="s">
         <v>1082</v>
-      </c>
-      <c r="Z33" s="12" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="108">
       <c r="A34" s="12" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>163</v>
@@ -15285,7 +15557,7 @@
         <v>166</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>597</v>
@@ -15294,16 +15566,16 @@
         <v>8</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="M34" s="12" t="s">
         <v>324</v>
       </c>
       <c r="N34" s="13" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="O34" s="13" t="s">
         <v>214</v>
@@ -15318,33 +15590,33 @@
         <v>244</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="T34" s="12" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="V34" s="12" t="s">
+        <v>1064</v>
+      </c>
+      <c r="W34" s="12" t="s">
         <v>1065</v>
       </c>
-      <c r="W34" s="12" t="s">
-        <v>1066</v>
-      </c>
       <c r="X34" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="Y34" s="12" t="s">
         <v>1081</v>
       </c>
-      <c r="Y34" s="12" t="s">
+      <c r="Z34" s="12" t="s">
         <v>1082</v>
-      </c>
-      <c r="Z34" s="12" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="90">
       <c r="A35" s="12" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>163</v>
@@ -15353,22 +15625,22 @@
         <v>166</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G35">
         <v>10</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="J35">
         <v>25</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>246</v>
@@ -15377,7 +15649,7 @@
         <v>271</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="O35" s="13" t="s">
         <v>664</v>
@@ -15392,33 +15664,33 @@
         <v>243</v>
       </c>
       <c r="S35" s="12" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="T35" s="12" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="V35" s="12" t="s">
+        <v>1067</v>
+      </c>
+      <c r="W35" s="12" t="s">
         <v>1068</v>
       </c>
-      <c r="W35" s="12" t="s">
-        <v>1069</v>
-      </c>
       <c r="X35" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="Y35" s="12" t="s">
         <v>1081</v>
       </c>
-      <c r="Y35" s="12" t="s">
+      <c r="Z35" s="12" t="s">
         <v>1082</v>
-      </c>
-      <c r="Z35" s="12" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="54">
       <c r="A36" s="12" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>163</v>
@@ -15436,13 +15708,13 @@
         <v>10</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="J36">
         <v>20</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>246</v>
@@ -15451,10 +15723,10 @@
         <v>689</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="O36" s="13" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="P36" s="12" t="s">
         <v>292</v>
@@ -15466,30 +15738,30 @@
         <v>243</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="T36" s="12" t="s">
         <v>312</v>
       </c>
       <c r="V36" s="12" t="s">
+        <v>1070</v>
+      </c>
+      <c r="W36" s="12" t="s">
         <v>1071</v>
       </c>
-      <c r="W36" s="12" t="s">
-        <v>1072</v>
-      </c>
       <c r="X36" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="Y36" s="12" t="s">
         <v>1081</v>
       </c>
-      <c r="Y36" s="12" t="s">
+      <c r="Z36" s="12" t="s">
         <v>1082</v>
-      </c>
-      <c r="Z36" s="12" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="36">
       <c r="A37" s="12" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>163</v>
@@ -15498,10 +15770,10 @@
         <v>166</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>214</v>
@@ -15513,22 +15785,22 @@
         <v>25</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L37" s="34" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="M37" s="12" t="s">
         <v>689</v>
       </c>
       <c r="N37" s="13" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="O37" s="12" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="P37" s="12" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="Q37" s="12" t="s">
         <v>214</v>
@@ -15537,33 +15809,33 @@
         <v>214</v>
       </c>
       <c r="S37" s="12" t="s">
+        <v>1074</v>
+      </c>
+      <c r="T37" s="12" t="s">
+        <v>1056</v>
+      </c>
+      <c r="U37" s="12" t="s">
         <v>1075</v>
       </c>
-      <c r="T37" s="12" t="s">
-        <v>1057</v>
-      </c>
-      <c r="U37" s="12" t="s">
-        <v>1076</v>
-      </c>
       <c r="V37" s="12" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="W37" s="12" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="X37" s="12" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Y37" s="12" t="s">
         <v>1084</v>
       </c>
-      <c r="Y37" s="12" t="s">
+      <c r="Z37" s="12" t="s">
         <v>1085</v>
-      </c>
-      <c r="Z37" s="12" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="36">
       <c r="A38" s="12" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>163</v>
@@ -15572,7 +15844,7 @@
         <v>166</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F38" s="13" t="s">
         <v>597</v>
@@ -15581,10 +15853,10 @@
         <v>13</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="M38" s="13" t="s">
         <v>324</v>
@@ -15605,31 +15877,31 @@
         <v>244</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="T38" s="13" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="U38" s="12"/>
       <c r="V38" s="12" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="W38" s="12" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="X38" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="Y38" s="12" t="s">
         <v>1209</v>
       </c>
-      <c r="Y38" s="12" t="s">
+      <c r="Z38" s="12" t="s">
         <v>1210</v>
-      </c>
-      <c r="Z38" s="12" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="36">
       <c r="A39" s="12" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>163</v>
@@ -15638,7 +15910,7 @@
         <v>166</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>657</v>
@@ -15647,10 +15919,10 @@
         <v>10</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L39" s="16" t="s">
         <v>688</v>
@@ -15674,31 +15946,31 @@
         <v>244</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="T39" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="U39" s="12"/>
       <c r="V39" s="12" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="W39" s="12" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="X39" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="Y39" s="12" t="s">
         <v>1209</v>
       </c>
-      <c r="Y39" s="12" t="s">
+      <c r="Z39" s="12" t="s">
         <v>1210</v>
-      </c>
-      <c r="Z39" s="12" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="36">
       <c r="A40" s="12" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>163</v>
@@ -15707,7 +15979,7 @@
         <v>166</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>597</v>
@@ -15716,16 +15988,16 @@
         <v>14</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="M40" s="12" t="s">
         <v>324</v>
       </c>
       <c r="N40" s="13" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="O40" s="13" t="s">
         <v>214</v>
@@ -15740,31 +16012,31 @@
         <v>244</v>
       </c>
       <c r="S40" s="12" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="T40" s="12" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="U40" s="12"/>
       <c r="V40" s="12" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="W40" s="12" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="X40" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="Y40" s="12" t="s">
         <v>1209</v>
       </c>
-      <c r="Y40" s="12" t="s">
+      <c r="Z40" s="12" t="s">
         <v>1210</v>
-      </c>
-      <c r="Z40" s="12" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="41" spans="1:26" ht="36">
       <c r="A41" s="12" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>163</v>
@@ -15773,7 +16045,7 @@
         <v>166</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>597</v>
@@ -15782,16 +16054,16 @@
         <v>8</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="M41" s="12" t="s">
         <v>324</v>
       </c>
       <c r="N41" s="13" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="O41" s="13" t="s">
         <v>214</v>
@@ -15806,33 +16078,33 @@
         <v>244</v>
       </c>
       <c r="S41" s="12" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="T41" s="12" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="U41" s="12" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="V41" s="12" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="W41" s="12" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="X41" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="Y41" s="12" t="s">
         <v>1209</v>
       </c>
-      <c r="Y41" s="12" t="s">
+      <c r="Z41" s="12" t="s">
         <v>1210</v>
-      </c>
-      <c r="Z41" s="12" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="36">
       <c r="A42" s="12" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>163</v>
@@ -15841,10 +16113,10 @@
         <v>166</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>214</v>
@@ -15856,7 +16128,7 @@
         <v>60</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L42" s="34" t="s">
         <v>644</v>
@@ -15865,13 +16137,13 @@
         <v>689</v>
       </c>
       <c r="N42" s="13" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="O42" s="12" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="P42" s="12" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="Q42" s="12" t="s">
         <v>214</v>
@@ -15881,147 +16153,147 @@
       </c>
       <c r="S42" s="12"/>
       <c r="T42" s="12" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="U42" s="12" t="s">
+        <v>1212</v>
+      </c>
+      <c r="V42" s="12" t="s">
         <v>1213</v>
       </c>
-      <c r="V42" s="12" t="s">
-        <v>1214</v>
-      </c>
       <c r="W42" s="12" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="X42" s="12" t="s">
+        <v>1215</v>
+      </c>
+      <c r="Y42" s="12" t="s">
         <v>1216</v>
       </c>
-      <c r="Y42" s="12" t="s">
+      <c r="Z42" s="12" t="s">
         <v>1217</v>
-      </c>
-      <c r="Z42" s="12" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="43" spans="1:26" ht="54">
       <c r="A43" s="12" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>391</v>
       </c>
       <c r="C43" s="12" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>1228</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="E43" s="12" t="s">
         <v>1229</v>
       </c>
-      <c r="E43" s="12" t="s">
-        <v>1230</v>
-      </c>
       <c r="F43" s="12" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G43" s="12" t="s">
         <v>1232</v>
       </c>
-      <c r="G43" s="12" t="s">
-        <v>1233</v>
-      </c>
       <c r="H43" s="16" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="L43" s="34" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>1233</v>
+      </c>
+      <c r="N43" s="13" t="s">
+        <v>1234</v>
+      </c>
+      <c r="O43" s="12" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P43" s="12" t="s">
+        <v>1235</v>
+      </c>
+      <c r="Q43" s="12" t="s">
         <v>1237</v>
       </c>
-      <c r="L43" s="34" t="s">
-        <v>1233</v>
-      </c>
-      <c r="M43" s="12" t="s">
-        <v>1234</v>
-      </c>
-      <c r="N43" s="13" t="s">
-        <v>1235</v>
-      </c>
-      <c r="O43" s="12" t="s">
-        <v>1233</v>
-      </c>
-      <c r="P43" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="Q43" s="12" t="s">
+      <c r="R43" s="12" t="s">
+        <v>1232</v>
+      </c>
+      <c r="T43" s="12" t="s">
+        <v>1229</v>
+      </c>
+      <c r="U43" s="12" t="s">
+        <v>1239</v>
+      </c>
+      <c r="V43" s="12" t="s">
         <v>1238</v>
       </c>
-      <c r="R43" s="12" t="s">
-        <v>1233</v>
-      </c>
-      <c r="T43" s="12" t="s">
-        <v>1230</v>
-      </c>
-      <c r="U43" s="12" t="s">
+      <c r="W43" s="12" t="s">
         <v>1240</v>
       </c>
-      <c r="V43" s="12" t="s">
-        <v>1239</v>
-      </c>
-      <c r="W43" s="12" t="s">
+      <c r="X43" s="12" t="s">
         <v>1241</v>
       </c>
-      <c r="X43" s="12" t="s">
+      <c r="Y43" s="12" t="s">
         <v>1242</v>
       </c>
-      <c r="Y43" s="12" t="s">
+      <c r="Z43" s="12" t="s">
         <v>1243</v>
-      </c>
-      <c r="Z43" s="12" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="48" spans="1:26" ht="72">
       <c r="A48" s="4" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C48" s="4"/>
       <c r="E48" s="4" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48" s="4" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L48" s="4" t="s">
         <v>1273</v>
       </c>
-      <c r="L48" s="4" t="s">
+      <c r="M48" s="4" t="s">
         <v>1274</v>
       </c>
-      <c r="M48" s="4" t="s">
+      <c r="N48" s="4" t="s">
+        <v>1272</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>1272</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="Q48" s="4" t="s">
+        <v>1272</v>
+      </c>
+      <c r="R48" s="4" t="s">
         <v>1275</v>
       </c>
-      <c r="N48" s="4" t="s">
-        <v>1273</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>1273</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>1275</v>
-      </c>
-      <c r="Q48" s="4" t="s">
-        <v>1273</v>
-      </c>
-      <c r="R48" s="4" t="s">
+      <c r="T48" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="U48" s="11" t="s">
         <v>1276</v>
-      </c>
-      <c r="T48" s="4" t="s">
-        <v>1271</v>
-      </c>
-      <c r="U48" s="11" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="49" spans="1:26" ht="72">
@@ -16675,7 +16947,7 @@
         <v>685</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="36">
@@ -16724,7 +16996,7 @@
         <v>644</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>731</v>
+        <v>1316</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>639</v>
@@ -16733,7 +17005,7 @@
         <v>704</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -16843,7 +17115,7 @@
         <v>639</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>719</v>
@@ -16905,6 +17177,159 @@
         <v>726</v>
       </c>
       <c r="T14" s="2"/>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" s="43" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F15" s="44">
+        <v>15</v>
+      </c>
+      <c r="G15" s="43" t="s">
+        <v>1294</v>
+      </c>
+      <c r="I15" s="45" t="s">
+        <v>1288</v>
+      </c>
+      <c r="J15" s="43" t="s">
+        <v>1295</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>1288</v>
+      </c>
+      <c r="L15" s="43" t="s">
+        <v>1296</v>
+      </c>
+      <c r="M15" s="43" t="s">
+        <v>1297</v>
+      </c>
+      <c r="N15" s="43" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O15" s="43" t="s">
+        <v>1298</v>
+      </c>
+      <c r="P15" s="43" t="s">
+        <v>1288</v>
+      </c>
+      <c r="Q15" s="43" t="s">
+        <v>1299</v>
+      </c>
+      <c r="R15" s="43" t="s">
+        <v>1288</v>
+      </c>
+      <c r="S15" s="43" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="36">
+      <c r="A16" s="43" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F16" s="44">
+        <v>5</v>
+      </c>
+      <c r="G16" s="43" t="s">
+        <v>1307</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>1288</v>
+      </c>
+      <c r="J16" s="43" t="s">
+        <v>1304</v>
+      </c>
+      <c r="K16" s="43" t="s">
+        <v>1288</v>
+      </c>
+      <c r="L16" s="43" t="s">
+        <v>1296</v>
+      </c>
+      <c r="M16" s="43" t="s">
+        <v>1303</v>
+      </c>
+      <c r="N16" s="43" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O16" s="43" t="s">
+        <v>1298</v>
+      </c>
+      <c r="Q16" s="43" t="s">
+        <v>1299</v>
+      </c>
+      <c r="R16" s="43" t="s">
+        <v>1305</v>
+      </c>
+      <c r="S16" s="43" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="54">
+      <c r="A17" s="43" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F17" s="44">
+        <v>5</v>
+      </c>
+      <c r="G17" s="43" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I17" s="45" t="s">
+        <v>1288</v>
+      </c>
+      <c r="J17" s="43" t="s">
+        <v>1312</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>1311</v>
+      </c>
+      <c r="L17" s="43" t="s">
+        <v>1296</v>
+      </c>
+      <c r="M17" s="43" t="s">
+        <v>1310</v>
+      </c>
+      <c r="O17" s="43" t="s">
+        <v>1298</v>
+      </c>
+      <c r="P17" s="43" t="s">
+        <v>1313</v>
+      </c>
+      <c r="Q17" s="43" t="s">
+        <v>1317</v>
+      </c>
+      <c r="S17" s="43" t="s">
+        <v>1308</v>
+      </c>
+      <c r="T17" s="43" t="s">
+        <v>1314</v>
+      </c>
     </row>
     <row r="18" spans="1:23">
       <c r="A18" s="3"/>
@@ -17084,7 +17509,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14.296875" customWidth="1"/>
@@ -17107,7 +17532,7 @@
         <v>82</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>197</v>
@@ -17245,7 +17670,7 @@
         <v>672</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>673</v>
@@ -17259,7 +17684,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>711</v>
@@ -17268,7 +17693,7 @@
         <v>712</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>713</v>
@@ -17282,79 +17707,79 @@
     </row>
     <row r="9" spans="1:7" ht="36">
       <c r="A9" s="4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>1251</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>1252</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>328</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>1259</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>1260</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="54">
       <c r="A10" s="4" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>1254</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>1255</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>328</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>1256</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>1257</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="108">
       <c r="A11" s="4" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>1246</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>1247</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>1248</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>1249</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="90">
       <c r="A12" s="4" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>289</v>
@@ -17363,59 +17788,76 @@
         <v>190</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>1267</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="G12" s="11" t="s">
         <v>1268</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="36">
       <c r="A13" s="4" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>1264</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>1265</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>1266</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>1279</v>
-      </c>
       <c r="G13" s="4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>1280</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>1281</v>
-      </c>
       <c r="C14" s="4" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E14" s="11" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>1282</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>1284</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>1283</v>
+    </row>
+    <row r="15" spans="1:7" ht="54">
+      <c r="A15" s="4" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>1320</v>
       </c>
     </row>
   </sheetData>
@@ -18398,7 +18840,7 @@
     </row>
     <row r="11" spans="1:45" ht="54">
       <c r="A11" s="12" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>615</v>
@@ -18455,7 +18897,7 @@
         <v>0.5</v>
       </c>
       <c r="T11" s="12" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="U11" s="33">
         <v>0</v>
@@ -18470,16 +18912,16 @@
         <v>629</v>
       </c>
       <c r="Y11" s="12" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="Z11" s="34" t="s">
         <v>660</v>
       </c>
       <c r="AA11" s="34" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AB11" s="12" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="54">
@@ -18559,10 +19001,10 @@
         <v>705</v>
       </c>
       <c r="AA12" s="4" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AB12" s="11" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="108">
@@ -18636,36 +19078,36 @@
         <v>663</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="Y13" s="16" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="Z13" s="34" t="s">
         <v>727</v>
       </c>
       <c r="AA13" s="34" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="AB13" s="11" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="36">
       <c r="A14" s="41" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B14" s="42" t="s">
         <v>1285</v>
-      </c>
-      <c r="B14" s="42" t="s">
-        <v>1286</v>
       </c>
       <c r="C14" s="43" t="s">
         <v>620</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E14" s="44">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -18710,7 +19152,7 @@
         <v>0.5</v>
       </c>
       <c r="T14" s="43" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="U14" s="33">
         <v>0</v>
@@ -18719,13 +19161,13 @@
         <v>0</v>
       </c>
       <c r="W14" s="43" t="s">
+        <v>1287</v>
+      </c>
+      <c r="X14" s="43" t="s">
         <v>1288</v>
       </c>
-      <c r="X14" s="43" t="s">
-        <v>1289</v>
-      </c>
       <c r="Y14" s="45" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
   </sheetData>
@@ -18914,7 +19356,7 @@
         <v>174</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>166</v>
@@ -18960,7 +19402,7 @@
         <v>175</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>166</v>
@@ -19272,213 +19714,213 @@
     </row>
     <row r="14" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>803</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>804</v>
-      </c>
       <c r="E14" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F14" s="11" t="s">
+        <v>983</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>849</v>
+      </c>
+      <c r="J14" s="11" t="s">
         <v>984</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>898</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>850</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="73.8" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E15" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F15" s="11" t="s">
+        <v>983</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>850</v>
+      </c>
+      <c r="J15" s="11" t="s">
         <v>984</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>899</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>851</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="73.8" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E16" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F16" s="11" t="s">
+        <v>983</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>904</v>
+      </c>
+      <c r="J16" s="11" t="s">
         <v>984</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>898</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>905</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="73.8" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E17" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F17" s="11" t="s">
+        <v>983</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="J17" s="11" t="s">
         <v>984</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>901</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>852</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="73.8" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E18" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F18" s="11" t="s">
+        <v>985</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>852</v>
+      </c>
+      <c r="J18" s="11" t="s">
         <v>986</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>902</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="73.8" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E19" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F19" s="11" t="s">
+        <v>985</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="J19" s="11" t="s">
         <v>986</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>902</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>854</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="73.8" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="E20" t="s">
         <v>807</v>
       </c>
-      <c r="E20" t="s">
-        <v>808</v>
-      </c>
       <c r="F20" s="11" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="36">
       <c r="A21" s="4" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>166</v>
@@ -19490,24 +19932,24 @@
         <v>662</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="54">
       <c r="A22" s="4" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>166</v>
@@ -19519,24 +19961,24 @@
         <v>662</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="36">
       <c r="A23" s="4" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>166</v>
@@ -19548,24 +19990,24 @@
         <v>662</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="36">
       <c r="A24" s="4" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>166</v>
@@ -19577,24 +20019,24 @@
         <v>662</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="36">
       <c r="A25" s="4" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>166</v>
@@ -19606,24 +20048,24 @@
         <v>662</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="36">
       <c r="A26" s="4" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>166</v>
@@ -19635,24 +20077,24 @@
         <v>662</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="36">
       <c r="A27" s="4" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>166</v>
@@ -19664,173 +20106,173 @@
         <v>662</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="54">
       <c r="A28" s="4" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>1168</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="54">
       <c r="A29" s="4" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="54">
       <c r="A30" s="4" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="72">
       <c r="A31" s="4" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="72">
       <c r="A32" s="4" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>1166</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>1167</v>
-      </c>
       <c r="D32" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>1172</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>1173</v>
-      </c>
       <c r="F32" s="11" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -20153,185 +20595,185 @@
     </row>
     <row r="8" spans="1:18" ht="36">
       <c r="A8" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>916</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>917</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="36">
       <c r="A10" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="36">
       <c r="A11" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="36">
       <c r="A12" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>922</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>923</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>166</v>
@@ -20340,30 +20782,30 @@
         <v>565</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>214</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="36">
       <c r="A14" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>166</v>
@@ -20372,33 +20814,33 @@
         <v>560</v>
       </c>
       <c r="E14" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="36">
       <c r="A15" s="4" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>166</v>
@@ -20407,33 +20849,33 @@
         <v>562</v>
       </c>
       <c r="E15" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="36">
       <c r="A16" s="4" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>166</v>
@@ -20442,33 +20884,33 @@
         <v>561</v>
       </c>
       <c r="E16" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F16" s="11" t="s">
+        <v>999</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>1000</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>1001</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="36">
       <c r="A17" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>166</v>
@@ -20477,33 +20919,33 @@
         <v>563</v>
       </c>
       <c r="E17" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="36">
       <c r="A18" s="4" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>166</v>
@@ -20512,33 +20954,33 @@
         <v>564</v>
       </c>
       <c r="E18" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F18" s="11" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>1005</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>1006</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>166</v>
@@ -20547,205 +20989,205 @@
         <v>565</v>
       </c>
       <c r="E19" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F19" s="11" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>1007</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>1008</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>214</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="36">
       <c r="A20" s="4" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="4" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="4" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="36">
       <c r="A23" s="4" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="4" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>1123</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>1124</v>
-      </c>
       <c r="F24" s="11" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="4" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>166</v>
@@ -20754,23 +21196,23 @@
         <v>565</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F25" s="11" t="s">
         <v>1124</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>1125</v>
-      </c>
       <c r="G25" s="4" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I25" s="11"/>
       <c r="K25" s="4" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
   </sheetData>
@@ -20806,10 +21248,10 @@
         <v>410</v>
       </c>
       <c r="C1" s="35" t="s">
+        <v>811</v>
+      </c>
+      <c r="D1" s="35" t="s">
         <v>812</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>813</v>
       </c>
       <c r="E1" s="21" t="s">
         <v>411</v>
@@ -20861,66 +21303,66 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>809</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>814</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>815</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>810</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>811</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>816</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>810</v>
-      </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>817</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>969</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>970</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>972</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>971</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>977</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>978</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>973</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>974</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>975</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -20928,32 +21370,32 @@
         <v>707</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>1099</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>1101</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>1100</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>1102</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>1103</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>1104</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>1102</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>1105</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>1106</v>
       </c>
     </row>
   </sheetData>
@@ -21029,7 +21471,7 @@
         <v>418</v>
       </c>
       <c r="O1" s="31" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="P1" s="32" t="s">
         <v>417</v>
@@ -21052,7 +21494,7 @@
         <v>498</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>500</v>
@@ -21149,75 +21591,75 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="4" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>749</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>751</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>755</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>756</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>757</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -21233,42 +21675,42 @@
         <v>15</v>
       </c>
       <c r="P9" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="R9" s="4" t="s">
         <v>758</v>
       </c>
-      <c r="R9" s="4" t="s">
-        <v>759</v>
-      </c>
       <c r="S9" s="4" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>756</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>757</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -21284,42 +21726,42 @@
         <v>40</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="F11" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>766</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>751</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>765</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>754</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>767</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>768</v>
-      </c>
       <c r="I11" s="4" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -21335,42 +21777,42 @@
         <v>150</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>751</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>765</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>754</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>771</v>
-      </c>
       <c r="H12" s="4" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -21386,74 +21828,74 @@
         <v>150</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>774</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>751</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>775</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="O13">
         <v>50</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="54">
       <c r="A14" s="4" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>780</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F14" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>782</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>784</v>
-      </c>
       <c r="I14" s="4" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -21465,228 +21907,228 @@
         <v>120</v>
       </c>
       <c r="Q14" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="R14" s="11" t="s">
         <v>787</v>
       </c>
-      <c r="R14" s="11" t="s">
+      <c r="S14" s="11" t="s">
         <v>788</v>
-      </c>
-      <c r="S14" s="11" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="4" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>779</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>780</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="O15">
         <v>70</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>943</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>941</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>942</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>944</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="O16">
         <v>50</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="O17">
         <v>70</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>979</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>980</v>
-      </c>
       <c r="C18" s="4" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="4" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>1093</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>1094</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="O19">
         <v>60</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>1092</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>1093</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>1094</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="O20">
         <v>80</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="4" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>1093</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>1094</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="O21">
         <v>110</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
   </sheetData>
@@ -21737,10 +22179,10 @@
         <v>439</v>
       </c>
       <c r="P2" s="23" t="s">
+        <v>1144</v>
+      </c>
+      <c r="Q2" s="23" t="s">
         <v>1145</v>
-      </c>
-      <c r="Q2" s="23" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="3" spans="2:17">
@@ -21772,7 +22214,7 @@
         <v>523</v>
       </c>
       <c r="Q3" s="23" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="4" spans="2:17">
@@ -21804,7 +22246,7 @@
         <v>524</v>
       </c>
       <c r="Q4" s="23" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="5" spans="2:17">
@@ -21836,7 +22278,7 @@
         <v>171</v>
       </c>
       <c r="Q5" s="23" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="6" spans="2:17">
@@ -21868,7 +22310,7 @@
         <v>526</v>
       </c>
       <c r="Q6" s="23" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="7" spans="2:17">
@@ -21900,7 +22342,7 @@
         <v>168</v>
       </c>
       <c r="Q7" s="23" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="8" spans="2:17">
@@ -21917,10 +22359,10 @@
         <v>461</v>
       </c>
       <c r="P8" s="40" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="9" spans="2:17">
@@ -21931,10 +22373,10 @@
         <v>458</v>
       </c>
       <c r="P9" s="40" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="10" spans="2:17">

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99ADC95D-5A8F-496C-B5D9-CBAEAF070D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5788A9D4-4E89-4EA4-8CCF-6542B19F280D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="1366">
   <si>
     <t>ID</t>
   </si>
@@ -11411,86 +11411,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>このスタックは特殊で表示名が「種」である。
-指定して強化されると、「発芽」「開花」「花名」の順番で名前が変化していく
-花名の枠はそのデバフを受けてるキャラによって変化する(ウルペス:ヘンルーダ)(リハス:紫のヒヤシンス)(スシア:キンセンカ)(アルジュナ:赤の彼岸花)
-この(種&gt;発芽&gt;開花&gt;花名)である
-効果はそれぞれHP再生率-(0.1/0.3/0.5/0.8)%</t>
-    <rPh sb="7" eb="9">
-      <t>トクシュ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>ヒョウジメイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>タネ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ハツガ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>カイカ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ハナメイ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ジュンバン</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ヘンカ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ハナメイ</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>ワク</t>
-    </rPh>
-    <rPh sb="70" eb="71">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="81" eb="83">
-      <t>ヘンカ</t>
-    </rPh>
-    <rPh sb="102" eb="103">
-      <t>ムラサキ</t>
-    </rPh>
-    <rPh sb="128" eb="129">
-      <t>アカ</t>
-    </rPh>
-    <rPh sb="130" eb="133">
-      <t>ヒガンバナ</t>
-    </rPh>
-    <rPh sb="138" eb="139">
-      <t>タネ</t>
-    </rPh>
-    <rPh sb="140" eb="142">
-      <t>ハツガ</t>
-    </rPh>
-    <rPh sb="143" eb="145">
-      <t>カイカ</t>
-    </rPh>
-    <rPh sb="146" eb="148">
-      <t>ハナメイ</t>
-    </rPh>
-    <rPh sb="153" eb="155">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="162" eb="165">
-      <t>サイセイリツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>生命力が吸われ、HPが徐々に減少する</t>
     <rPh sb="0" eb="3">
       <t>セイメイリョク</t>
@@ -11742,99 +11662,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>スタックがある間与ダメ率+10%,被ダメ率-10%、敵にドットダメージ以外のダメージを与えた時１スタック消費される。このスタックは新しくスタックを獲得した時継続時間を更新しない。
-効果時間が終わった時、軽蔑の全スタックを解除する。
-軽蔑が敵にダメージ与えて解除(スタックが０になった)されたとき、軽蔑がついていたユニットに悔恨(状態ID:debuff_regret)を付与する</t>
-    <rPh sb="7" eb="8">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>イガイ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ショウヒ</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>アタラ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>カクトク</t>
-    </rPh>
-    <rPh sb="77" eb="78">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="78" eb="82">
-      <t>ケイゾクジカン</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="90" eb="94">
-      <t>コウカジカン</t>
-    </rPh>
-    <rPh sb="95" eb="96">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="99" eb="100">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>ケイベツ</t>
-    </rPh>
-    <rPh sb="104" eb="105">
-      <t>ゼン</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>カイジョ</t>
-    </rPh>
-    <rPh sb="116" eb="118">
-      <t>ケイベツ</t>
-    </rPh>
-    <rPh sb="119" eb="120">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="125" eb="126">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="128" eb="130">
-      <t>カイジョ</t>
-    </rPh>
-    <rPh sb="148" eb="150">
-      <t>ケイベツ</t>
-    </rPh>
-    <rPh sb="161" eb="163">
-      <t>カイコン</t>
-    </rPh>
-    <rPh sb="164" eb="166">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="184" eb="186">
-      <t>フヨ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>スタックがある間与えるダメージが上昇し、受けるダメージが減少する。
 敵にダメージを与えた時、１スタック消費する。</t>
     <rPh sb="7" eb="8">
@@ -11863,68 +11690,6 @@
     </rPh>
     <rPh sb="51" eb="53">
       <t>ショウヒ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>スタックがある間、与ダメージ率+10%,被ダメージ率-10%される。敵にドットダメージ以外のダメージを与えた時、
-１スタック消費される。新しくスタックを得ても効果時間は延長されず、効果時間が終了した時、全スタックが解除される</t>
-    <rPh sb="7" eb="8">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>イガイ</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>ショウヒ</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>アタラ</t>
-    </rPh>
-    <rPh sb="76" eb="77">
-      <t>エ</t>
-    </rPh>
-    <rPh sb="79" eb="83">
-      <t>コウカジカン</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>エンチョウ</t>
-    </rPh>
-    <rPh sb="90" eb="94">
-      <t>コウカジカン</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>シュウリョウ</t>
-    </rPh>
-    <rPh sb="99" eb="100">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="101" eb="102">
-      <t>ゼン</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>カイジョ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -12049,10 +11814,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ひどいことをしてしまった…</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>debuff_sorrow</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -12199,6 +11960,13 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>範囲指定</t>
+    <rPh sb="0" eb="4">
+      <t>ハンイシテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>対象指定</t>
     <rPh sb="0" eb="4">
       <t>タイショウシテイ</t>
@@ -12242,6 +12010,13 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>15秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>130px</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -12306,47 +12081,6 @@
     <t>4秒</t>
     <rPh sb="1" eb="2">
       <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>スキル効果時間中、対象と自身を行動不可(行動CDすら上がらない)にさせ、毎秒ダメージを与える
-与えたダメージ分発動者のHPを回復させる</t>
-    <rPh sb="3" eb="8">
-      <t>コウカジカンチュウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>コウドウフカ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>コウドウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>マイビョウ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="55" eb="58">
-      <t>ハツドウシャ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>カイフク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -12442,6 +12176,767 @@
     </rPh>
     <rPh sb="129" eb="131">
       <t>ジブン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スキル効果時間中、対象と自身を行動不可(行動CDすら上がらない)にさせ、毎秒ダメージを与える
+与えたダメージの2倍の値分発動者のHPを回復させる</t>
+    <rPh sb="3" eb="8">
+      <t>コウカジカンチュウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>コウドウフカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="60" eb="63">
+      <t>ハツドウシャ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>種まき</t>
+    <rPh sb="0" eb="1">
+      <t>タネ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>範囲攻撃</t>
+    <rPh sb="0" eb="4">
+      <t>ハンイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sowing_seeds</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>25秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>500px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.05</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:debuff_plant)</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>既に(状態ID:debuff_plant)が付与されている対象には付与できない</t>
+    <rPh sb="0" eb="1">
+      <t>スデ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>恵みの雨</t>
+    <rPh sb="0" eb="1">
+      <t>メグ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アメ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>welcome_rain</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力 * 0.2</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>400px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象に(状態ID:debuff_plant)が付与されている場合
+それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態:debuff_plant)が解除されている必要がある</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ダンカイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>フタタ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>カイジョ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>木漏れ日</t>
+    <rPh sb="0" eb="2">
+      <t>コモ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>dappled_sunlight</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>範囲回復</t>
+    <rPh sb="0" eb="4">
+      <t>ハンイカイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力 * 0.3</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>600px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全員</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>回復</t>
+    <rPh sb="0" eb="2">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>発動者はこのスキルでの回復量が3倍になる
+対象に(状態ID:debuff_plant)が付与されている場合
+それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態:debuff_plant)が解除されている必要がある</t>
+    <rPh sb="0" eb="3">
+      <t>ハツドウシャ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>カイフクリョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>絡み合う根</t>
+    <rPh sb="0" eb="1">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ネ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Intertwined_roots</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃 * 0.2</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>350px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象に(状態ID:debuff_plant)が付与されている場合
+それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態:debuff_plant)が解除されている必要がある</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お花摘み</t>
+    <rPh sb="1" eb="3">
+      <t>ハナツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>picking_flowers</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃 * 0.1</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>700px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:debuff_wound)</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ヘンルーダ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>rue</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>300px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>((状態ID:buff_contempt)*3)22s</t>
+    <rPh sb="2" eb="4">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スタックがある間与ダメ率+15%,被ダメ率-15%、敵にドットダメージ以外のダメージを与えた時１スタック消費される。このスタックは新しくスタックを獲得した時継続時間を更新しない。
+効果時間が終わった時、軽蔑の全スタックを解除する。
+軽蔑が敵にダメージ与えて解除(スタックが０になった)されたとき、軽蔑がついていたユニットに悔恨(状態ID:debuff_regret)を付与する</t>
+    <rPh sb="7" eb="8">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="78" eb="82">
+      <t>ケイゾクジカン</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="90" eb="94">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="95" eb="96">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>ケイベツ</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>カイジョ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>ケイベツ</t>
+    </rPh>
+    <rPh sb="119" eb="120">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="125" eb="126">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>カイジョ</t>
+    </rPh>
+    <rPh sb="148" eb="150">
+      <t>ケイベツ</t>
+    </rPh>
+    <rPh sb="161" eb="163">
+      <t>カイコン</t>
+    </rPh>
+    <rPh sb="164" eb="166">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="184" eb="186">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スタックがある間、与ダメージ率+15%,被ダメージ率-15%される。敵にドットダメージ以外のダメージを与えた時、
+１スタック消費される。新しくスタックを得ても効果時間は延長されず、効果時間が終了した時、全スタックが解除される</t>
+    <rPh sb="7" eb="8">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="79" eb="83">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>エンチョウ</t>
+    </rPh>
+    <rPh sb="90" eb="94">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>紫のヒヤシンス</t>
+    <rPh sb="0" eb="1">
+      <t>ムラサキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>purple_hyacinth</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:debuff_sorrow)5s</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キンセンカ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>red_spider_lily</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>calendula</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>赤い彼岸花</t>
+    <rPh sb="0" eb="1">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ヒガンバナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>このスタックは特殊で始めは表示名が「種」である。
+強化されると、「発芽」「開花」「花名」の順番で名前が変化していく、「花名」の時強化を受けた場合、何も変化しない
+花名の枠はそのデバフを受けてるキャラによって変化する(ウルペス:ヘンルーダ)(リハス:紫のヒヤシンス)(スシア:キンセンカ)(アルジュナ:赤い彼岸花)
+この(種&gt;発芽&gt;開花&gt;花名)である
+効果はそれぞれHP再生率-(0.1/0.3/0.5/0.8)%</t>
+    <rPh sb="7" eb="9">
+      <t>トクシュ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ヒョウジメイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>タネ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ハツガ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カイカ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ハナメイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ハナメイ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ハナメイ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="124" eb="125">
+      <t>ムラサキ</t>
+    </rPh>
+    <rPh sb="150" eb="151">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="152" eb="155">
+      <t>ヒガンバナ</t>
+    </rPh>
+    <rPh sb="160" eb="161">
+      <t>タネ</t>
+    </rPh>
+    <rPh sb="162" eb="164">
+      <t>ハツガ</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>カイカ</t>
+    </rPh>
+    <rPh sb="168" eb="170">
+      <t>ハナメイ</t>
+    </rPh>
+    <rPh sb="175" eb="177">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="184" eb="187">
+      <t>サイセイリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>このスキルは敵に(状態ID:debuff_plant)が最後まで強化されている敵がいないと発動できないかつ、その対象にしか発動することができない
+対象の(状態ID:debuff_plant)を解除し、お花を獲得する。獲得した花の名前によって自身の次の行動が強制される、もし次の行動の命中対象がいない場合、見つかるまでは違うスキルを代替で使える
+花名が"ヘンルーダ"だった場合は(敵スキルID:rue),"紫のヒヤシンス"だった場合は(敵スキルID:purple_hyacinth),"キンセンカ"だった場合は(敵スキルID:calendula),"赤い彼岸花"だった場合は(敵スキルID:red_spider_lily)を次に発動する</t>
+    <rPh sb="6" eb="7">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>カイジョ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="108" eb="110">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="112" eb="113">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>キョウセイ</t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="138" eb="140">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="141" eb="145">
+      <t>メイチュウタイショウ</t>
+    </rPh>
+    <rPh sb="149" eb="151">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="152" eb="153">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="159" eb="160">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>ダイタイ</t>
+    </rPh>
+    <rPh sb="168" eb="169">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="172" eb="174">
+      <t>ハナメイ</t>
+    </rPh>
+    <rPh sb="185" eb="187">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="189" eb="190">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="202" eb="203">
+      <t>ムラサキ</t>
+    </rPh>
+    <rPh sb="213" eb="215">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="217" eb="218">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="251" eb="253">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="255" eb="256">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="274" eb="275">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="276" eb="279">
+      <t>ヒガンバナ</t>
+    </rPh>
+    <rPh sb="283" eb="285">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="287" eb="288">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="311" eb="312">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="313" eb="315">
+      <t>ハツドウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -14711,7 +15206,7 @@
         <v>20</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>20</v>
@@ -16250,50 +16745,50 @@
     </row>
     <row r="48" spans="1:26" ht="72">
       <c r="A48" s="4" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="C48" s="4"/>
       <c r="E48" s="4" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48" s="4" t="s">
+        <v>1269</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>1269</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>1269</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="Q48" s="4" t="s">
+        <v>1269</v>
+      </c>
+      <c r="R48" s="4" t="s">
         <v>1272</v>
       </c>
-      <c r="L48" s="4" t="s">
+      <c r="T48" s="4" t="s">
+        <v>1267</v>
+      </c>
+      <c r="U48" s="11" t="s">
         <v>1273</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>1274</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>1272</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>1272</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>1274</v>
-      </c>
-      <c r="Q48" s="4" t="s">
-        <v>1272</v>
-      </c>
-      <c r="R48" s="4" t="s">
-        <v>1275</v>
-      </c>
-      <c r="T48" s="4" t="s">
-        <v>1270</v>
-      </c>
-      <c r="U48" s="11" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="49" spans="1:26" ht="72">
@@ -16396,7 +16891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E325287-6FF5-4811-9C1B-B61C8E79C27E}">
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -16996,7 +17491,7 @@
         <v>644</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>639</v>
@@ -17180,310 +17675,563 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="43" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="F15" s="44">
         <v>15</v>
       </c>
       <c r="G15" s="43" t="s">
+        <v>1290</v>
+      </c>
+      <c r="I15" s="45" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J15" s="43" t="s">
+        <v>1291</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L15" s="43" t="s">
+        <v>1293</v>
+      </c>
+      <c r="M15" s="43" t="s">
         <v>1294</v>
       </c>
-      <c r="I15" s="45" t="s">
-        <v>1288</v>
-      </c>
-      <c r="J15" s="43" t="s">
+      <c r="N15" s="43" t="s">
+        <v>1284</v>
+      </c>
+      <c r="O15" s="43" t="s">
         <v>1295</v>
       </c>
-      <c r="K15" s="43" t="s">
-        <v>1288</v>
-      </c>
-      <c r="L15" s="43" t="s">
+      <c r="P15" s="43" t="s">
+        <v>1284</v>
+      </c>
+      <c r="Q15" s="43" t="s">
         <v>1296</v>
       </c>
-      <c r="M15" s="43" t="s">
+      <c r="R15" s="43" t="s">
+        <v>1284</v>
+      </c>
+      <c r="S15" s="43" t="s">
         <v>1297</v>
-      </c>
-      <c r="N15" s="43" t="s">
-        <v>1288</v>
-      </c>
-      <c r="O15" s="43" t="s">
-        <v>1298</v>
-      </c>
-      <c r="P15" s="43" t="s">
-        <v>1288</v>
-      </c>
-      <c r="Q15" s="43" t="s">
-        <v>1299</v>
-      </c>
-      <c r="R15" s="43" t="s">
-        <v>1288</v>
-      </c>
-      <c r="S15" s="43" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="36">
       <c r="A16" s="43" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="F16" s="44">
         <v>5</v>
       </c>
       <c r="G16" s="43" t="s">
+        <v>1305</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J16" s="43" t="s">
+        <v>1302</v>
+      </c>
+      <c r="K16" s="43" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L16" s="43" t="s">
+        <v>1293</v>
+      </c>
+      <c r="M16" s="43" t="s">
+        <v>1301</v>
+      </c>
+      <c r="N16" s="43" t="s">
+        <v>1284</v>
+      </c>
+      <c r="O16" s="43" t="s">
+        <v>1295</v>
+      </c>
+      <c r="Q16" s="43" t="s">
+        <v>1296</v>
+      </c>
+      <c r="R16" s="43" t="s">
+        <v>1303</v>
+      </c>
+      <c r="S16" s="43" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="72">
+      <c r="A17" s="43" t="s">
         <v>1307</v>
       </c>
-      <c r="I16" s="45" t="s">
-        <v>1288</v>
-      </c>
-      <c r="J16" s="43" t="s">
-        <v>1304</v>
-      </c>
-      <c r="K16" s="43" t="s">
-        <v>1288</v>
-      </c>
-      <c r="L16" s="43" t="s">
-        <v>1296</v>
-      </c>
-      <c r="M16" s="43" t="s">
-        <v>1303</v>
-      </c>
-      <c r="N16" s="43" t="s">
-        <v>1288</v>
-      </c>
-      <c r="O16" s="43" t="s">
-        <v>1298</v>
-      </c>
-      <c r="Q16" s="43" t="s">
-        <v>1299</v>
-      </c>
-      <c r="R16" s="43" t="s">
-        <v>1305</v>
-      </c>
-      <c r="S16" s="43" t="s">
+      <c r="C17" s="5" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D17" s="43" t="s">
         <v>1306</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" ht="54">
-      <c r="A17" s="43" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>1286</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>1308</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="F17" s="44">
         <v>5</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="I17" s="45" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="J17" s="43" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="K17" s="43" t="s">
+        <v>1309</v>
+      </c>
+      <c r="L17" s="43" t="s">
+        <v>1293</v>
+      </c>
+      <c r="M17" s="43" t="s">
+        <v>1308</v>
+      </c>
+      <c r="O17" s="43" t="s">
+        <v>1295</v>
+      </c>
+      <c r="P17" s="43" t="s">
         <v>1311</v>
       </c>
-      <c r="L17" s="43" t="s">
+      <c r="Q17" s="43" t="s">
+        <v>1314</v>
+      </c>
+      <c r="S17" s="43" t="s">
+        <v>1306</v>
+      </c>
+      <c r="T17" s="43" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="36">
+      <c r="A18" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="F18" s="2">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="Q18" s="3" t="s">
         <v>1296</v>
       </c>
-      <c r="M17" s="43" t="s">
-        <v>1310</v>
-      </c>
-      <c r="O17" s="43" t="s">
-        <v>1298</v>
-      </c>
-      <c r="P17" s="43" t="s">
-        <v>1313</v>
-      </c>
-      <c r="Q17" s="43" t="s">
-        <v>1317</v>
-      </c>
-      <c r="S17" s="43" t="s">
-        <v>1308</v>
-      </c>
-      <c r="T17" s="43" t="s">
-        <v>1314</v>
+      <c r="R18" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>1326</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
-      <c r="A18" s="3"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="3"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="2"/>
+    <row r="19" spans="1:23" ht="72">
+      <c r="A19" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="F19" s="2">
+        <v>10</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="R19" s="2"/>
+      <c r="S19" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>1332</v>
+      </c>
     </row>
-    <row r="19" spans="1:23">
-      <c r="A19" s="3"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="3"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="2"/>
+    <row r="20" spans="1:23" ht="90">
+      <c r="A20" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>1335</v>
+      </c>
+      <c r="F20" s="2">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="R20" s="2"/>
+      <c r="S20" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>1340</v>
+      </c>
     </row>
-    <row r="20" spans="1:23">
-      <c r="A20" s="3"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="3"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="2"/>
+    <row r="21" spans="1:23" ht="72">
+      <c r="A21" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="F21" s="2">
+        <v>10</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="R21" s="2"/>
+      <c r="S21" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>1345</v>
+      </c>
     </row>
-    <row r="21" spans="1:23">
-      <c r="A21" s="3"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="3"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="2"/>
-    </row>
-    <row r="22" spans="1:23">
-      <c r="A22" s="3"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+    <row r="22" spans="1:23" ht="216">
+      <c r="A22" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F22" s="2">
+        <v>10</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>1348</v>
+      </c>
       <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+      <c r="I22" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>1295</v>
+      </c>
       <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
+      <c r="Q22" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>1365</v>
+      </c>
       <c r="U22" s="13"/>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
     </row>
-    <row r="23" spans="1:23">
-      <c r="A23" s="3"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+    <row r="23" spans="1:23" ht="54">
+      <c r="A23" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F23" s="2">
+        <v>25</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>1284</v>
+      </c>
       <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
+      <c r="I23" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>1351</v>
+      </c>
       <c r="T23" s="3"/>
       <c r="U23" s="12"/>
       <c r="V23" s="12"/>
       <c r="W23" s="12"/>
     </row>
-    <row r="24" spans="1:23">
-      <c r="A24" s="3"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+    <row r="24" spans="1:23" ht="36">
+      <c r="A24" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F24" s="2">
+        <v>25</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>1284</v>
+      </c>
       <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
+      <c r="I24" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>1357</v>
+      </c>
       <c r="T24" s="3"/>
       <c r="U24" s="12"/>
       <c r="V24" s="12"/>
       <c r="W24" s="12"/>
     </row>
     <row r="25" spans="1:23">
-      <c r="A25" s="3"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="2"/>
+      <c r="A25" s="3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>1360</v>
+      </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -17499,6 +18247,17 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="3"/>
+    </row>
+    <row r="26" spans="1:23">
+      <c r="A26" s="43" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>1363</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S25" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -17707,51 +18466,51 @@
     </row>
     <row r="9" spans="1:7" ht="36">
       <c r="A9" s="4" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>1250</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>1251</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>328</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>1258</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>1259</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="54">
       <c r="A10" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>1253</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>1254</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>328</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>1255</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>1256</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>1257</v>
-      </c>
     </row>
-    <row r="11" spans="1:7" ht="108">
+    <row r="11" spans="1:7" ht="126">
       <c r="A11" s="4" t="s">
         <v>1245</v>
       </c>
@@ -17765,21 +18524,21 @@
         <v>190</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>1247</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>1248</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="90">
       <c r="A12" s="4" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>289</v>
@@ -17788,77 +18547,75 @@
         <v>190</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>1266</v>
+        <v>1355</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>1268</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="36">
       <c r="A13" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>1263</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>1264</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>1265</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>1277</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>1278</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>1278</v>
-      </c>
+        <v>1274</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="54">
       <c r="A15" s="4" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>1320</v>
-      </c>
+        <v>1317</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
@@ -19095,16 +19852,16 @@
     </row>
     <row r="14" spans="1:45" ht="36">
       <c r="A14" s="41" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="C14" s="43" t="s">
         <v>620</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="E14" s="44">
         <v>2300</v>
@@ -19152,7 +19909,7 @@
         <v>0.5</v>
       </c>
       <c r="T14" s="43" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="U14" s="33">
         <v>0</v>
@@ -19161,13 +19918,13 @@
         <v>0</v>
       </c>
       <c r="W14" s="43" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="X14" s="43" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="Y14" s="45" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
     </row>
   </sheetData>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5788A9D4-4E89-4EA4-8CCF-6542B19F280D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B630DB0-FE76-40A1-A054-D61927F6F496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="1366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2746" uniqueCount="1384">
   <si>
     <t>ID</t>
   </si>
@@ -6537,26 +6537,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>(状態ID:Injury)4s</t>
-    <rPh sb="1" eb="3">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>(状態ID:Injury)を4秒付与</t>
-    <rPh sb="1" eb="3">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>フヨ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>shadow_dash</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -7524,13 +7504,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>方向指定攻撃</t>
-    <rPh sb="0" eb="6">
-      <t>ホウコウシテイコウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>-</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -11249,10 +11222,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ディスタンス</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>distance</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -12056,10 +12025,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>absorption of Reunion</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>120px</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -12117,66 +12082,6 @@
   </si>
   <si>
     <t>reunion</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>この状態が付与されている間に付与してきた相手にドット以外のダメージを与えた場合
-付与してきた相手の次の行動が(敵スキル:absorption of Reunion)に強制される
-相手の(敵スキル:absorption of Reunion)のターゲットは必ず自分になる</t>
-    <rPh sb="2" eb="4">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>イガイ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>コウドウ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>キョウセイ</t>
-    </rPh>
-    <rPh sb="89" eb="91">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="93" eb="94">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="127" eb="128">
-      <t>カナラ</t>
-    </rPh>
-    <rPh sb="129" eb="131">
-      <t>ジブン</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -12321,59 +12226,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>対象に(状態ID:debuff_plant)が付与されている場合
-それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態:debuff_plant)が解除されている必要がある</t>
-    <rPh sb="0" eb="2">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ダンカイ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="64" eb="65">
-      <t>フタタ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="92" eb="94">
-      <t>カイジョ</t>
-    </rPh>
-    <rPh sb="99" eb="101">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>木漏れ日</t>
     <rPh sb="0" eb="2">
       <t>コモ</t>
@@ -12420,21 +12272,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>発動者はこのスキルでの回復量が3倍になる
-対象に(状態ID:debuff_plant)が付与されている場合
-それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態:debuff_plant)が解除されている必要がある</t>
-    <rPh sb="0" eb="3">
-      <t>ハツドウシャ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>カイフクリョウ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>バイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>絡み合う根</t>
     <rPh sb="0" eb="1">
       <t>カラ</t>
@@ -12448,23 +12285,108 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Intertwined_roots</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>攻撃 * 0.2</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>350px</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>対象に(状態ID:debuff_plant)が付与されている場合
-それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態:debuff_plant)が解除されている必要がある</t>
+    <t>このスタックは特殊で始めは表示名が「種」である。
+強化されると、「発芽」「開花」「花名」の順番で名前が変化していく、「花名」の時強化を受けた場合、何も変化しない
+花名の枠はそのデバフを受けてるキャラによって変化する(ウルペス:ヘンルーダ)(リハス:紫のヒヤシンス)(スシア:キンセンカ)(アルジュナ:赤の彼岸花)
+この(種&gt;発芽&gt;開花&gt;花名)である
+効果はそれぞれHP再生率-(0.1/0.3/0.5/0.8)%</t>
+    <rPh sb="7" eb="9">
+      <t>トクシュ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ヒョウジメイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>タネ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ハツガ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カイカ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ハナメイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ハナメイ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ハナメイ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="124" eb="125">
+      <t>ムラサキ</t>
+    </rPh>
+    <rPh sb="150" eb="151">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="152" eb="155">
+      <t>ヒガンバナ</t>
+    </rPh>
+    <rPh sb="160" eb="161">
+      <t>タネ</t>
+    </rPh>
+    <rPh sb="162" eb="164">
+      <t>ハツガ</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>カイカ</t>
+    </rPh>
+    <rPh sb="168" eb="170">
+      <t>ハナメイ</t>
+    </rPh>
+    <rPh sb="175" eb="177">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="184" eb="187">
+      <t>サイセイリツ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -12479,13 +12401,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>攻撃 * 0.1</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>700px</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -12502,10 +12417,6 @@
   </si>
   <si>
     <t>rue</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>300px</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -12701,7 +12612,250 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>赤い彼岸花</t>
+    <t>キンセンカビーム</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>calendula_beam</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:debuff_sleep)5s</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>このスキルが命中した場合、自身の行動CDを即座に残り0秒にし、同じ対象に向けて(敵スキルID:calendula_beam)を発動する</t>
+    <rPh sb="6" eb="8">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ソクザ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ハツドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>方向指定</t>
+    <rPh sb="0" eb="4">
+      <t>ホウコウシテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5.2秒</t>
+    <rPh sb="3" eb="4">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>800px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>半径150px</t>
+    <rPh sb="0" eb="2">
+      <t>ハンケイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>このスキルは詠唱中、効果時間中に予測線を出す</t>
+    <rPh sb="6" eb="9">
+      <t>エイショウチュウ</t>
+    </rPh>
+    <rPh sb="10" eb="15">
+      <t>コウカジカンチュウ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ヨソクセン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>absorption_of_reunion</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:reunion)10s</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>このスキルは敵に(状態ID:debuff_plant)が最後まで強化されている敵がいないと発動できないかつ、その対象にしか発動することができない
+対象の(状態ID:debuff_plant)を解除し、お花を獲得する。獲得した花の名前によって自身の次の行動が強制される、もし次の行動の命中対象がいない場合、見つかるまでは違うスキルを代替で使える
+花名が"ヘンルーダ"だった場合は(敵スキルID:rue),"紫のヒヤシンス"だった場合は(敵スキルID:purple_hyacinth),"キンセンカ"だった場合は(敵スキルID:calendula),"赤の彼岸花"だった場合は(敵スキルID:red_spider_lily)を次に発動する</t>
+    <rPh sb="6" eb="7">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>カイジョ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="108" eb="110">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="112" eb="113">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>キョウセイ</t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="138" eb="140">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="141" eb="145">
+      <t>メイチュウタイショウ</t>
+    </rPh>
+    <rPh sb="149" eb="151">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="152" eb="153">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="159" eb="160">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>ダイタイ</t>
+    </rPh>
+    <rPh sb="168" eb="169">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="172" eb="174">
+      <t>ハナメイ</t>
+    </rPh>
+    <rPh sb="185" eb="187">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="189" eb="190">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="202" eb="203">
+      <t>ムラサキ</t>
+    </rPh>
+    <rPh sb="213" eb="215">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="217" eb="218">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="251" eb="253">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="255" eb="256">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="274" eb="275">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="276" eb="279">
+      <t>ヒガンバナ</t>
+    </rPh>
+    <rPh sb="283" eb="285">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="287" eb="288">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="311" eb="312">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="313" eb="315">
+      <t>ハツドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>赤の彼岸花</t>
     <rPh sb="0" eb="1">
       <t>アカ</t>
     </rPh>
@@ -12711,232 +12865,107 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>このスタックは特殊で始めは表示名が「種」である。
-強化されると、「発芽」「開花」「花名」の順番で名前が変化していく、「花名」の時強化を受けた場合、何も変化しない
-花名の枠はそのデバフを受けてるキャラによって変化する(ウルペス:ヘンルーダ)(リハス:紫のヒヤシンス)(スシア:キンセンカ)(アルジュナ:赤い彼岸花)
-この(種&gt;発芽&gt;開花&gt;花名)である
-効果はそれぞれHP再生率-(0.1/0.3/0.5/0.8)%</t>
-    <rPh sb="7" eb="9">
-      <t>トクシュ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
+    <t>方向指定攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クロユリ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>chocolate_lily</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>6秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>半径200px</t>
+    <rPh sb="0" eb="2">
+      <t>ハンケイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(このスキルの詠唱中に受けたダメージ) * 0.7</t>
+    <rPh sb="7" eb="10">
+      <t>エイショウチュウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>8秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵スキルID(vine_whip,poisonous_stinger,sowing_seeds,welcome_rain,dappled_sunlight,intertwined_roots,picking_flowers,chocolate_lily)テキ</t>
+  </si>
+  <si>
+    <t>intertwined_roots</t>
+  </si>
+  <si>
+    <t>攻撃力 * 0.2コウゲキリョク</t>
+  </si>
+  <si>
+    <t>攻撃力 * 0.1コウゲキリョク</t>
+  </si>
+  <si>
+    <t>(状態ID:debuff_Injury)4sジョウタイ</t>
+  </si>
+  <si>
+    <t>(状態ID:debuff_Injury)を4秒付与ジョウタイビョウフヨ</t>
+  </si>
+  <si>
+    <t>この状態が付与されている間に付与してきた相手にドット以外のダメージを与えた場合
+付与してきた相手の次の行動が(敵スキルID:absorption_of_reunion)に強制される
+相手の(敵スキルID:absorption_of_reunion)のターゲットは必ず自分になるジョウタイフヨアイダフヨアイテイガイアタバアイフヨアイテツギコウドウテキキョウセイアイテテキカナラジブン</t>
+  </si>
+  <si>
+    <t>対象に(状態ID:debuff_plant)が付与されている場合
+それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態ID:debuff_plant)が解除されている必要があるタイショウジョウタイフヨバアイダンカイキョウカドキョウカタイショウジョウタイフタタキョウカイチドジョウタイカイジョヒツヨウ</t>
+  </si>
+  <si>
+    <t>発動者はこのスキルでの回復量が3倍になる
+対象に(状態ID:debuff_plant)が付与されている場合
+それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態ID:debuff_plant)が解除されている必要があるハツドウシャカイフクリョウバイ</t>
+  </si>
+  <si>
+    <t>対象に(状態ID:debuff_plant)が付与されている場合
+それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態ID:debuff_plant)が解除されている必要がある</t>
+  </si>
+  <si>
+    <t>ノータッチ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>このスキルのセリフのタイミングは詠唱を始めた時になる</t>
+    <rPh sb="16" eb="18">
+      <t>エイショウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
       <t>ハジ</t>
     </rPh>
-    <rPh sb="13" eb="16">
-      <t>ヒョウジメイ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>タネ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ハツガ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>カイカ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ハナメイ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ジュンバン</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>ヘンカ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ハナメイ</t>
-    </rPh>
-    <rPh sb="63" eb="64">
+    <rPh sb="22" eb="23">
       <t>トキ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="67" eb="68">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="73" eb="74">
-      <t>ナニ</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>ヘンカ</t>
-    </rPh>
-    <rPh sb="81" eb="83">
-      <t>ハナメイ</t>
-    </rPh>
-    <rPh sb="84" eb="85">
-      <t>ワク</t>
-    </rPh>
-    <rPh sb="92" eb="93">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="103" eb="105">
-      <t>ヘンカ</t>
-    </rPh>
-    <rPh sb="124" eb="125">
-      <t>ムラサキ</t>
-    </rPh>
-    <rPh sb="150" eb="151">
-      <t>アカ</t>
-    </rPh>
-    <rPh sb="152" eb="155">
-      <t>ヒガンバナ</t>
-    </rPh>
-    <rPh sb="160" eb="161">
-      <t>タネ</t>
-    </rPh>
-    <rPh sb="162" eb="164">
-      <t>ハツガ</t>
-    </rPh>
-    <rPh sb="165" eb="167">
-      <t>カイカ</t>
-    </rPh>
-    <rPh sb="168" eb="170">
-      <t>ハナメイ</t>
-    </rPh>
-    <rPh sb="175" eb="177">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="184" eb="187">
-      <t>サイセイリツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>このスキルは敵に(状態ID:debuff_plant)が最後まで強化されている敵がいないと発動できないかつ、その対象にしか発動することができない
-対象の(状態ID:debuff_plant)を解除し、お花を獲得する。獲得した花の名前によって自身の次の行動が強制される、もし次の行動の命中対象がいない場合、見つかるまでは違うスキルを代替で使える
-花名が"ヘンルーダ"だった場合は(敵スキルID:rue),"紫のヒヤシンス"だった場合は(敵スキルID:purple_hyacinth),"キンセンカ"だった場合は(敵スキルID:calendula),"赤い彼岸花"だった場合は(敵スキルID:red_spider_lily)を次に発動する</t>
-    <rPh sb="6" eb="7">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ハツドウ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ハツドウ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="96" eb="98">
-      <t>カイジョ</t>
-    </rPh>
-    <rPh sb="101" eb="102">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="103" eb="105">
-      <t>カクトク</t>
-    </rPh>
-    <rPh sb="108" eb="110">
-      <t>カクトク</t>
-    </rPh>
-    <rPh sb="112" eb="113">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="114" eb="116">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="120" eb="122">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="123" eb="124">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="125" eb="127">
-      <t>コウドウ</t>
-    </rPh>
-    <rPh sb="128" eb="130">
-      <t>キョウセイ</t>
-    </rPh>
-    <rPh sb="136" eb="137">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="138" eb="140">
-      <t>コウドウ</t>
-    </rPh>
-    <rPh sb="141" eb="145">
-      <t>メイチュウタイショウ</t>
-    </rPh>
-    <rPh sb="149" eb="151">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="152" eb="153">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="159" eb="160">
-      <t>チガ</t>
-    </rPh>
-    <rPh sb="165" eb="167">
-      <t>ダイタイ</t>
-    </rPh>
-    <rPh sb="168" eb="169">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="172" eb="174">
-      <t>ハナメイ</t>
-    </rPh>
-    <rPh sb="185" eb="187">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="189" eb="190">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="202" eb="203">
-      <t>ムラサキ</t>
-    </rPh>
-    <rPh sb="213" eb="215">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="217" eb="218">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="251" eb="253">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="255" eb="256">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="274" eb="275">
-      <t>アカ</t>
-    </rPh>
-    <rPh sb="276" eb="279">
-      <t>ヒガンバナ</t>
-    </rPh>
-    <rPh sb="283" eb="285">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="287" eb="288">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="311" eb="312">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="313" eb="315">
-      <t>ハツドウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -13129,7 +13158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -13230,21 +13259,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13712,7 +13726,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>19</v>
@@ -13721,10 +13735,10 @@
         <v>313</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>292</v>
@@ -13801,7 +13815,7 @@
         <v>25</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>26</v>
@@ -13881,7 +13895,7 @@
         <v>318</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>214</v>
@@ -14030,7 +14044,7 @@
         <v>20</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>20</v>
@@ -14039,10 +14053,10 @@
         <v>25</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>41</v>
@@ -14119,10 +14133,10 @@
         <v>258</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>292</v>
@@ -14268,7 +14282,7 @@
         <v>20</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>214</v>
@@ -14357,7 +14371,7 @@
         <v>247</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>248</v>
@@ -14437,10 +14451,10 @@
         <v>48</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>41</v>
@@ -14506,7 +14520,7 @@
         <v>20</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>19</v>
@@ -14518,7 +14532,7 @@
         <v>217</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>233</v>
@@ -14540,7 +14554,7 @@
         <v>302</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="X12" s="12" t="s">
         <v>367</v>
@@ -14676,7 +14690,7 @@
         <v>20</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>233</v>
@@ -14765,7 +14779,7 @@
         <v>20</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>128</v>
@@ -14845,7 +14859,7 @@
         <v>20</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>129</v>
@@ -14916,7 +14930,7 @@
         <v>214</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>27</v>
@@ -14925,7 +14939,7 @@
         <v>20</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>128</v>
@@ -14996,7 +15010,7 @@
         <v>214</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>27</v>
@@ -15005,7 +15019,7 @@
         <v>20</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="S18" s="2" t="s">
         <v>129</v>
@@ -15151,7 +15165,7 @@
         <v>696</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>695</v>
@@ -15206,7 +15220,7 @@
         <v>20</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>20</v>
@@ -15342,7 +15356,7 @@
         <v>492</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="O23" s="13" t="s">
         <v>490</v>
@@ -15363,16 +15377,16 @@
         <v>489</v>
       </c>
       <c r="U23" s="12" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="V23" s="12" t="s">
         <v>494</v>
       </c>
       <c r="W23" s="12" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="X23" s="12" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="Y23" s="12" t="s">
         <v>384</v>
@@ -15383,415 +15397,415 @@
     </row>
     <row r="24" spans="1:26" ht="36">
       <c r="A24" s="12" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="G24">
         <v>13</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="O24" s="13" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="R24" s="12" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="T24" s="13" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="V24" s="12" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="W24" s="12" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="X24" s="12" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="Y24" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z24" s="12" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="36">
       <c r="A25" s="12" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>820</v>
       </c>
-      <c r="E25" s="12" t="s">
-        <v>822</v>
-      </c>
       <c r="F25" s="12" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="G25">
         <v>10</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="M25" s="12" t="s">
+        <v>833</v>
+      </c>
+      <c r="N25" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="N25" s="13" t="s">
-        <v>839</v>
-      </c>
       <c r="O25" s="13" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="R25" s="12" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="T25" s="12" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="V25" s="12" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="W25" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="X25" s="12" t="s">
         <v>871</v>
-      </c>
-      <c r="X25" s="12" t="s">
-        <v>874</v>
       </c>
       <c r="Y25" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z25" s="12" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="36">
       <c r="A26" s="12" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="G26">
         <v>14</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="O26" s="13" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="R26" s="12" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="T26" s="12" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="V26" s="12" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="W26" s="12" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="X26" s="12" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="Y26" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z26" s="12" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="36">
       <c r="A27" s="12" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E27" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="F27" s="12" t="s">
         <v>824</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>826</v>
       </c>
       <c r="G27">
         <v>8</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="O27" s="13" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="R27" s="12" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="T27" s="12" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="V27" s="12" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="W27" s="12" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="X27" s="12" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="Y27" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z27" s="12" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="72">
       <c r="A28" s="12" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>828</v>
+        <v>1365</v>
       </c>
       <c r="G28">
         <v>10</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="J28">
         <v>25</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="O28" s="13" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="T28" s="12" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="V28" s="12" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="W28" s="12" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="X28" s="12" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="Y28" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z28" s="12" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="36">
       <c r="A29" s="12" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>312</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="G29">
         <v>10</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="J29">
         <v>20</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="O29" s="13" t="s">
+        <v>842</v>
+      </c>
+      <c r="P29" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="Q29" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="R29" s="12" t="s">
         <v>845</v>
-      </c>
-      <c r="P29" s="12" t="s">
-        <v>846</v>
-      </c>
-      <c r="Q29" s="12" t="s">
-        <v>829</v>
-      </c>
-      <c r="R29" s="12" t="s">
-        <v>848</v>
       </c>
       <c r="T29" s="12" t="s">
         <v>312</v>
       </c>
       <c r="V29" s="12" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="W29" s="12" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="X29" s="12" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="Y29" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z29" s="12" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="36">
       <c r="A30" s="12" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>163</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>598</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="H30" s="16" t="s">
         <v>214</v>
@@ -15800,51 +15814,51 @@
         <v>20</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L30" s="34" t="s">
+        <v>827</v>
+      </c>
+      <c r="M30" s="12" t="s">
         <v>830</v>
       </c>
-      <c r="M30" s="12" t="s">
-        <v>833</v>
-      </c>
       <c r="N30" s="13" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="P30" s="12" t="s">
         <v>292</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="R30" s="12" t="s">
         <v>214</v>
       </c>
       <c r="T30" s="12" t="s">
+        <v>946</v>
+      </c>
+      <c r="V30" s="12" t="s">
+        <v>1073</v>
+      </c>
+      <c r="W30" s="12" t="s">
+        <v>1074</v>
+      </c>
+      <c r="X30" s="12" t="s">
+        <v>947</v>
+      </c>
+      <c r="Y30" s="12" t="s">
+        <v>948</v>
+      </c>
+      <c r="Z30" s="12" t="s">
         <v>949</v>
-      </c>
-      <c r="V30" s="12" t="s">
-        <v>1076</v>
-      </c>
-      <c r="W30" s="12" t="s">
-        <v>1077</v>
-      </c>
-      <c r="X30" s="12" t="s">
-        <v>950</v>
-      </c>
-      <c r="Y30" s="12" t="s">
-        <v>951</v>
-      </c>
-      <c r="Z30" s="12" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="36">
       <c r="A31" s="12" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>163</v>
@@ -15853,7 +15867,7 @@
         <v>166</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>597</v>
@@ -15862,10 +15876,10 @@
         <v>13</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>324</v>
@@ -15886,31 +15900,31 @@
         <v>244</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="T31" s="13" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="U31" s="12"/>
       <c r="V31" s="12" t="s">
+        <v>1054</v>
+      </c>
+      <c r="W31" s="12" t="s">
         <v>1057</v>
       </c>
-      <c r="W31" s="12" t="s">
-        <v>1060</v>
-      </c>
       <c r="X31" s="12" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="Y31" s="12" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="Z31" s="12" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="54">
       <c r="A32" s="12" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>163</v>
@@ -15919,7 +15933,7 @@
         <v>166</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>657</v>
@@ -15928,10 +15942,10 @@
         <v>10</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>688</v>
@@ -15955,30 +15969,30 @@
         <v>244</v>
       </c>
       <c r="S32" s="12" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="T32" s="12" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="V32" s="12" t="s">
+        <v>1055</v>
+      </c>
+      <c r="W32" s="12" t="s">
         <v>1058</v>
       </c>
-      <c r="W32" s="12" t="s">
-        <v>1061</v>
-      </c>
       <c r="X32" s="12" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="Y32" s="12" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="Z32" s="12" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="36">
       <c r="A33" s="12" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>163</v>
@@ -15987,7 +16001,7 @@
         <v>166</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>597</v>
@@ -15996,16 +16010,16 @@
         <v>14</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>324</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="O33" s="13" t="s">
         <v>214</v>
@@ -16020,30 +16034,30 @@
         <v>244</v>
       </c>
       <c r="S33" s="12" t="s">
+        <v>1056</v>
+      </c>
+      <c r="T33" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="V33" s="12" t="s">
         <v>1059</v>
       </c>
-      <c r="T33" s="12" t="s">
-        <v>823</v>
-      </c>
-      <c r="V33" s="12" t="s">
-        <v>1062</v>
-      </c>
       <c r="W33" s="12" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="X33" s="12" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="Y33" s="12" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="Z33" s="12" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="108">
       <c r="A34" s="12" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>163</v>
@@ -16052,7 +16066,7 @@
         <v>166</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>597</v>
@@ -16061,16 +16075,16 @@
         <v>8</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="M34" s="12" t="s">
         <v>324</v>
       </c>
       <c r="N34" s="13" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="O34" s="13" t="s">
         <v>214</v>
@@ -16085,33 +16099,33 @@
         <v>244</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="T34" s="12" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="V34" s="12" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="W34" s="12" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="X34" s="12" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="Y34" s="12" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="Z34" s="12" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="90">
       <c r="A35" s="12" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>163</v>
@@ -16120,22 +16134,22 @@
         <v>166</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>828</v>
+        <v>1365</v>
       </c>
       <c r="G35">
         <v>10</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="J35">
         <v>25</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>246</v>
@@ -16144,7 +16158,7 @@
         <v>271</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="O35" s="13" t="s">
         <v>664</v>
@@ -16159,33 +16173,33 @@
         <v>243</v>
       </c>
       <c r="S35" s="12" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="T35" s="12" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="V35" s="12" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="W35" s="12" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="X35" s="12" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="Y35" s="12" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="Z35" s="12" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="54">
       <c r="A36" s="12" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>163</v>
@@ -16203,13 +16217,13 @@
         <v>10</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="J36">
         <v>20</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>246</v>
@@ -16218,10 +16232,10 @@
         <v>689</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="O36" s="13" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="P36" s="12" t="s">
         <v>292</v>
@@ -16233,30 +16247,30 @@
         <v>243</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="T36" s="12" t="s">
         <v>312</v>
       </c>
       <c r="V36" s="12" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="W36" s="12" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="X36" s="12" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="Y36" s="12" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="Z36" s="12" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="36">
       <c r="A37" s="12" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>163</v>
@@ -16265,10 +16279,10 @@
         <v>166</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>214</v>
@@ -16280,22 +16294,22 @@
         <v>25</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L37" s="34" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="M37" s="12" t="s">
         <v>689</v>
       </c>
       <c r="N37" s="13" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="O37" s="12" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="P37" s="12" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="Q37" s="12" t="s">
         <v>214</v>
@@ -16304,33 +16318,33 @@
         <v>214</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="T37" s="12" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="U37" s="12" t="s">
+        <v>1072</v>
+      </c>
+      <c r="V37" s="12" t="s">
         <v>1075</v>
       </c>
-      <c r="V37" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="W37" s="12" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="X37" s="12" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="Y37" s="12" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="Z37" s="12" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="36">
       <c r="A38" s="12" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>163</v>
@@ -16339,7 +16353,7 @@
         <v>166</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F38" s="13" t="s">
         <v>597</v>
@@ -16348,10 +16362,10 @@
         <v>13</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="M38" s="13" t="s">
         <v>324</v>
@@ -16372,31 +16386,31 @@
         <v>244</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="T38" s="13" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="U38" s="12"/>
       <c r="V38" s="12" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="W38" s="12" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="X38" s="12" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="Y38" s="12" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="Z38" s="12" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="36">
       <c r="A39" s="12" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>163</v>
@@ -16405,7 +16419,7 @@
         <v>166</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>657</v>
@@ -16414,10 +16428,10 @@
         <v>10</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L39" s="16" t="s">
         <v>688</v>
@@ -16441,31 +16455,31 @@
         <v>244</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="T39" s="12" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="U39" s="12"/>
       <c r="V39" s="12" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="W39" s="12" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="X39" s="12" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="Y39" s="12" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="Z39" s="12" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="36">
       <c r="A40" s="12" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>163</v>
@@ -16474,7 +16488,7 @@
         <v>166</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>597</v>
@@ -16483,16 +16497,16 @@
         <v>14</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="M40" s="12" t="s">
         <v>324</v>
       </c>
       <c r="N40" s="13" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="O40" s="13" t="s">
         <v>214</v>
@@ -16507,31 +16521,31 @@
         <v>244</v>
       </c>
       <c r="S40" s="12" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="T40" s="12" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="U40" s="12"/>
       <c r="V40" s="12" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="W40" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="X40" s="12" t="s">
         <v>1205</v>
       </c>
-      <c r="X40" s="12" t="s">
-        <v>1208</v>
-      </c>
       <c r="Y40" s="12" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="Z40" s="12" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="41" spans="1:26" ht="36">
       <c r="A41" s="12" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>163</v>
@@ -16540,7 +16554,7 @@
         <v>166</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>597</v>
@@ -16549,16 +16563,16 @@
         <v>8</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="M41" s="12" t="s">
         <v>324</v>
       </c>
       <c r="N41" s="13" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="O41" s="13" t="s">
         <v>214</v>
@@ -16573,33 +16587,33 @@
         <v>244</v>
       </c>
       <c r="S41" s="12" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="T41" s="12" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="U41" s="12" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="V41" s="12" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="W41" s="12" t="s">
+        <v>1203</v>
+      </c>
+      <c r="X41" s="12" t="s">
+        <v>1205</v>
+      </c>
+      <c r="Y41" s="12" t="s">
         <v>1206</v>
       </c>
-      <c r="X41" s="12" t="s">
-        <v>1208</v>
-      </c>
-      <c r="Y41" s="12" t="s">
-        <v>1209</v>
-      </c>
       <c r="Z41" s="12" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="36">
       <c r="A42" s="12" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>163</v>
@@ -16608,10 +16622,10 @@
         <v>166</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>214</v>
@@ -16623,7 +16637,7 @@
         <v>60</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="L42" s="34" t="s">
         <v>644</v>
@@ -16632,13 +16646,13 @@
         <v>689</v>
       </c>
       <c r="N42" s="13" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="O42" s="12" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="P42" s="12" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="Q42" s="12" t="s">
         <v>214</v>
@@ -16648,147 +16662,147 @@
       </c>
       <c r="S42" s="12"/>
       <c r="T42" s="12" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="U42" s="12" t="s">
+        <v>1209</v>
+      </c>
+      <c r="V42" s="12" t="s">
+        <v>1210</v>
+      </c>
+      <c r="W42" s="12" t="s">
+        <v>1219</v>
+      </c>
+      <c r="X42" s="12" t="s">
         <v>1212</v>
       </c>
-      <c r="V42" s="12" t="s">
+      <c r="Y42" s="12" t="s">
         <v>1213</v>
       </c>
-      <c r="W42" s="12" t="s">
-        <v>1222</v>
-      </c>
-      <c r="X42" s="12" t="s">
-        <v>1215</v>
-      </c>
-      <c r="Y42" s="12" t="s">
-        <v>1216</v>
-      </c>
       <c r="Z42" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="43" spans="1:26" ht="54">
       <c r="A43" s="12" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>391</v>
       </c>
       <c r="C43" s="12" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F43" s="12" t="s">
         <v>1227</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="G43" s="12" t="s">
         <v>1228</v>
       </c>
-      <c r="E43" s="12" t="s">
-        <v>1229</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>1231</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>1232</v>
-      </c>
       <c r="H43" s="16" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43" s="12" t="s">
+        <v>1232</v>
+      </c>
+      <c r="L43" s="34" t="s">
+        <v>1228</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N43" s="13" t="s">
+        <v>1230</v>
+      </c>
+      <c r="O43" s="12" t="s">
+        <v>1228</v>
+      </c>
+      <c r="P43" s="12" t="s">
+        <v>1231</v>
+      </c>
+      <c r="Q43" s="12" t="s">
+        <v>1233</v>
+      </c>
+      <c r="R43" s="12" t="s">
+        <v>1228</v>
+      </c>
+      <c r="T43" s="12" t="s">
+        <v>1382</v>
+      </c>
+      <c r="U43" s="12" t="s">
+        <v>1235</v>
+      </c>
+      <c r="V43" s="12" t="s">
+        <v>1234</v>
+      </c>
+      <c r="W43" s="12" t="s">
         <v>1236</v>
       </c>
-      <c r="L43" s="34" t="s">
-        <v>1232</v>
-      </c>
-      <c r="M43" s="12" t="s">
-        <v>1233</v>
-      </c>
-      <c r="N43" s="13" t="s">
-        <v>1234</v>
-      </c>
-      <c r="O43" s="12" t="s">
-        <v>1232</v>
-      </c>
-      <c r="P43" s="12" t="s">
-        <v>1235</v>
-      </c>
-      <c r="Q43" s="12" t="s">
+      <c r="X43" s="12" t="s">
         <v>1237</v>
       </c>
-      <c r="R43" s="12" t="s">
-        <v>1232</v>
-      </c>
-      <c r="T43" s="12" t="s">
-        <v>1229</v>
-      </c>
-      <c r="U43" s="12" t="s">
+      <c r="Y43" s="12" t="s">
+        <v>1238</v>
+      </c>
+      <c r="Z43" s="12" t="s">
         <v>1239</v>
-      </c>
-      <c r="V43" s="12" t="s">
-        <v>1238</v>
-      </c>
-      <c r="W43" s="12" t="s">
-        <v>1240</v>
-      </c>
-      <c r="X43" s="12" t="s">
-        <v>1241</v>
-      </c>
-      <c r="Y43" s="12" t="s">
-        <v>1242</v>
-      </c>
-      <c r="Z43" s="12" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="48" spans="1:26" ht="72">
       <c r="A48" s="4" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="C48" s="4"/>
       <c r="E48" s="4" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>1267</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>1267</v>
+      </c>
+      <c r="Q48" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="R48" s="4" t="s">
+        <v>1268</v>
+      </c>
+      <c r="T48" s="4" t="s">
+        <v>1263</v>
+      </c>
+      <c r="U48" s="11" t="s">
         <v>1269</v>
-      </c>
-      <c r="L48" s="4" t="s">
-        <v>1270</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>1271</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>1269</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>1269</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>1271</v>
-      </c>
-      <c r="Q48" s="4" t="s">
-        <v>1269</v>
-      </c>
-      <c r="R48" s="4" t="s">
-        <v>1272</v>
-      </c>
-      <c r="T48" s="4" t="s">
-        <v>1267</v>
-      </c>
-      <c r="U48" s="11" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="49" spans="1:26" ht="72">
@@ -16891,7 +16905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E325287-6FF5-4811-9C1B-B61C8E79C27E}">
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -17291,7 +17305,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="3" t="s">
@@ -17442,7 +17456,7 @@
         <v>685</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="36">
@@ -17491,7 +17505,7 @@
         <v>644</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>639</v>
@@ -17500,10 +17514,10 @@
         <v>704</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" ht="54">
       <c r="A12" s="3" t="s">
         <v>708</v>
       </c>
@@ -17552,28 +17566,28 @@
         <v>648</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>716</v>
+        <v>1376</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>667</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>717</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="36">
       <c r="A13" s="3" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="14" t="s">
         <v>623</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>639</v>
@@ -17592,7 +17606,7 @@
         <v>639</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>639</v>
@@ -17601,7 +17615,7 @@
         <v>639</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>639</v>
@@ -17610,23 +17624,23 @@
         <v>639</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="T13" s="3"/>
     </row>
     <row r="14" spans="1:25" ht="54">
       <c r="A14" s="3" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="14" t="s">
         <v>623</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>633</v>
@@ -17635,7 +17649,7 @@
         <v>10</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="3" t="s">
@@ -17669,438 +17683,438 @@
         <v>639</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="T14" s="2"/>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="43" t="s">
-        <v>1288</v>
+      <c r="A15" s="12" t="s">
+        <v>1284</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1282</v>
-      </c>
-      <c r="D15" s="43" t="s">
-        <v>1287</v>
+        <v>1278</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>1283</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="F15" s="13">
+        <v>15</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>1280</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>1371</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="L15" s="12" t="s">
         <v>1289</v>
       </c>
-      <c r="F15" s="44">
-        <v>15</v>
-      </c>
-      <c r="G15" s="43" t="s">
+      <c r="M15" s="12" t="s">
         <v>1290</v>
       </c>
-      <c r="I15" s="45" t="s">
-        <v>1284</v>
-      </c>
-      <c r="J15" s="43" t="s">
+      <c r="N15" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="O15" s="12" t="s">
         <v>1291</v>
       </c>
-      <c r="K15" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="L15" s="43" t="s">
+      <c r="P15" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="R15" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="S15" s="12" t="s">
         <v>1293</v>
-      </c>
-      <c r="M15" s="43" t="s">
-        <v>1294</v>
-      </c>
-      <c r="N15" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="O15" s="43" t="s">
-        <v>1295</v>
-      </c>
-      <c r="P15" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="Q15" s="43" t="s">
-        <v>1296</v>
-      </c>
-      <c r="R15" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="S15" s="43" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="36">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="F16" s="13">
+        <v>5</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>1280</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>1291</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="R16" s="12" t="s">
         <v>1299</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>1282</v>
-      </c>
-      <c r="D16" s="43" t="s">
-        <v>1298</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F16" s="44">
-        <v>5</v>
-      </c>
-      <c r="G16" s="43" t="s">
-        <v>1305</v>
-      </c>
-      <c r="I16" s="45" t="s">
-        <v>1284</v>
-      </c>
-      <c r="J16" s="43" t="s">
-        <v>1302</v>
-      </c>
-      <c r="K16" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="L16" s="43" t="s">
-        <v>1293</v>
-      </c>
-      <c r="M16" s="43" t="s">
-        <v>1301</v>
-      </c>
-      <c r="N16" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="O16" s="43" t="s">
-        <v>1295</v>
-      </c>
-      <c r="Q16" s="43" t="s">
-        <v>1296</v>
-      </c>
-      <c r="R16" s="43" t="s">
-        <v>1303</v>
-      </c>
-      <c r="S16" s="43" t="s">
-        <v>1304</v>
+      <c r="S16" s="12" t="s">
+        <v>1300</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="72">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="12" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="F17" s="13">
+        <v>5</v>
+      </c>
+      <c r="G17" s="12" t="s">
         <v>1307</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>1282</v>
-      </c>
-      <c r="D17" s="43" t="s">
+      <c r="I17" s="16" t="s">
+        <v>1280</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>1305</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>1304</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>1303</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>1291</v>
+      </c>
+      <c r="P17" s="12" t="s">
         <v>1306</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F17" s="44">
-        <v>5</v>
-      </c>
-      <c r="G17" s="43" t="s">
+      <c r="Q17" s="12" t="s">
+        <v>1309</v>
+      </c>
+      <c r="S17" s="12" t="s">
+        <v>1302</v>
+      </c>
+      <c r="T17" s="12" t="s">
         <v>1312</v>
-      </c>
-      <c r="I17" s="45" t="s">
-        <v>1284</v>
-      </c>
-      <c r="J17" s="43" t="s">
-        <v>1310</v>
-      </c>
-      <c r="K17" s="43" t="s">
-        <v>1309</v>
-      </c>
-      <c r="L17" s="43" t="s">
-        <v>1293</v>
-      </c>
-      <c r="M17" s="43" t="s">
-        <v>1308</v>
-      </c>
-      <c r="O17" s="43" t="s">
-        <v>1295</v>
-      </c>
-      <c r="P17" s="43" t="s">
-        <v>1311</v>
-      </c>
-      <c r="Q17" s="43" t="s">
-        <v>1314</v>
-      </c>
-      <c r="S17" s="43" t="s">
-        <v>1306</v>
-      </c>
-      <c r="T17" s="43" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="36">
       <c r="A18" s="3" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>1320</v>
+        <v>1314</v>
       </c>
       <c r="F18" s="2">
         <v>5</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="126">
+      <c r="A19" s="3" t="s">
         <v>1322</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>1284</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>1292</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>1323</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>1295</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>1284</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>1296</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>1325</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>1319</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" ht="72">
-      <c r="A19" s="3" t="s">
-        <v>1328</v>
-      </c>
       <c r="C19" s="14" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1327</v>
+        <v>1321</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>1320</v>
+        <v>1314</v>
       </c>
       <c r="F19" s="2">
         <v>10</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1329</v>
+        <v>1323</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>1331</v>
+        <v>1325</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>243</v>
       </c>
       <c r="R19" s="2"/>
       <c r="S19" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="108">
+      <c r="A20" s="3" t="s">
         <v>1327</v>
       </c>
-      <c r="T19" s="3" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" ht="90">
-      <c r="A20" s="3" t="s">
-        <v>1334</v>
-      </c>
       <c r="C20" s="14" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1333</v>
+        <v>1326</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>1335</v>
+        <v>1328</v>
       </c>
       <c r="F20" s="2">
         <v>10</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>1336</v>
+        <v>1329</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="K20" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="N20" s="3" t="s">
         <v>1330</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>1292</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>1337</v>
-      </c>
       <c r="O20" s="3" t="s">
-        <v>1338</v>
+        <v>1331</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>1339</v>
+        <v>1332</v>
       </c>
       <c r="R20" s="2"/>
       <c r="S20" s="3" t="s">
-        <v>1333</v>
+        <v>1326</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>1340</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="72">
       <c r="A21" s="3" t="s">
-        <v>1342</v>
+        <v>1373</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1341</v>
+        <v>1333</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>1320</v>
+        <v>1314</v>
       </c>
       <c r="F21" s="2">
         <v>10</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1343</v>
+        <v>1374</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="L21" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="Q21" s="3" t="s">
         <v>1292</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>1344</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>1295</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>1284</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>1296</v>
       </c>
       <c r="R21" s="2"/>
       <c r="S21" s="3" t="s">
-        <v>1341</v>
+        <v>1333</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>1345</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="216">
       <c r="A22" s="3" t="s">
-        <v>1347</v>
+        <v>1337</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1346</v>
+        <v>1336</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="F22" s="2">
         <v>10</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1348</v>
+        <v>1375</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>1291</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>1284</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>1293</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>1349</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>1295</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="3" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>1350</v>
+        <v>1339</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>1346</v>
+        <v>1336</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="U22" s="13"/>
       <c r="V22" s="12"/>
@@ -18108,56 +18122,56 @@
     </row>
     <row r="23" spans="1:23" ht="54">
       <c r="A23" s="3" t="s">
-        <v>1352</v>
+        <v>1341</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1351</v>
+        <v>1340</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="F23" s="2">
         <v>25</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>1353</v>
+        <v>885</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>1354</v>
+        <v>1342</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>1351</v>
+        <v>1340</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="12"/>
@@ -18166,97 +18180,271 @@
     </row>
     <row r="24" spans="1:23" ht="36">
       <c r="A24" s="3" t="s">
-        <v>1358</v>
+        <v>1346</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1357</v>
+        <v>1345</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="F24" s="2">
         <v>25</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>1353</v>
+        <v>885</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>1359</v>
+        <v>1347</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>1357</v>
+        <v>1345</v>
       </c>
       <c r="T24" s="3"/>
       <c r="U24" s="12"/>
       <c r="V24" s="12"/>
       <c r="W24" s="12"/>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" ht="54">
       <c r="A25" s="3" t="s">
-        <v>1362</v>
+        <v>1350</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1360</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+        <v>1348</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="F25" s="2">
+        <v>25</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>1280</v>
+      </c>
       <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+      <c r="I25" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>1291</v>
+      </c>
       <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="3"/>
+      <c r="Q25" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>1354</v>
+      </c>
     </row>
     <row r="26" spans="1:23">
-      <c r="A26" s="43" t="s">
-        <v>1361</v>
+      <c r="A26" s="12" t="s">
+        <v>1352</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>1282</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>1363</v>
+        <v>1278</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="F26" s="13">
+        <v>5</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>1305</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>1356</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>1357</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>1358</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>1291</v>
+      </c>
+      <c r="P26" s="13" t="s">
+        <v>1305</v>
+      </c>
+      <c r="Q26" s="12" t="s">
+        <v>1359</v>
+      </c>
+      <c r="T26" s="12" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23">
+      <c r="A27" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="F27" s="13">
+        <v>25</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>1305</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>885</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>1281</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>1291</v>
+      </c>
+      <c r="P27" s="13" t="s">
+        <v>1280</v>
+      </c>
+      <c r="Q27" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="R27" s="16" t="s">
+        <v>1362</v>
+      </c>
+      <c r="S27" s="39" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="54">
+      <c r="A28" s="12" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="F28" s="13">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>1370</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>1368</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>1288</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>1281</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>1369</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>1291</v>
+      </c>
+      <c r="P28" s="13" t="s">
+        <v>1280</v>
+      </c>
+      <c r="Q28" s="12" t="s">
+        <v>1359</v>
+      </c>
+      <c r="S28" s="39" t="s">
+        <v>1366</v>
+      </c>
+      <c r="T28" s="34" t="s">
+        <v>1383</v>
       </c>
     </row>
   </sheetData>
@@ -18291,7 +18479,7 @@
         <v>82</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>197</v>
@@ -18429,7 +18617,7 @@
         <v>672</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>673</v>
@@ -18443,7 +18631,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>711</v>
@@ -18452,7 +18640,7 @@
         <v>712</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>713</v>
@@ -18466,79 +18654,79 @@
     </row>
     <row r="9" spans="1:7" ht="36">
       <c r="A9" s="4" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>328</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="54">
       <c r="A10" s="4" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>328</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>1251</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>1254</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>1255</v>
-      </c>
       <c r="G10" s="4" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="126">
       <c r="A11" s="4" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>1364</v>
+        <v>1335</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="90">
       <c r="A12" s="4" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>289</v>
@@ -18547,72 +18735,72 @@
         <v>190</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>1355</v>
+        <v>1343</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>1356</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="36">
       <c r="A13" s="4" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="54">
+    <row r="15" spans="1:7" ht="72">
       <c r="A15" s="4" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>1317</v>
+        <v>1378</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -18693,7 +18881,7 @@
         <v>446</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>93</v>
@@ -19597,7 +19785,7 @@
     </row>
     <row r="11" spans="1:45" ht="54">
       <c r="A11" s="12" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>615</v>
@@ -19654,7 +19842,7 @@
         <v>0.5</v>
       </c>
       <c r="T11" s="12" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="U11" s="33">
         <v>0</v>
@@ -19669,16 +19857,16 @@
         <v>629</v>
       </c>
       <c r="Y11" s="12" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="Z11" s="34" t="s">
         <v>660</v>
       </c>
       <c r="AA11" s="34" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="AB11" s="12" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="54">
@@ -19758,10 +19946,10 @@
         <v>705</v>
       </c>
       <c r="AA12" s="4" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="AB12" s="11" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="108">
@@ -19835,50 +20023,50 @@
         <v>663</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="Y13" s="16" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="Z13" s="34" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="AA13" s="34" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="AB13" s="11" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
     </row>
-    <row r="14" spans="1:45" ht="36">
-      <c r="A14" s="41" t="s">
-        <v>1280</v>
-      </c>
-      <c r="B14" s="42" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C14" s="43" t="s">
+    <row r="14" spans="1:45" ht="72">
+      <c r="A14" s="39" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>620</v>
       </c>
-      <c r="D14" s="43" t="s">
-        <v>1282</v>
-      </c>
-      <c r="E14" s="44">
+      <c r="D14" s="12" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E14" s="13">
         <v>2300</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="13">
         <v>60</v>
       </c>
-      <c r="H14" s="44">
+      <c r="H14" s="13">
         <v>90</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="13">
         <v>100</v>
       </c>
-      <c r="J14" s="44">
+      <c r="J14" s="13">
         <v>100</v>
       </c>
       <c r="K14" s="33">
@@ -19908,8 +20096,8 @@
       <c r="S14" s="33">
         <v>0.5</v>
       </c>
-      <c r="T14" s="43" t="s">
-        <v>1285</v>
+      <c r="T14" s="12" t="s">
+        <v>1281</v>
       </c>
       <c r="U14" s="33">
         <v>0</v>
@@ -19917,14 +20105,17 @@
       <c r="V14" s="33">
         <v>0</v>
       </c>
-      <c r="W14" s="43" t="s">
-        <v>1283</v>
-      </c>
-      <c r="X14" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="Y14" s="45" t="s">
-        <v>1286</v>
+      <c r="W14" s="12" t="s">
+        <v>1279</v>
+      </c>
+      <c r="X14" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="Y14" s="16" t="s">
+        <v>1282</v>
+      </c>
+      <c r="Z14" s="34" t="s">
+        <v>1372</v>
       </c>
     </row>
   </sheetData>
@@ -20113,7 +20304,7 @@
         <v>174</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>166</v>
@@ -20159,7 +20350,7 @@
         <v>175</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>166</v>
@@ -20471,213 +20662,213 @@
     </row>
     <row r="14" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="E14" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="73.8" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="E15" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="73.8" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="E16" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="73.8" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="E17" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="73.8" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="E18" t="s">
         <v>805</v>
       </c>
-      <c r="E18" t="s">
-        <v>807</v>
-      </c>
       <c r="F18" s="11" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="73.8" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="E19" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="73.8" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E20" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F20" s="11" t="s">
+        <v>980</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="J20" s="11" t="s">
         <v>983</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>902</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>854</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="36">
       <c r="A21" s="4" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>166</v>
@@ -20689,24 +20880,24 @@
         <v>662</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="54">
       <c r="A22" s="4" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>166</v>
@@ -20718,24 +20909,24 @@
         <v>662</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="36">
       <c r="A23" s="4" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>166</v>
@@ -20747,24 +20938,24 @@
         <v>662</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="36">
       <c r="A24" s="4" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>166</v>
@@ -20776,24 +20967,24 @@
         <v>662</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="36">
       <c r="A25" s="4" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>166</v>
@@ -20805,24 +20996,24 @@
         <v>662</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="36">
       <c r="A26" s="4" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>166</v>
@@ -20834,24 +21025,24 @@
         <v>662</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="36">
       <c r="A27" s="4" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>166</v>
@@ -20863,173 +21054,173 @@
         <v>662</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="G27" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>1185</v>
+      </c>
+      <c r="J27" s="11" t="s">
         <v>1045</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>1188</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="54">
       <c r="A28" s="4" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="54">
       <c r="A29" s="4" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="E29" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F29" s="11" t="s">
         <v>1172</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>1175</v>
-      </c>
       <c r="G29" s="4" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="54">
       <c r="A30" s="4" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>1163</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="E30" s="4" t="s">
         <v>1169</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>1172</v>
-      </c>
       <c r="F30" s="11" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="72">
       <c r="A31" s="4" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="72">
       <c r="A32" s="4" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -21352,185 +21543,185 @@
     </row>
     <row r="8" spans="1:18" ht="36">
       <c r="A8" s="4" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>914</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>917</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="36">
       <c r="A10" s="4" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="36">
       <c r="A11" s="4" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>988</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>926</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>903</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>991</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>929</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="36">
       <c r="A12" s="4" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="4" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>166</v>
@@ -21539,30 +21730,30 @@
         <v>565</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>214</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="36">
       <c r="A14" s="4" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>166</v>
@@ -21571,33 +21762,33 @@
         <v>560</v>
       </c>
       <c r="E14" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="36">
       <c r="A15" s="4" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>166</v>
@@ -21606,33 +21797,33 @@
         <v>562</v>
       </c>
       <c r="E15" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="36">
       <c r="A16" s="4" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>166</v>
@@ -21641,33 +21832,33 @@
         <v>561</v>
       </c>
       <c r="E16" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="36">
       <c r="A17" s="4" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>166</v>
@@ -21676,33 +21867,33 @@
         <v>563</v>
       </c>
       <c r="E17" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="36">
       <c r="A18" s="4" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>166</v>
@@ -21711,33 +21902,33 @@
         <v>564</v>
       </c>
       <c r="E18" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="4" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>166</v>
@@ -21746,205 +21937,205 @@
         <v>565</v>
       </c>
       <c r="E19" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>214</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="36">
       <c r="A20" s="4" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="4" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>1123</v>
       </c>
-      <c r="F21" s="11" t="s">
-        <v>1126</v>
-      </c>
       <c r="G21" s="4" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="4" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>1120</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>1123</v>
-      </c>
       <c r="F22" s="11" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="36">
       <c r="A23" s="4" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="4" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="4" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>166</v>
@@ -21953,23 +22144,23 @@
         <v>565</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I25" s="11"/>
       <c r="K25" s="4" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
   </sheetData>
@@ -22005,10 +22196,10 @@
         <v>410</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E1" s="21" t="s">
         <v>411</v>
@@ -22060,66 +22251,66 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>808</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>813</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="I3" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>814</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>809</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>810</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>815</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>809</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>968</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>969</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="I4" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>971</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>970</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>976</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>977</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>972</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>973</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>974</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -22127,32 +22318,32 @@
         <v>707</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>1098</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>1100</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>1099</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>1101</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>1102</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>1101</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>1104</v>
-      </c>
       <c r="K5" s="4" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -22228,7 +22419,7 @@
         <v>418</v>
       </c>
       <c r="O1" s="31" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="P1" s="32" t="s">
         <v>417</v>
@@ -22251,7 +22442,7 @@
         <v>498</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>500</v>
@@ -22348,75 +22539,75 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="4" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="4" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="4" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="4" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="4" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>750</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>752</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>754</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>755</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>756</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -22432,42 +22623,42 @@
         <v>15</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="4" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>750</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>752</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>761</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>755</v>
-      </c>
       <c r="I10" s="4" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -22483,42 +22674,42 @@
         <v>40</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>765</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>750</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>752</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>766</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>767</v>
-      </c>
       <c r="I11" s="4" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -22534,42 +22725,42 @@
         <v>150</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="4" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>750</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>752</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>770</v>
-      </c>
       <c r="H12" s="4" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -22585,74 +22776,74 @@
         <v>150</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="4" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="O13">
         <v>50</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="54">
       <c r="A14" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>778</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>781</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>782</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="I14" s="4" t="s">
         <v>783</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>785</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -22664,228 +22855,228 @@
         <v>120</v>
       </c>
       <c r="Q14" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="R14" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="S14" s="11" t="s">
         <v>786</v>
-      </c>
-      <c r="R14" s="11" t="s">
-        <v>787</v>
-      </c>
-      <c r="S14" s="11" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="4" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="O15">
         <v>70</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="4" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>940</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>941</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>943</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="O16">
         <v>50</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="4" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="O17">
         <v>70</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="4" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>1089</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>1092</v>
-      </c>
       <c r="D19" s="4" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="O19">
         <v>60</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="4" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="O20">
         <v>80</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>1090</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>1093</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="O21">
         <v>110</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
     </row>
   </sheetData>
@@ -22936,10 +23127,10 @@
         <v>439</v>
       </c>
       <c r="P2" s="23" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="Q2" s="23" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="3" spans="2:17">
@@ -22971,7 +23162,7 @@
         <v>523</v>
       </c>
       <c r="Q3" s="23" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="4" spans="2:17">
@@ -23003,7 +23194,7 @@
         <v>524</v>
       </c>
       <c r="Q4" s="23" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="5" spans="2:17">
@@ -23035,7 +23226,7 @@
         <v>171</v>
       </c>
       <c r="Q5" s="23" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="6" spans="2:17">
@@ -23067,7 +23258,7 @@
         <v>526</v>
       </c>
       <c r="Q6" s="23" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="7" spans="2:17">
@@ -23099,7 +23290,7 @@
         <v>168</v>
       </c>
       <c r="Q7" s="23" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="8" spans="2:17">
@@ -23116,10 +23307,10 @@
         <v>461</v>
       </c>
       <c r="P8" s="40" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="9" spans="2:17">
@@ -23130,10 +23321,10 @@
         <v>458</v>
       </c>
       <c r="P9" s="40" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="10" spans="2:17">

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B630DB0-FE76-40A1-A054-D61927F6F496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7F6CE2-AA9D-4554-AF0B-0F3CAF55EB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2746" uniqueCount="1384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2784" uniqueCount="1407">
   <si>
     <t>ID</t>
   </si>
@@ -11207,13 +11207,6 @@
     <t>(アイテムID:shadow_wolf_fur)*1+(アイテムID:shadow_wolf_nail)*1+65G</t>
   </si>
   <si>
-    <t>２秒</t>
-    <rPh sb="1" eb="2">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>スキル</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -11915,20 +11908,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>攻撃力 * 0.3</t>
-    <rPh sb="0" eb="3">
-      <t>コウゲキリョク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>10秒</t>
-    <rPh sb="2" eb="3">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>範囲指定</t>
     <rPh sb="0" eb="4">
       <t>ハンイシテイ</t>
@@ -11976,13 +11955,6 @@
   </si>
   <si>
     <t>poisonous_stinger</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>15秒</t>
-    <rPh sb="2" eb="3">
-      <t>ビョウ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -12150,21 +12122,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>25秒</t>
-    <rPh sb="2" eb="3">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>500px</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>攻撃力 * 0.05</t>
-    <rPh sb="0" eb="3">
-      <t>コウゲキリョク</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -12910,23 +12868,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>8秒</t>
-    <rPh sb="1" eb="2">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>敵スキルID(vine_whip,poisonous_stinger,sowing_seeds,welcome_rain,dappled_sunlight,intertwined_roots,picking_flowers,chocolate_lily)テキ</t>
   </si>
   <si>
     <t>intertwined_roots</t>
-  </si>
-  <si>
-    <t>攻撃力 * 0.2コウゲキリョク</t>
-  </si>
-  <si>
-    <t>攻撃力 * 0.1コウゲキリョク</t>
   </si>
   <si>
     <t>(状態ID:debuff_Injury)4sジョウタイ</t>
@@ -12941,15 +12886,6 @@
   </si>
   <si>
     <t>対象に(状態ID:debuff_plant)が付与されている場合
-それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態ID:debuff_plant)が解除されている必要があるタイショウジョウタイフヨバアイダンカイキョウカドキョウカタイショウジョウタイフタタキョウカイチドジョウタイカイジョヒツヨウ</t>
-  </si>
-  <si>
-    <t>発動者はこのスキルでの回復量が3倍になる
-対象に(状態ID:debuff_plant)が付与されている場合
-それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態ID:debuff_plant)が解除されている必要があるハツドウシャカイフクリョウバイ</t>
-  </si>
-  <si>
-    <t>対象に(状態ID:debuff_plant)が付与されている場合
 それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態ID:debuff_plant)が解除されている必要がある</t>
   </si>
   <si>
@@ -12967,6 +12903,417 @@
     <rPh sb="22" eb="23">
       <t>トキ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.4</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>16秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(行動速度-15%)5s</t>
+    <rPh sb="1" eb="3">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>発動者はこのスキルでの回復量が5倍になる
+対象に(状態ID:debuff_plant)が付与されている場合
+それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態ID:debuff_plant)が解除されている必要がある</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象に(状態ID:debuff_plant)が付与されている場合
+それの段階を１つ強化する。1度強化した対象の状態をこのスキルで再び強化するには一度(状態ID:debuff_plant)が解除されている必要がある</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パッシブ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>手数勝負</t>
+    <rPh sb="0" eb="2">
+      <t>テカズ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自身</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スキル速度</t>
+    <rPh sb="3" eb="5">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>行動回数が増える代わりに1回あたりのダメージが低下する</t>
+    <rPh sb="0" eb="4">
+      <t>コウドウカイスウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>行動速度+50%、スキル速度+50%上昇
+代わりに与ダメージ率-40%</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リハス/拳具</t>
+    <rPh sb="4" eb="6">
+      <t>ケング</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>剛拳</t>
+    <rPh sb="0" eb="1">
+      <t>ゴウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>コブシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>同じ敵に合計3回物理ダメージを与えた時、状態を付与する。付与したらカウントはリセットされる</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>睡眠(debuff_sleep)6秒</t>
+    <rPh sb="0" eb="2">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に物理ダメージを与え続けると"睡眠"を付与する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に3回物理ダメージを与えるたびに6秒の"睡眠"を付与する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力上乗せ</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ウワノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱速度-50%,消費MP量+30%,魔法与ダメージ率+20%</t>
+    <rPh sb="0" eb="4">
+      <t>エイショウソクド</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>マホウヨ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱にかかる時間と消費MPが増加する代わりに与える魔法ダメージが増加する</t>
+    <rPh sb="0" eb="2">
+      <t>エイショウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法与ダメージ率が20%上昇する代わりに詠唱速度-50%、消費MP量+30%</t>
+    <rPh sb="0" eb="3">
+      <t>マホウヨ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>エイショウソクド</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>リョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>身軽援助</t>
+    <rPh sb="0" eb="2">
+      <t>ミガル</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>エンジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>行動速度+50%,スキル速度+50%,与ダメージ率-40%</t>
+    <rPh sb="0" eb="4">
+      <t>コウドウソクド</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動速度+30%,
+詠唱速度+50%,MP再生率-4%</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>エイショウソクド</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>サイセイリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MPを消費し続け、移動速度と詠唱速度を上昇させる</t>
+    <rPh sb="3" eb="5">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>エイショウソクド</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MP再生率-4%で移動速度+30%、詠唱速度+50%のバフを自身に与える</t>
+    <rPh sb="2" eb="5">
+      <t>サイセイリツ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t>エイショウソクド</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>number_of_times</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>gouken</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>magic_add_on</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>lightweight_buff</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -13158,7 +13505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -13259,6 +13606,19 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13726,7 +14086,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>19</v>
@@ -14044,7 +14404,7 @@
         <v>20</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>20</v>
@@ -14282,7 +14642,7 @@
         <v>20</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>214</v>
@@ -14520,7 +14880,7 @@
         <v>20</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>19</v>
@@ -15220,7 +15580,7 @@
         <v>20</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>20</v>
@@ -15418,7 +15778,7 @@
         <v>852</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>829</v>
@@ -15480,7 +15840,7 @@
         <v>896</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="L25" s="16" t="s">
         <v>832</v>
@@ -15545,7 +15905,7 @@
         <v>853</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>829</v>
@@ -15607,7 +15967,7 @@
         <v>854</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>829</v>
@@ -15663,7 +16023,7 @@
         <v>823</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="G28">
         <v>10</v>
@@ -15675,7 +16035,7 @@
         <v>25</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>828</v>
@@ -15746,7 +16106,7 @@
         <v>20</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>828</v>
@@ -15814,7 +16174,7 @@
         <v>20</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="L30" s="34" t="s">
         <v>827</v>
@@ -15879,7 +16239,7 @@
         <v>1046</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>324</v>
@@ -15945,7 +16305,7 @@
         <v>1047</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>688</v>
@@ -16013,7 +16373,7 @@
         <v>1048</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>324</v>
@@ -16078,7 +16438,7 @@
         <v>1049</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="M34" s="12" t="s">
         <v>324</v>
@@ -16137,7 +16497,7 @@
         <v>823</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="G35">
         <v>10</v>
@@ -16149,7 +16509,7 @@
         <v>25</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>246</v>
@@ -16223,7 +16583,7 @@
         <v>20</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>246</v>
@@ -16294,7 +16654,7 @@
         <v>25</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>1223</v>
+        <v>651</v>
       </c>
       <c r="L37" s="34" t="s">
         <v>1069</v>
@@ -16365,7 +16725,7 @@
         <v>1046</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="M38" s="13" t="s">
         <v>324</v>
@@ -16431,7 +16791,7 @@
         <v>1047</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="L39" s="16" t="s">
         <v>688</v>
@@ -16500,7 +16860,7 @@
         <v>1048</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="M40" s="12" t="s">
         <v>324</v>
@@ -16566,7 +16926,7 @@
         <v>1049</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>1223</v>
+        <v>1362</v>
       </c>
       <c r="M41" s="12" t="s">
         <v>324</v>
@@ -16637,7 +16997,7 @@
         <v>60</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>1223</v>
+        <v>682</v>
       </c>
       <c r="L42" s="34" t="s">
         <v>644</v>
@@ -16685,124 +17045,246 @@
     </row>
     <row r="43" spans="1:26" ht="54">
       <c r="A43" s="12" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>391</v>
       </c>
       <c r="C43" s="12" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>1224</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>1225</v>
-      </c>
       <c r="E43" s="12" t="s">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F43" s="12" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G43" s="12" t="s">
         <v>1227</v>
       </c>
-      <c r="G43" s="12" t="s">
-        <v>1228</v>
-      </c>
       <c r="H43" s="16" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43" s="12" t="s">
+        <v>1231</v>
+      </c>
+      <c r="L43" s="34" t="s">
+        <v>1227</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>1228</v>
+      </c>
+      <c r="N43" s="13" t="s">
+        <v>1229</v>
+      </c>
+      <c r="O43" s="12" t="s">
+        <v>1227</v>
+      </c>
+      <c r="P43" s="12" t="s">
+        <v>1230</v>
+      </c>
+      <c r="Q43" s="12" t="s">
         <v>1232</v>
       </c>
-      <c r="L43" s="34" t="s">
-        <v>1228</v>
-      </c>
-      <c r="M43" s="12" t="s">
-        <v>1229</v>
-      </c>
-      <c r="N43" s="13" t="s">
-        <v>1230</v>
-      </c>
-      <c r="O43" s="12" t="s">
-        <v>1228</v>
-      </c>
-      <c r="P43" s="12" t="s">
-        <v>1231</v>
-      </c>
-      <c r="Q43" s="12" t="s">
+      <c r="R43" s="12" t="s">
+        <v>1227</v>
+      </c>
+      <c r="T43" s="12" t="s">
+        <v>1371</v>
+      </c>
+      <c r="U43" s="12" t="s">
+        <v>1234</v>
+      </c>
+      <c r="V43" s="12" t="s">
         <v>1233</v>
       </c>
-      <c r="R43" s="12" t="s">
-        <v>1228</v>
-      </c>
-      <c r="T43" s="12" t="s">
+      <c r="W43" s="12" t="s">
+        <v>1235</v>
+      </c>
+      <c r="X43" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="Y43" s="12" t="s">
+        <v>1237</v>
+      </c>
+      <c r="Z43" s="12" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" ht="36">
+      <c r="A44" s="4" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C44" s="41" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E44" s="41" t="s">
         <v>1382</v>
       </c>
-      <c r="U43" s="12" t="s">
-        <v>1235</v>
-      </c>
-      <c r="V43" s="12" t="s">
-        <v>1234</v>
-      </c>
-      <c r="W43" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="X43" s="12" t="s">
-        <v>1237</v>
-      </c>
-      <c r="Y43" s="12" t="s">
-        <v>1238</v>
-      </c>
-      <c r="Z43" s="12" t="s">
-        <v>1239</v>
+      <c r="P44" s="41" t="s">
+        <v>1383</v>
+      </c>
+      <c r="S44" s="41" t="s">
+        <v>1399</v>
+      </c>
+      <c r="U44" s="41"/>
+      <c r="V44" s="41" t="s">
+        <v>1385</v>
+      </c>
+      <c r="W44" s="41" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" ht="36">
+      <c r="A45" s="43" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C45" s="41" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E45" s="41" t="s">
+        <v>1388</v>
+      </c>
+      <c r="P45" s="41" t="s">
+        <v>1389</v>
+      </c>
+      <c r="S45" s="4" t="s">
+        <v>1391</v>
+      </c>
+      <c r="U45" s="41" t="s">
+        <v>1390</v>
+      </c>
+      <c r="V45" s="41" t="s">
+        <v>1392</v>
+      </c>
+      <c r="W45" s="41" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" ht="54">
+      <c r="A46" s="43" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B46" s="42" t="s">
+        <v>394</v>
+      </c>
+      <c r="C46" s="41" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E46" s="41" t="s">
+        <v>1394</v>
+      </c>
+      <c r="P46" s="41" t="s">
+        <v>1383</v>
+      </c>
+      <c r="S46" s="43" t="s">
+        <v>1395</v>
+      </c>
+      <c r="U46" s="41"/>
+      <c r="V46" s="41" t="s">
+        <v>1396</v>
+      </c>
+      <c r="W46" s="11" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" ht="54">
+      <c r="A47" s="43" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>391</v>
+      </c>
+      <c r="C47" s="41" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E47" s="41" t="s">
+        <v>1398</v>
+      </c>
+      <c r="P47" s="41" t="s">
+        <v>1383</v>
+      </c>
+      <c r="S47" s="44" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U47" s="44"/>
+      <c r="V47" s="41" t="s">
+        <v>1401</v>
+      </c>
+      <c r="W47" s="45" t="s">
+        <v>1402</v>
       </c>
     </row>
     <row r="48" spans="1:26" ht="72">
       <c r="A48" s="4" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C48" s="4"/>
       <c r="E48" s="4" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48" s="4" t="s">
+        <v>1264</v>
+      </c>
+      <c r="L48" s="4" t="s">
         <v>1265</v>
       </c>
-      <c r="L48" s="4" t="s">
+      <c r="M48" s="4" t="s">
         <v>1266</v>
       </c>
-      <c r="M48" s="4" t="s">
+      <c r="N48" s="4" t="s">
+        <v>1264</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>1264</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="Q48" s="4" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R48" s="4" t="s">
         <v>1267</v>
       </c>
-      <c r="N48" s="4" t="s">
-        <v>1265</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>1265</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>1267</v>
-      </c>
-      <c r="Q48" s="4" t="s">
-        <v>1265</v>
-      </c>
-      <c r="R48" s="4" t="s">
+      <c r="T48" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="U48" s="11" t="s">
         <v>1268</v>
-      </c>
-      <c r="T48" s="4" t="s">
-        <v>1263</v>
-      </c>
-      <c r="U48" s="11" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="49" spans="1:26" ht="72">
@@ -17505,7 +17987,7 @@
         <v>644</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>639</v>
@@ -17566,13 +18048,13 @@
         <v>648</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>1376</v>
+        <v>1367</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>667</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>1377</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="36">
@@ -17689,391 +18171,393 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="12" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>1284</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>1278</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>1283</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>1285</v>
       </c>
       <c r="F15" s="13">
         <v>15</v>
       </c>
       <c r="G15" s="12" t="s">
+        <v>1373</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>1279</v>
+      </c>
+      <c r="L15" s="12" t="s">
         <v>1286</v>
       </c>
-      <c r="I15" s="16" t="s">
-        <v>1280</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>1371</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>1280</v>
-      </c>
-      <c r="L15" s="12" t="s">
+      <c r="M15" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>1279</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>1288</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>1279</v>
+      </c>
+      <c r="Q15" s="12" t="s">
         <v>1289</v>
       </c>
-      <c r="M15" s="12" t="s">
+      <c r="R15" s="12" t="s">
+        <v>1279</v>
+      </c>
+      <c r="S15" s="12" t="s">
         <v>1290</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>1280</v>
-      </c>
-      <c r="O15" s="12" t="s">
-        <v>1291</v>
-      </c>
-      <c r="P15" s="12" t="s">
-        <v>1280</v>
-      </c>
-      <c r="Q15" s="12" t="s">
-        <v>1292</v>
-      </c>
-      <c r="R15" s="12" t="s">
-        <v>1280</v>
-      </c>
-      <c r="S15" s="12" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="36">
       <c r="A16" s="12" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F16" s="13">
         <v>5</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="L16" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>1279</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>1288</v>
+      </c>
+      <c r="Q16" s="12" t="s">
         <v>1289</v>
       </c>
-      <c r="M16" s="12" t="s">
-        <v>1297</v>
-      </c>
-      <c r="N16" s="12" t="s">
-        <v>1280</v>
-      </c>
-      <c r="O16" s="12" t="s">
-        <v>1291</v>
-      </c>
-      <c r="Q16" s="12" t="s">
-        <v>1292</v>
-      </c>
       <c r="R16" s="12" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="S16" s="12" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="72">
       <c r="A17" s="12" t="s">
-        <v>1361</v>
+        <v>1355</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F17" s="13">
         <v>5</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J17" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>1300</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>1299</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>1288</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Q17" s="12" t="s">
         <v>1305</v>
       </c>
-      <c r="K17" s="12" t="s">
-        <v>1304</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>1289</v>
-      </c>
-      <c r="M17" s="12" t="s">
-        <v>1303</v>
-      </c>
-      <c r="O17" s="12" t="s">
-        <v>1291</v>
-      </c>
-      <c r="P17" s="12" t="s">
-        <v>1306</v>
-      </c>
-      <c r="Q17" s="12" t="s">
-        <v>1309</v>
-      </c>
       <c r="S17" s="12" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="T17" s="12" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="36">
       <c r="A18" s="3" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="F18" s="2">
         <v>5</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1318</v>
+        <v>1297</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>1280</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="N18" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="72">
+      <c r="A19" s="3" t="s">
         <v>1316</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>1288</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>1281</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>1317</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>1291</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>1292</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>1319</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>1313</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" ht="126">
-      <c r="A19" s="3" t="s">
-        <v>1322</v>
-      </c>
       <c r="C19" s="14" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="F19" s="2">
         <v>10</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1323</v>
+        <v>1317</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>1280</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>1296</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="L19" s="3" t="s">
+      <c r="N19" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>1288</v>
       </c>
-      <c r="M19" s="3" t="s">
-        <v>1281</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>1325</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>1291</v>
-      </c>
       <c r="P19" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>243</v>
       </c>
       <c r="R19" s="2"/>
       <c r="S19" s="3" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="T19" s="3" t="s">
         <v>1379</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="108">
+    <row r="20" spans="1:23" ht="90">
       <c r="A20" s="3" t="s">
-        <v>1327</v>
+        <v>1321</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1326</v>
+        <v>1320</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>1328</v>
+        <v>1322</v>
       </c>
       <c r="F20" s="2">
         <v>10</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>1329</v>
+        <v>1323</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>1280</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>1296</v>
-      </c>
-      <c r="K20" s="3" t="s">
+      <c r="N20" s="3" t="s">
         <v>1324</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>1288</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>1281</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>1330</v>
-      </c>
       <c r="O20" s="3" t="s">
-        <v>1331</v>
+        <v>1325</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>1332</v>
+        <v>1326</v>
       </c>
       <c r="R20" s="2"/>
       <c r="S20" s="3" t="s">
-        <v>1326</v>
+        <v>1320</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="72">
       <c r="A21" s="3" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="F21" s="2">
         <v>10</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>1280</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>1296</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="L21" s="3" t="s">
+      <c r="N21" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>1288</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>1281</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>1334</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>1291</v>
-      </c>
       <c r="P21" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>1292</v>
-      </c>
-      <c r="R21" s="2"/>
+        <v>1289</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>1377</v>
+      </c>
       <c r="S21" s="3" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>1381</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="216">
       <c r="A22" s="3" t="s">
-        <v>1337</v>
+        <v>1331</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F22" s="2">
         <v>10</v>
@@ -18083,38 +18567,38 @@
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>1280</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>1287</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>1289</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>1338</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>1281</v>
-      </c>
       <c r="O22" s="3" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="3" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>1363</v>
+        <v>1357</v>
       </c>
       <c r="U22" s="13"/>
       <c r="V22" s="12"/>
@@ -18122,56 +18606,56 @@
     </row>
     <row r="23" spans="1:23" ht="54">
       <c r="A23" s="3" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F23" s="2">
         <v>25</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>885</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="12"/>
@@ -18180,56 +18664,56 @@
     </row>
     <row r="24" spans="1:23" ht="36">
       <c r="A24" s="3" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F24" s="2">
         <v>25</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>885</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="T24" s="3"/>
       <c r="U24" s="12"/>
@@ -18238,213 +18722,213 @@
     </row>
     <row r="25" spans="1:23" ht="54">
       <c r="A25" s="3" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F25" s="2">
         <v>25</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>885</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" s="3" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
       <c r="S25" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="T25" s="3" t="s">
         <v>1348</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="12" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="F26" s="13">
         <v>5</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>1323</v>
+        <v>1317</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="O26" s="12" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="P26" s="13" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>1359</v>
+        <v>1353</v>
       </c>
       <c r="T26" s="12" t="s">
-        <v>1360</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="27" spans="1:23">
       <c r="A27" s="12" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F27" s="13">
         <v>25</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>885</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="O27" s="12" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="P27" s="13" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="R27" s="16" t="s">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="S27" s="39" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="28" spans="1:23" ht="54">
       <c r="A28" s="12" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="F28" s="13">
         <v>0</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>1370</v>
+        <v>1364</v>
       </c>
       <c r="I28" s="12" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>1362</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="M28" s="12" t="s">
         <v>1280</v>
       </c>
-      <c r="J28" s="12" t="s">
-        <v>1298</v>
-      </c>
-      <c r="K28" s="12" t="s">
-        <v>1368</v>
-      </c>
-      <c r="L28" s="12" t="s">
+      <c r="N28" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="O28" s="12" t="s">
         <v>1288</v>
       </c>
-      <c r="M28" s="12" t="s">
-        <v>1281</v>
-      </c>
-      <c r="N28" s="12" t="s">
-        <v>1369</v>
-      </c>
-      <c r="O28" s="12" t="s">
-        <v>1291</v>
-      </c>
       <c r="P28" s="13" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>1359</v>
+        <v>1353</v>
       </c>
       <c r="S28" s="39" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="T28" s="34" t="s">
-        <v>1383</v>
+        <v>1372</v>
       </c>
     </row>
   </sheetData>
@@ -18654,79 +19138,79 @@
     </row>
     <row r="9" spans="1:7" ht="36">
       <c r="A9" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>1245</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>1246</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>328</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>1253</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>1254</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="54">
       <c r="A10" s="4" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>1248</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>1249</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>328</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>1250</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>1251</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="126">
       <c r="A11" s="4" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>1241</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>1240</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>1242</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>1335</v>
+        <v>1329</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>1243</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="90">
       <c r="A12" s="4" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>289</v>
@@ -18735,72 +19219,72 @@
         <v>190</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>1344</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="36">
       <c r="A13" s="4" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>1258</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>1259</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>1260</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>1271</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>1272</v>
-      </c>
       <c r="C14" s="4" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E14" s="11" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>1273</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>1275</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="72">
       <c r="A15" s="4" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>1378</v>
+        <v>1369</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -18875,7 +19359,7 @@
         <v>92</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>445</v>
+        <v>1384</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>446</v>
@@ -20040,34 +20524,34 @@
     </row>
     <row r="14" spans="1:45" ht="72">
       <c r="A14" s="39" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>1276</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>1277</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>620</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="E14" s="13">
-        <v>2300</v>
+        <v>3800</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14" s="13">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H14" s="13">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="I14" s="13">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J14" s="13">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K14" s="33">
         <v>0</v>
@@ -20097,7 +20581,7 @@
         <v>0.5</v>
       </c>
       <c r="T14" s="12" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="U14" s="33">
         <v>0</v>
@@ -20106,16 +20590,16 @@
         <v>0</v>
       </c>
       <c r="W14" s="12" t="s">
+        <v>1278</v>
+      </c>
+      <c r="X14" s="12" t="s">
         <v>1279</v>
       </c>
-      <c r="X14" s="12" t="s">
-        <v>1280</v>
-      </c>
       <c r="Y14" s="16" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Z14" s="34" t="s">
-        <v>1372</v>
+        <v>1365</v>
       </c>
     </row>
   </sheetData>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7F6CE2-AA9D-4554-AF0B-0F3CAF55EB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0E6E72-D53B-40FB-B5C3-CDE6E09FD510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2784" uniqueCount="1407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3103" uniqueCount="1544">
   <si>
     <t>ID</t>
   </si>
@@ -7758,10 +7758,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>詠唱後、魔力で生成された弾を発射する</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>少しのチャージを行い、敵に剣を振りかざし、物理ダメージを与える</t>
     <rPh sb="0" eb="1">
       <t>スコ</t>
@@ -9553,17 +9549,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>詠唱後、魔力で生成された弾を発射する。
-まれに"睡眠"を付与する</t>
-    <rPh sb="24" eb="26">
-      <t>スイミン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>フヨ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>１秒の詠唱を行った後、指定した方向に魔力で生成した弾を発射する。当たった敵に(式=値)の魔法ダメージを与える。魔力弾は敵に当たるか最大射程まで飛ぶと消滅する。20%の確率で敵に３秒の"睡眠"を付与する</t>
     <rPh sb="1" eb="2">
       <t>ビョウ</t>
@@ -11190,9 +11175,6 @@
   <si>
     <t>(アイテムID:shadow_wolf_fur)*2+(アイテムID:shadow_wolf_nail)*2+130G</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>(アイテムID:shadow_wolf_fur)*1+(アイテムID:shadow_wolf_fang)*1+(アイテムID:shadow_wolf_nail)*1+130G</t>
   </si>
   <si>
     <t>3秒の詠唱後、範囲内の味方の行動CDが残り0.3秒以上の場合、即座に残り0.3秒にまで短縮する</t>
@@ -12057,53 +12039,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>スキル効果時間中、対象と自身を行動不可(行動CDすら上がらない)にさせ、毎秒ダメージを与える
-与えたダメージの2倍の値分発動者のHPを回復させる</t>
-    <rPh sb="3" eb="8">
-      <t>コウカジカンチュウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>コウドウフカ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>コウドウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>マイビョウ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>バイ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="60" eb="63">
-      <t>ハツドウシャ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>カイフク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>種まき</t>
     <rPh sb="0" eb="1">
       <t>タネ</t>
@@ -12119,10 +12054,6 @@
   </si>
   <si>
     <t>sowing_seeds</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>500px</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -12868,9 +12799,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>敵スキルID(vine_whip,poisonous_stinger,sowing_seeds,welcome_rain,dappled_sunlight,intertwined_roots,picking_flowers,chocolate_lily)テキ</t>
-  </si>
-  <si>
     <t>intertwined_roots</t>
   </si>
   <si>
@@ -12878,11 +12806,6 @@
   </si>
   <si>
     <t>(状態ID:debuff_Injury)を4秒付与ジョウタイビョウフヨ</t>
-  </si>
-  <si>
-    <t>この状態が付与されている間に付与してきた相手にドット以外のダメージを与えた場合
-付与してきた相手の次の行動が(敵スキルID:absorption_of_reunion)に強制される
-相手の(敵スキルID:absorption_of_reunion)のターゲットは必ず自分になるジョウタイフヨアイダフヨアイテイガイアタバアイフヨアイテツギコウドウテキキョウセイアイテテキカナラジブン</t>
   </si>
   <si>
     <t>対象に(状態ID:debuff_plant)が付与されている場合
@@ -13314,6 +13237,1494 @@
   </si>
   <si>
     <t>lightweight_buff</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_crystal</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_flower</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フロスティーニのツル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フロスティーニの花</t>
+    <rPh sb="8" eb="9">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素材</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フロスティーニの苔</t>
+    <rPh sb="8" eb="9">
+      <t>コケ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_moss</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>毒針があるフロスティーニのツル</t>
+    <rPh sb="0" eb="2">
+      <t>ドクバリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フロスティーニの頭に咲いていた
+たくさんの花の一つ</t>
+    <rPh sb="8" eb="9">
+      <t>アタマ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヒト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フロスティーニの苔がたくさんついていた頭</t>
+    <rPh sb="8" eb="9">
+      <t>コケ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アタマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フロスティーニの石</t>
+    <rPh sb="8" eb="9">
+      <t>イシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フロスティーニ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生命力</t>
+    <rPh sb="0" eb="3">
+      <t>セイメイリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>運命</t>
+    <rPh sb="0" eb="2">
+      <t>ウンメイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HP再生率+5%</t>
+    <rPh sb="2" eb="5">
+      <t>サイセイリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ガード率+30%</t>
+    <rPh sb="3" eb="4">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HP再生率が上昇する</t>
+    <rPh sb="2" eb="5">
+      <t>サイセイリツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HP再生率が5%上昇する</t>
+    <rPh sb="2" eb="5">
+      <t>サイセイリツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ガード率が上昇する</t>
+    <rPh sb="3" eb="4">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ガード率が30%上昇する</t>
+    <rPh sb="3" eb="4">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_helm</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_armor</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_leggings</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_boots</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_glove</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_pendant</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスティニヘルム</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスティニレギンス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスティニブーツ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスティニグローブ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスティニペンダント</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>頭</t>
+    <rPh sb="0" eb="1">
+      <t>アタマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>胴</t>
+    <rPh sb="0" eb="1">
+      <t>ドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>足</t>
+    <rPh sb="0" eb="1">
+      <t>アシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>靴</t>
+    <rPh sb="0" eb="1">
+      <t>クツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>手</t>
+    <rPh sb="0" eb="1">
+      <t>テ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HP+5%,攻撃+10%,
+魔力+10%</t>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+15%,
+魔力+15%</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HP+10%,防御+10%,
+魔防+10%</t>
+    <rPh sb="7" eb="9">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>マボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HP+20%</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HP再生率+10%</t>
+    <rPh sb="2" eb="5">
+      <t>サイセイリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_attack_knife</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_attack_sword</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_attack_fist</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_attack_staff</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_attack_stick</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_attack_book</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_attack_flute</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>予知の音</t>
+    <rPh sb="0" eb="2">
+      <t>ヨチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>半径220px・40度</t>
+    <rPh sb="0" eb="2">
+      <t>ハンケイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フィール</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>buff_feel</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ステータスバフ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この状態が付与されている間に付与してきた相手にドット以外のダメージを与えた場合
+付与してきた相手の次の行動が(敵スキルID:absorption_of_reunion)に強制される
+相手の(敵スキルID:absorption_of_reunion)のターゲットは必ず自分になる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディステ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ガード率が50%上昇する、また効果終了時に効果時間中にガードした回数だけ"ディステ"を獲得する</t>
+    <rPh sb="3" eb="4">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="15" eb="20">
+      <t>コウカシュウリョウジ</t>
+    </rPh>
+    <rPh sb="21" eb="26">
+      <t>コウカジカンチュウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>カクトク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ガード率が上昇する、またガードした回数だけ"ディステ"を獲得する</t>
+    <rPh sb="3" eb="4">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カクトク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>会心率+100%、会心ダメージを与えるたびに1スタック消費する</t>
+    <rPh sb="0" eb="3">
+      <t>カイシンリツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイシン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ショウヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>会心率が上昇する</t>
+    <rPh sb="0" eb="3">
+      <t>カイシンリツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>会心率が100%上昇する、会心ダメージを与えた時にスタックを消費する</t>
+    <rPh sb="0" eb="3">
+      <t>カイシンリツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイシン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ショウヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>buff_deste</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:buff_feel)5s</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、範囲内の味方に"フィール"を付与する</t>
+    <rPh sb="0" eb="3">
+      <t>エイショウゴ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ハンイナイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>0.5秒の詠唱後、範囲内の味方に5秒の"フィール"を付与する</t>
+    <rPh sb="3" eb="4">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ハンイナイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルごとに範囲指定の角度が+(0/10/20/30/40/50)度</t>
+    <rPh sb="6" eb="10">
+      <t>ハンイシテイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとにスキルの範囲が+(10/20/30/40/50)度拡大する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カクダイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に剣を突き刺し、物理ダメージを与え、体力を吸収する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キュウシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>少しのチャージを行い、敵に剣を振りかざし、物理ダメージを与え、体力を吸収する</t>
+    <rPh sb="0" eb="1">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵の顔を殴り、物理ダメージを与え、体力を吸収する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナグ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>棒具を振り、端を1回ずつ当て、物理ダメージを与え、体力を吸収する</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(このスキルが命中した敵の数*5)だけ使用者のMPを回復する</t>
+    <rPh sb="7" eb="9">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>シヨウシャ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、魔力で生成された弾を発射し、命中した敵に魔法ダメージを与える。敵に命中した時MPを回復する</t>
+    <rPh sb="18" eb="20">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、指定した範囲内の敵に衝撃を与え、魔法ダメージを与える。敵に命中した数に応じてMPを回復する</t>
+    <rPh sb="0" eb="3">
+      <t>エイショウゴ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショウゲキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、魔力で生成された弾を発射し、命中した敵に魔法ダメージを与える。
+まれに"睡眠"を付与する</t>
+    <rPh sb="18" eb="20">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、魔力で生成された弾を発射すし、命中した敵に魔法ダメージを与える</t>
+    <rPh sb="19" eb="21">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1秒の詠唱後、指定した範囲内の敵に衝撃を与え、(式=値)の魔法ダメージを与える。敵に命中した数1体につきMPを５回復する</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>エイショウゴ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショウゲキ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>このスキルで与えたダメージの40%分使用者を回復させる</t>
+    <rPh sb="6" eb="7">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>シヨウシャ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に剣を突き刺し、(式=値)の物理ダメージを与え、与えたダメージの40%分の体力を吸収する。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>キュウシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1秒のチャージ後、敵に剣を振りかざし、(式=値)の物理ダメージを与え、与えたダメージの40%分の体力を吸収する。</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵の顔を殴り、(式=値)の物理ダメージを与え、与えたダメージの40%分の体力を吸収する。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナグ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>このスキルは2回ヒットする
+このスキルで与えたダメージの40%分使用者を回復させる。回復も2回分行われる</t>
+    <rPh sb="7" eb="8">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>シヨウシャ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>カイブン</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>棒具を振り、端を2回ずつ当て、(式=値)の物理ダメージを2度与え、与えたダメージの40%分の体力を吸収する。</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルごとに体力の回復量が+(0/10/20/30/40/50)%増加</t>
+    <rPh sb="6" eb="8">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに体力の吸収量が増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>キュウシュウリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルごとにMPの回復量が+(0/5/10/15/20/25)増加</t>
+    <rPh sb="9" eb="12">
+      <t>カイフクリョウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>このスキルが敵に命中した時、使用者のMPを15回復する</t>
+    <rPh sb="6" eb="7">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>シヨウシャ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>１秒の詠唱を行った後、指定した方向に魔力で生成した弾を発射する。当たった敵に(式=値)の魔法ダメージを与える。魔力弾は敵に当たるか最大射程まで飛ぶと消滅する。魔力弾が敵に命中した場合、MPを15回復する</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エイショウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ハッシャ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="55" eb="58">
+      <t>マリョクダン</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="65" eb="69">
+      <t>サイダイシャテイ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ショウメツ</t>
+    </rPh>
+    <rPh sb="79" eb="82">
+      <t>マリョクダン</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとにMPの回復量が増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>カイフクリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに体力の吸収量が+(10/20/30/40/50)%増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>キュウシュウリョウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルごとにこのスキルの範囲+(0/6/12/18/24/30)px増加</t>
+    <rPh sb="12" eb="14">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとにスキルの範囲が増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとにスキルの範囲が(10/20/30/40/50)%増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとにMPの回復量が+(0/5/10/15/20/25)増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>カイフクリョウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アイテムID((flostiny_moss)*4+(flostiny_flower)*3)+300G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アイテムID((flostiny_moss)*5+(flostiny_flower)*3)+300G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:flostiny_crystal)*3+500G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アイテムID((flostiny_moss)*1+(flostiny_flower)*1)+150G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_knife</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_sword</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_fist</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_staff</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_stick</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_book</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>flostiny_flute</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスティニナイフ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスティニソード</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスティニフィスト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスティニスタッフ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスティニステッキ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔導書・ディスティニ</t>
+    <rPh sb="0" eb="3">
+      <t>マドウショ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスティニフルート</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*1+(アイテムID:shadow_wolf_fang)*1+(アイテムID:shadow_wolf_nail)*1+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID:shadow_wolf_fur)*1+(アイテムID:shadow_wolf_fang)*1+(アイテムID:shadow_wolf_nail)*1+130G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID(flostiny_moss)*3+(flostiny_flower)*2)+300G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID(flostiny_moss)*2+(flostiny_flower)*1+(flostiny_crystal)*1)+300G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID(flostiny_moss)*4+(flostiny_flower)*3)+300G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID(flostiny_crystal)*2+(flostiny_flower)*2+(flostiny_moss)*1)+300G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃+35</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力+22</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力+18</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID(flostiny_flower)*1)+150G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(アイテムID(flostiny_moss)*2)+150G</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディスティニアーマー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フロスティーニの頭についていた苔</t>
+    <rPh sb="8" eb="9">
+      <t>アタマ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>コケ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この状態が付与されている間、ガード率が50%上昇する。この効果の間にガードした回数を記録する。この効果終了時、ガードした回数だけのスタック数で自身に(状態ID:buff_deste)を付与する</t>
+    <rPh sb="17" eb="18">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="49" eb="54">
+      <t>コウカシュウリョウジ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵スキルID(vine_whip,poisonous_stinger,sowing_seeds,welcome_rain,dappled_sunlight,intertwined_roots,picking_flowers,chocolate_lily)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>150G/100%,((アイテムID:flostiny_vine)*1/60%)*3,((アイテムID:flostiny_flower)*1/60%)*2,((アイテムID:flostiny_moss)*1/60%)*2,(アイテムID:flostiny_crystal)*1/30%,((アイテムID:d_power_flag)*1/80%)*3</t>
+  </si>
+  <si>
+    <t>(アイテムID(flostiny_vine)*2+(flostiny_flower)*2)+300G</t>
+  </si>
+  <si>
+    <t>(アイテムID(flostiny_vine)*1)+150G</t>
+  </si>
+  <si>
+    <t>(アイテムID(flostiny_vine)*3+(flostiny_flower)*2)+300G</t>
+  </si>
+  <si>
+    <t>(アイテムID(flostiny_vine)*1+(flostiny_flower)*1+(flostiny_moss)*2)+300G</t>
+  </si>
+  <si>
+    <t>アイテムID((flostiny_moss)*2+(flostiny_flower)*1+(flostiny_vine)*2)+300G</t>
+  </si>
+  <si>
+    <t>アイテムID((flostiny_moss)*1+(flostiny_vine)*1)+150G</t>
+  </si>
+  <si>
+    <t>アイテムID((flostiny_moss)*1+(flostiny_vine)*5)+300G</t>
+  </si>
+  <si>
+    <t>(アイテムID:flostiny_vine)*2+150G</t>
+  </si>
+  <si>
+    <t>flostiny_vine</t>
+  </si>
+  <si>
+    <t>スキル効果時間中、対象と自身を行動不可(行動CDすら上がらない)にさせ、毎秒ダメージを与える
+与えたダメージの5倍の値分発動者のHPを回復させる</t>
+    <rPh sb="3" eb="8">
+      <t>コウカジカンチュウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>コウドウフカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="60" eb="63">
+      <t>ハツドウシャ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>incapacitated</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>戦闘不能</t>
+    <rPh sb="0" eb="4">
+      <t>セントウフノウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>行動不可、行動CDやスキルCD等は進まない。この状態がある時、すべての状態を解除する。
+あらゆるものからターゲットにされない。宿屋、もしくは特殊なものでないと解除不可</t>
+    <rPh sb="0" eb="4">
+      <t>コウドウフカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>カイジョ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ヤドヤ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>トクシュ</t>
+    </rPh>
+    <rPh sb="79" eb="83">
+      <t>カイジョフカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>戦闘不能なため、行動できない</t>
+    <rPh sb="0" eb="4">
+      <t>セントウフノウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウドウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -13505,7 +14916,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -13606,19 +15017,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13954,7 +15352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z49"/>
+  <dimension ref="A1:Z62"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -14086,7 +15484,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>19</v>
@@ -14095,10 +15493,10 @@
         <v>313</v>
       </c>
       <c r="N2" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>873</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>874</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>292</v>
@@ -14175,7 +15573,7 @@
         <v>25</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>26</v>
@@ -14255,7 +15653,7 @@
         <v>318</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>214</v>
@@ -14404,7 +15802,7 @@
         <v>20</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>20</v>
@@ -14416,7 +15814,7 @@
         <v>835</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>41</v>
@@ -14493,10 +15891,10 @@
         <v>258</v>
       </c>
       <c r="N7" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>878</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>879</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>292</v>
@@ -14642,7 +16040,7 @@
         <v>20</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>214</v>
@@ -14811,10 +16209,10 @@
         <v>48</v>
       </c>
       <c r="N11" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>880</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>881</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>41</v>
@@ -14880,7 +16278,7 @@
         <v>20</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>19</v>
@@ -14892,7 +16290,7 @@
         <v>217</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>233</v>
@@ -14914,7 +16312,7 @@
         <v>302</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="X12" s="12" t="s">
         <v>367</v>
@@ -15050,7 +16448,7 @@
         <v>20</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>233</v>
@@ -15290,7 +16688,7 @@
         <v>214</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>27</v>
@@ -15370,7 +16768,7 @@
         <v>214</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>27</v>
@@ -15580,7 +16978,7 @@
         <v>20</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>20</v>
@@ -15716,7 +17114,7 @@
         <v>492</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="O23" s="13" t="s">
         <v>490</v>
@@ -15778,7 +17176,7 @@
         <v>852</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>829</v>
@@ -15805,16 +17203,16 @@
         <v>857</v>
       </c>
       <c r="W24" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="X24" s="12" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="Y24" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z24" s="12" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="36">
@@ -15837,10 +17235,10 @@
         <v>10</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L25" s="16" t="s">
         <v>832</v>
@@ -15867,24 +17265,24 @@
         <v>820</v>
       </c>
       <c r="V25" s="12" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="W25" s="12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="X25" s="12" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="Y25" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z25" s="12" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="36">
       <c r="A26" s="12" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>163</v>
@@ -15905,7 +17303,7 @@
         <v>853</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>829</v>
@@ -15932,16 +17330,16 @@
         <v>858</v>
       </c>
       <c r="W26" s="12" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="X26" s="12" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="Y26" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z26" s="12" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="36">
@@ -15967,7 +17365,7 @@
         <v>854</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>829</v>
@@ -15991,22 +17389,22 @@
         <v>822</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="V27" s="12" t="s">
         <v>859</v>
       </c>
       <c r="W27" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="X27" s="12" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="Y27" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z27" s="12" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="72">
@@ -16023,7 +17421,7 @@
         <v>823</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="G28">
         <v>10</v>
@@ -16035,7 +17433,7 @@
         <v>25</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>828</v>
@@ -16044,7 +17442,7 @@
         <v>834</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="O28" s="13" t="s">
         <v>841</v>
@@ -16065,19 +17463,19 @@
         <v>860</v>
       </c>
       <c r="V28" s="12" t="s">
-        <v>861</v>
+        <v>1477</v>
       </c>
       <c r="W28" s="12" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="X28" s="12" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="Y28" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z28" s="12" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="36">
@@ -16106,7 +17504,7 @@
         <v>20</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>828</v>
@@ -16115,7 +17513,7 @@
         <v>830</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="O29" s="13" t="s">
         <v>842</v>
@@ -16133,19 +17531,19 @@
         <v>312</v>
       </c>
       <c r="V29" s="12" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="W29" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="X29" s="12" t="s">
         <v>870</v>
-      </c>
-      <c r="X29" s="12" t="s">
-        <v>871</v>
       </c>
       <c r="Y29" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Z29" s="12" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="36">
@@ -16159,13 +17557,13 @@
         <v>818</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>598</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H30" s="16" t="s">
         <v>214</v>
@@ -16174,7 +17572,7 @@
         <v>20</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L30" s="34" t="s">
         <v>827</v>
@@ -16186,7 +17584,7 @@
         <v>840</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="P30" s="12" t="s">
         <v>292</v>
@@ -16198,27 +17596,27 @@
         <v>214</v>
       </c>
       <c r="T30" s="12" t="s">
+        <v>945</v>
+      </c>
+      <c r="V30" s="12" t="s">
+        <v>1071</v>
+      </c>
+      <c r="W30" s="12" t="s">
+        <v>1072</v>
+      </c>
+      <c r="X30" s="12" t="s">
         <v>946</v>
       </c>
-      <c r="V30" s="12" t="s">
-        <v>1073</v>
-      </c>
-      <c r="W30" s="12" t="s">
-        <v>1074</v>
-      </c>
-      <c r="X30" s="12" t="s">
+      <c r="Y30" s="12" t="s">
         <v>947</v>
       </c>
-      <c r="Y30" s="12" t="s">
+      <c r="Z30" s="12" t="s">
         <v>948</v>
-      </c>
-      <c r="Z30" s="12" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="36">
       <c r="A31" s="12" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>163</v>
@@ -16236,10 +17634,10 @@
         <v>13</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>324</v>
@@ -16260,31 +17658,31 @@
         <v>244</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="T31" s="13" t="s">
         <v>819</v>
       </c>
       <c r="U31" s="12"/>
       <c r="V31" s="12" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="W31" s="12" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="X31" s="12" t="s">
+        <v>1075</v>
+      </c>
+      <c r="Y31" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Z31" s="12" t="s">
         <v>1077</v>
-      </c>
-      <c r="Y31" s="12" t="s">
-        <v>1078</v>
-      </c>
-      <c r="Z31" s="12" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="54">
       <c r="A32" s="12" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>163</v>
@@ -16302,10 +17700,10 @@
         <v>10</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>688</v>
@@ -16329,30 +17727,30 @@
         <v>244</v>
       </c>
       <c r="S32" s="12" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="T32" s="12" t="s">
         <v>820</v>
       </c>
       <c r="V32" s="12" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="W32" s="12" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="X32" s="12" t="s">
+        <v>1075</v>
+      </c>
+      <c r="Y32" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Z32" s="12" t="s">
         <v>1077</v>
-      </c>
-      <c r="Y32" s="12" t="s">
-        <v>1078</v>
-      </c>
-      <c r="Z32" s="12" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="36">
       <c r="A33" s="12" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>163</v>
@@ -16370,10 +17768,10 @@
         <v>14</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>324</v>
@@ -16394,30 +17792,30 @@
         <v>244</v>
       </c>
       <c r="S33" s="12" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="T33" s="12" t="s">
         <v>821</v>
       </c>
       <c r="V33" s="12" t="s">
+        <v>1058</v>
+      </c>
+      <c r="W33" s="12" t="s">
         <v>1059</v>
       </c>
-      <c r="W33" s="12" t="s">
-        <v>1060</v>
-      </c>
       <c r="X33" s="12" t="s">
+        <v>1075</v>
+      </c>
+      <c r="Y33" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Z33" s="12" t="s">
         <v>1077</v>
-      </c>
-      <c r="Y33" s="12" t="s">
-        <v>1078</v>
-      </c>
-      <c r="Z33" s="12" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="108">
       <c r="A34" s="12" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>163</v>
@@ -16435,10 +17833,10 @@
         <v>8</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="M34" s="12" t="s">
         <v>324</v>
@@ -16459,33 +17857,33 @@
         <v>244</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="T34" s="12" t="s">
         <v>822</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="V34" s="12" t="s">
+        <v>1060</v>
+      </c>
+      <c r="W34" s="12" t="s">
         <v>1061</v>
       </c>
-      <c r="W34" s="12" t="s">
-        <v>1062</v>
-      </c>
       <c r="X34" s="12" t="s">
+        <v>1075</v>
+      </c>
+      <c r="Y34" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Z34" s="12" t="s">
         <v>1077</v>
-      </c>
-      <c r="Y34" s="12" t="s">
-        <v>1078</v>
-      </c>
-      <c r="Z34" s="12" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="90">
       <c r="A35" s="12" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>163</v>
@@ -16497,19 +17895,19 @@
         <v>823</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="G35">
         <v>10</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="J35">
         <v>25</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>246</v>
@@ -16518,7 +17916,7 @@
         <v>271</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="O35" s="13" t="s">
         <v>664</v>
@@ -16533,7 +17931,7 @@
         <v>243</v>
       </c>
       <c r="S35" s="12" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="T35" s="12" t="s">
         <v>823</v>
@@ -16542,24 +17940,24 @@
         <v>860</v>
       </c>
       <c r="V35" s="12" t="s">
-        <v>1064</v>
+        <v>1476</v>
       </c>
       <c r="W35" s="12" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="X35" s="12" t="s">
+        <v>1075</v>
+      </c>
+      <c r="Y35" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Z35" s="12" t="s">
         <v>1077</v>
-      </c>
-      <c r="Y35" s="12" t="s">
-        <v>1078</v>
-      </c>
-      <c r="Z35" s="12" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="54">
       <c r="A36" s="12" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>163</v>
@@ -16577,13 +17975,13 @@
         <v>10</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="J36">
         <v>20</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>246</v>
@@ -16592,7 +17990,7 @@
         <v>689</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="O36" s="13" t="s">
         <v>842</v>
@@ -16607,30 +18005,30 @@
         <v>243</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="T36" s="12" t="s">
         <v>312</v>
       </c>
       <c r="V36" s="12" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="W36" s="12" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="X36" s="12" t="s">
+        <v>1075</v>
+      </c>
+      <c r="Y36" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Z36" s="12" t="s">
         <v>1077</v>
-      </c>
-      <c r="Y36" s="12" t="s">
-        <v>1078</v>
-      </c>
-      <c r="Z36" s="12" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="36">
       <c r="A37" s="12" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>163</v>
@@ -16639,10 +18037,10 @@
         <v>166</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>214</v>
@@ -16657,7 +18055,7 @@
         <v>651</v>
       </c>
       <c r="L37" s="34" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="M37" s="12" t="s">
         <v>689</v>
@@ -16666,10 +18064,10 @@
         <v>840</v>
       </c>
       <c r="O37" s="12" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="P37" s="12" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="Q37" s="12" t="s">
         <v>214</v>
@@ -16678,33 +18076,33 @@
         <v>214</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="T37" s="12" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="U37" s="12" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="V37" s="12" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="W37" s="12" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="X37" s="12" t="s">
+        <v>1078</v>
+      </c>
+      <c r="Y37" s="12" t="s">
+        <v>1079</v>
+      </c>
+      <c r="Z37" s="12" t="s">
         <v>1080</v>
-      </c>
-      <c r="Y37" s="12" t="s">
-        <v>1081</v>
-      </c>
-      <c r="Z37" s="12" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="36">
       <c r="A38" s="12" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>163</v>
@@ -16722,10 +18120,10 @@
         <v>13</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="M38" s="13" t="s">
         <v>324</v>
@@ -16746,31 +18144,31 @@
         <v>244</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="T38" s="13" t="s">
         <v>819</v>
       </c>
       <c r="U38" s="12"/>
       <c r="V38" s="12" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="W38" s="12" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="X38" s="12" t="s">
+        <v>1203</v>
+      </c>
+      <c r="Y38" s="12" t="s">
+        <v>1204</v>
+      </c>
+      <c r="Z38" s="12" t="s">
         <v>1205</v>
-      </c>
-      <c r="Y38" s="12" t="s">
-        <v>1206</v>
-      </c>
-      <c r="Z38" s="12" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="36">
       <c r="A39" s="12" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>163</v>
@@ -16788,10 +18186,10 @@
         <v>10</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L39" s="16" t="s">
         <v>688</v>
@@ -16815,31 +18213,31 @@
         <v>244</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="T39" s="12" t="s">
         <v>820</v>
       </c>
       <c r="U39" s="12"/>
       <c r="V39" s="12" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="W39" s="12" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="X39" s="12" t="s">
+        <v>1203</v>
+      </c>
+      <c r="Y39" s="12" t="s">
+        <v>1204</v>
+      </c>
+      <c r="Z39" s="12" t="s">
         <v>1205</v>
-      </c>
-      <c r="Y39" s="12" t="s">
-        <v>1206</v>
-      </c>
-      <c r="Z39" s="12" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="36">
       <c r="A40" s="12" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>163</v>
@@ -16857,10 +18255,10 @@
         <v>14</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="M40" s="12" t="s">
         <v>324</v>
@@ -16881,31 +18279,31 @@
         <v>244</v>
       </c>
       <c r="S40" s="12" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="T40" s="12" t="s">
         <v>821</v>
       </c>
       <c r="U40" s="12"/>
       <c r="V40" s="12" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="W40" s="12" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="X40" s="12" t="s">
+        <v>1203</v>
+      </c>
+      <c r="Y40" s="12" t="s">
+        <v>1204</v>
+      </c>
+      <c r="Z40" s="12" t="s">
         <v>1205</v>
-      </c>
-      <c r="Y40" s="12" t="s">
-        <v>1206</v>
-      </c>
-      <c r="Z40" s="12" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="41" spans="1:26" ht="36">
       <c r="A41" s="12" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>163</v>
@@ -16923,10 +18321,10 @@
         <v>8</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="M41" s="12" t="s">
         <v>324</v>
@@ -16947,33 +18345,33 @@
         <v>244</v>
       </c>
       <c r="S41" s="12" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="T41" s="12" t="s">
         <v>822</v>
       </c>
       <c r="U41" s="12" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="V41" s="12" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="W41" s="12" t="s">
+        <v>1201</v>
+      </c>
+      <c r="X41" s="12" t="s">
         <v>1203</v>
       </c>
-      <c r="X41" s="12" t="s">
+      <c r="Y41" s="12" t="s">
+        <v>1204</v>
+      </c>
+      <c r="Z41" s="12" t="s">
         <v>1205</v>
-      </c>
-      <c r="Y41" s="12" t="s">
-        <v>1206</v>
-      </c>
-      <c r="Z41" s="12" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="36">
       <c r="A42" s="12" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>163</v>
@@ -16982,10 +18380,10 @@
         <v>166</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>214</v>
@@ -17009,10 +18407,10 @@
         <v>840</v>
       </c>
       <c r="O42" s="12" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="P42" s="12" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="Q42" s="12" t="s">
         <v>214</v>
@@ -17022,348 +18420,831 @@
       </c>
       <c r="S42" s="12"/>
       <c r="T42" s="12" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="V42" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="W42" s="12" t="s">
+        <v>1216</v>
+      </c>
+      <c r="X42" s="12" t="s">
         <v>1210</v>
       </c>
-      <c r="W42" s="12" t="s">
-        <v>1219</v>
-      </c>
-      <c r="X42" s="12" t="s">
+      <c r="Y42" s="12" t="s">
+        <v>1211</v>
+      </c>
+      <c r="Z42" s="12" t="s">
         <v>1212</v>
-      </c>
-      <c r="Y42" s="12" t="s">
-        <v>1213</v>
-      </c>
-      <c r="Z42" s="12" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="43" spans="1:26" ht="54">
       <c r="A43" s="12" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>391</v>
       </c>
       <c r="C43" s="12" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F43" s="12" t="s">
         <v>1223</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="G43" s="12" t="s">
         <v>1224</v>
       </c>
-      <c r="E43" s="12" t="s">
-        <v>1371</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>1226</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>1227</v>
-      </c>
       <c r="H43" s="16" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43" s="12" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L43" s="34" t="s">
+        <v>1224</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N43" s="13" t="s">
+        <v>1226</v>
+      </c>
+      <c r="O43" s="12" t="s">
+        <v>1224</v>
+      </c>
+      <c r="P43" s="12" t="s">
+        <v>1227</v>
+      </c>
+      <c r="Q43" s="12" t="s">
+        <v>1229</v>
+      </c>
+      <c r="R43" s="12" t="s">
+        <v>1224</v>
+      </c>
+      <c r="T43" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="U43" s="12" t="s">
         <v>1231</v>
       </c>
-      <c r="L43" s="34" t="s">
-        <v>1227</v>
-      </c>
-      <c r="M43" s="12" t="s">
-        <v>1228</v>
-      </c>
-      <c r="N43" s="13" t="s">
-        <v>1229</v>
-      </c>
-      <c r="O43" s="12" t="s">
-        <v>1227</v>
-      </c>
-      <c r="P43" s="12" t="s">
+      <c r="V43" s="12" t="s">
         <v>1230</v>
       </c>
-      <c r="Q43" s="12" t="s">
+      <c r="W43" s="12" t="s">
         <v>1232</v>
       </c>
-      <c r="R43" s="12" t="s">
-        <v>1227</v>
-      </c>
-      <c r="T43" s="12" t="s">
-        <v>1371</v>
-      </c>
-      <c r="U43" s="12" t="s">
+      <c r="X43" s="12" t="s">
+        <v>1233</v>
+      </c>
+      <c r="Y43" s="12" t="s">
         <v>1234</v>
       </c>
-      <c r="V43" s="12" t="s">
-        <v>1233</v>
-      </c>
-      <c r="W43" s="12" t="s">
+      <c r="Z43" s="12" t="s">
         <v>1235</v>
-      </c>
-      <c r="X43" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="Y43" s="12" t="s">
-        <v>1237</v>
-      </c>
-      <c r="Z43" s="12" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="44" spans="1:26" ht="36">
       <c r="A44" s="4" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="C44" s="41" t="s">
-        <v>1380</v>
+      <c r="C44" s="12" t="s">
+        <v>1373</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>1381</v>
-      </c>
-      <c r="E44" s="41" t="s">
-        <v>1382</v>
-      </c>
-      <c r="P44" s="41" t="s">
-        <v>1383</v>
-      </c>
-      <c r="S44" s="41" t="s">
-        <v>1399</v>
-      </c>
-      <c r="U44" s="41"/>
-      <c r="V44" s="41" t="s">
-        <v>1385</v>
-      </c>
-      <c r="W44" s="41" t="s">
-        <v>1386</v>
+        <v>1374</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>1375</v>
+      </c>
+      <c r="P44" s="12" t="s">
+        <v>1376</v>
+      </c>
+      <c r="S44" s="12" t="s">
+        <v>1392</v>
+      </c>
+      <c r="U44" s="12"/>
+      <c r="V44" s="12" t="s">
+        <v>1378</v>
+      </c>
+      <c r="W44" s="12" t="s">
+        <v>1379</v>
       </c>
     </row>
     <row r="45" spans="1:26" ht="36">
-      <c r="A45" s="43" t="s">
-        <v>1404</v>
+      <c r="A45" s="34" t="s">
+        <v>1397</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1387</v>
-      </c>
-      <c r="C45" s="41" t="s">
         <v>1380</v>
       </c>
+      <c r="C45" s="12" t="s">
+        <v>1373</v>
+      </c>
       <c r="D45" s="5" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E45" s="12" t="s">
         <v>1381</v>
       </c>
-      <c r="E45" s="41" t="s">
-        <v>1388</v>
-      </c>
-      <c r="P45" s="41" t="s">
-        <v>1389</v>
+      <c r="P45" s="12" t="s">
+        <v>1382</v>
       </c>
       <c r="S45" s="4" t="s">
-        <v>1391</v>
-      </c>
-      <c r="U45" s="41" t="s">
-        <v>1390</v>
-      </c>
-      <c r="V45" s="41" t="s">
-        <v>1392</v>
-      </c>
-      <c r="W45" s="41" t="s">
-        <v>1393</v>
+        <v>1384</v>
+      </c>
+      <c r="U45" s="12" t="s">
+        <v>1383</v>
+      </c>
+      <c r="V45" s="12" t="s">
+        <v>1385</v>
+      </c>
+      <c r="W45" s="12" t="s">
+        <v>1386</v>
       </c>
     </row>
     <row r="46" spans="1:26" ht="54">
-      <c r="A46" s="43" t="s">
-        <v>1405</v>
-      </c>
-      <c r="B46" s="42" t="s">
+      <c r="A46" s="34" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="C46" s="41" t="s">
-        <v>1380</v>
+      <c r="C46" s="12" t="s">
+        <v>1373</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>1381</v>
-      </c>
-      <c r="E46" s="41" t="s">
-        <v>1394</v>
-      </c>
-      <c r="P46" s="41" t="s">
-        <v>1383</v>
-      </c>
-      <c r="S46" s="43" t="s">
-        <v>1395</v>
-      </c>
-      <c r="U46" s="41"/>
-      <c r="V46" s="41" t="s">
-        <v>1396</v>
+        <v>1374</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>1387</v>
+      </c>
+      <c r="P46" s="12" t="s">
+        <v>1376</v>
+      </c>
+      <c r="S46" s="34" t="s">
+        <v>1388</v>
+      </c>
+      <c r="U46" s="12"/>
+      <c r="V46" s="12" t="s">
+        <v>1389</v>
       </c>
       <c r="W46" s="11" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="47" spans="1:26" ht="54">
-      <c r="A47" s="43" t="s">
-        <v>1406</v>
-      </c>
-      <c r="B47" s="42" t="s">
+      <c r="A47" s="34" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="C47" s="41" t="s">
-        <v>1380</v>
+      <c r="C47" s="12" t="s">
+        <v>1373</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>1381</v>
-      </c>
-      <c r="E47" s="41" t="s">
-        <v>1398</v>
-      </c>
-      <c r="P47" s="41" t="s">
-        <v>1383</v>
-      </c>
-      <c r="S47" s="44" t="s">
-        <v>1400</v>
-      </c>
-      <c r="U47" s="44"/>
-      <c r="V47" s="41" t="s">
-        <v>1401</v>
-      </c>
-      <c r="W47" s="45" t="s">
-        <v>1402</v>
+        <v>1374</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>1391</v>
+      </c>
+      <c r="P47" s="12" t="s">
+        <v>1376</v>
+      </c>
+      <c r="S47" s="11" t="s">
+        <v>1393</v>
+      </c>
+      <c r="U47" s="11"/>
+      <c r="V47" s="12" t="s">
+        <v>1394</v>
+      </c>
+      <c r="W47" s="16" t="s">
+        <v>1395</v>
       </c>
     </row>
     <row r="48" spans="1:26" ht="72">
       <c r="A48" s="4" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="C48" s="4"/>
       <c r="E48" s="4" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48" s="4" t="s">
+        <v>1261</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>1263</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>1261</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>1261</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>1263</v>
+      </c>
+      <c r="Q48" s="4" t="s">
+        <v>1261</v>
+      </c>
+      <c r="R48" s="4" t="s">
         <v>1264</v>
       </c>
-      <c r="L48" s="4" t="s">
+      <c r="T48" s="4" t="s">
+        <v>1259</v>
+      </c>
+      <c r="U48" s="11" t="s">
         <v>1265</v>
       </c>
-      <c r="M48" s="4" t="s">
-        <v>1266</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>1264</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>1264</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>1266</v>
-      </c>
-      <c r="Q48" s="4" t="s">
-        <v>1264</v>
-      </c>
-      <c r="R48" s="4" t="s">
-        <v>1267</v>
-      </c>
-      <c r="T48" s="4" t="s">
-        <v>1262</v>
-      </c>
-      <c r="U48" s="11" t="s">
-        <v>1268</v>
-      </c>
     </row>
-    <row r="49" spans="1:26" ht="72">
-      <c r="A49" s="3" t="s">
+    <row r="49" spans="1:26" ht="36">
+      <c r="A49" s="12" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>819</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>597</v>
+      </c>
+      <c r="G49">
+        <v>13</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M49" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="N49" s="13" t="s">
+        <v>646</v>
+      </c>
+      <c r="O49" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="P49" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q49" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="R49" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="S49" s="12"/>
+      <c r="T49" s="13" t="s">
+        <v>819</v>
+      </c>
+      <c r="U49" s="12" t="s">
+        <v>1479</v>
+      </c>
+      <c r="V49" s="12" t="s">
+        <v>1469</v>
+      </c>
+      <c r="W49" s="12" t="s">
+        <v>1480</v>
+      </c>
+      <c r="X49" s="12" t="s">
+        <v>1485</v>
+      </c>
+      <c r="Y49" s="12" t="s">
+        <v>1486</v>
+      </c>
+      <c r="Z49" s="12" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" ht="54">
+      <c r="A50" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>820</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>657</v>
+      </c>
+      <c r="G50">
+        <v>10</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>1046</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M50" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="N50" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="O50" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="P50" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q50" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="R50" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="S50" s="12"/>
+      <c r="T50" s="12" t="s">
+        <v>820</v>
+      </c>
+      <c r="U50" s="12" t="s">
+        <v>1479</v>
+      </c>
+      <c r="V50" s="12" t="s">
+        <v>1470</v>
+      </c>
+      <c r="W50" s="12" t="s">
+        <v>1481</v>
+      </c>
+      <c r="X50" s="12" t="s">
+        <v>1485</v>
+      </c>
+      <c r="Y50" s="12" t="s">
+        <v>1486</v>
+      </c>
+      <c r="Z50" s="12" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" ht="36">
+      <c r="A51" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="G51">
+        <v>14</v>
+      </c>
+      <c r="H51" s="16" t="s">
+        <v>1047</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M51" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="N51" s="13" t="s">
+        <v>837</v>
+      </c>
+      <c r="O51" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="P51" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q51" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="R51" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="S51" s="12"/>
+      <c r="T51" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="U51" s="12" t="s">
+        <v>1479</v>
+      </c>
+      <c r="V51" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="W51" s="12" t="s">
+        <v>1482</v>
+      </c>
+      <c r="X51" s="12" t="s">
+        <v>1485</v>
+      </c>
+      <c r="Y51" s="12" t="s">
+        <v>1486</v>
+      </c>
+      <c r="Z51" s="12" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" ht="54">
+      <c r="A52" s="12" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="G52">
+        <v>8</v>
+      </c>
+      <c r="H52" s="16" t="s">
+        <v>1048</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M52" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="N52" s="13" t="s">
+        <v>838</v>
+      </c>
+      <c r="O52" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="P52" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q52" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="R52" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="S52" s="12"/>
+      <c r="T52" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="U52" s="12" t="s">
+        <v>1483</v>
+      </c>
+      <c r="V52" s="12" t="s">
+        <v>1472</v>
+      </c>
+      <c r="W52" s="12" t="s">
+        <v>1484</v>
+      </c>
+      <c r="X52" s="12" t="s">
+        <v>1485</v>
+      </c>
+      <c r="Y52" s="12" t="s">
+        <v>1486</v>
+      </c>
+      <c r="Z52" s="12" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" ht="90">
+      <c r="A53" s="12" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>823</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G53">
+        <v>10</v>
+      </c>
+      <c r="H53" s="16" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J53">
+        <v>25</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="M53" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="N53" s="12" t="s">
+        <v>885</v>
+      </c>
+      <c r="O53" s="13" t="s">
+        <v>664</v>
+      </c>
+      <c r="P53" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q53" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="R53" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="S53" s="12"/>
+      <c r="T53" s="12" t="s">
+        <v>823</v>
+      </c>
+      <c r="U53" s="12" t="s">
+        <v>1488</v>
+      </c>
+      <c r="V53" s="12" t="s">
+        <v>1474</v>
+      </c>
+      <c r="W53" s="12" t="s">
+        <v>1489</v>
+      </c>
+      <c r="X53" s="12" t="s">
+        <v>1487</v>
+      </c>
+      <c r="Y53" s="12" t="s">
+        <v>1490</v>
+      </c>
+      <c r="Z53" s="12" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" ht="54">
+      <c r="A54" s="12" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="G54">
+        <v>10</v>
+      </c>
+      <c r="H54" s="16" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J54">
+        <v>20</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="M54" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="N54" s="12" t="s">
+        <v>886</v>
+      </c>
+      <c r="O54" s="13" t="s">
+        <v>842</v>
+      </c>
+      <c r="P54" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q54" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="R54" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="S54" s="12"/>
+      <c r="T54" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="U54" s="12" t="s">
+        <v>1473</v>
+      </c>
+      <c r="V54" s="12" t="s">
+        <v>1475</v>
+      </c>
+      <c r="W54" s="12" t="s">
+        <v>1478</v>
+      </c>
+      <c r="X54" s="12" t="s">
+        <v>1492</v>
+      </c>
+      <c r="Y54" s="12" t="s">
+        <v>1493</v>
+      </c>
+      <c r="Z54" s="12" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" ht="36">
+      <c r="A55" s="12" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J55">
+        <v>25</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="L55" s="34" t="s">
+        <v>652</v>
+      </c>
+      <c r="M55" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="N55" s="13" t="s">
+        <v>840</v>
+      </c>
+      <c r="O55" s="12" t="s">
+        <v>1452</v>
+      </c>
+      <c r="P55" s="12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="Q55" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="R55" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="S55" s="12" t="s">
+        <v>1464</v>
+      </c>
+      <c r="T55" s="12" t="s">
+        <v>1451</v>
+      </c>
+      <c r="U55" s="12"/>
+      <c r="V55" s="12" t="s">
+        <v>1465</v>
+      </c>
+      <c r="W55" s="12" t="s">
+        <v>1466</v>
+      </c>
+      <c r="X55" s="12" t="s">
+        <v>1467</v>
+      </c>
+      <c r="Y55" s="12" t="s">
+        <v>1079</v>
+      </c>
+      <c r="Z55" s="12" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26" ht="72">
+      <c r="A62" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B62" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D62" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="F49" s="12" t="s">
+      <c r="F62" s="12" t="s">
         <v>593</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G62" s="3">
         <v>32</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="H62" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="I49" s="2" t="s">
+      <c r="I62" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J62" s="2">
         <v>40</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="K62" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="L62" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M49" s="3" t="s">
+      <c r="M62" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="N49" s="3" t="s">
+      <c r="N62" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="O49" s="3" t="s">
+      <c r="O62" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="P49" s="3" t="s">
+      <c r="P62" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="Q49" s="3" t="s">
+      <c r="Q62" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="R49" s="3" t="s">
+      <c r="R62" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="S49" s="2" t="s">
+      <c r="S62" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="T49" s="3" t="s">
+      <c r="T62" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="U49" s="3" t="s">
+      <c r="U62" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="V49" s="12" t="s">
+      <c r="V62" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="W49" s="12" t="s">
+      <c r="W62" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="X49" s="12" t="s">
+      <c r="X62" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="Y49" s="12" t="s">
+      <c r="Y62" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="Z49" s="12" t="s">
+      <c r="Z62" s="12" t="s">
         <v>372</v>
       </c>
     </row>
@@ -17938,7 +19819,7 @@
         <v>685</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="36">
@@ -17987,7 +19868,7 @@
         <v>644</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>639</v>
@@ -17996,7 +19877,7 @@
         <v>704</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="54">
@@ -18048,13 +19929,13 @@
         <v>648</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>667</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>1368</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="36">
@@ -18106,7 +19987,7 @@
         <v>639</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>717</v>
@@ -18171,434 +20052,434 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="12" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F15" s="13">
         <v>15</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="L15" s="12" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M15" s="12" t="s">
+        <v>1284</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>1276</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>1276</v>
+      </c>
+      <c r="Q15" s="12" t="s">
         <v>1286</v>
       </c>
-      <c r="M15" s="12" t="s">
+      <c r="R15" s="12" t="s">
+        <v>1276</v>
+      </c>
+      <c r="S15" s="12" t="s">
         <v>1287</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>1279</v>
-      </c>
-      <c r="O15" s="12" t="s">
-        <v>1288</v>
-      </c>
-      <c r="P15" s="12" t="s">
-        <v>1279</v>
-      </c>
-      <c r="Q15" s="12" t="s">
-        <v>1289</v>
-      </c>
-      <c r="R15" s="12" t="s">
-        <v>1279</v>
-      </c>
-      <c r="S15" s="12" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="36">
       <c r="A16" s="12" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F16" s="13">
         <v>5</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="L16" s="12" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>1276</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="Q16" s="12" t="s">
         <v>1286</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="R16" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="S16" s="12" t="s">
         <v>1293</v>
-      </c>
-      <c r="N16" s="12" t="s">
-        <v>1279</v>
-      </c>
-      <c r="O16" s="12" t="s">
-        <v>1288</v>
-      </c>
-      <c r="Q16" s="12" t="s">
-        <v>1289</v>
-      </c>
-      <c r="R16" s="12" t="s">
-        <v>1295</v>
-      </c>
-      <c r="S16" s="12" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="72">
       <c r="A17" s="12" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F17" s="13">
         <v>5</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="M17" s="12" t="s">
+        <v>1296</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P17" s="12" t="s">
         <v>1299</v>
       </c>
-      <c r="O17" s="12" t="s">
-        <v>1288</v>
-      </c>
-      <c r="P17" s="12" t="s">
+      <c r="Q17" s="12" t="s">
         <v>1302</v>
       </c>
-      <c r="Q17" s="12" t="s">
-        <v>1305</v>
-      </c>
       <c r="S17" s="12" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="T17" s="12" t="s">
-        <v>1308</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="36">
       <c r="A18" s="3" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="F18" s="2">
         <v>5</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>491</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="L18" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>1285</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>1312</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>1288</v>
-      </c>
       <c r="P18" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="S18" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="T18" s="3" t="s">
         <v>1309</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="19" spans="1:23" ht="72">
       <c r="A19" s="3" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="F19" s="2">
         <v>10</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>658</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="L19" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>1285</v>
       </c>
-      <c r="M19" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>1319</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>1288</v>
-      </c>
       <c r="P19" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>243</v>
       </c>
       <c r="R19" s="2"/>
       <c r="S19" s="3" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>1379</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="90">
       <c r="A20" s="3" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="F20" s="2">
         <v>10</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>682</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="R20" s="2"/>
       <c r="S20" s="3" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>1378</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="72">
       <c r="A21" s="3" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="F21" s="2">
         <v>10</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1376</v>
+        <v>1369</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>1374</v>
+        <v>1367</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="L21" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>1285</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>1328</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>1288</v>
-      </c>
       <c r="P21" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>1377</v>
+        <v>1370</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="216">
       <c r="A22" s="3" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F22" s="2">
         <v>10</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1375</v>
+        <v>1368</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>688</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="3" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="U22" s="13"/>
       <c r="V22" s="12"/>
@@ -18606,56 +20487,56 @@
     </row>
     <row r="23" spans="1:23" ht="54">
       <c r="A23" s="3" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F23" s="2">
         <v>25</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="L23" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="Q23" s="3" t="s">
         <v>1286</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>1288</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>1289</v>
-      </c>
       <c r="R23" s="3" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="12"/>
@@ -18664,56 +20545,56 @@
     </row>
     <row r="24" spans="1:23" ht="36">
       <c r="A24" s="3" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F24" s="2">
         <v>25</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="L24" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="Q24" s="3" t="s">
         <v>1286</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>1288</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>1289</v>
-      </c>
       <c r="R24" s="3" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="T24" s="3"/>
       <c r="U24" s="12"/>
@@ -18722,213 +20603,213 @@
     </row>
     <row r="25" spans="1:23" ht="54">
       <c r="A25" s="3" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F25" s="2">
         <v>25</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" s="3" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="12" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="F26" s="13">
         <v>5</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="L26" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>1346</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>1347</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P26" s="13" t="s">
+        <v>1298</v>
+      </c>
+      <c r="Q26" s="12" t="s">
+        <v>1348</v>
+      </c>
+      <c r="T26" s="12" t="s">
         <v>1349</v>
-      </c>
-      <c r="M26" s="12" t="s">
-        <v>1351</v>
-      </c>
-      <c r="N26" s="12" t="s">
-        <v>1352</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>1288</v>
-      </c>
-      <c r="P26" s="13" t="s">
-        <v>1301</v>
-      </c>
-      <c r="Q26" s="12" t="s">
-        <v>1353</v>
-      </c>
-      <c r="T26" s="12" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="27" spans="1:23">
       <c r="A27" s="12" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F27" s="13">
         <v>25</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="L27" s="12" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>884</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>1277</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P27" s="13" t="s">
+        <v>1276</v>
+      </c>
+      <c r="Q27" s="12" t="s">
         <v>1286</v>
       </c>
-      <c r="M27" s="12" t="s">
-        <v>885</v>
-      </c>
-      <c r="N27" s="12" t="s">
-        <v>1280</v>
-      </c>
-      <c r="O27" s="12" t="s">
-        <v>1288</v>
-      </c>
-      <c r="P27" s="13" t="s">
-        <v>1279</v>
-      </c>
-      <c r="Q27" s="12" t="s">
-        <v>1289</v>
-      </c>
       <c r="R27" s="16" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="S27" s="39" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="28" spans="1:23" ht="54">
       <c r="A28" s="12" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="F28" s="13">
         <v>0</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="L28" s="12" t="s">
+        <v>1282</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>1277</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>1358</v>
+      </c>
+      <c r="O28" s="12" t="s">
         <v>1285</v>
       </c>
-      <c r="M28" s="12" t="s">
-        <v>1280</v>
-      </c>
-      <c r="N28" s="12" t="s">
-        <v>1363</v>
-      </c>
-      <c r="O28" s="12" t="s">
-        <v>1288</v>
-      </c>
       <c r="P28" s="13" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="S28" s="39" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="T28" s="34" t="s">
-        <v>1372</v>
+        <v>1365</v>
       </c>
     </row>
   </sheetData>
@@ -18940,7 +20821,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14.296875" customWidth="1"/>
@@ -18975,35 +20856,35 @@
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="37.200000000000003" customHeight="1">
+    <row r="2" spans="1:7" ht="36">
       <c r="A2" s="4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="37.200000000000003" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="36">
-      <c r="A3" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>289</v>
@@ -19012,165 +20893,165 @@
         <v>190</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>285</v>
+        <v>263</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>284</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="54">
+    <row r="4" spans="1:7" ht="36">
       <c r="A4" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>260</v>
+      <c r="E4" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>285</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="54">
       <c r="A5" s="4" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>288</v>
+      <c r="E5" s="11" t="s">
+        <v>259</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="36">
+    <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>326</v>
+        <v>281</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>327</v>
+        <v>282</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>328</v>
+        <v>291</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>676</v>
+      <c r="E6" s="4" t="s">
+        <v>288</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>482</v>
+        <v>286</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>677</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="36">
       <c r="A7" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>676</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="36">
+      <c r="A8" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>672</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>673</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
-        <v>1193</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>712</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>733</v>
       </c>
       <c r="E8" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>713</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="36">
-      <c r="A9" s="4" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>1246</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>1252</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>1253</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="54">
+    <row r="10" spans="1:7" ht="36">
       <c r="A10" s="4" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>328</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>1249</v>
@@ -19182,112 +21063,181 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="126">
+    <row r="11" spans="1:7" ht="54">
       <c r="A11" s="4" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1241</v>
+        <v>328</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>190</v>
+        <v>1243</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>1329</v>
+        <v>1246</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="90">
+    <row r="12" spans="1:7" ht="126">
       <c r="A12" s="4" t="s">
-        <v>1256</v>
+        <v>1237</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1255</v>
+        <v>1236</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>289</v>
+        <v>1238</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>1337</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>1260</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>1338</v>
+        <v>1324</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>1240</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="36">
+    <row r="13" spans="1:7" ht="90">
       <c r="A13" s="4" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1259</v>
+        <v>289</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>1269</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+        <v>1332</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>1333</v>
+      </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" ht="36">
       <c r="A14" s="4" t="s">
-        <v>1270</v>
+        <v>1254</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>1272</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>1274</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>1273</v>
-      </c>
+        <v>1266</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:7" ht="72">
+    <row r="15" spans="1:7">
       <c r="A15" s="4" t="s">
-        <v>1307</v>
+        <v>1267</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1306</v>
+        <v>1268</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>1369</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
+        <v>1269</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="54">
+      <c r="A16" s="4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" ht="54">
+      <c r="A17" s="4" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>1459</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="4" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>1461</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>1462</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
@@ -19359,7 +21309,7 @@
         <v>92</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1384</v>
+        <v>1377</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>446</v>
@@ -20341,7 +22291,7 @@
         <v>629</v>
       </c>
       <c r="Y11" s="12" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="Z11" s="34" t="s">
         <v>660</v>
@@ -20350,7 +22300,7 @@
         <v>787</v>
       </c>
       <c r="AB11" s="12" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="54">
@@ -20433,7 +22383,7 @@
         <v>788</v>
       </c>
       <c r="AB12" s="11" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="108">
@@ -20507,10 +22457,10 @@
         <v>663</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="Y13" s="16" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="Z13" s="34" t="s">
         <v>725</v>
@@ -20519,33 +22469,33 @@
         <v>789</v>
       </c>
       <c r="AB13" s="11" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="72">
       <c r="A14" s="39" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>620</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="E14" s="13">
-        <v>3800</v>
+        <v>4200</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14" s="13">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H14" s="13">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="I14" s="13">
         <v>120</v>
@@ -20572,7 +22522,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="33">
-        <v>1</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="R14" s="33">
         <v>0</v>
@@ -20581,7 +22531,7 @@
         <v>0.5</v>
       </c>
       <c r="T14" s="12" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="U14" s="33">
         <v>0</v>
@@ -20590,16 +22540,19 @@
         <v>0</v>
       </c>
       <c r="W14" s="12" t="s">
+        <v>1275</v>
+      </c>
+      <c r="X14" s="12" t="s">
+        <v>1276</v>
+      </c>
+      <c r="Y14" s="16" t="s">
         <v>1278</v>
       </c>
-      <c r="X14" s="12" t="s">
-        <v>1279</v>
-      </c>
-      <c r="Y14" s="16" t="s">
-        <v>1281</v>
-      </c>
       <c r="Z14" s="34" t="s">
-        <v>1365</v>
+        <v>1528</v>
+      </c>
+      <c r="AB14" s="34" t="s">
+        <v>1529</v>
       </c>
     </row>
   </sheetData>
@@ -20611,7 +22564,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19.59765625" customWidth="1"/>
@@ -21149,7 +23102,7 @@
         <v>797</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>800</v>
@@ -21161,53 +23114,53 @@
         <v>805</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>846</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="73.8" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E15" t="s">
         <v>805</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="I15" s="12" t="s">
         <v>847</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="73.8" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>166</v>
@@ -21219,45 +23172,45 @@
         <v>805</v>
       </c>
       <c r="F16" s="11" t="s">
+        <v>979</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>900</v>
+      </c>
+      <c r="J16" s="11" t="s">
         <v>980</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>894</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>901</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="73.8" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E17" t="s">
         <v>805</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I17" s="12" t="s">
         <v>848</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="73.8" customHeight="1">
@@ -21265,7 +23218,7 @@
         <v>798</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>166</v>
@@ -21277,45 +23230,45 @@
         <v>805</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>849</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="73.8" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E19" t="s">
         <v>805</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>850</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="73.8" customHeight="1">
@@ -21323,7 +23276,7 @@
         <v>799</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>166</v>
@@ -21335,24 +23288,24 @@
         <v>805</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>851</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="36">
       <c r="A21" s="4" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>166</v>
@@ -21364,24 +23317,24 @@
         <v>662</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="54">
       <c r="A22" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>166</v>
@@ -21393,24 +23346,24 @@
         <v>662</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="36">
       <c r="A23" s="4" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>166</v>
@@ -21422,24 +23375,24 @@
         <v>662</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="36">
       <c r="A24" s="4" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>166</v>
@@ -21451,24 +23404,24 @@
         <v>662</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="36">
       <c r="A25" s="4" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>166</v>
@@ -21480,24 +23433,24 @@
         <v>662</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="36">
       <c r="A26" s="4" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>166</v>
@@ -21509,24 +23462,24 @@
         <v>662</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="36">
       <c r="A27" s="4" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>166</v>
@@ -21538,177 +23491,377 @@
         <v>662</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="54">
       <c r="A28" s="4" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="E28" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F28" s="11" t="s">
         <v>1169</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>1171</v>
-      </c>
       <c r="G28" s="4" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="54">
       <c r="A29" s="4" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>1163</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>1165</v>
-      </c>
       <c r="E29" s="4" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="F29" s="11" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>1172</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>1174</v>
-      </c>
       <c r="I29" s="12" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="54">
       <c r="A30" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>1187</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>1214</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="84" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>1515</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>1188</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="83.4" customHeight="1">
+      <c r="A32" s="4" t="s">
         <v>1155</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>1160</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>1163</v>
-      </c>
-      <c r="D30" s="7" t="s">
+      <c r="C32" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>1217</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I30" s="12" t="s">
+      <c r="E32" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>1514</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="I32" s="12" t="s">
         <v>1189</v>
       </c>
-      <c r="J30" s="11" t="s">
-        <v>1216</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>1204</v>
+      <c r="J32" s="11" t="s">
+        <v>1213</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="72">
-      <c r="A31" s="4" t="s">
-        <v>1156</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>1163</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>1167</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>1177</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>1190</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>1215</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>1204</v>
+    <row r="33" spans="1:10" ht="54">
+      <c r="A33" s="4" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>1530</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>1444</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>1531</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="72">
-      <c r="A32" s="4" t="s">
-        <v>1157</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>1163</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>1168</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>1178</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>1191</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>1215</v>
+    <row r="34" spans="1:10" ht="54">
+      <c r="A34" s="4" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>1532</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>1520</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>1531</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="4"/>
+    <row r="35" spans="1:10" ht="54">
+      <c r="A35" s="4" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="54">
+      <c r="A36" s="4" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>1533</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>1447</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="54">
+      <c r="A37" s="4" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>1517</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>1448</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="54">
+      <c r="A38" s="4" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>1518</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>1449</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="54">
+      <c r="A39" s="4" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>1522</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>1450</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>1524</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -21720,11 +23873,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74530E38-EDB4-4883-BA3E-6C72C076C507}">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="26.3984375" customWidth="1"/>
-    <col min="2" max="2" width="20.69921875" customWidth="1"/>
+    <col min="1" max="2" width="26.3984375" customWidth="1"/>
     <col min="3" max="5" width="16.69921875" customWidth="1"/>
     <col min="6" max="6" width="40.296875" customWidth="1"/>
     <col min="7" max="8" width="16.69921875" customWidth="1"/>
@@ -22027,185 +24179,185 @@
     </row>
     <row r="8" spans="1:18" ht="36">
       <c r="A8" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>912</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>913</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="36">
       <c r="A10" s="4" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="36">
       <c r="A11" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="36">
       <c r="A12" s="4" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>918</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>919</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>166</v>
@@ -22214,30 +24366,30 @@
         <v>565</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>214</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="36">
       <c r="A14" s="4" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>166</v>
@@ -22246,33 +24398,33 @@
         <v>560</v>
       </c>
       <c r="E14" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="36">
       <c r="A15" s="4" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>166</v>
@@ -22281,33 +24433,33 @@
         <v>562</v>
       </c>
       <c r="E15" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="36">
       <c r="A16" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>166</v>
@@ -22316,33 +24468,33 @@
         <v>561</v>
       </c>
       <c r="E16" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F16" s="11" t="s">
+        <v>995</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>996</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>997</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="36">
       <c r="A17" s="4" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>166</v>
@@ -22351,33 +24503,33 @@
         <v>563</v>
       </c>
       <c r="E17" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="36">
       <c r="A18" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>166</v>
@@ -22386,33 +24538,33 @@
         <v>564</v>
       </c>
       <c r="E18" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F18" s="11" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>1001</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>1002</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="4" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>166</v>
@@ -22421,205 +24573,205 @@
         <v>565</v>
       </c>
       <c r="E19" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F19" s="11" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>1003</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>1004</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>214</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="36">
       <c r="A20" s="4" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>1120</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>1122</v>
-      </c>
       <c r="G20" s="4" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="4" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I21" s="11" t="s">
+        <v>1132</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>1134</v>
       </c>
-      <c r="K21" s="4" t="s">
-        <v>1136</v>
-      </c>
       <c r="L21" s="4" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="4" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="36">
       <c r="A23" s="4" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>1118</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>1120</v>
-      </c>
       <c r="F23" s="11" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>1111</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>1113</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>1112</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>1114</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>166</v>
@@ -22628,23 +24780,176 @@
         <v>565</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>214</v>
       </c>
       <c r="I25" s="11"/>
       <c r="K25" s="4" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>1140</v>
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="54">
+      <c r="A26" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>1441</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="54">
+      <c r="A27" s="4" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>1442</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="54">
+      <c r="A28" s="4" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>1534</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>1439</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="54">
+      <c r="A29" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>1534</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>1439</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="36">
+      <c r="A30" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>1536</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>1440</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>1443</v>
       </c>
     </row>
   </sheetData>
@@ -22656,7 +24961,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{679D6C04-1546-44B7-B4BC-9388FD23F265}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.69921875" customWidth="1"/>
@@ -22735,7 +25040,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>806</v>
@@ -22767,34 +25072,34 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>965</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>966</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>968</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>967</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>973</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>974</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>969</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>970</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>971</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -22802,32 +25107,64 @@
         <v>707</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>1095</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>1097</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>1099</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>1100</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>1098</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>1101</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>1102</v>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>1421</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>1422</v>
       </c>
     </row>
   </sheetData>
@@ -22839,7 +25176,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD2C904-A80C-4DD6-9EC2-BF8829F6BFCA}">
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.69921875" customWidth="1"/>
@@ -23368,7 +25705,7 @@
         <v>778</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="O15">
         <v>70</v>
@@ -23382,185 +25719,301 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>939</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>937</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>938</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>940</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="O16">
         <v>50</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="4" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="O17">
         <v>70</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>976</v>
-      </c>
       <c r="C18" s="4" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="4" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="O19">
         <v>60</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>1088</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>1090</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="O20">
         <v>80</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>1087</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>1089</v>
-      </c>
       <c r="D21" s="4" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="O21">
         <v>110</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>1094</v>
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="4" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="O22">
+        <v>100</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>1409</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="36">
+      <c r="A23" s="4" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="O23">
+        <v>130</v>
+      </c>
+      <c r="R23" s="11" t="s">
+        <v>1410</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" s="4" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="O24">
+        <v>100</v>
+      </c>
+      <c r="R24" s="4" t="s">
+        <v>1526</v>
+      </c>
+      <c r="S24" s="4" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" s="4" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="O25">
+        <v>300</v>
+      </c>
+      <c r="R25" s="4" t="s">
+        <v>1411</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>1411</v>
       </c>
     </row>
   </sheetData>
@@ -23611,10 +26064,10 @@
         <v>439</v>
       </c>
       <c r="P2" s="23" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="Q2" s="23" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="3" spans="2:17">
@@ -23646,7 +26099,7 @@
         <v>523</v>
       </c>
       <c r="Q3" s="23" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="4" spans="2:17">
@@ -23678,7 +26131,7 @@
         <v>524</v>
       </c>
       <c r="Q4" s="23" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="5" spans="2:17">
@@ -23710,7 +26163,7 @@
         <v>171</v>
       </c>
       <c r="Q5" s="23" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="6" spans="2:17">
@@ -23742,7 +26195,7 @@
         <v>526</v>
       </c>
       <c r="Q6" s="23" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="7" spans="2:17">
@@ -23774,7 +26227,7 @@
         <v>168</v>
       </c>
       <c r="Q7" s="23" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="8" spans="2:17">
@@ -23791,10 +26244,10 @@
         <v>461</v>
       </c>
       <c r="P8" s="40" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="9" spans="2:17">
@@ -23805,10 +26258,10 @@
         <v>458</v>
       </c>
       <c r="P9" s="40" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="10" spans="2:17">

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA58A69-F727-4F2A-9355-B37D5350E8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED04A2F-B9B3-4E8D-9E46-BF713A446E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -15159,10 +15159,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アイス</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ice</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -15390,6 +15386,10 @@
     <rPh sb="2" eb="5">
       <t>サイセイリツ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コルド</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -19991,7 +19991,7 @@
     </row>
     <row r="58" spans="1:26" ht="54">
       <c r="A58" s="12" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>163</v>
@@ -20003,7 +20003,7 @@
         <v>165</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>1566</v>
+        <v>1580</v>
       </c>
       <c r="F58" s="12" t="s">
         <v>595</v>
@@ -20045,26 +20045,26 @@
         <v>242</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="T58" s="12" t="s">
-        <v>1566</v>
+        <v>1580</v>
       </c>
       <c r="U58" s="12"/>
       <c r="V58" s="16" t="s">
+        <v>1573</v>
+      </c>
+      <c r="W58" s="12" t="s">
         <v>1574</v>
       </c>
-      <c r="W58" s="12" t="s">
+      <c r="X58" s="12" t="s">
         <v>1575</v>
       </c>
-      <c r="X58" s="12" t="s">
+      <c r="Y58" s="12" t="s">
         <v>1576</v>
       </c>
-      <c r="Y58" s="12" t="s">
+      <c r="Z58" s="12" t="s">
         <v>1577</v>
-      </c>
-      <c r="Z58" s="12" t="s">
-        <v>1578</v>
       </c>
     </row>
     <row r="62" spans="1:26" ht="72">
@@ -22186,10 +22186,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>710</v>
@@ -22198,13 +22198,13 @@
         <v>189</v>
       </c>
       <c r="E21" s="11" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>1570</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>1571</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>1572</v>
       </c>
     </row>
   </sheetData>
@@ -25917,7 +25917,7 @@
         <v>1494</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
   </sheetData>
@@ -26117,7 +26117,7 @@
         <v>1414</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1415</v>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED04A2F-B9B3-4E8D-9E46-BF713A446E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D876F8F-DB35-42C9-A6EF-4EB76EAD8D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="1581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3227" uniqueCount="1611">
   <si>
     <t>ID</t>
   </si>
@@ -15390,6 +15390,255 @@
   </si>
   <si>
     <t>コルド</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スキル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>棒具</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単体攻撃</t>
+    <rPh sb="0" eb="4">
+      <t>タンタイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.15</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>16秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2秒</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象指定</t>
+    <rPh sb="0" eb="4">
+      <t>タイショウシテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>100px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>物理</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10連撃</t>
+    <rPh sb="2" eb="4">
+      <t>レンゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ten_hit_combo</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>このスキルは10回ヒットする</t>
+    <rPh sb="8" eb="9">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、敵1体に10連撃をお見舞いし物理ダメージを与える</t>
+    <rPh sb="0" eb="3">
+      <t>エイショウゴ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>レンゲキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ミマ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルごとに基礎ダメージが+(0/2/4/6/8/10)増加</t>
+    <rPh sb="6" eb="8">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとにダメージが上昇する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに基礎ダメージが+(2/4/6/8/10)増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2秒の詠唱を行った後、敵1体に10連撃をお見舞いし、(式=値)の物理ダメージを10回与える。</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エイショウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>レンゲキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ミマ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>研磨</t>
+    <rPh sb="0" eb="2">
+      <t>ケンマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スキル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>片手剣/両手剣</t>
+    <rPh sb="0" eb="3">
+      <t>カタテケン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>リョウテケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sharpen_blade</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自己バフ</t>
+    <rPh sb="0" eb="2">
+      <t>ジコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>３秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>20秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自身</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -15581,7 +15830,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -15682,6 +15931,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16017,7 +16275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z62"/>
+  <dimension ref="A1:Z74"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -20067,83 +20325,207 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="62" spans="1:26" ht="72">
-      <c r="A62" s="3" t="s">
+    <row r="59" spans="1:26" ht="36">
+      <c r="A59" s="12" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G59">
+        <v>5</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>1585</v>
+      </c>
+      <c r="J59" s="34" t="s">
+        <v>1586</v>
+      </c>
+      <c r="K59" s="12" t="s">
+        <v>1587</v>
+      </c>
+      <c r="L59" s="12" t="s">
+        <v>1588</v>
+      </c>
+      <c r="M59" s="13" t="s">
+        <v>1589</v>
+      </c>
+      <c r="N59" s="12" t="s">
+        <v>1590</v>
+      </c>
+      <c r="O59" s="13" t="s">
+        <v>1586</v>
+      </c>
+      <c r="P59" s="13" t="s">
+        <v>1591</v>
+      </c>
+      <c r="Q59" s="12" t="s">
+        <v>1586</v>
+      </c>
+      <c r="R59" s="13" t="s">
+        <v>1592</v>
+      </c>
+      <c r="S59" s="12" t="s">
+        <v>1586</v>
+      </c>
+      <c r="T59" s="12" t="s">
+        <v>1593</v>
+      </c>
+      <c r="U59" s="12" t="s">
+        <v>1595</v>
+      </c>
+      <c r="V59" s="16" t="s">
+        <v>1596</v>
+      </c>
+      <c r="W59" s="12" t="s">
+        <v>1600</v>
+      </c>
+      <c r="X59" s="12" t="s">
+        <v>1597</v>
+      </c>
+      <c r="Y59" s="12" t="s">
+        <v>1598</v>
+      </c>
+      <c r="Z59" s="12" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26">
+      <c r="A60" s="41" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C60" s="42" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>1602</v>
+      </c>
+      <c r="E60" s="41" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F60" s="41" t="s">
+        <v>1606</v>
+      </c>
+      <c r="G60" s="41" t="s">
+        <v>1607</v>
+      </c>
+      <c r="H60" s="43" t="s">
+        <v>1607</v>
+      </c>
+      <c r="J60">
+        <v>10</v>
+      </c>
+      <c r="K60" s="41" t="s">
+        <v>1609</v>
+      </c>
+      <c r="L60" s="41" t="s">
+        <v>1608</v>
+      </c>
+      <c r="M60" s="42" t="s">
+        <v>1610</v>
+      </c>
+      <c r="N60" s="41" t="s">
+        <v>1607</v>
+      </c>
+      <c r="O60" s="42" t="s">
+        <v>1607</v>
+      </c>
+      <c r="P60" s="42" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26" ht="72">
+      <c r="A74" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B74" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D74" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="F62" s="12" t="s">
+      <c r="F74" s="12" t="s">
         <v>591</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G74" s="3">
         <v>32</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="H74" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="I62" s="2" t="s">
+      <c r="I74" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J62" s="2">
+      <c r="J74" s="2">
         <v>40</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="K74" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L62" s="2" t="s">
+      <c r="L74" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M62" s="3" t="s">
+      <c r="M74" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="N62" s="3" t="s">
+      <c r="N74" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="O62" s="3" t="s">
+      <c r="O74" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="P62" s="3" t="s">
+      <c r="P74" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="Q62" s="3" t="s">
+      <c r="Q74" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="R62" s="3" t="s">
+      <c r="R74" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="S62" s="2" t="s">
+      <c r="S74" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="T62" s="3" t="s">
+      <c r="T74" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="U62" s="3" t="s">
+      <c r="U74" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="V62" s="12" t="s">
+      <c r="V74" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="W62" s="12" t="s">
+      <c r="W74" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="X62" s="12" t="s">
+      <c r="X74" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="Y62" s="12" t="s">
+      <c r="Y74" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="Z62" s="12" t="s">
+      <c r="Z74" s="12" t="s">
         <v>371</v>
       </c>
     </row>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B46A48A-AF76-46E3-9877-CD491FFF29ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CB0889-8887-4FC6-9053-0132355F02E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3296" uniqueCount="1665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3317" uniqueCount="1683">
   <si>
     <t>ID</t>
   </si>
@@ -16435,37 +16435,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>1秒のチャージを行った後、敵の溝落を突き、3秒間の"怯み"を付与する</t>
-    <rPh sb="1" eb="2">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>アト</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ミゾオチ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ビョウカン</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ヒル</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>フヨ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>レベルが上がるごとにダメージが増加する</t>
     <rPh sb="4" eb="5">
       <t>ア</t>
@@ -16488,6 +16457,223 @@
     </rPh>
     <rPh sb="41" eb="42">
       <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>頭突き</t>
+    <rPh sb="0" eb="1">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スキル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>拳具</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>グ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>headbutt</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単体攻撃</t>
+    <rPh sb="0" eb="4">
+      <t>タンタイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.5</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>27秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象指定</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>60px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>不変</t>
+    <rPh sb="0" eb="2">
+      <t>フヘン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に強力な頭突きを放ち、不変ダメージを与える</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョウリョク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>フヘン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1秒のチャージを行った後、敵の溝落を突き、(式=値)の物理ダメージを与え、3秒間の"怯み"を付与する</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ミゾオチ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ヒル</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に強力な頭突きを放ち、(式=値)の不変ダメージを与える</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョウリョク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>フヘン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルごとに基礎ダメージが+(0/5/10/15/20/25)増加</t>
+    <rPh sb="6" eb="8">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとにダメージが増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとにこのスキルの基礎ダメージが+(5/10/15/20/25)増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ゾウカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -16680,7 +16866,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -16782,22 +16968,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -21392,78 +21575,149 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="62" spans="1:26" ht="35.4" customHeight="1">
-      <c r="A62" s="42" t="s">
+    <row r="62" spans="1:26" ht="51" customHeight="1">
+      <c r="A62" s="12" t="s">
         <v>1650</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>1646</v>
       </c>
-      <c r="C62" s="41" t="s">
+      <c r="C62" s="13" t="s">
         <v>1647</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>1649</v>
       </c>
-      <c r="E62" s="42" t="s">
+      <c r="E62" s="12" t="s">
         <v>1648</v>
       </c>
-      <c r="F62" s="42" t="s">
+      <c r="F62" s="12" t="s">
         <v>1651</v>
       </c>
       <c r="G62">
         <v>10</v>
       </c>
-      <c r="H62" s="43" t="s">
+      <c r="H62" s="16" t="s">
         <v>1652</v>
       </c>
-      <c r="J62" s="44">
+      <c r="J62" s="34">
         <v>30</v>
       </c>
-      <c r="K62" s="42" t="s">
+      <c r="K62" s="12" t="s">
         <v>1654</v>
       </c>
-      <c r="L62" s="42" t="s">
+      <c r="L62" s="12" t="s">
         <v>1655</v>
       </c>
-      <c r="M62" s="41" t="s">
+      <c r="M62" s="13" t="s">
         <v>1656</v>
       </c>
-      <c r="N62" s="42" t="s">
+      <c r="N62" s="12" t="s">
         <v>1657</v>
       </c>
-      <c r="O62" s="41" t="s">
+      <c r="O62" s="13" t="s">
         <v>1653</v>
       </c>
-      <c r="P62" s="42" t="s">
+      <c r="P62" s="12" t="s">
         <v>1658</v>
       </c>
-      <c r="Q62" s="43" t="s">
+      <c r="Q62" s="16" t="s">
         <v>1653</v>
       </c>
-      <c r="R62" s="45" t="s">
+      <c r="R62" s="41" t="s">
         <v>1659</v>
       </c>
-      <c r="S62" s="46" t="s">
+      <c r="S62" s="39" t="s">
         <v>1660</v>
       </c>
-      <c r="T62" s="42" t="s">
+      <c r="T62" s="12" t="s">
         <v>1648</v>
       </c>
-      <c r="V62" s="43" t="s">
+      <c r="V62" s="16" t="s">
         <v>1661</v>
       </c>
-      <c r="W62" s="42" t="s">
+      <c r="W62" s="12" t="s">
+        <v>1678</v>
+      </c>
+      <c r="X62" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="Y62" s="12" t="s">
         <v>1662</v>
       </c>
-      <c r="X62" s="42" t="s">
-        <v>865</v>
-      </c>
-      <c r="Y62" s="42" t="s">
+      <c r="Z62" s="12" t="s">
         <v>1663</v>
       </c>
-      <c r="Z62" s="42" t="s">
+    </row>
+    <row r="63" spans="1:26" ht="35.4" customHeight="1">
+      <c r="A63" s="42" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C63" s="43" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E63" s="42" t="s">
         <v>1664</v>
+      </c>
+      <c r="F63" s="42" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G63">
+        <v>30</v>
+      </c>
+      <c r="H63" s="44" t="s">
+        <v>1670</v>
+      </c>
+      <c r="J63">
+        <v>15</v>
+      </c>
+      <c r="K63" s="42" t="s">
+        <v>1671</v>
+      </c>
+      <c r="L63" s="42" t="s">
+        <v>1672</v>
+      </c>
+      <c r="M63" s="43" t="s">
+        <v>1673</v>
+      </c>
+      <c r="N63" s="42" t="s">
+        <v>1674</v>
+      </c>
+      <c r="O63" s="43" t="s">
+        <v>1672</v>
+      </c>
+      <c r="P63" s="42" t="s">
+        <v>1675</v>
+      </c>
+      <c r="Q63" s="44" t="s">
+        <v>1672</v>
+      </c>
+      <c r="R63" s="45" t="s">
+        <v>1676</v>
+      </c>
+      <c r="T63" s="42" t="s">
+        <v>1664</v>
+      </c>
+      <c r="V63" s="44" t="s">
+        <v>1677</v>
+      </c>
+      <c r="W63" s="42" t="s">
+        <v>1679</v>
+      </c>
+      <c r="X63" s="42" t="s">
+        <v>1680</v>
+      </c>
+      <c r="Y63" s="42" t="s">
+        <v>1681</v>
+      </c>
+      <c r="Z63" s="42" t="s">
+        <v>1682</v>
       </c>
     </row>
     <row r="74" spans="1:26" ht="72">

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\細川翔平\Desktop\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CB0889-8887-4FC6-9053-0132355F02E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AC2084-0215-4629-B872-CEB1FA021B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">セット効果!$A$1:$B$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">敵スキル!$A$1:$S$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">防具!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">味方スキル!$A$1:$S$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">味方スキル!$A$1:$S$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -16866,7 +16866,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -16969,18 +16969,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -21650,73 +21638,73 @@
       </c>
     </row>
     <row r="63" spans="1:26" ht="35.4" customHeight="1">
-      <c r="A63" s="42" t="s">
+      <c r="A63" s="12" t="s">
         <v>1668</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>1667</v>
       </c>
-      <c r="C63" s="43" t="s">
+      <c r="C63" s="13" t="s">
         <v>1666</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>1665</v>
       </c>
-      <c r="E63" s="42" t="s">
+      <c r="E63" s="12" t="s">
         <v>1664</v>
       </c>
-      <c r="F63" s="42" t="s">
+      <c r="F63" s="12" t="s">
         <v>1669</v>
       </c>
       <c r="G63">
         <v>30</v>
       </c>
-      <c r="H63" s="44" t="s">
+      <c r="H63" s="16" t="s">
         <v>1670</v>
       </c>
       <c r="J63">
         <v>15</v>
       </c>
-      <c r="K63" s="42" t="s">
+      <c r="K63" s="12" t="s">
         <v>1671</v>
       </c>
-      <c r="L63" s="42" t="s">
+      <c r="L63" s="12" t="s">
         <v>1672</v>
       </c>
-      <c r="M63" s="43" t="s">
+      <c r="M63" s="13" t="s">
         <v>1673</v>
       </c>
-      <c r="N63" s="42" t="s">
+      <c r="N63" s="12" t="s">
         <v>1674</v>
       </c>
-      <c r="O63" s="43" t="s">
+      <c r="O63" s="13" t="s">
         <v>1672</v>
       </c>
-      <c r="P63" s="42" t="s">
+      <c r="P63" s="12" t="s">
         <v>1675</v>
       </c>
-      <c r="Q63" s="44" t="s">
+      <c r="Q63" s="16" t="s">
         <v>1672</v>
       </c>
-      <c r="R63" s="45" t="s">
+      <c r="R63" s="41" t="s">
         <v>1676</v>
       </c>
-      <c r="T63" s="42" t="s">
+      <c r="T63" s="12" t="s">
         <v>1664</v>
       </c>
-      <c r="V63" s="44" t="s">
+      <c r="V63" s="16" t="s">
         <v>1677</v>
       </c>
-      <c r="W63" s="42" t="s">
+      <c r="W63" s="12" t="s">
         <v>1679</v>
       </c>
-      <c r="X63" s="42" t="s">
+      <c r="X63" s="12" t="s">
         <v>1680</v>
       </c>
-      <c r="Y63" s="42" t="s">
+      <c r="Y63" s="12" t="s">
         <v>1681</v>
       </c>
-      <c r="Z63" s="42" t="s">
+      <c r="Z63" s="12" t="s">
         <v>1682</v>
       </c>
     </row>
@@ -21801,7 +21789,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S62" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:S63" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CB0889-8887-4FC6-9053-0132355F02E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15F6AD0-34CE-4DDF-ACF1-FDF3D4BF3AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3317" uniqueCount="1683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3318" uniqueCount="1683">
   <si>
     <t>ID</t>
   </si>
@@ -16539,38 +16539,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>不変</t>
-    <rPh sb="0" eb="2">
-      <t>フヘン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>敵に強力な頭突きを放ち、不変ダメージを与える</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キョウリョク</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>フヘン</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>アタ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>1秒のチャージを行った後、敵の溝落を突き、(式=値)の物理ダメージを与え、3秒間の"怯み"を付与する</t>
     <rPh sb="1" eb="2">
       <t>ビョウ</t>
@@ -16614,37 +16582,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>敵に強力な頭突きを放ち、(式=値)の不変ダメージを与える</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キョウリョク</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>シキ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>フヘン</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>アタ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>レベルごとに基礎ダメージが+(0/5/10/15/20/25)増加</t>
     <rPh sb="6" eb="8">
       <t>キソ</t>
@@ -16674,6 +16611,93 @@
     </rPh>
     <rPh sb="39" eb="41">
       <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象の防御力の20%を無視する</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ムシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に強力な頭突きを放ち、物理ダメージを与える。相手の防御力を無視する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョウリョク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ムシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵に強力な頭突きを放ち、(式=値)の物理ダメージを与える。相手の防御力の20%を無視する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョウリョク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ムシ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -16866,7 +16890,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -16971,16 +16995,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -21637,7 +21652,7 @@
         <v>1661</v>
       </c>
       <c r="W62" s="12" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="X62" s="12" t="s">
         <v>865</v>
@@ -21650,74 +21665,77 @@
       </c>
     </row>
     <row r="63" spans="1:26" ht="35.4" customHeight="1">
-      <c r="A63" s="42" t="s">
+      <c r="A63" s="12" t="s">
         <v>1668</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>1667</v>
       </c>
-      <c r="C63" s="43" t="s">
+      <c r="C63" s="13" t="s">
         <v>1666</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>1665</v>
       </c>
-      <c r="E63" s="42" t="s">
+      <c r="E63" s="12" t="s">
         <v>1664</v>
       </c>
-      <c r="F63" s="42" t="s">
+      <c r="F63" s="12" t="s">
         <v>1669</v>
       </c>
       <c r="G63">
         <v>30</v>
       </c>
-      <c r="H63" s="44" t="s">
+      <c r="H63" s="16" t="s">
         <v>1670</v>
       </c>
       <c r="J63">
         <v>15</v>
       </c>
-      <c r="K63" s="42" t="s">
+      <c r="K63" s="12" t="s">
         <v>1671</v>
       </c>
-      <c r="L63" s="42" t="s">
+      <c r="L63" s="12" t="s">
         <v>1672</v>
       </c>
-      <c r="M63" s="43" t="s">
+      <c r="M63" s="13" t="s">
         <v>1673</v>
       </c>
-      <c r="N63" s="42" t="s">
+      <c r="N63" s="12" t="s">
         <v>1674</v>
       </c>
-      <c r="O63" s="43" t="s">
+      <c r="O63" s="13" t="s">
         <v>1672</v>
       </c>
-      <c r="P63" s="42" t="s">
+      <c r="P63" s="12" t="s">
         <v>1675</v>
       </c>
-      <c r="Q63" s="44" t="s">
+      <c r="Q63" s="16" t="s">
         <v>1672</v>
       </c>
-      <c r="R63" s="45" t="s">
-        <v>1676</v>
-      </c>
-      <c r="T63" s="42" t="s">
+      <c r="R63" s="34" t="s">
+        <v>242</v>
+      </c>
+      <c r="T63" s="12" t="s">
         <v>1664</v>
       </c>
-      <c r="V63" s="44" t="s">
+      <c r="U63" s="42" t="s">
+        <v>1680</v>
+      </c>
+      <c r="V63" s="16" t="s">
+        <v>1681</v>
+      </c>
+      <c r="W63" s="12" t="s">
+        <v>1682</v>
+      </c>
+      <c r="X63" s="12" t="s">
         <v>1677</v>
       </c>
-      <c r="W63" s="42" t="s">
+      <c r="Y63" s="12" t="s">
+        <v>1678</v>
+      </c>
+      <c r="Z63" s="12" t="s">
         <v>1679</v>
-      </c>
-      <c r="X63" s="42" t="s">
-        <v>1680</v>
-      </c>
-      <c r="Y63" s="42" t="s">
-        <v>1681</v>
-      </c>
-      <c r="Z63" s="42" t="s">
-        <v>1682</v>
       </c>
     </row>
     <row r="74" spans="1:26" ht="72">

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15F6AD0-34CE-4DDF-ACF1-FDF3D4BF3AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECC2B57-1452-4986-82BF-4A6B59349407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -16890,7 +16890,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -16993,9 +16993,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -21719,7 +21716,7 @@
       <c r="T63" s="12" t="s">
         <v>1664</v>
       </c>
-      <c r="U63" s="42" t="s">
+      <c r="U63" s="34" t="s">
         <v>1680</v>
       </c>
       <c r="V63" s="16" t="s">
@@ -27884,7 +27881,6 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD2C904-A80C-4DD6-9EC2-BF8829F6BFCA}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:S25"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
@@ -28006,7 +28002,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1">
+    <row r="3" spans="1:19">
       <c r="A3" s="4" t="s">
         <v>526</v>
       </c>
@@ -28035,7 +28031,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="72" hidden="1">
+    <row r="4" spans="1:19" ht="72">
       <c r="A4" s="4" t="s">
         <v>577</v>
       </c>
@@ -28067,7 +28063,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="5" spans="1:19" hidden="1">
+    <row r="5" spans="1:19">
       <c r="A5" s="4" t="s">
         <v>733</v>
       </c>
@@ -28078,7 +28074,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="6" spans="1:19" hidden="1">
+    <row r="6" spans="1:19">
       <c r="A6" s="4" t="s">
         <v>734</v>
       </c>
@@ -28089,7 +28085,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="7" spans="1:19" hidden="1">
+    <row r="7" spans="1:19">
       <c r="A7" s="4" t="s">
         <v>735</v>
       </c>
@@ -28100,7 +28096,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="8" spans="1:19" hidden="1">
+    <row r="8" spans="1:19">
       <c r="A8" s="4" t="s">
         <v>736</v>
       </c>
@@ -28315,7 +28311,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1">
+    <row r="13" spans="1:19">
       <c r="A13" s="4" t="s">
         <v>789</v>
       </c>
@@ -28347,7 +28343,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="54" hidden="1">
+    <row r="14" spans="1:19" ht="54">
       <c r="A14" s="4" t="s">
         <v>790</v>
       </c>
@@ -28394,7 +28390,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="15" spans="1:19" hidden="1">
+    <row r="15" spans="1:19">
       <c r="A15" s="4" t="s">
         <v>791</v>
       </c>
@@ -28426,7 +28422,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="16" spans="1:19" hidden="1">
+    <row r="16" spans="1:19">
       <c r="A16" s="4" t="s">
         <v>933</v>
       </c>
@@ -28458,7 +28454,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1">
+    <row r="17" spans="1:19">
       <c r="A17" s="4" t="s">
         <v>937</v>
       </c>
@@ -28490,7 +28486,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="18" spans="1:19" hidden="1">
+    <row r="18" spans="1:19">
       <c r="A18" s="4" t="s">
         <v>969</v>
       </c>
@@ -28522,7 +28518,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1">
+    <row r="19" spans="1:19">
       <c r="A19" s="4" t="s">
         <v>1079</v>
       </c>
@@ -28551,7 +28547,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="20" spans="1:19" hidden="1">
+    <row r="20" spans="1:19">
       <c r="A20" s="4" t="s">
         <v>1081</v>
       </c>
@@ -28580,7 +28576,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="21" spans="1:19" hidden="1">
+    <row r="21" spans="1:19">
       <c r="A21" s="4" t="s">
         <v>1080</v>
       </c>
@@ -28609,7 +28605,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1">
+    <row r="22" spans="1:19">
       <c r="A22" s="4" t="s">
         <v>1531</v>
       </c>
@@ -28638,7 +28634,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="36" hidden="1">
+    <row r="23" spans="1:19" ht="36">
       <c r="A23" s="4" t="s">
         <v>1396</v>
       </c>
@@ -28667,7 +28663,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="24" spans="1:19" hidden="1">
+    <row r="24" spans="1:19">
       <c r="A24" s="4" t="s">
         <v>1402</v>
       </c>
@@ -28696,7 +28692,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1">
+    <row r="25" spans="1:19">
       <c r="A25" s="4" t="s">
         <v>1395</v>
       </c>
@@ -28726,13 +28722,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O25" xr:uid="{7CD2C904-A80C-4DD6-9EC2-BF8829F6BFCA}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="消耗品"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:O25" xr:uid="{7CD2C904-A80C-4DD6-9EC2-BF8829F6BFCA}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECC2B57-1452-4986-82BF-4A6B59349407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF26E40-F816-4FFD-A601-762F6B3D5ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">セット効果!$A$1:$B$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">敵スキル!$A$1:$S$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">防具!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">味方スキル!$A$1:$S$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">味方スキル!$A$1:$S$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3318" uniqueCount="1683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3390" uniqueCount="1732">
   <si>
     <t>ID</t>
   </si>
@@ -16698,6 +16698,524 @@
     </rPh>
     <rPh sb="40" eb="42">
       <t>ムシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スキル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>杖/魔導書/楽器</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>マドウショ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガッキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>film_in</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単体バフ</t>
+    <rPh sb="0" eb="2">
+      <t>タンタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>24秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象指定</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>280px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味方</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>buff_film_in</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>被膜</t>
+    <rPh sb="0" eb="2">
+      <t>ヒマク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>被ダメージ率-15%</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受けるダメージが減少する</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>被ダメージ率が-15%下がる</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:buff_film_in)5s</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、指定した味方に"フィリン"を付与する</t>
+    <rPh sb="0" eb="3">
+      <t>エイショウゴ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>１秒の詠唱後、指定した味方に5秒間の"フィリン"を付与する</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>エイショウゴ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>付与する状態の継続時間+(0/1/2/3/4/5)秒増加</t>
+    <rPh sb="0" eb="2">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ケイゾク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに"フィリン"の効果時間が増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに"フィリン"の効果時間が+(1/2/3/4/5)秒増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フィルム</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スキル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>拳具/棒具</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>グ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ボウグ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単体攻撃</t>
+    <rPh sb="0" eb="4">
+      <t>タンタイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 1</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>28秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象指定</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>70px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>物理</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全力アタック</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>full_power_attack</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>指定した敵１体を全力で攻撃し、物理ダメージを与える</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゼンリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>指定した敵１体を全力で攻撃し、(式=値)の物理ダメージを与える</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゼンリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>足狩</t>
+    <rPh sb="0" eb="1">
+      <t>アシ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>棒具/片手剣/
+両手剣</t>
+    <rPh sb="0" eb="1">
+      <t>ボウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>グ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>カタテケン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>リョウテケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>feet_hunt</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.4</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>32秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>80px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>指定した敵の足を攻撃し、物理ダメージを与え、"怯み"を付与する</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アシ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヒル</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>指定した敵１体の足を攻撃し、(式=値)の物理ダメージを与え、3秒間の"怯み"を付与する</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アシ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ヒル</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに"怯み"の効果時間が増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヒル</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに"怯み"の効果時間が+(1/2/3/4/5)秒増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヒル</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ゾウカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -16890,7 +17408,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -16993,6 +17511,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -17329,6 +17859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z74"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
@@ -17431,7 +17962,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="36">
+    <row r="2" spans="1:26" ht="36" hidden="1">
       <c r="A2" s="3" t="s">
         <v>174</v>
       </c>
@@ -17669,7 +18200,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="54">
+    <row r="5" spans="1:26" ht="54" hidden="1">
       <c r="A5" s="3" t="s">
         <v>176</v>
       </c>
@@ -17749,7 +18280,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="36">
+    <row r="6" spans="1:26" ht="36" hidden="1">
       <c r="A6" s="3" t="s">
         <v>177</v>
       </c>
@@ -17907,7 +18438,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="54">
+    <row r="8" spans="1:26" ht="54" hidden="1">
       <c r="A8" s="3" t="s">
         <v>179</v>
       </c>
@@ -17987,7 +18518,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="36">
+    <row r="9" spans="1:26" ht="36" hidden="1">
       <c r="A9" s="3" t="s">
         <v>387</v>
       </c>
@@ -18145,7 +18676,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="36">
+    <row r="11" spans="1:26" ht="36" hidden="1">
       <c r="A11" s="3" t="s">
         <v>330</v>
       </c>
@@ -18225,7 +18756,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="72">
+    <row r="12" spans="1:26" ht="72" hidden="1">
       <c r="A12" s="3" t="s">
         <v>386</v>
       </c>
@@ -18381,7 +18912,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="143.4" customHeight="1">
+    <row r="14" spans="1:26" ht="143.4" hidden="1" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>180</v>
       </c>
@@ -18781,7 +19312,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="36">
+    <row r="19" spans="1:26" ht="36" hidden="1">
       <c r="A19" s="3" t="s">
         <v>185</v>
       </c>
@@ -18850,7 +19381,7 @@
       </c>
       <c r="X19" s="12"/>
     </row>
-    <row r="20" spans="1:26" ht="90">
+    <row r="20" spans="1:26" ht="90" hidden="1">
       <c r="A20" s="3" t="s">
         <v>186</v>
       </c>
@@ -18920,7 +19451,7 @@
       <c r="X20" s="12"/>
       <c r="Y20" s="16"/>
     </row>
-    <row r="21" spans="1:26" ht="72">
+    <row r="21" spans="1:26" ht="72" hidden="1">
       <c r="A21" s="3" t="s">
         <v>187</v>
       </c>
@@ -18989,7 +19520,7 @@
       </c>
       <c r="X21" s="12"/>
     </row>
-    <row r="22" spans="1:26" ht="54">
+    <row r="22" spans="1:26" ht="54" hidden="1">
       <c r="A22" s="3" t="s">
         <v>209</v>
       </c>
@@ -19130,7 +19661,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="36">
+    <row r="24" spans="1:26" ht="36" hidden="1">
       <c r="A24" s="12" t="s">
         <v>841</v>
       </c>
@@ -19192,7 +19723,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="36">
+    <row r="25" spans="1:26" ht="36" hidden="1">
       <c r="A25" s="12" t="s">
         <v>842</v>
       </c>
@@ -19257,7 +19788,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="36">
+    <row r="26" spans="1:26" ht="36" hidden="1">
       <c r="A26" s="12" t="s">
         <v>895</v>
       </c>
@@ -19319,7 +19850,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="36">
+    <row r="27" spans="1:26" ht="36" hidden="1">
       <c r="A27" s="12" t="s">
         <v>843</v>
       </c>
@@ -19384,7 +19915,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="72">
+    <row r="28" spans="1:26" ht="72" hidden="1">
       <c r="A28" s="12" t="s">
         <v>844</v>
       </c>
@@ -19455,7 +19986,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="36">
+    <row r="29" spans="1:26" ht="36" hidden="1">
       <c r="A29" s="12" t="s">
         <v>845</v>
       </c>
@@ -19523,7 +20054,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="36">
+    <row r="30" spans="1:26" ht="36" hidden="1">
       <c r="A30" s="12" t="s">
         <v>846</v>
       </c>
@@ -19591,7 +20122,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="36">
+    <row r="31" spans="1:26" ht="36" hidden="1">
       <c r="A31" s="12" t="s">
         <v>1172</v>
       </c>
@@ -19657,7 +20188,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="54">
+    <row r="32" spans="1:26" ht="54" hidden="1">
       <c r="A32" s="12" t="s">
         <v>1173</v>
       </c>
@@ -19725,7 +20256,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="36">
+    <row r="33" spans="1:26" ht="36" hidden="1">
       <c r="A33" s="12" t="s">
         <v>1179</v>
       </c>
@@ -19790,7 +20321,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="108">
+    <row r="34" spans="1:26" ht="108" hidden="1">
       <c r="A34" s="12" t="s">
         <v>1175</v>
       </c>
@@ -19858,7 +20389,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="90">
+    <row r="35" spans="1:26" ht="90" hidden="1">
       <c r="A35" s="12" t="s">
         <v>1176</v>
       </c>
@@ -19932,7 +20463,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="54">
+    <row r="36" spans="1:26" ht="54" hidden="1">
       <c r="A36" s="12" t="s">
         <v>1177</v>
       </c>
@@ -20003,7 +20534,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="36">
+    <row r="37" spans="1:26" ht="36" hidden="1">
       <c r="A37" s="12" t="s">
         <v>1178</v>
       </c>
@@ -20077,7 +20608,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="36">
+    <row r="38" spans="1:26" ht="36" hidden="1">
       <c r="A38" s="12" t="s">
         <v>1180</v>
       </c>
@@ -20143,7 +20674,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="36">
+    <row r="39" spans="1:26" ht="36" hidden="1">
       <c r="A39" s="12" t="s">
         <v>1181</v>
       </c>
@@ -20212,7 +20743,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="36">
+    <row r="40" spans="1:26" ht="36" hidden="1">
       <c r="A40" s="12" t="s">
         <v>1182</v>
       </c>
@@ -20278,7 +20809,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="36">
+    <row r="41" spans="1:26" ht="36" hidden="1">
       <c r="A41" s="12" t="s">
         <v>1183</v>
       </c>
@@ -20346,7 +20877,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="36">
+    <row r="42" spans="1:26" ht="36" hidden="1">
       <c r="A42" s="12" t="s">
         <v>1184</v>
       </c>
@@ -20492,7 +21023,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="44" spans="1:26" ht="36">
+    <row r="44" spans="1:26" ht="36" hidden="1">
       <c r="A44" s="4" t="s">
         <v>1391</v>
       </c>
@@ -20522,7 +21053,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="45" spans="1:26" ht="36">
+    <row r="45" spans="1:26" ht="36" hidden="1">
       <c r="A45" s="34" t="s">
         <v>1392</v>
       </c>
@@ -20554,7 +21085,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="54">
+    <row r="46" spans="1:26" ht="54" hidden="1">
       <c r="A46" s="34" t="s">
         <v>1393</v>
       </c>
@@ -20584,7 +21115,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="54">
+    <row r="47" spans="1:26" ht="54" hidden="1">
       <c r="A47" s="34" t="s">
         <v>1394</v>
       </c>
@@ -20614,7 +21145,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="48" spans="1:26" ht="72">
+    <row r="48" spans="1:26" ht="72" hidden="1">
       <c r="A48" s="4" t="s">
         <v>1253</v>
       </c>
@@ -20662,7 +21193,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="36">
+    <row r="49" spans="1:26" ht="36" hidden="1">
       <c r="A49" s="12" t="s">
         <v>1437</v>
       </c>
@@ -20728,7 +21259,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="54">
+    <row r="50" spans="1:26" ht="54" hidden="1">
       <c r="A50" s="12" t="s">
         <v>1438</v>
       </c>
@@ -20797,7 +21328,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="51" spans="1:26" ht="36">
+    <row r="51" spans="1:26" ht="36" hidden="1">
       <c r="A51" s="12" t="s">
         <v>1439</v>
       </c>
@@ -20863,7 +21394,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="54">
+    <row r="52" spans="1:26" ht="54" hidden="1">
       <c r="A52" s="12" t="s">
         <v>1440</v>
       </c>
@@ -20929,7 +21460,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="90">
+    <row r="53" spans="1:26" ht="90" hidden="1">
       <c r="A53" s="12" t="s">
         <v>1441</v>
       </c>
@@ -21001,7 +21532,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="54" spans="1:26" ht="54">
+    <row r="54" spans="1:26" ht="54" hidden="1">
       <c r="A54" s="12" t="s">
         <v>1442</v>
       </c>
@@ -21073,7 +21604,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="36">
+    <row r="55" spans="1:26" ht="36" hidden="1">
       <c r="A55" s="12" t="s">
         <v>1443</v>
       </c>
@@ -21735,6 +22266,216 @@
         <v>1679</v>
       </c>
     </row>
+    <row r="64" spans="1:26" ht="36">
+      <c r="A64" s="12" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>1683</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>1687</v>
+      </c>
+      <c r="G64" s="12" t="s">
+        <v>1688</v>
+      </c>
+      <c r="J64">
+        <v>30</v>
+      </c>
+      <c r="K64" s="12" t="s">
+        <v>1689</v>
+      </c>
+      <c r="L64" s="12" t="s">
+        <v>1690</v>
+      </c>
+      <c r="M64" s="13" t="s">
+        <v>1691</v>
+      </c>
+      <c r="N64" s="12" t="s">
+        <v>1692</v>
+      </c>
+      <c r="O64" s="13" t="s">
+        <v>1688</v>
+      </c>
+      <c r="P64" s="12" t="s">
+        <v>1693</v>
+      </c>
+      <c r="Q64" s="16" t="s">
+        <v>1688</v>
+      </c>
+      <c r="R64" s="34" t="s">
+        <v>1688</v>
+      </c>
+      <c r="S64" s="39" t="s">
+        <v>1699</v>
+      </c>
+      <c r="T64" s="12" t="s">
+        <v>1705</v>
+      </c>
+      <c r="V64" s="16" t="s">
+        <v>1700</v>
+      </c>
+      <c r="W64" s="12" t="s">
+        <v>1701</v>
+      </c>
+      <c r="X64" s="12" t="s">
+        <v>1702</v>
+      </c>
+      <c r="Y64" s="12" t="s">
+        <v>1703</v>
+      </c>
+      <c r="Z64" s="12" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" ht="36">
+      <c r="A65" s="42" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C65" s="43" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>1706</v>
+      </c>
+      <c r="E65" s="42" t="s">
+        <v>1718</v>
+      </c>
+      <c r="F65" s="42" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G65">
+        <v>20</v>
+      </c>
+      <c r="H65" s="44" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J65" s="45" t="s">
+        <v>1711</v>
+      </c>
+      <c r="K65" s="42" t="s">
+        <v>1712</v>
+      </c>
+      <c r="L65" s="42" t="s">
+        <v>1713</v>
+      </c>
+      <c r="M65" s="43" t="s">
+        <v>1714</v>
+      </c>
+      <c r="N65" s="42" t="s">
+        <v>1715</v>
+      </c>
+      <c r="O65" s="43" t="s">
+        <v>1711</v>
+      </c>
+      <c r="P65" s="42" t="s">
+        <v>1716</v>
+      </c>
+      <c r="R65" s="45" t="s">
+        <v>1717</v>
+      </c>
+      <c r="T65" s="42" t="s">
+        <v>1718</v>
+      </c>
+      <c r="V65" s="44" t="s">
+        <v>1720</v>
+      </c>
+      <c r="W65" s="42" t="s">
+        <v>1721</v>
+      </c>
+      <c r="X65" s="42" t="s">
+        <v>865</v>
+      </c>
+      <c r="Y65" s="12" t="s">
+        <v>1662</v>
+      </c>
+      <c r="Z65" s="12" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" ht="36">
+      <c r="A66" s="42" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C66" s="43" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>1706</v>
+      </c>
+      <c r="E66" s="42" t="s">
+        <v>1722</v>
+      </c>
+      <c r="F66" s="42" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G66">
+        <v>10</v>
+      </c>
+      <c r="H66" s="44" t="s">
+        <v>1725</v>
+      </c>
+      <c r="J66" s="45" t="s">
+        <v>1711</v>
+      </c>
+      <c r="K66" s="42" t="s">
+        <v>1726</v>
+      </c>
+      <c r="L66" s="42" t="s">
+        <v>1711</v>
+      </c>
+      <c r="M66" s="43" t="s">
+        <v>1714</v>
+      </c>
+      <c r="N66" s="42" t="s">
+        <v>1727</v>
+      </c>
+      <c r="O66" s="43" t="s">
+        <v>1711</v>
+      </c>
+      <c r="P66" s="42" t="s">
+        <v>1716</v>
+      </c>
+      <c r="R66" s="45" t="s">
+        <v>1717</v>
+      </c>
+      <c r="S66" s="45" t="s">
+        <v>1660</v>
+      </c>
+      <c r="T66" s="42" t="s">
+        <v>1722</v>
+      </c>
+      <c r="V66" s="44" t="s">
+        <v>1728</v>
+      </c>
+      <c r="W66" s="42" t="s">
+        <v>1729</v>
+      </c>
+      <c r="X66" s="12" t="s">
+        <v>1702</v>
+      </c>
+      <c r="Y66" s="12" t="s">
+        <v>1730</v>
+      </c>
+      <c r="Z66" s="12" t="s">
+        <v>1731</v>
+      </c>
+    </row>
     <row r="74" spans="1:26" ht="72">
       <c r="A74" s="3" t="s">
         <v>402</v>
@@ -21816,7 +22557,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S62" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:S63" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="スキル"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -23388,7 +24135,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -23942,6 +24689,29 @@
       </c>
       <c r="G24" s="4" t="s">
         <v>1644</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>1696</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>1697</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>1698</v>
       </c>
     </row>
   </sheetData>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF26E40-F816-4FFD-A601-762F6B3D5ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8998E2C1-A0E9-482C-9EB2-B0E3E4CF4825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16821,47 +16821,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>詠唱後、指定した味方に"フィリン"を付与する</t>
-    <rPh sb="0" eb="3">
-      <t>エイショウゴ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ミカタ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>フヨ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>１秒の詠唱後、指定した味方に5秒間の"フィリン"を付与する</t>
-    <rPh sb="1" eb="2">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>エイショウゴ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ミカタ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>フヨ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>付与する状態の継続時間+(0/1/2/3/4/5)秒増加</t>
     <rPh sb="0" eb="2">
       <t>フヨ</t>
@@ -16879,35 +16838,6 @@
       <t>ビョウ</t>
     </rPh>
     <rPh sb="26" eb="28">
-      <t>ゾウカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>レベルが上がるごとに"フィリン"の効果時間が増加する</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="17" eb="21">
-      <t>コウカジカン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ゾウカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>レベルが上がるごとに"フィリン"の効果時間が+(1/2/3/4/5)秒増加する</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="17" eb="21">
-      <t>コウカジカン</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
       <t>ゾウカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
@@ -17207,6 +17137,88 @@
     </rPh>
     <rPh sb="11" eb="12">
       <t>ヒル</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詠唱後、指定した味方に"被膜"を付与する</t>
+    <rPh sb="0" eb="3">
+      <t>エイショウゴ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒマク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>１秒の詠唱後、指定した味方に5秒間の"被膜"を付与する</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>エイショウゴ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒマク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに"被膜"の効果時間が増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒマク</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レベルが上がるごとに"被膜"の効果時間が+(1/2/3/4/5)秒増加する</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒマク</t>
     </rPh>
     <rPh sb="15" eb="19">
       <t>コウカジカン</t>
@@ -17408,7 +17420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -17511,18 +17523,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -22280,7 +22280,7 @@
         <v>1683</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>1705</v>
+        <v>1701</v>
       </c>
       <c r="F64" s="12" t="s">
         <v>1687</v>
@@ -22319,83 +22319,83 @@
         <v>1699</v>
       </c>
       <c r="T64" s="12" t="s">
-        <v>1705</v>
+        <v>1701</v>
       </c>
       <c r="V64" s="16" t="s">
+        <v>1728</v>
+      </c>
+      <c r="W64" s="12" t="s">
+        <v>1729</v>
+      </c>
+      <c r="X64" s="12" t="s">
         <v>1700</v>
       </c>
-      <c r="W64" s="12" t="s">
-        <v>1701</v>
-      </c>
-      <c r="X64" s="12" t="s">
-        <v>1702</v>
-      </c>
       <c r="Y64" s="12" t="s">
-        <v>1703</v>
+        <v>1730</v>
       </c>
       <c r="Z64" s="12" t="s">
-        <v>1704</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="65" spans="1:26" ht="36">
-      <c r="A65" s="42" t="s">
-        <v>1719</v>
+      <c r="A65" s="12" t="s">
+        <v>1715</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1708</v>
-      </c>
-      <c r="C65" s="43" t="s">
-        <v>1707</v>
+        <v>1704</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>1703</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>1706</v>
-      </c>
-      <c r="E65" s="42" t="s">
-        <v>1718</v>
-      </c>
-      <c r="F65" s="42" t="s">
-        <v>1709</v>
+        <v>1702</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>1714</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>1705</v>
       </c>
       <c r="G65">
         <v>20</v>
       </c>
-      <c r="H65" s="44" t="s">
+      <c r="H65" s="16" t="s">
+        <v>1706</v>
+      </c>
+      <c r="J65" s="34" t="s">
+        <v>1707</v>
+      </c>
+      <c r="K65" s="12" t="s">
+        <v>1708</v>
+      </c>
+      <c r="L65" s="12" t="s">
+        <v>1709</v>
+      </c>
+      <c r="M65" s="13" t="s">
         <v>1710</v>
       </c>
-      <c r="J65" s="45" t="s">
+      <c r="N65" s="12" t="s">
         <v>1711</v>
       </c>
-      <c r="K65" s="42" t="s">
+      <c r="O65" s="13" t="s">
+        <v>1707</v>
+      </c>
+      <c r="P65" s="12" t="s">
         <v>1712</v>
       </c>
-      <c r="L65" s="42" t="s">
+      <c r="R65" s="34" t="s">
         <v>1713</v>
       </c>
-      <c r="M65" s="43" t="s">
+      <c r="T65" s="12" t="s">
         <v>1714</v>
       </c>
-      <c r="N65" s="42" t="s">
-        <v>1715</v>
-      </c>
-      <c r="O65" s="43" t="s">
-        <v>1711</v>
-      </c>
-      <c r="P65" s="42" t="s">
+      <c r="V65" s="16" t="s">
         <v>1716</v>
       </c>
-      <c r="R65" s="45" t="s">
+      <c r="W65" s="12" t="s">
         <v>1717</v>
       </c>
-      <c r="T65" s="42" t="s">
-        <v>1718</v>
-      </c>
-      <c r="V65" s="44" t="s">
-        <v>1720</v>
-      </c>
-      <c r="W65" s="42" t="s">
-        <v>1721</v>
-      </c>
-      <c r="X65" s="42" t="s">
+      <c r="X65" s="12" t="s">
         <v>865</v>
       </c>
       <c r="Y65" s="12" t="s">
@@ -22406,74 +22406,74 @@
       </c>
     </row>
     <row r="66" spans="1:26" ht="36">
-      <c r="A66" s="42" t="s">
-        <v>1724</v>
+      <c r="A66" s="12" t="s">
+        <v>1720</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>1723</v>
-      </c>
-      <c r="C66" s="43" t="s">
-        <v>1707</v>
+        <v>1719</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>1703</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>1706</v>
-      </c>
-      <c r="E66" s="42" t="s">
-        <v>1722</v>
-      </c>
-      <c r="F66" s="42" t="s">
-        <v>1709</v>
+        <v>1702</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>1718</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>1705</v>
       </c>
       <c r="G66">
         <v>10</v>
       </c>
-      <c r="H66" s="44" t="s">
+      <c r="H66" s="16" t="s">
+        <v>1721</v>
+      </c>
+      <c r="J66" s="34" t="s">
+        <v>1707</v>
+      </c>
+      <c r="K66" s="12" t="s">
+        <v>1722</v>
+      </c>
+      <c r="L66" s="12" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M66" s="13" t="s">
+        <v>1710</v>
+      </c>
+      <c r="N66" s="12" t="s">
+        <v>1723</v>
+      </c>
+      <c r="O66" s="13" t="s">
+        <v>1707</v>
+      </c>
+      <c r="P66" s="12" t="s">
+        <v>1712</v>
+      </c>
+      <c r="R66" s="34" t="s">
+        <v>1713</v>
+      </c>
+      <c r="S66" s="34" t="s">
+        <v>1660</v>
+      </c>
+      <c r="T66" s="12" t="s">
+        <v>1718</v>
+      </c>
+      <c r="V66" s="16" t="s">
+        <v>1724</v>
+      </c>
+      <c r="W66" s="12" t="s">
         <v>1725</v>
       </c>
-      <c r="J66" s="45" t="s">
-        <v>1711</v>
-      </c>
-      <c r="K66" s="42" t="s">
+      <c r="X66" s="12" t="s">
+        <v>1700</v>
+      </c>
+      <c r="Y66" s="12" t="s">
         <v>1726</v>
       </c>
-      <c r="L66" s="42" t="s">
-        <v>1711</v>
-      </c>
-      <c r="M66" s="43" t="s">
-        <v>1714</v>
-      </c>
-      <c r="N66" s="42" t="s">
+      <c r="Z66" s="12" t="s">
         <v>1727</v>
-      </c>
-      <c r="O66" s="43" t="s">
-        <v>1711</v>
-      </c>
-      <c r="P66" s="42" t="s">
-        <v>1716</v>
-      </c>
-      <c r="R66" s="45" t="s">
-        <v>1717</v>
-      </c>
-      <c r="S66" s="45" t="s">
-        <v>1660</v>
-      </c>
-      <c r="T66" s="42" t="s">
-        <v>1722</v>
-      </c>
-      <c r="V66" s="44" t="s">
-        <v>1728</v>
-      </c>
-      <c r="W66" s="42" t="s">
-        <v>1729</v>
-      </c>
-      <c r="X66" s="12" t="s">
-        <v>1702</v>
-      </c>
-      <c r="Y66" s="12" t="s">
-        <v>1730</v>
-      </c>
-      <c r="Z66" s="12" t="s">
-        <v>1731</v>
       </c>
     </row>
     <row r="74" spans="1:26" ht="72">

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8998E2C1-A0E9-482C-9EB2-B0E3E4CF4825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9A9397-86BB-4663-8E2D-C3815C34D674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">セット効果!$A$1:$B$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">敵スキル!$A$1:$S$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">防具!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">味方スキル!$A$1:$S$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">味方スキル!$A$1:$S$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -17859,7 +17859,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z74"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
@@ -17962,7 +17961,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="36" hidden="1">
+    <row r="2" spans="1:26" ht="36">
       <c r="A2" s="3" t="s">
         <v>174</v>
       </c>
@@ -18200,7 +18199,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="54" hidden="1">
+    <row r="5" spans="1:26" ht="54">
       <c r="A5" s="3" t="s">
         <v>176</v>
       </c>
@@ -18280,7 +18279,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="36" hidden="1">
+    <row r="6" spans="1:26" ht="36">
       <c r="A6" s="3" t="s">
         <v>177</v>
       </c>
@@ -18438,7 +18437,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="54" hidden="1">
+    <row r="8" spans="1:26" ht="54">
       <c r="A8" s="3" t="s">
         <v>179</v>
       </c>
@@ -18518,7 +18517,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="36" hidden="1">
+    <row r="9" spans="1:26" ht="36">
       <c r="A9" s="3" t="s">
         <v>387</v>
       </c>
@@ -18676,7 +18675,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="36" hidden="1">
+    <row r="11" spans="1:26" ht="36">
       <c r="A11" s="3" t="s">
         <v>330</v>
       </c>
@@ -18756,7 +18755,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="72" hidden="1">
+    <row r="12" spans="1:26" ht="72">
       <c r="A12" s="3" t="s">
         <v>386</v>
       </c>
@@ -18912,7 +18911,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="143.4" hidden="1" customHeight="1">
+    <row r="14" spans="1:26" ht="143.4" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>180</v>
       </c>
@@ -19312,7 +19311,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="36" hidden="1">
+    <row r="19" spans="1:26" ht="36">
       <c r="A19" s="3" t="s">
         <v>185</v>
       </c>
@@ -19381,7 +19380,7 @@
       </c>
       <c r="X19" s="12"/>
     </row>
-    <row r="20" spans="1:26" ht="90" hidden="1">
+    <row r="20" spans="1:26" ht="90">
       <c r="A20" s="3" t="s">
         <v>186</v>
       </c>
@@ -19451,7 +19450,7 @@
       <c r="X20" s="12"/>
       <c r="Y20" s="16"/>
     </row>
-    <row r="21" spans="1:26" ht="72" hidden="1">
+    <row r="21" spans="1:26" ht="72">
       <c r="A21" s="3" t="s">
         <v>187</v>
       </c>
@@ -19520,7 +19519,7 @@
       </c>
       <c r="X21" s="12"/>
     </row>
-    <row r="22" spans="1:26" ht="54" hidden="1">
+    <row r="22" spans="1:26" ht="54">
       <c r="A22" s="3" t="s">
         <v>209</v>
       </c>
@@ -19661,7 +19660,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="36" hidden="1">
+    <row r="24" spans="1:26" ht="36">
       <c r="A24" s="12" t="s">
         <v>841</v>
       </c>
@@ -19723,7 +19722,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="36" hidden="1">
+    <row r="25" spans="1:26" ht="36">
       <c r="A25" s="12" t="s">
         <v>842</v>
       </c>
@@ -19788,7 +19787,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="36" hidden="1">
+    <row r="26" spans="1:26" ht="36">
       <c r="A26" s="12" t="s">
         <v>895</v>
       </c>
@@ -19850,7 +19849,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="36" hidden="1">
+    <row r="27" spans="1:26" ht="36">
       <c r="A27" s="12" t="s">
         <v>843</v>
       </c>
@@ -19915,7 +19914,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="72" hidden="1">
+    <row r="28" spans="1:26" ht="72">
       <c r="A28" s="12" t="s">
         <v>844</v>
       </c>
@@ -19986,7 +19985,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="36" hidden="1">
+    <row r="29" spans="1:26" ht="36">
       <c r="A29" s="12" t="s">
         <v>845</v>
       </c>
@@ -20054,7 +20053,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="36" hidden="1">
+    <row r="30" spans="1:26" ht="36">
       <c r="A30" s="12" t="s">
         <v>846</v>
       </c>
@@ -20122,7 +20121,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="36" hidden="1">
+    <row r="31" spans="1:26" ht="36">
       <c r="A31" s="12" t="s">
         <v>1172</v>
       </c>
@@ -20188,7 +20187,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="54" hidden="1">
+    <row r="32" spans="1:26" ht="54">
       <c r="A32" s="12" t="s">
         <v>1173</v>
       </c>
@@ -20256,7 +20255,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="36" hidden="1">
+    <row r="33" spans="1:26" ht="36">
       <c r="A33" s="12" t="s">
         <v>1179</v>
       </c>
@@ -20321,7 +20320,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="108" hidden="1">
+    <row r="34" spans="1:26" ht="108">
       <c r="A34" s="12" t="s">
         <v>1175</v>
       </c>
@@ -20389,7 +20388,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="90" hidden="1">
+    <row r="35" spans="1:26" ht="90">
       <c r="A35" s="12" t="s">
         <v>1176</v>
       </c>
@@ -20463,7 +20462,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="54" hidden="1">
+    <row r="36" spans="1:26" ht="54">
       <c r="A36" s="12" t="s">
         <v>1177</v>
       </c>
@@ -20534,7 +20533,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="36" hidden="1">
+    <row r="37" spans="1:26" ht="36">
       <c r="A37" s="12" t="s">
         <v>1178</v>
       </c>
@@ -20608,7 +20607,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="36" hidden="1">
+    <row r="38" spans="1:26" ht="36">
       <c r="A38" s="12" t="s">
         <v>1180</v>
       </c>
@@ -20674,7 +20673,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="36" hidden="1">
+    <row r="39" spans="1:26" ht="36">
       <c r="A39" s="12" t="s">
         <v>1181</v>
       </c>
@@ -20743,7 +20742,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="36" hidden="1">
+    <row r="40" spans="1:26" ht="36">
       <c r="A40" s="12" t="s">
         <v>1182</v>
       </c>
@@ -20809,7 +20808,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="36" hidden="1">
+    <row r="41" spans="1:26" ht="36">
       <c r="A41" s="12" t="s">
         <v>1183</v>
       </c>
@@ -20877,7 +20876,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="36" hidden="1">
+    <row r="42" spans="1:26" ht="36">
       <c r="A42" s="12" t="s">
         <v>1184</v>
       </c>
@@ -21023,7 +21022,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="44" spans="1:26" ht="36" hidden="1">
+    <row r="44" spans="1:26" ht="36">
       <c r="A44" s="4" t="s">
         <v>1391</v>
       </c>
@@ -21053,7 +21052,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="45" spans="1:26" ht="36" hidden="1">
+    <row r="45" spans="1:26" ht="36">
       <c r="A45" s="34" t="s">
         <v>1392</v>
       </c>
@@ -21085,7 +21084,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="54" hidden="1">
+    <row r="46" spans="1:26" ht="54">
       <c r="A46" s="34" t="s">
         <v>1393</v>
       </c>
@@ -21115,7 +21114,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="54" hidden="1">
+    <row r="47" spans="1:26" ht="54">
       <c r="A47" s="34" t="s">
         <v>1394</v>
       </c>
@@ -21145,7 +21144,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="48" spans="1:26" ht="72" hidden="1">
+    <row r="48" spans="1:26" ht="72">
       <c r="A48" s="4" t="s">
         <v>1253</v>
       </c>
@@ -21193,7 +21192,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="36" hidden="1">
+    <row r="49" spans="1:26" ht="36">
       <c r="A49" s="12" t="s">
         <v>1437</v>
       </c>
@@ -21259,7 +21258,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="54" hidden="1">
+    <row r="50" spans="1:26" ht="54">
       <c r="A50" s="12" t="s">
         <v>1438</v>
       </c>
@@ -21328,7 +21327,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="51" spans="1:26" ht="36" hidden="1">
+    <row r="51" spans="1:26" ht="36">
       <c r="A51" s="12" t="s">
         <v>1439</v>
       </c>
@@ -21394,7 +21393,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="54" hidden="1">
+    <row r="52" spans="1:26" ht="54">
       <c r="A52" s="12" t="s">
         <v>1440</v>
       </c>
@@ -21460,7 +21459,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="90" hidden="1">
+    <row r="53" spans="1:26" ht="90">
       <c r="A53" s="12" t="s">
         <v>1441</v>
       </c>
@@ -21532,7 +21531,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="54" spans="1:26" ht="54" hidden="1">
+    <row r="54" spans="1:26" ht="54">
       <c r="A54" s="12" t="s">
         <v>1442</v>
       </c>
@@ -21604,7 +21603,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="36" hidden="1">
+    <row r="55" spans="1:26" ht="36">
       <c r="A55" s="12" t="s">
         <v>1443</v>
       </c>
@@ -22557,13 +22556,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S63" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="スキル"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:S66" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3390" uniqueCount="1732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3396" uniqueCount="1759">
   <si>
     <t>ID</t>
   </si>
@@ -17230,6 +17230,87 @@
       <t>ゾウカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kari_waist</t>
+  </si>
+  <si>
+    <t>仮ベルト</t>
+  </si>
+  <si>
+    <t>腰</t>
+  </si>
+  <si>
+    <t>仮グリーブ</t>
+  </si>
+  <si>
+    <t>脚</t>
+  </si>
+  <si>
+    <t>horn_rabbit_waist</t>
+  </si>
+  <si>
+    <t>ツサギベルト</t>
+  </si>
+  <si>
+    <t>ツノウサギの毛皮を元に作られた暖かい腰装備</t>
+  </si>
+  <si>
+    <t>ツサギグリーブ</t>
+  </si>
+  <si>
+    <t>ツノウサギの毛皮を元に作られた暖かい脚装備</t>
+  </si>
+  <si>
+    <t>bud_alraune_waist</t>
+  </si>
+  <si>
+    <t>アルラベルト</t>
+  </si>
+  <si>
+    <t>アルラウネの葉を元に作られた腰装備</t>
+  </si>
+  <si>
+    <t>アルラグリーブ</t>
+  </si>
+  <si>
+    <t>アルラウネの葉を元に作られた脚装備</t>
+  </si>
+  <si>
+    <t>shadow_wolf_waist</t>
+  </si>
+  <si>
+    <t>影狼帯</t>
+  </si>
+  <si>
+    <t>シャドウウルフの毛皮を元に作られた腰装備</t>
+  </si>
+  <si>
+    <t>影狼脚甲</t>
+  </si>
+  <si>
+    <t>シャドウウルフの毛皮を元に作られた脚装備</t>
+  </si>
+  <si>
+    <t>flostiny_waist</t>
+  </si>
+  <si>
+    <t>ディスティニベルト</t>
+  </si>
+  <si>
+    <t>フロスティーニ素材で作られた腰装備</t>
+  </si>
+  <si>
+    <t>ディスティニグリーブ</t>
+  </si>
+  <si>
+    <t>フロスティーニ素材で作られた脚装備</t>
+  </si>
+  <si>
+    <t>仮ブーツ</t>
+  </si>
+  <si>
+    <t>影狼靴</t>
   </si>
 </sst>
 </file>
@@ -27495,16 +27576,16 @@
     </row>
     <row r="4" spans="1:18" ht="36">
       <c r="A4" s="4" t="s">
-        <v>544</v>
+        <v>1732</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>551</v>
+        <v>1733</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>517</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>556</v>
+        <v>1734</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>561</v>
@@ -27536,13 +27617,13 @@
         <v>545</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>552</v>
+        <v>1757</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>517</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>558</v>
+        <v>1736</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>561</v>
@@ -27717,16 +27798,16 @@
     </row>
     <row r="10" spans="1:18" ht="36">
       <c r="A10" s="4" t="s">
-        <v>897</v>
+        <v>1737</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>909</v>
+        <v>1738</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>916</v>
+        <v>1734</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>894</v>
@@ -27744,10 +27825,10 @@
         <v>979</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>1004</v>
+        <v>1739</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>1004</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="36">
@@ -27761,7 +27842,7 @@
         <v>164</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>917</v>
+        <v>1736</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>894</v>
@@ -27779,10 +27860,10 @@
         <v>983</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>1005</v>
+        <v>1741</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>1005</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="36">
@@ -27924,16 +28005,16 @@
     </row>
     <row r="16" spans="1:18" ht="36">
       <c r="A16" s="4" t="s">
-        <v>955</v>
+        <v>1742</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>948</v>
+        <v>1743</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>556</v>
+        <v>1734</v>
       </c>
       <c r="E16" t="s">
         <v>952</v>
@@ -27951,10 +28032,10 @@
         <v>999</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>1009</v>
+        <v>1744</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>1009</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="36">
@@ -27968,7 +28049,7 @@
         <v>164</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>558</v>
+        <v>1736</v>
       </c>
       <c r="E17" t="s">
         <v>952</v>
@@ -27986,10 +28067,10 @@
         <v>1001</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>1010</v>
+        <v>1746</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>1010</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="36">
@@ -28131,16 +28212,16 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="4" t="s">
-        <v>1102</v>
+        <v>1747</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1098</v>
+        <v>1748</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>1110</v>
+        <v>1734</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>1113</v>
@@ -28158,10 +28239,10 @@
         <v>1126</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>1130</v>
+        <v>1749</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>1130</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="36">
@@ -28169,13 +28250,13 @@
         <v>1103</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1099</v>
+        <v>1758</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1111</v>
+        <v>1736</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>1113</v>
@@ -28193,10 +28274,10 @@
         <v>1214</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>1131</v>
+        <v>1751</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>1131</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -28321,16 +28402,16 @@
     </row>
     <row r="28" spans="1:12" ht="54">
       <c r="A28" s="4" t="s">
-        <v>1419</v>
+        <v>1752</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1424</v>
+        <v>1753</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1430</v>
+        <v>1734</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>1408</v>
@@ -28343,6 +28424,12 @@
       </c>
       <c r="I28" s="11" t="s">
         <v>1528</v>
+      </c>
+      <c r="K28" t="s">
+        <v>1754</v>
+      </c>
+      <c r="L28" t="s">
+        <v>1754</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="54">
@@ -28356,7 +28443,7 @@
         <v>164</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1431</v>
+        <v>1736</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>1408</v>
@@ -28369,6 +28456,12 @@
       </c>
       <c r="I29" s="11" t="s">
         <v>1528</v>
+      </c>
+      <c r="K29" t="s">
+        <v>1756</v>
+      </c>
+      <c r="L29" t="s">
+        <v>1756</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="36">

--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8575E10F-CF73-4C1A-8500-C295CC88E649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801D46D2-068A-4C48-B0F4-402A15DAE0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16534" yWindow="686" windowWidth="35057" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3454" uniqueCount="1759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3614" uniqueCount="1829">
   <si>
     <t>ID</t>
   </si>
@@ -16047,42 +16047,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>移動速度と行動速度が低下する</t>
-    <rPh sb="0" eb="4">
-      <t>イドウソクド</t>
-    </rPh>
-    <rPh sb="5" eb="9">
-      <t>コウドウソクド</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>テイカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>移動速度が-10%、行動速度が-50%低下する</t>
-    <rPh sb="0" eb="4">
-      <t>イドウソクド</t>
-    </rPh>
-    <rPh sb="10" eb="14">
-      <t>コウドウソクド</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>テイカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>移動速度-10%,行動速度-50%</t>
-    <rPh sb="0" eb="4">
-      <t>イドウソクド</t>
-    </rPh>
-    <rPh sb="9" eb="13">
-      <t>コウドウソクド</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>拳具/棒具</t>
     <rPh sb="0" eb="1">
       <t>ケン</t>
@@ -17153,13 +17117,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>(状態ID:debuff_flinching)3s</t>
-    <rPh sb="1" eb="3">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ultrasound</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -17369,6 +17326,730 @@
     <rPh sb="73" eb="75">
       <t>コウシン</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>spider_thread</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>粘糸</t>
+    <rPh sb="0" eb="2">
+      <t>ネンシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単体攻撃</t>
+    <rPh sb="0" eb="4">
+      <t>タンタイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単体デバフ</t>
+    <rPh sb="0" eb="2">
+      <t>タンタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>16秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>１秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象指定</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>150px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動速度-10%,行動速度-50%,ガード率-100%</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>コウドウソクド</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動速度と行動速度とガード率が低下する</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>コウドウソクド</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動速度が-10%、行動速度が-50%、ガード率が-100%低下する</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>コウドウソクド</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>debuff_stickiness</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>粘り気</t>
+    <rPh sb="0" eb="1">
+      <t>ネバ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動速度と行動速度が低下する</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>コウドウソクド</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動速度が-50%、行動速度が-80%低下する</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>コウドウソクド</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動速度-50%,行動速度-80%</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>コウドウソクド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:debuff_stickiness)3s</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>jamp_attack</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>飛びつく</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.4</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>180px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>物理</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃を行った対象のそばに移動する</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>硬化</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hardening</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自己バフ</t>
+    <rPh sb="0" eb="2">
+      <t>ジコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>15秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>２秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自身</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自身の防御力を今回の戦闘でのみ
+恒久的に+5%する</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>リョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>コウキュウテキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>tail_cutting</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>尻尾切り</t>
+    <rPh sb="0" eb="3">
+      <t>シッポギ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>回復</t>
+    <rPh sb="0" eb="2">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>20秒</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>３秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受けたダメージの1/3の値*(受けたダメージが物理(1)ミックス(0.5))</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ブツリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>睨みつける</t>
+    <rPh sb="0" eb="1">
+      <t>ニラ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>glare_at</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>石化</t>
+    <rPh sb="0" eb="2">
+      <t>セキカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>debuff_petrification</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>行動デバフ</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>行動不可になり、スキルCDや行動CDが進まなくなり、ターゲットの対象から外れる。時間の指定がない場合、解除されるまで続く</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ハズ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>カイジョ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あらゆる行動ができなくなる</t>
+    <rPh sb="4" eb="6">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>石化の目</t>
+    <rPh sb="0" eb="2">
+      <t>セキカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>debuff_petrification_eye</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>行動バフ</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この状態がある間、対象指定で何かを受けた時、その相手に(状態ID:debuff_petrification)を付与する。１度付与するとこの状態は解除される</t>
+    <rPh sb="2" eb="4">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一度だけ目をあわせてきた対象に"石化"を付与する</t>
+    <rPh sb="0" eb="2">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セキカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一度だけ対象指定を行ってきた相手に対して"石化"を付与する</t>
+    <rPh sb="0" eb="2">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セキカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態Id:debuff_petrification_eye)5s</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>poison_fang</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>毒牙</t>
+    <rPh sb="0" eb="2">
+      <t>ドクガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.1</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>80px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:
+debuff_poison)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力吸収</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キュウシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>magic_eat</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ドットダメージと魔法ダメージを除く、ダメージを受けた際に行動CDに関係なく自動で発動される、効果時間中毎秒回復する、このスキルは自動発動でのみ発動できる</t>
+    <rPh sb="8" eb="10">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="46" eb="50">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="64" eb="68">
+      <t>ジドウハツドウ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ハツドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力放出</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウシュツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受けたダメージ分 * 2</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ブン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法ダメージを受けた際に行動CDに関係なく自動で発動される。受けるはずだった魔法ダメージを95%軽減し、MPを回復する</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ケイゲン</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>magic_vomit</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(消費したmp * 0.01) * 魔力</t>
+    <rPh sb="1" eb="3">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>360px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全mp(1以上)</t>
+    <rPh sb="0" eb="1">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>溶液</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウエキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>solution</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>４秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>230px</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -17560,7 +18241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -17663,6 +18344,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -22259,360 +22953,360 @@
     </row>
     <row r="62" spans="1:26" ht="51" customHeight="1">
       <c r="A62" s="12" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D62" s="5" t="s">
         <v>1619</v>
       </c>
-      <c r="C62" s="13" t="s">
-        <v>1620</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>1622</v>
-      </c>
       <c r="E62" s="12" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F62" s="12" t="s">
         <v>1621</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>1624</v>
       </c>
       <c r="G62">
         <v>10</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="J62" s="34">
         <v>30</v>
       </c>
       <c r="K62" s="12" t="s">
+        <v>1624</v>
+      </c>
+      <c r="L62" s="12" t="s">
+        <v>1625</v>
+      </c>
+      <c r="M62" s="13" t="s">
+        <v>1626</v>
+      </c>
+      <c r="N62" s="12" t="s">
         <v>1627</v>
       </c>
-      <c r="L62" s="12" t="s">
+      <c r="O62" s="13" t="s">
+        <v>1623</v>
+      </c>
+      <c r="P62" s="12" t="s">
         <v>1628</v>
       </c>
-      <c r="M62" s="13" t="s">
+      <c r="Q62" s="16" t="s">
+        <v>1623</v>
+      </c>
+      <c r="R62" s="41" t="s">
         <v>1629</v>
       </c>
-      <c r="N62" s="12" t="s">
+      <c r="S62" s="39" t="s">
         <v>1630</v>
       </c>
-      <c r="O62" s="13" t="s">
-        <v>1626</v>
-      </c>
-      <c r="P62" s="12" t="s">
+      <c r="T62" s="12" t="s">
+        <v>1618</v>
+      </c>
+      <c r="V62" s="16" t="s">
         <v>1631</v>
       </c>
-      <c r="Q62" s="16" t="s">
-        <v>1626</v>
-      </c>
-      <c r="R62" s="41" t="s">
-        <v>1632</v>
-      </c>
-      <c r="S62" s="39" t="s">
-        <v>1633</v>
-      </c>
-      <c r="T62" s="12" t="s">
-        <v>1621</v>
-      </c>
-      <c r="V62" s="16" t="s">
-        <v>1634</v>
-      </c>
       <c r="W62" s="12" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="X62" s="12" t="s">
         <v>860</v>
       </c>
       <c r="Y62" s="12" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="Z62" s="12" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="63" spans="1:26" ht="35.4" customHeight="1">
       <c r="A63" s="12" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="C63" s="13" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F63" s="12" t="s">
         <v>1639</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>1638</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>1637</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>1642</v>
       </c>
       <c r="G63">
         <v>30</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="J63">
         <v>15</v>
       </c>
       <c r="K63" s="12" t="s">
+        <v>1641</v>
+      </c>
+      <c r="L63" s="12" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M63" s="13" t="s">
+        <v>1643</v>
+      </c>
+      <c r="N63" s="12" t="s">
         <v>1644</v>
       </c>
-      <c r="L63" s="12" t="s">
+      <c r="O63" s="13" t="s">
+        <v>1642</v>
+      </c>
+      <c r="P63" s="12" t="s">
         <v>1645</v>
       </c>
-      <c r="M63" s="13" t="s">
-        <v>1646</v>
-      </c>
-      <c r="N63" s="12" t="s">
-        <v>1647</v>
-      </c>
-      <c r="O63" s="13" t="s">
-        <v>1645</v>
-      </c>
-      <c r="P63" s="12" t="s">
-        <v>1648</v>
-      </c>
       <c r="Q63" s="16" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="R63" s="34" t="s">
         <v>242</v>
       </c>
       <c r="T63" s="12" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="U63" s="34" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="V63" s="16" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="W63" s="12" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="X63" s="12" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="Y63" s="12" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="Z63" s="12" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="64" spans="1:26" ht="36">
       <c r="A64" s="12" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
       <c r="B64" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G64" s="12" t="s">
         <v>1658</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>1657</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>1656</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>1674</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>1660</v>
-      </c>
-      <c r="G64" s="12" t="s">
-        <v>1661</v>
       </c>
       <c r="J64">
         <v>30</v>
       </c>
       <c r="K64" s="12" t="s">
+        <v>1659</v>
+      </c>
+      <c r="L64" s="12" t="s">
+        <v>1660</v>
+      </c>
+      <c r="M64" s="13" t="s">
+        <v>1661</v>
+      </c>
+      <c r="N64" s="12" t="s">
         <v>1662</v>
       </c>
-      <c r="L64" s="12" t="s">
+      <c r="O64" s="13" t="s">
+        <v>1658</v>
+      </c>
+      <c r="P64" s="12" t="s">
         <v>1663</v>
       </c>
-      <c r="M64" s="13" t="s">
-        <v>1664</v>
-      </c>
-      <c r="N64" s="12" t="s">
-        <v>1665</v>
-      </c>
-      <c r="O64" s="13" t="s">
-        <v>1661</v>
-      </c>
-      <c r="P64" s="12" t="s">
-        <v>1666</v>
-      </c>
       <c r="Q64" s="16" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="R64" s="34" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="S64" s="39" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="T64" s="12" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="V64" s="16" t="s">
+        <v>1698</v>
+      </c>
+      <c r="W64" s="12" t="s">
+        <v>1699</v>
+      </c>
+      <c r="X64" s="12" t="s">
+        <v>1670</v>
+      </c>
+      <c r="Y64" s="12" t="s">
+        <v>1700</v>
+      </c>
+      <c r="Z64" s="12" t="s">
         <v>1701</v>
-      </c>
-      <c r="W64" s="12" t="s">
-        <v>1702</v>
-      </c>
-      <c r="X64" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="Y64" s="12" t="s">
-        <v>1703</v>
-      </c>
-      <c r="Z64" s="12" t="s">
-        <v>1704</v>
       </c>
     </row>
     <row r="65" spans="1:26" ht="36">
       <c r="A65" s="12" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="D65" s="5" t="s">
+        <v>1672</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>1684</v>
+      </c>
+      <c r="F65" s="12" t="s">
         <v>1675</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>1687</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>1678</v>
       </c>
       <c r="G65">
         <v>20</v>
       </c>
       <c r="H65" s="16" t="s">
+        <v>1676</v>
+      </c>
+      <c r="J65" s="34" t="s">
+        <v>1677</v>
+      </c>
+      <c r="K65" s="12" t="s">
+        <v>1678</v>
+      </c>
+      <c r="L65" s="12" t="s">
         <v>1679</v>
       </c>
-      <c r="J65" s="34" t="s">
+      <c r="M65" s="13" t="s">
         <v>1680</v>
       </c>
-      <c r="K65" s="12" t="s">
+      <c r="N65" s="12" t="s">
         <v>1681</v>
       </c>
-      <c r="L65" s="12" t="s">
+      <c r="O65" s="13" t="s">
+        <v>1677</v>
+      </c>
+      <c r="P65" s="12" t="s">
         <v>1682</v>
       </c>
-      <c r="M65" s="13" t="s">
+      <c r="R65" s="34" t="s">
         <v>1683</v>
       </c>
-      <c r="N65" s="12" t="s">
+      <c r="T65" s="12" t="s">
         <v>1684</v>
       </c>
-      <c r="O65" s="13" t="s">
-        <v>1680</v>
-      </c>
-      <c r="P65" s="12" t="s">
-        <v>1685</v>
-      </c>
-      <c r="R65" s="34" t="s">
+      <c r="V65" s="16" t="s">
         <v>1686</v>
       </c>
-      <c r="T65" s="12" t="s">
+      <c r="W65" s="12" t="s">
         <v>1687</v>
-      </c>
-      <c r="V65" s="16" t="s">
-        <v>1689</v>
-      </c>
-      <c r="W65" s="12" t="s">
-        <v>1690</v>
       </c>
       <c r="X65" s="12" t="s">
         <v>860</v>
       </c>
       <c r="Y65" s="12" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="Z65" s="12" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="36">
       <c r="A66" s="12" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="D66" s="5" t="s">
+        <v>1672</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>1688</v>
+      </c>
+      <c r="F66" s="12" t="s">
         <v>1675</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>1691</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>1678</v>
       </c>
       <c r="G66">
         <v>10</v>
       </c>
       <c r="H66" s="16" t="s">
+        <v>1691</v>
+      </c>
+      <c r="J66" s="34" t="s">
+        <v>1677</v>
+      </c>
+      <c r="K66" s="12" t="s">
+        <v>1692</v>
+      </c>
+      <c r="L66" s="12" t="s">
+        <v>1677</v>
+      </c>
+      <c r="M66" s="13" t="s">
+        <v>1680</v>
+      </c>
+      <c r="N66" s="12" t="s">
+        <v>1693</v>
+      </c>
+      <c r="O66" s="13" t="s">
+        <v>1677</v>
+      </c>
+      <c r="P66" s="12" t="s">
+        <v>1682</v>
+      </c>
+      <c r="R66" s="34" t="s">
+        <v>1683</v>
+      </c>
+      <c r="S66" s="34" t="s">
+        <v>1630</v>
+      </c>
+      <c r="T66" s="12" t="s">
+        <v>1688</v>
+      </c>
+      <c r="V66" s="16" t="s">
         <v>1694</v>
       </c>
-      <c r="J66" s="34" t="s">
-        <v>1680</v>
-      </c>
-      <c r="K66" s="12" t="s">
+      <c r="W66" s="12" t="s">
         <v>1695</v>
       </c>
-      <c r="L66" s="12" t="s">
-        <v>1680</v>
-      </c>
-      <c r="M66" s="13" t="s">
-        <v>1683</v>
-      </c>
-      <c r="N66" s="12" t="s">
+      <c r="X66" s="12" t="s">
+        <v>1670</v>
+      </c>
+      <c r="Y66" s="12" t="s">
         <v>1696</v>
       </c>
-      <c r="O66" s="13" t="s">
-        <v>1680</v>
-      </c>
-      <c r="P66" s="12" t="s">
-        <v>1685</v>
-      </c>
-      <c r="R66" s="34" t="s">
-        <v>1686</v>
-      </c>
-      <c r="S66" s="34" t="s">
-        <v>1633</v>
-      </c>
-      <c r="T66" s="12" t="s">
-        <v>1691</v>
-      </c>
-      <c r="V66" s="16" t="s">
+      <c r="Z66" s="12" t="s">
         <v>1697</v>
-      </c>
-      <c r="W66" s="12" t="s">
-        <v>1698</v>
-      </c>
-      <c r="X66" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="Y66" s="12" t="s">
-        <v>1699</v>
-      </c>
-      <c r="Z66" s="12" t="s">
-        <v>1700</v>
       </c>
     </row>
     <row r="74" spans="1:26" ht="72">
@@ -22715,7 +23409,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E325287-6FF5-4811-9C1B-B61C8E79C27E}">
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -24261,205 +24955,661 @@
     </row>
     <row r="29" spans="1:23" ht="54">
       <c r="A29" s="34" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
       <c r="F29" s="13">
         <v>30</v>
       </c>
       <c r="G29" s="12" t="s">
+        <v>1733</v>
+      </c>
+      <c r="I29" s="39" t="s">
+        <v>1726</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>1735</v>
+      </c>
+      <c r="K29" s="12" t="s">
         <v>1736</v>
       </c>
-      <c r="I29" s="39" t="s">
+      <c r="L29" s="12" t="s">
+        <v>1727</v>
+      </c>
+      <c r="M29" s="12" t="s">
+        <v>1737</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>1726</v>
+      </c>
+      <c r="O29" s="12" t="s">
         <v>1729</v>
       </c>
-      <c r="J29" s="12" t="s">
-        <v>1738</v>
-      </c>
-      <c r="K29" s="12" t="s">
-        <v>1739</v>
-      </c>
-      <c r="L29" s="12" t="s">
+      <c r="P29" s="13" t="s">
+        <v>1726</v>
+      </c>
+      <c r="Q29" s="12" t="s">
         <v>1730</v>
       </c>
-      <c r="M29" s="12" t="s">
-        <v>1740</v>
-      </c>
-      <c r="N29" s="12" t="s">
-        <v>1729</v>
-      </c>
-      <c r="O29" s="12" t="s">
+      <c r="R29" s="12" t="s">
+        <v>1630</v>
+      </c>
+      <c r="S29" s="39" t="s">
         <v>1732</v>
-      </c>
-      <c r="P29" s="13" t="s">
-        <v>1729</v>
-      </c>
-      <c r="Q29" s="12" t="s">
-        <v>1733</v>
-      </c>
-      <c r="R29" s="12" t="s">
-        <v>1741</v>
-      </c>
-      <c r="S29" s="39" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="30" spans="1:23">
       <c r="A30" s="34" t="s">
-        <v>1742</v>
+        <v>1738</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>1743</v>
+        <v>1739</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>1744</v>
+        <v>1740</v>
       </c>
       <c r="F30" s="13">
         <v>10</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>1745</v>
+        <v>1741</v>
       </c>
       <c r="I30">
         <v>10</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>1746</v>
+        <v>1742</v>
       </c>
       <c r="K30" s="12" t="s">
+        <v>1736</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>1743</v>
+      </c>
+      <c r="M30" s="12" t="s">
+        <v>1726</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>1744</v>
+      </c>
+      <c r="O30" s="12" t="s">
+        <v>1729</v>
+      </c>
+      <c r="Q30" s="12" t="s">
+        <v>1745</v>
+      </c>
+      <c r="S30" s="39" t="s">
         <v>1739</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>1747</v>
-      </c>
-      <c r="M30" s="12" t="s">
-        <v>1729</v>
-      </c>
-      <c r="N30" s="12" t="s">
-        <v>1748</v>
-      </c>
-      <c r="O30" s="12" t="s">
-        <v>1732</v>
-      </c>
-      <c r="Q30" s="12" t="s">
-        <v>1749</v>
-      </c>
-      <c r="S30" s="39" t="s">
-        <v>1743</v>
       </c>
     </row>
     <row r="31" spans="1:23" ht="54">
       <c r="A31" s="34" t="s">
-        <v>1750</v>
+        <v>1746</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
       <c r="F31" s="13">
         <v>10</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="I31" s="39" t="s">
+        <v>1726</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>1742</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>1726</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>1727</v>
+      </c>
+      <c r="M31" s="12" t="s">
+        <v>1748</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>1726</v>
+      </c>
+      <c r="O31" s="12" t="s">
         <v>1729</v>
       </c>
-      <c r="J31" s="12" t="s">
-        <v>1746</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>1729</v>
-      </c>
-      <c r="L31" s="12" t="s">
+      <c r="P31" s="13" t="s">
+        <v>1726</v>
+      </c>
+      <c r="Q31" s="12" t="s">
         <v>1730</v>
       </c>
-      <c r="M31" s="12" t="s">
-        <v>1752</v>
-      </c>
-      <c r="N31" s="12" t="s">
-        <v>1729</v>
-      </c>
-      <c r="O31" s="12" t="s">
-        <v>1732</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>1729</v>
-      </c>
-      <c r="Q31" s="12" t="s">
-        <v>1733</v>
-      </c>
       <c r="S31" s="39" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="T31" s="34" t="s">
-        <v>1753</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="32" spans="1:23">
       <c r="A32" s="34" t="s">
-        <v>1754</v>
+        <v>1750</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
       <c r="F32" s="13">
         <v>0</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
       <c r="I32" s="16" t="s">
+        <v>1726</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>1751</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>1726</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>1727</v>
+      </c>
+      <c r="M32" s="12" t="s">
+        <v>1728</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>1726</v>
+      </c>
+      <c r="O32" s="12" t="s">
         <v>1729</v>
       </c>
-      <c r="J32" s="12" t="s">
+      <c r="Q32" s="12" t="s">
+        <v>1730</v>
+      </c>
+      <c r="S32" s="39" t="s">
+        <v>1752</v>
+      </c>
+      <c r="T32" s="4" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="54">
+      <c r="A33" s="42" t="s">
         <v>1755</v>
       </c>
-      <c r="K32" s="12" t="s">
-        <v>1729</v>
-      </c>
-      <c r="L32" s="12" t="s">
-        <v>1730</v>
-      </c>
-      <c r="M32" s="12" t="s">
-        <v>1731</v>
-      </c>
-      <c r="N32" s="12" t="s">
-        <v>1729</v>
-      </c>
-      <c r="O32" s="12" t="s">
-        <v>1732</v>
-      </c>
-      <c r="Q32" s="12" t="s">
-        <v>1733</v>
-      </c>
-      <c r="S32" s="39" t="s">
+      <c r="C33" s="5" t="s">
         <v>1756</v>
       </c>
-      <c r="T32" s="4" t="s">
+      <c r="D33" s="43" t="s">
         <v>1757</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>1759</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G33" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="I33">
+        <v>15</v>
+      </c>
+      <c r="J33" s="43" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K33" s="43" t="s">
+        <v>1762</v>
+      </c>
+      <c r="L33" s="43" t="s">
+        <v>1763</v>
+      </c>
+      <c r="M33" s="43" t="s">
+        <v>1764</v>
+      </c>
+      <c r="N33" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="O33" s="43" t="s">
+        <v>1765</v>
+      </c>
+      <c r="Q33" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="R33" s="43" t="s">
+        <v>1774</v>
+      </c>
+      <c r="S33" s="44" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34" s="42" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D34" s="43" t="s">
+        <v>1776</v>
+      </c>
+      <c r="E34" s="45" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F34" s="46">
+        <v>5</v>
+      </c>
+      <c r="G34" s="43" t="s">
+        <v>1777</v>
+      </c>
+      <c r="I34" s="42" t="s">
+        <v>1760</v>
+      </c>
+      <c r="J34" s="43" t="s">
+        <v>1778</v>
+      </c>
+      <c r="K34" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="L34" s="43" t="s">
+        <v>1763</v>
+      </c>
+      <c r="M34" s="43" t="s">
+        <v>1779</v>
+      </c>
+      <c r="O34" s="43" t="s">
+        <v>1765</v>
+      </c>
+      <c r="Q34" s="43" t="s">
+        <v>1780</v>
+      </c>
+      <c r="S34" s="44" t="s">
+        <v>1776</v>
+      </c>
+      <c r="T34" s="4" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="36">
+      <c r="A35" s="42" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D35" s="43" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E35" s="45" t="s">
+        <v>1784</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G35" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="I35">
+        <v>5</v>
+      </c>
+      <c r="J35" s="43" t="s">
+        <v>1785</v>
+      </c>
+      <c r="K35" s="43" t="s">
+        <v>1786</v>
+      </c>
+      <c r="L35" s="43" t="s">
+        <v>1787</v>
+      </c>
+      <c r="M35" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="N35" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="O35" s="43" t="s">
+        <v>1787</v>
+      </c>
+      <c r="Q35" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="S35" s="44" t="s">
+        <v>1782</v>
+      </c>
+      <c r="T35" s="11" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="72">
+      <c r="A36" s="42" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D36" s="43" t="s">
+        <v>1790</v>
+      </c>
+      <c r="E36" s="45" t="s">
+        <v>1791</v>
+      </c>
+      <c r="F36" s="46">
+        <v>0</v>
+      </c>
+      <c r="G36" s="43" t="s">
+        <v>1794</v>
+      </c>
+      <c r="I36">
+        <v>20</v>
+      </c>
+      <c r="J36" s="43" t="s">
+        <v>1792</v>
+      </c>
+      <c r="K36" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="L36" s="43" t="s">
+        <v>1787</v>
+      </c>
+      <c r="M36" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="N36" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="O36" s="43" t="s">
+        <v>1787</v>
+      </c>
+      <c r="P36" s="43" t="s">
+        <v>1793</v>
+      </c>
+      <c r="Q36" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="S36" s="44" t="s">
+        <v>1790</v>
+      </c>
+      <c r="T36" s="42" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="54">
+      <c r="A37" s="42" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D37" s="43" t="s">
+        <v>1795</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>1784</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G37" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="J37" s="43" t="s">
+        <v>1792</v>
+      </c>
+      <c r="K37" s="43" t="s">
+        <v>1793</v>
+      </c>
+      <c r="L37" s="43" t="s">
+        <v>1787</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="N37" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="O37" s="43" t="s">
+        <v>1787</v>
+      </c>
+      <c r="P37" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="Q37" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="R37" s="43" t="s">
+        <v>1808</v>
+      </c>
+      <c r="S37" s="44" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="36">
+      <c r="A38" s="42" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D38" s="43" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E38" s="45" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F38">
+        <v>40</v>
+      </c>
+      <c r="G38" s="43" t="s">
+        <v>1811</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="J38" s="43" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K38" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="L38" s="43" t="s">
+        <v>1763</v>
+      </c>
+      <c r="M38" s="43" t="s">
+        <v>1812</v>
+      </c>
+      <c r="N38" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="O38" s="43" t="s">
+        <v>1765</v>
+      </c>
+      <c r="Q38" s="43" t="s">
+        <v>1780</v>
+      </c>
+      <c r="R38" s="11" t="s">
+        <v>1813</v>
+      </c>
+      <c r="S38" s="44" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="54">
+      <c r="A39" s="42" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D39" s="43" t="s">
+        <v>1814</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>1791</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G39" s="43" t="s">
+        <v>1818</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="J39" s="43" t="s">
+        <v>1827</v>
+      </c>
+      <c r="K39" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="L39" s="43" t="s">
+        <v>1787</v>
+      </c>
+      <c r="M39" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="N39" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="O39" s="43" t="s">
+        <v>1787</v>
+      </c>
+      <c r="P39" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="Q39" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="S39" s="44" t="s">
+        <v>1814</v>
+      </c>
+      <c r="T39" s="42" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="36">
+      <c r="A40" s="42" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D40" s="43" t="s">
+        <v>1817</v>
+      </c>
+      <c r="E40" s="45" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" s="43" t="s">
+        <v>1821</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>1824</v>
+      </c>
+      <c r="J40" s="43" t="s">
+        <v>1792</v>
+      </c>
+      <c r="K40" s="43" t="s">
+        <v>1793</v>
+      </c>
+      <c r="L40" s="43" t="s">
+        <v>1763</v>
+      </c>
+      <c r="M40" s="43" t="s">
+        <v>1822</v>
+      </c>
+      <c r="N40" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="O40" s="43" t="s">
+        <v>1765</v>
+      </c>
+      <c r="P40" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="Q40" s="43" t="s">
+        <v>1823</v>
+      </c>
+      <c r="S40" s="44" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="36">
+      <c r="A41" s="42" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D41" s="43" t="s">
+        <v>1825</v>
+      </c>
+      <c r="E41" s="45" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G41" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="J41" s="43" t="s">
+        <v>1785</v>
+      </c>
+      <c r="K41" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="L41" s="43" t="s">
+        <v>1763</v>
+      </c>
+      <c r="M41" s="43" t="s">
+        <v>1828</v>
+      </c>
+      <c r="N41" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="O41" s="43" t="s">
+        <v>1765</v>
+      </c>
+      <c r="Q41" s="43" t="s">
+        <v>1823</v>
+      </c>
+      <c r="R41" s="11" t="s">
+        <v>1813</v>
+      </c>
+      <c r="S41" s="44" t="s">
+        <v>1825</v>
       </c>
     </row>
   </sheetData>
@@ -24471,10 +25621,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="21.8984375" customWidth="1"/>
     <col min="2" max="2" width="15.296875" customWidth="1"/>
     <col min="3" max="3" width="17.3984375" customWidth="1"/>
     <col min="4" max="4" width="10.59765625" customWidth="1"/>
@@ -24704,7 +25854,7 @@
         <v>1216</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>1222</v>
@@ -25018,21 +26168,21 @@
         <v>188</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>1618</v>
+        <v>1766</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>1616</v>
+        <v>1767</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>1617</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>286</v>
@@ -25041,13 +26191,82 @@
         <v>188</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>1671</v>
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="4" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>1773</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>1771</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="36">
+      <c r="A27" s="4" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>1800</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="36">
+      <c r="A28" s="4" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>1805</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>1806</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>1807</v>
       </c>
     </row>
   </sheetData>
@@ -27838,16 +29057,16 @@
     </row>
     <row r="4" spans="1:18" ht="36">
       <c r="A4" s="4" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>517</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>556</v>
@@ -27879,13 +29098,13 @@
         <v>544</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>517</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>556</v>
@@ -28060,16 +29279,16 @@
     </row>
     <row r="10" spans="1:18" ht="36">
       <c r="A10" s="4" t="s">
-        <v>1709</v>
+        <v>1706</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1710</v>
+        <v>1707</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>889</v>
@@ -28087,10 +29306,10 @@
         <v>968</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="36">
@@ -28104,7 +29323,7 @@
         <v>164</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>889</v>
@@ -28122,10 +29341,10 @@
         <v>972</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="36">
@@ -28267,16 +29486,16 @@
     </row>
     <row r="16" spans="1:18" ht="36">
       <c r="A16" s="4" t="s">
-        <v>1713</v>
+        <v>1710</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
       <c r="E16" t="s">
         <v>942</v>
@@ -28294,10 +29513,10 @@
         <v>988</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="36">
@@ -28311,7 +29530,7 @@
         <v>164</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
       <c r="E17" t="s">
         <v>942</v>
@@ -28329,10 +29548,10 @@
         <v>990</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="36">
@@ -28474,16 +29693,16 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="4" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1718</v>
+        <v>1715</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>1093</v>
@@ -28501,10 +29720,10 @@
         <v>1106</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="36">
@@ -28512,13 +29731,13 @@
         <v>1085</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>1093</v>
@@ -28536,10 +29755,10 @@
         <v>1192</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -28664,16 +29883,16 @@
     </row>
     <row r="28" spans="1:12" ht="54">
       <c r="A28" s="4" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>1385</v>
@@ -28688,10 +29907,10 @@
         <v>1501</v>
       </c>
       <c r="K28" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="L28" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="54">
@@ -28705,7 +29924,7 @@
         <v>164</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>1385</v>
@@ -28720,10 +29939,10 @@
         <v>1501</v>
       </c>
       <c r="K29" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
       <c r="L29" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="36">
